--- a/M044_submission_package_v1_0/04_tables.xlsx
+++ b/M044_submission_package_v1_0/04_tables.xlsx
@@ -1368,11 +1368,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -513.1710224690692,
-  "aic": 1068.3420449381383,
-  "pseudo_r2_mcfadden": 0.13698819433050213,
-  "lr_vs_null_chi2": 162.91404425514202,
+  "n_events": 193,
+  "llf": -654.0326151062296,
+  "aic": 1350.0652302124593,
+  "pseudo_r2_mcfadden": 0.14040257814284918,
+  "lr_vs_null_chi2": 213.65318930815624,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "label": "strict-DTC primary \u2014 without RAI covariate"
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="B3" s="18" t="n">
-        <v>0.01988594511462632</v>
+        <v>0.03052220194197974</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>0.009863719699586729</v>
+        <v>0.01669454927553033</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>0.04009144877854741</v>
+        <v>0.05580293280229319</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>6.536582072092165e-28</v>
+        <v>8.856417170795826e-30</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="19">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>0.5206463545221203</v>
+        <v>0.6669255032178935</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>0.2208502401334555</v>
+        <v>0.3177659954934816</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>1.227404716940174</v>
+        <v>1.399739535225268</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>0.1357850626236052</v>
+        <v>0.2842080600304258</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="19">
@@ -1425,16 +1425,16 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>1.803142473049089</v>
+        <v>2.076021874744788</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>1.216513912993913</v>
+        <v>1.47858360953565</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>2.672655646092765</v>
+        <v>2.914861761366597</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>0.003324166076161661</v>
+        <v>2.458209087953318e-05</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="19">
@@ -1444,16 +1444,16 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>1.415612656293561</v>
+        <v>1.243365865671108</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>0.9581423942358214</v>
+        <v>0.8826065421803896</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>2.091504566246435</v>
+        <v>1.751583069050145</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0.08094065547071054</v>
+        <v>0.2128480394355131</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="19">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>0.9499944309815264</v>
+        <v>1.041542433253086</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>0.6030069709102068</v>
+        <v>0.7041041255179393</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>1.496648401151407</v>
+        <v>1.540696327363191</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0.8249314914809625</v>
+        <v>0.8385463175879454</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="19">
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>4.064670487927986</v>
+        <v>5.589610780216073</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>1.916630062128165</v>
+        <v>2.888512518705153</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>8.620101761884987</v>
+        <v>10.81655297388619</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0.0002560862557023006</v>
+        <v>3.235499429458743e-07</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="19">
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>0.4032548237157987</v>
+        <v>0.4437282968749986</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>0.09349528866863414</v>
+        <v>0.1329051128210752</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>1.739279648907206</v>
+        <v>1.481468976386622</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>0.223298329848848</v>
+        <v>0.1865048194220119</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="19">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>1.000000000008999</v>
+        <v>1.000000000181017</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>0.9999999520573437</v>
+        <v>0.999999567207104</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>1.000000047960657</v>
+        <v>1.000000433155118</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>0.9997065048579439</v>
+        <v>0.9993461969791613</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="19">
@@ -1539,16 +1539,16 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>0.4025658212119982</v>
+        <v>0.5113539780108236</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>0.1790133646743275</v>
+        <v>0.2699812706456613</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>0.9052912932110907</v>
+        <v>0.9685223356500121</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0.02776413268177263</v>
+        <v>0.03957954869899567</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="19">
@@ -1558,16 +1558,16 @@
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>9.263262405819614</v>
+        <v>8.57905103879509</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>4.810900420995365</v>
+        <v>4.741888142926279</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>17.83616846954348</v>
+        <v>15.52126800714273</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>2.75126119173499e-11</v>
+        <v>1.201350488743744e-12</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="19">
@@ -1577,16 +1577,16 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>1.865793604816147</v>
+        <v>1.715255922337146</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>0.5997323531271797</v>
+        <v>0.6113741691283806</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>5.804565582665188</v>
+        <v>4.812278679204144</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>0.2814594132836409</v>
+        <v>0.3053064560865795</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="19">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>8.234027685038964e-10</v>
+        <v>5.16727771697659e-10</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -1605,7 +1605,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>0.9992368963210904</v>
+        <v>0.9992030750468766</v>
       </c>
     </row>
     <row r="15">
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>0.8900578758120717</v>
+        <v>0.7384752852970617</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>0.4972517251809985</v>
+        <v>0.4452543797335514</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1.593162943792175</v>
+        <v>1.224795918506005</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.6949870010775352</v>
+        <v>0.2402193969427563</v>
       </c>
     </row>
     <row r="16">
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>2.471075365116653</v>
+        <v>1.757893717879382</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>0.9552563654630083</v>
+        <v>0.7279395352184567</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>6.392224831840555</v>
+        <v>4.245119510417058</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>0.06210208227991102</v>
+        <v>0.2098197201769865</v>
       </c>
     </row>
     <row r="17">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>1.149473450125798e-09</v>
+        <v>7.668397975541751e-10</v>
       </c>
       <c r="C17" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -1662,7 +1662,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0.9994853005338252</v>
+        <v>0.999474226098751</v>
       </c>
     </row>
     <row r="18">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>0.8994143043047927</v>
+        <v>0.6744064518387922</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>0.3327371250746836</v>
+        <v>0.2721746782092361</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>2.431186753226002</v>
+        <v>1.671074125169499</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>0.8344867055868811</v>
+        <v>0.3948394123437013</v>
       </c>
     </row>
     <row r="19">
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>1.730704538765684</v>
+        <v>1.823942570144014</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>0.9825439306168026</v>
+        <v>1.112341481819554</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>3.048553970125065</v>
+        <v>2.990778060116638</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>0.05756478400617536</v>
+        <v>0.01722257193913048</v>
       </c>
     </row>
     <row r="20">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>2.295459213080084</v>
+        <v>2.39090079920365</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>1.149102116321473</v>
+        <v>1.317147438489974</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>4.585434944443309</v>
+        <v>4.339989939308657</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0.01859114256048034</v>
+        <v>0.004162942684026138</v>
       </c>
     </row>
     <row r="21">
@@ -1729,16 +1729,16 @@
         </is>
       </c>
       <c r="B21" s="18" t="n">
-        <v>2.426078408991356</v>
+        <v>2.788892715938317</v>
       </c>
       <c r="C21" s="18" t="n">
-        <v>1.060571024699771</v>
+        <v>1.376348027128713</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>5.549705120635568</v>
+        <v>5.651130693477159</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>0.03579426143389187</v>
+        <v>0.004420333345359666</v>
       </c>
     </row>
     <row r="22">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>1.12362744109839</v>
+        <v>1.304747414145783</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>0.2422511546911795</v>
+        <v>0.3606986337620886</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>5.211692914317758</v>
+        <v>4.719634773673588</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>0.8816355286876525</v>
+        <v>0.6851050284367951</v>
       </c>
     </row>
     <row r="23">
@@ -1767,16 +1767,16 @@
         </is>
       </c>
       <c r="B23" s="18" t="n">
-        <v>0.9590876471583448</v>
+        <v>0.9342008179855855</v>
       </c>
       <c r="C23" s="18" t="n">
-        <v>0.855857777736727</v>
+        <v>0.84698924688341</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1.074768657666727</v>
+        <v>1.030392264761622</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>0.472169331137781</v>
+        <v>0.1734490646119403</v>
       </c>
     </row>
     <row r="24">
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="B24" s="18" t="n">
-        <v>1.05396825090431</v>
+        <v>1.047101558155796</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>0.9751068751851638</v>
+        <v>0.9772115482993279</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1.139207508616274</v>
+        <v>1.121990090068454</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>0.1852806869483926</v>
+        <v>0.1915859030131092</v>
       </c>
     </row>
     <row r="25"/>
@@ -1811,11 +1811,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -487.8345854673767,
-  "aic": 1019.6691709347534,
-  "pseudo_r2_mcfadden": 0.179597077702088,
-  "lr_vs_null_chi2": 213.5869182585269,
+  "n_events": 193,
+  "llf": -615.6138897275603,
+  "aic": 1275.2277794551205,
+  "pseudo_r2_mcfadden": 0.1908964472921395,
+  "lr_vs_null_chi2": 290.490640065495,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + rai_received_flag + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))"
 }</t>
@@ -1829,16 +1829,16 @@
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>0.01243735367104338</v>
+        <v>0.01852597376749012</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.00601956305150336</v>
+        <v>0.009880024697097232</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>0.02569750744615653</v>
+        <v>0.03473793988941832</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>2.186170219602465e-32</v>
+        <v>1.683886297117039e-35</v>
       </c>
     </row>
     <row r="29">
@@ -1848,16 +1848,16 @@
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>0.5247295914671026</v>
+        <v>0.6605652523227008</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>0.2195589178881915</v>
+        <v>0.3089484868535126</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>1.254064953542208</v>
+        <v>1.412359895399152</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>0.1468679320291499</v>
+        <v>0.2848553724927133</v>
       </c>
     </row>
     <row r="30">
@@ -1867,16 +1867,16 @@
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>1.399180970657792</v>
+        <v>1.588785874419103</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>0.931990309061838</v>
+        <v>1.117522728799781</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>2.100566250116434</v>
+        <v>2.258782295609063</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>0.1051856235318305</v>
+        <v>0.009911220692569871</v>
       </c>
     </row>
     <row r="31">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="B31" s="18" t="n">
-        <v>1.495807058820033</v>
+        <v>1.327158313740222</v>
       </c>
       <c r="C31" s="18" t="n">
-        <v>1.006369220819683</v>
+        <v>0.9351044686229039</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>2.223278207369512</v>
+        <v>1.88358546967877</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>0.04644102251401835</v>
+        <v>0.1131084878470058</v>
       </c>
     </row>
     <row r="32">
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="B32" s="18" t="n">
-        <v>0.8993458401500429</v>
+        <v>0.990583944558754</v>
       </c>
       <c r="C32" s="18" t="n">
-        <v>0.5677923957007568</v>
+        <v>0.6655851393719214</v>
       </c>
       <c r="D32" s="18" t="n">
-        <v>1.424504706860252</v>
+        <v>1.474276532290883</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>0.6511941300107797</v>
+        <v>0.9628057759983004</v>
       </c>
     </row>
     <row r="33">
@@ -1924,16 +1924,16 @@
         </is>
       </c>
       <c r="B33" s="18" t="n">
-        <v>3.135690419140053</v>
+        <v>4.604586434968516</v>
       </c>
       <c r="C33" s="18" t="n">
-        <v>1.4225267452047</v>
+        <v>2.283886415442775</v>
       </c>
       <c r="D33" s="18" t="n">
-        <v>6.912034826643505</v>
+        <v>9.283393470767507</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>0.004598600726392241</v>
+        <v>1.967841372061901e-05</v>
       </c>
     </row>
     <row r="34">
@@ -1943,16 +1943,16 @@
         </is>
       </c>
       <c r="B34" s="18" t="n">
-        <v>0.4027848314215929</v>
+        <v>0.4506894604405457</v>
       </c>
       <c r="C34" s="18" t="n">
-        <v>0.09155304331996808</v>
+        <v>0.1317159434817318</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>1.772039623590937</v>
+        <v>1.542113918656794</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>0.2289571348823807</v>
+        <v>0.2041484951130681</v>
       </c>
     </row>
     <row r="35">
@@ -1962,16 +1962,16 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>0.9999999998962703</v>
+        <v>0.9999999999279252</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>0.9999997410976182</v>
+        <v>0.999999874087424</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>1.000000258694989</v>
+        <v>1.000000125768442</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.9993731999724306</v>
+        <v>0.9991043239232837</v>
       </c>
     </row>
     <row r="36">
@@ -1981,16 +1981,16 @@
         </is>
       </c>
       <c r="B36" s="18" t="n">
-        <v>0.4045534434906543</v>
+        <v>0.5182946546370739</v>
       </c>
       <c r="C36" s="18" t="n">
-        <v>0.1780840267777004</v>
+        <v>0.2701503346559783</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>0.9190239663911277</v>
+        <v>0.9943698547234768</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.03064363216471419</v>
+        <v>0.04804753128137115</v>
       </c>
     </row>
     <row r="37">
@@ -2000,16 +2000,16 @@
         </is>
       </c>
       <c r="B37" s="18" t="n">
-        <v>7.508894512361091</v>
+        <v>7.235365489821646</v>
       </c>
       <c r="C37" s="18" t="n">
-        <v>3.825406307449728</v>
+        <v>3.912752753308382</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>14.73921781536339</v>
+        <v>13.3794586757463</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>4.656099624166374e-09</v>
+        <v>2.798472448423662e-10</v>
       </c>
     </row>
     <row r="38">
@@ -2019,16 +2019,16 @@
         </is>
       </c>
       <c r="B38" s="18" t="n">
-        <v>1.909544811489763</v>
+        <v>1.77940635884233</v>
       </c>
       <c r="C38" s="18" t="n">
-        <v>0.6094850006112782</v>
+        <v>0.6231982024830175</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>5.982692573944206</v>
+        <v>5.080706230013237</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>0.2669215222801871</v>
+        <v>0.2816799942444455</v>
       </c>
     </row>
     <row r="39">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="B39" s="18" t="n">
-        <v>1.077090615988379e-09</v>
+        <v>7.100757734654775e-10</v>
       </c>
       <c r="C39" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2047,7 +2047,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>0.9992531277044018</v>
+        <v>0.9992245316664904</v>
       </c>
     </row>
     <row r="40">
@@ -2057,16 +2057,16 @@
         </is>
       </c>
       <c r="B40" s="18" t="n">
-        <v>0.8692340403524873</v>
+        <v>0.7203248889034003</v>
       </c>
       <c r="C40" s="18" t="n">
-        <v>0.478446874587955</v>
+        <v>0.4268775794085984</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>1.579209431680821</v>
+        <v>1.215495895316268</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>0.6454873097500982</v>
+        <v>0.219105558193422</v>
       </c>
     </row>
     <row r="41">
@@ -2076,16 +2076,16 @@
         </is>
       </c>
       <c r="B41" s="18" t="n">
-        <v>2.40298664876395</v>
+        <v>1.698928214493524</v>
       </c>
       <c r="C41" s="18" t="n">
-        <v>0.9167869948080993</v>
+        <v>0.6880356978898791</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>6.298458493454608</v>
+        <v>4.195068783282983</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>0.07454589178826011</v>
+        <v>0.2504733611055728</v>
       </c>
     </row>
     <row r="42">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="B42" s="18" t="n">
-        <v>1.738799098240321e-09</v>
+        <v>1.201370520861789e-09</v>
       </c>
       <c r="C42" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2104,7 +2104,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>0.9994975570889663</v>
+        <v>0.9994877572298072</v>
       </c>
     </row>
     <row r="43">
@@ -2114,16 +2114,16 @@
         </is>
       </c>
       <c r="B43" s="18" t="n">
-        <v>0.9393529280851824</v>
+        <v>0.7132757540808904</v>
       </c>
       <c r="C43" s="18" t="n">
-        <v>0.3445997066246413</v>
+        <v>0.2849891561050739</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>2.560605556357455</v>
+        <v>1.785198806554187</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0.9026773658212145</v>
+        <v>0.4703804923977388</v>
       </c>
     </row>
     <row r="44">
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="B44" s="18" t="n">
-        <v>1.744516643641336</v>
+        <v>1.841779165835708</v>
       </c>
       <c r="C44" s="18" t="n">
-        <v>0.9741142391444224</v>
+        <v>1.101608279690727</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>3.124210896059417</v>
+        <v>3.079271060543237</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0.06124136822890173</v>
+        <v>0.01985927502901846</v>
       </c>
     </row>
     <row r="45">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B45" s="18" t="n">
-        <v>2.011792359717571</v>
+        <v>2.062891729377959</v>
       </c>
       <c r="C45" s="18" t="n">
-        <v>1.006452458439709</v>
+        <v>1.130608886225852</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>4.021360834959344</v>
+        <v>3.763920785499557</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0.04791008918686219</v>
+        <v>0.01827203960239072</v>
       </c>
     </row>
     <row r="46">
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="B46" s="18" t="n">
-        <v>2.361508813625388</v>
+        <v>2.729766659902919</v>
       </c>
       <c r="C46" s="18" t="n">
-        <v>1.019631967664402</v>
+        <v>1.325706536412232</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>5.469349778827149</v>
+        <v>5.620871446922123</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>0.04492726244467932</v>
+        <v>0.0064290669584959</v>
       </c>
     </row>
     <row r="47">
@@ -2190,16 +2190,16 @@
         </is>
       </c>
       <c r="B47" s="18" t="n">
-        <v>0.9991545856558507</v>
+        <v>1.145187691339581</v>
       </c>
       <c r="C47" s="18" t="n">
-        <v>0.2019767086438209</v>
+        <v>0.2935567622878745</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>4.942698060287736</v>
+        <v>4.46746597889511</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>0.9991727079719656</v>
+        <v>0.8452404506108612</v>
       </c>
     </row>
     <row r="48">
@@ -2209,16 +2209,16 @@
         </is>
       </c>
       <c r="B48" s="18" t="n">
-        <v>0.9917146052517893</v>
+        <v>0.9675883940055234</v>
       </c>
       <c r="C48" s="18" t="n">
-        <v>0.8833885879583027</v>
+        <v>0.8753594456019949</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1.113324160710275</v>
+        <v>1.069534697909535</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>0.8878888867769235</v>
+        <v>0.5191419700053839</v>
       </c>
     </row>
     <row r="49">
@@ -2228,16 +2228,16 @@
         </is>
       </c>
       <c r="B49" s="18" t="n">
-        <v>1.0684336730161</v>
+        <v>1.058002054934856</v>
       </c>
       <c r="C49" s="18" t="n">
-        <v>0.9865597660959139</v>
+        <v>0.9851955209249599</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>1.1571022383693</v>
+        <v>1.136189035040931</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>0.1036716254647825</v>
+        <v>0.1211542894693701</v>
       </c>
     </row>
     <row r="50">
@@ -2247,16 +2247,16 @@
         </is>
       </c>
       <c r="B50" s="18" t="n">
-        <v>4.045155914882562</v>
+        <v>4.413484571074677</v>
       </c>
       <c r="C50" s="18" t="n">
-        <v>2.780534009197913</v>
+        <v>3.192075222553084</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>5.884943799133611</v>
+        <v>6.102251576494701</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>2.739210328395703e-13</v>
+        <v>2.675251785808035e-19</v>
       </c>
     </row>
     <row r="51">
@@ -2274,11 +2274,11 @@
         <is>
           <t>{
   "n_obs": 4028,
-  "n_events": 144,
-  "llf": -523.6470212148317,
-  "aic": 1091.2940424296635,
-  "pseudo_r2_mcfadden": 0.15718550828722877,
-  "lr_vs_null_chi2": 195.32109141948058,
+  "n_events": 203,
+  "llf": -668.4548944332049,
+  "aic": 1380.9097888664098,
+  "pseudo_r2_mcfadden": 0.16924339565274382,
+  "lr_vs_null_chi2": 272.3579339184719,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + rai_received_flag + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "label": "full cohort sensitivity \u2014 includes non-DTC histologies (RAI covariate)"
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="B54" s="18" t="n">
-        <v>0.01270332224925259</v>
+        <v>0.01820768988501063</v>
       </c>
       <c r="C54" s="18" t="n">
-        <v>0.006259101047817402</v>
+        <v>0.009912962075123204</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>0.02578235994841916</v>
+        <v>0.03344307871213138</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>1.206018657244035e-33</v>
+        <v>3.775467573871243e-38</v>
       </c>
     </row>
     <row r="55">
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="B55" s="18" t="n">
-        <v>1.025049938589364</v>
+        <v>1.224487779211359</v>
       </c>
       <c r="C55" s="18" t="n">
-        <v>0.4683176194958099</v>
+        <v>0.6249861848359756</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>2.243621279364356</v>
+        <v>2.39904554343304</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.9506396590407828</v>
+        <v>0.5550575699205013</v>
       </c>
     </row>
     <row r="56">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="B56" s="18" t="n">
-        <v>1.393944822862145</v>
+        <v>1.590964961232916</v>
       </c>
       <c r="C56" s="18" t="n">
-        <v>0.9410113793459456</v>
+        <v>1.134847190953743</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>2.06488700544166</v>
+        <v>2.23040558063471</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>0.0975811859505394</v>
+        <v>0.007063602444180204</v>
       </c>
     </row>
     <row r="57">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B57" s="18" t="n">
-        <v>1.394437366502058</v>
+        <v>1.285465042605963</v>
       </c>
       <c r="C57" s="18" t="n">
-        <v>0.9501430309170126</v>
+        <v>0.9203333460739046</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>2.046487219109042</v>
+        <v>1.795458550764341</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>0.08937978111985546</v>
+        <v>0.140751701646049</v>
       </c>
     </row>
     <row r="58">
@@ -2373,16 +2373,16 @@
         </is>
       </c>
       <c r="B58" s="18" t="n">
-        <v>1.124476587154783</v>
+        <v>1.246981532406513</v>
       </c>
       <c r="C58" s="18" t="n">
-        <v>0.7193888068432794</v>
+        <v>0.8471999299335975</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1.757669264563259</v>
+        <v>1.83541438947566</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>0.6067050029762839</v>
+        <v>0.2630612138995111</v>
       </c>
     </row>
     <row r="59">
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B59" s="18" t="n">
-        <v>3.624879465068497</v>
+        <v>5.235949933040403</v>
       </c>
       <c r="C59" s="18" t="n">
-        <v>1.715186957471684</v>
+        <v>2.713948858097169</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>7.660827339571349</v>
+        <v>10.1015800719721</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0.0007432851677790656</v>
+        <v>7.902637423371317e-07</v>
       </c>
     </row>
     <row r="60">
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="B60" s="18" t="n">
-        <v>0.4268404740169416</v>
+        <v>0.4856241442953312</v>
       </c>
       <c r="C60" s="18" t="n">
-        <v>0.09818096425209358</v>
+        <v>0.1440922993926894</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>1.855683447874901</v>
+        <v>1.636664905179087</v>
       </c>
       <c r="E60" s="18" t="n">
-        <v>0.256200965502836</v>
+        <v>0.243929361824139</v>
       </c>
     </row>
     <row r="61">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B61" s="18" t="n">
-        <v>2.795833776242406e-09</v>
+        <v>2.087527512272552e-09</v>
       </c>
       <c r="C61" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2439,7 +2439,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>0.9988837449101163</v>
+        <v>0.9988791109878108</v>
       </c>
     </row>
     <row r="62">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B62" s="18" t="n">
-        <v>0.5300008549744339</v>
+        <v>0.6797721604528594</v>
       </c>
       <c r="C62" s="18" t="n">
-        <v>0.2547763212322116</v>
+        <v>0.3781808465470493</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>1.102539297667339</v>
+        <v>1.221876238169718</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0.08936281649688967</v>
+        <v>0.196988782715572</v>
       </c>
     </row>
     <row r="63">
@@ -2468,16 +2468,16 @@
         </is>
       </c>
       <c r="B63" s="18" t="n">
-        <v>1.011167251748234</v>
+        <v>1.802192782210647</v>
       </c>
       <c r="C63" s="18" t="n">
-        <v>0.3530242293264869</v>
+        <v>0.8581125686501837</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>2.896286220803492</v>
+        <v>3.784933286038587</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.9834978583234898</v>
+        <v>0.1197602232866131</v>
       </c>
     </row>
     <row r="64">
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="B64" s="18" t="n">
-        <v>3.346147516101708</v>
+        <v>3.319979904968426</v>
       </c>
       <c r="C64" s="18" t="n">
-        <v>1.879470574501078</v>
+        <v>1.984907808615645</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>5.957370842310681</v>
+        <v>5.553037033534335</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>4.060796033652029e-05</v>
+        <v>4.826342779005567e-06</v>
       </c>
     </row>
     <row r="65">
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="B65" s="18" t="n">
-        <v>0.6993857076936851</v>
+        <v>0.6883312598936068</v>
       </c>
       <c r="C65" s="18" t="n">
-        <v>0.3972178880373128</v>
+        <v>0.4232788864596663</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>1.231415761619097</v>
+        <v>1.119356382997544</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>0.2154326418632305</v>
+        <v>0.1322037264095022</v>
       </c>
     </row>
     <row r="66">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B66" s="18" t="n">
-        <v>1.867041169548184</v>
+        <v>1.474355572683133</v>
       </c>
       <c r="C66" s="18" t="n">
-        <v>0.7291459923331521</v>
+        <v>0.6089309908457249</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>4.780719863293363</v>
+        <v>3.569738422547343</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>0.1930889255205546</v>
+        <v>0.3895236467276599</v>
       </c>
     </row>
     <row r="67">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B67" s="18" t="n">
-        <v>1.967499466289988e-09</v>
+        <v>1.519426391063587e-09</v>
       </c>
       <c r="C67" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2553,7 +2553,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.9995051108016799</v>
+        <v>0.9994983792860411</v>
       </c>
     </row>
     <row r="68">
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="B68" s="18" t="n">
-        <v>0.782266691299264</v>
+        <v>0.7729909728052788</v>
       </c>
       <c r="C68" s="18" t="n">
-        <v>0.2907571989680857</v>
+        <v>0.3310228843539463</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>2.104646689705751</v>
+        <v>1.805056605692428</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>0.6267592813543881</v>
+        <v>0.5517965668261866</v>
       </c>
     </row>
     <row r="69">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="B69" s="18" t="n">
-        <v>1.951533944343512</v>
+        <v>1.767254545007356</v>
       </c>
       <c r="C69" s="18" t="n">
-        <v>1.127259713107545</v>
+        <v>1.097064020587842</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>3.378533528379189</v>
+        <v>2.846860865217009</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>0.01695159136087453</v>
+        <v>0.0192438176112148</v>
       </c>
     </row>
     <row r="70">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="B70" s="18" t="n">
-        <v>1.846461638634073</v>
+        <v>1.895292977177866</v>
       </c>
       <c r="C70" s="18" t="n">
-        <v>0.9392237780518112</v>
+        <v>1.066053509139101</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>3.63004074494284</v>
+        <v>3.369563946410716</v>
       </c>
       <c r="E70" s="18" t="n">
-        <v>0.07537713785538518</v>
+        <v>0.0294181865662252</v>
       </c>
     </row>
     <row r="71">
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="B71" s="18" t="n">
-        <v>1.767427766572182</v>
+        <v>1.889931828279741</v>
       </c>
       <c r="C71" s="18" t="n">
-        <v>0.8150472828021249</v>
+        <v>0.9813552951043095</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>3.832662197597585</v>
+        <v>3.639703513461096</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>0.1492690751587219</v>
+        <v>0.05695218216704147</v>
       </c>
     </row>
     <row r="72">
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="B72" s="18" t="n">
-        <v>1.157281133992585</v>
+        <v>1.175760709576873</v>
       </c>
       <c r="C72" s="18" t="n">
-        <v>0.2485972594914997</v>
+        <v>0.3201459619406088</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>5.387427141532742</v>
+        <v>4.318071787646562</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>0.852326658780355</v>
+        <v>0.8072723661594022</v>
       </c>
     </row>
     <row r="73">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B73" s="18" t="n">
-        <v>0.9613849807648458</v>
+        <v>0.9373124632003611</v>
       </c>
       <c r="C73" s="18" t="n">
-        <v>0.859363357623902</v>
+        <v>0.8513049699952649</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>1.075518374201758</v>
+        <v>1.032009308809292</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0.4914410663063975</v>
+        <v>0.1873899203736279</v>
       </c>
     </row>
     <row r="74">
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="B74" s="18" t="n">
-        <v>1.068719542189801</v>
+        <v>1.061823647341721</v>
       </c>
       <c r="C74" s="18" t="n">
-        <v>0.9888601932405231</v>
+        <v>0.9914338598591365</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>1.155028251380494</v>
+        <v>1.137210966563384</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>0.09349251578155092</v>
+        <v>0.08650398849992604</v>
       </c>
     </row>
     <row r="75">
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="B75" s="18" t="n">
-        <v>4.516453266765985</v>
+        <v>4.741474162290238</v>
       </c>
       <c r="C75" s="18" t="n">
-        <v>3.132621844155955</v>
+        <v>3.458823434089347</v>
       </c>
       <c r="D75" s="18" t="n">
-        <v>6.511590330934824</v>
+        <v>6.499775909372186</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>6.628142749372092e-16</v>
+        <v>4.009029942074579e-22</v>
       </c>
     </row>
     <row r="76">
@@ -2722,9 +2722,9 @@
       <c r="A78" s="18" t="inlineStr">
         <is>
           <t>{
-  "lr_chi2": 6.295421355438748,
+  "lr_chi2": 3.6960718240545702,
   "df": 6,
-  "p_value": 0.39092335445939086,
+  "p_value": 0.7177264638482881,
   "formula_full": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) * C(ajcc8_n_fac, Treatment(reference='N0')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "formula_reduced": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + C(ajcc8_n_fac, Treatment(reference='N0')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))"
 }</t>
@@ -2758,12 +2758,12 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 164,
-  "llf": -622.5570074555555,
-  "aic": 1287.114014911111,
-  "pseudo_r2_mcfadden": 0.07617446500325997,
-  "lr_vs_null_chi2": 102.66645633934513,
-  "lr_vs_null_pvalue": 4.18554080283684e-13
+  "n_events": 14,
+  "llf": -81.0638843247846,
+  "aic": 204.1277686495692,
+  "pseudo_r2_mcfadden": 0.12137881887901447,
+  "lr_vs_null_chi2": 22.39745352037565,
+  "lr_vs_null_pvalue": 0.31933887897609237
 }</t>
         </is>
       </c>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="B82" s="18" t="n">
-        <v>0.0101144269724082</v>
+        <v>0.001786923068411454</v>
       </c>
       <c r="C82" s="18" t="n">
-        <v>0.005247331152928585</v>
+        <v>0.0002115687708741055</v>
       </c>
       <c r="D82" s="18" t="n">
-        <v>0.01949593612423014</v>
+        <v>0.01509246397390598</v>
       </c>
       <c r="E82" s="18" t="n">
-        <v>7.704796697345512e-43</v>
+        <v>6.170743635778745e-09</v>
       </c>
     </row>
     <row r="83">
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="B83" s="18" t="n">
-        <v>1.112346002753871</v>
+        <v>2.355604278444697</v>
       </c>
       <c r="C83" s="18" t="n">
-        <v>0.5157852313966473</v>
+        <v>0.1946082032947651</v>
       </c>
       <c r="D83" s="18" t="n">
-        <v>2.398893094500023</v>
+        <v>28.513040163175</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0.7859841270048189</v>
+        <v>0.5006607963547791</v>
       </c>
     </row>
     <row r="84">
@@ -2817,16 +2817,16 @@
         </is>
       </c>
       <c r="B84" s="18" t="n">
-        <v>1.45823618682736</v>
+        <v>2.375717141246138</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>1.016637791648721</v>
+        <v>0.7381737066014609</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>2.091652301380856</v>
+        <v>7.645940087998728</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>0.04040156790282207</v>
+        <v>0.1467995693644507</v>
       </c>
     </row>
     <row r="85">
@@ -2836,16 +2836,16 @@
         </is>
       </c>
       <c r="B85" s="18" t="n">
-        <v>0.9210188500376359</v>
+        <v>0.9193439069638312</v>
       </c>
       <c r="C85" s="18" t="n">
-        <v>0.6378273246208879</v>
+        <v>0.2684093137257994</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>1.329945722580713</v>
+        <v>3.148896763451923</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>0.6607377976150222</v>
+        <v>0.8934992612409755</v>
       </c>
     </row>
     <row r="86">
@@ -2855,16 +2855,16 @@
         </is>
       </c>
       <c r="B86" s="18" t="n">
-        <v>0.9443510963277069</v>
+        <v>0.8377688957101103</v>
       </c>
       <c r="C86" s="18" t="n">
-        <v>0.6403355095363852</v>
+        <v>0.2386806653638656</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>1.392705823515896</v>
+        <v>2.940567982535855</v>
       </c>
       <c r="E86" s="18" t="n">
-        <v>0.772691680573577</v>
+        <v>0.7823100301725159</v>
       </c>
     </row>
     <row r="87">
@@ -2874,16 +2874,16 @@
         </is>
       </c>
       <c r="B87" s="18" t="n">
-        <v>2.260483412399697</v>
+        <v>2.691336535594656</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>1.047981474908718</v>
+        <v>0.2557976385597303</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>4.875835479991913</v>
+        <v>28.31649419678006</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>0.03757540366265261</v>
+        <v>0.4096422478169726</v>
       </c>
     </row>
     <row r="88">
@@ -2893,16 +2893,16 @@
         </is>
       </c>
       <c r="B88" s="18" t="n">
-        <v>0.4804491592959691</v>
+        <v>1.767155055363416</v>
       </c>
       <c r="C88" s="18" t="n">
-        <v>0.1661081913916158</v>
+        <v>0.1811306545993918</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>1.38964486178768</v>
+        <v>17.24079779098289</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>0.1761389910725185</v>
+        <v>0.6242047862455105</v>
       </c>
     </row>
     <row r="89">
@@ -2912,16 +2912,16 @@
         </is>
       </c>
       <c r="B89" s="18" t="n">
-        <v>0.9999999999947753</v>
+        <v>0.9999999999960187</v>
       </c>
       <c r="C89" s="18" t="n">
-        <v>0.9999999933515661</v>
+        <v>0.9999997899039276</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>1.000000006637985</v>
+        <v>1.000000210088154</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0.9987701017384494</v>
+        <v>0.9999703654559708</v>
       </c>
     </row>
     <row r="90">
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="B90" s="18" t="n">
-        <v>1.050618861452907</v>
+        <v>2.878946803441325</v>
       </c>
       <c r="C90" s="18" t="n">
-        <v>0.6029305182472595</v>
+        <v>0.5889034971326118</v>
       </c>
       <c r="D90" s="18" t="n">
-        <v>1.830725031549886</v>
+        <v>14.07418148712169</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>0.8616476402837158</v>
+        <v>0.1915526072694045</v>
       </c>
     </row>
     <row r="91">
@@ -2950,16 +2950,16 @@
         </is>
       </c>
       <c r="B91" s="18" t="n">
-        <v>4.836014686208752</v>
+        <v>2.380401768922977</v>
       </c>
       <c r="C91" s="18" t="n">
-        <v>2.439273004658978</v>
+        <v>0.1785689893148111</v>
       </c>
       <c r="D91" s="18" t="n">
-        <v>9.58770830512116</v>
+        <v>31.7317839073509</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>6.372993394384357e-06</v>
+        <v>0.5116393020940575</v>
       </c>
     </row>
     <row r="92">
@@ -2969,16 +2969,16 @@
         </is>
       </c>
       <c r="B92" s="18" t="n">
-        <v>2.269681815883829</v>
+        <v>9.117152013220499</v>
       </c>
       <c r="C92" s="18" t="n">
-        <v>0.7883398076778311</v>
+        <v>0.6821678137134559</v>
       </c>
       <c r="D92" s="18" t="n">
-        <v>6.534562247374105</v>
+        <v>121.8504584373226</v>
       </c>
       <c r="E92" s="18" t="n">
-        <v>0.1287211332116586</v>
+        <v>0.09475729860505173</v>
       </c>
     </row>
     <row r="93">
@@ -2988,16 +2988,16 @@
         </is>
       </c>
       <c r="B93" s="18" t="n">
-        <v>3.418923711874625</v>
+        <v>2.477532991957287e-09</v>
       </c>
       <c r="C93" s="18" t="n">
-        <v>0.6613762473322452</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D93" s="18" t="n">
-        <v>17.67381183519662</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E93" s="18" t="n">
-        <v>0.1424575417206377</v>
+        <v>0.9997357907928893</v>
       </c>
     </row>
     <row r="94">
@@ -3007,16 +3007,16 @@
         </is>
       </c>
       <c r="B94" s="18" t="n">
-        <v>1.858868116491178</v>
+        <v>2.100268075359052</v>
       </c>
       <c r="C94" s="18" t="n">
-        <v>1.107979986381057</v>
+        <v>0.4591337909409427</v>
       </c>
       <c r="D94" s="18" t="n">
-        <v>3.118639972725174</v>
+        <v>9.607495844146682</v>
       </c>
       <c r="E94" s="18" t="n">
-        <v>0.01885585952083379</v>
+        <v>0.3387921663504317</v>
       </c>
     </row>
     <row r="95">
@@ -3026,16 +3026,16 @@
         </is>
       </c>
       <c r="B95" s="18" t="n">
-        <v>4.645579194783793</v>
+        <v>2.011022141784835e-09</v>
       </c>
       <c r="C95" s="18" t="n">
-        <v>1.811177361925224</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D95" s="18" t="n">
-        <v>11.91567789477431</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E95" s="18" t="n">
-        <v>0.001393967102755869</v>
+        <v>0.9994414708553463</v>
       </c>
     </row>
     <row r="96">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="B96" s="18" t="n">
-        <v>1.21409489610437e-08</v>
+        <v>1.976731211879618e-09</v>
       </c>
       <c r="C96" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3054,7 +3054,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E96" s="18" t="n">
-        <v>0.9987700734230877</v>
+        <v>0.9998126242745856</v>
       </c>
     </row>
     <row r="97">
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="B97" s="18" t="n">
-        <v>1.118793904964756</v>
+        <v>2.968183959850206e-09</v>
       </c>
       <c r="C97" s="18" t="n">
-        <v>0.4291663195525017</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D97" s="18" t="n">
-        <v>2.916584421376433</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E97" s="18" t="n">
-        <v>0.8183909384795416</v>
+        <v>0.9990297347742679</v>
       </c>
     </row>
     <row r="98">
@@ -3083,16 +3083,16 @@
         </is>
       </c>
       <c r="B98" s="18" t="n">
-        <v>0.7535902522229887</v>
+        <v>1.594915489366299</v>
       </c>
       <c r="C98" s="18" t="n">
-        <v>0.4398546600548576</v>
+        <v>0.2687277948110208</v>
       </c>
       <c r="D98" s="18" t="n">
-        <v>1.291104357459077</v>
+        <v>9.465918551556614</v>
       </c>
       <c r="E98" s="18" t="n">
-        <v>0.3030710714444524</v>
+        <v>0.6074164792059515</v>
       </c>
     </row>
     <row r="99">
@@ -3102,16 +3102,16 @@
         </is>
       </c>
       <c r="B99" s="18" t="n">
-        <v>1.205770931891847</v>
+        <v>7.992098005631019</v>
       </c>
       <c r="C99" s="18" t="n">
-        <v>0.6349173758540275</v>
+        <v>1.753182671062876</v>
       </c>
       <c r="D99" s="18" t="n">
-        <v>2.289878329821598</v>
+        <v>36.43295794892131</v>
       </c>
       <c r="E99" s="18" t="n">
-        <v>0.5674511906641296</v>
+        <v>0.007245923079154247</v>
       </c>
     </row>
     <row r="100">
@@ -3121,16 +3121,16 @@
         </is>
       </c>
       <c r="B100" s="18" t="n">
-        <v>1.166818766849705</v>
+        <v>1.650396770245106</v>
       </c>
       <c r="C100" s="18" t="n">
-        <v>0.5509732658789788</v>
+        <v>0.121632055434126</v>
       </c>
       <c r="D100" s="18" t="n">
-        <v>2.471020136522763</v>
+        <v>22.39384584527266</v>
       </c>
       <c r="E100" s="18" t="n">
-        <v>0.6869538871434049</v>
+        <v>0.7065032591764135</v>
       </c>
     </row>
     <row r="101">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="B101" s="18" t="n">
-        <v>0.3811431586791824</v>
+        <v>5.38394050011315e-09</v>
       </c>
       <c r="C101" s="18" t="n">
-        <v>0.05004921576376131</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D101" s="18" t="n">
-        <v>2.902545128651723</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0.3517374133949144</v>
+        <v>0.9994607925343963</v>
       </c>
     </row>
     <row r="102">
@@ -3159,16 +3159,16 @@
         </is>
       </c>
       <c r="B102" s="18" t="n">
-        <v>1.189984662056925</v>
+        <v>0.9461255572965408</v>
       </c>
       <c r="C102" s="18" t="n">
-        <v>1.073099930910414</v>
+        <v>0.6711845132547247</v>
       </c>
       <c r="D102" s="18" t="n">
-        <v>1.319600770758929</v>
+        <v>1.333692229918847</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>0.0009757554982066839</v>
+        <v>0.751891675586252</v>
       </c>
     </row>
     <row r="103">
@@ -3178,16 +3178,16 @@
         </is>
       </c>
       <c r="B103" s="18" t="n">
-        <v>1.081225534087192</v>
+        <v>0.8932782057804017</v>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.007725173214805</v>
+        <v>0.6529378085699872</v>
       </c>
       <c r="D103" s="18" t="n">
-        <v>1.160086784209906</v>
+        <v>1.222085690932574</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>0.02968933634341998</v>
+        <v>0.4803384917184649</v>
       </c>
     </row>
     <row r="104">
@@ -3213,11 +3213,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 303,
-  "llf": -925.5042689800755,
-  "aic": 1893.008537960151,
-  "pseudo_r2_mcfadden": 0.12124632139453095,
-  "lr_vs_null_chi2": 255.3934982709734,
+  "n_events": 207,
+  "llf": -691.6903656209505,
+  "aic": 1425.380731241901,
+  "pseudo_r2_mcfadden": 0.13663363535423334,
+  "lr_vs_null_chi2": 218.92946740649404,
   "lr_vs_null_pvalue": 0.0
 }</t>
         </is>
@@ -3234,16 +3234,16 @@
         </is>
       </c>
       <c r="B107" s="18" t="n">
-        <v>0.0267669840247112</v>
+        <v>0.03297932471141883</v>
       </c>
       <c r="C107" s="18" t="n">
-        <v>0.01629113621897699</v>
+        <v>0.01842066428832918</v>
       </c>
       <c r="D107" s="18" t="n">
-        <v>0.04397921815573248</v>
+        <v>0.05904433419973331</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>2.486438197939571e-46</v>
+        <v>1.626547486868297e-30</v>
       </c>
     </row>
     <row r="108">
@@ -3253,16 +3253,16 @@
         </is>
       </c>
       <c r="B108" s="18" t="n">
-        <v>0.6094490406365375</v>
+        <v>0.7123964730954562</v>
       </c>
       <c r="C108" s="18" t="n">
-        <v>0.3211991318489871</v>
+        <v>0.3463188194251166</v>
       </c>
       <c r="D108" s="18" t="n">
-        <v>1.156379629654242</v>
+        <v>1.465437932946586</v>
       </c>
       <c r="E108" s="18" t="n">
-        <v>0.1296832465925762</v>
+        <v>0.3567825087481744</v>
       </c>
     </row>
     <row r="109">
@@ -3272,16 +3272,16 @@
         </is>
       </c>
       <c r="B109" s="18" t="n">
-        <v>1.652402622603324</v>
+        <v>2.115753263314071</v>
       </c>
       <c r="C109" s="18" t="n">
-        <v>1.254797962615909</v>
+        <v>1.524694902902878</v>
       </c>
       <c r="D109" s="18" t="n">
-        <v>2.175995266595857</v>
+        <v>2.935939421520638</v>
       </c>
       <c r="E109" s="18" t="n">
-        <v>0.0003487040661778908</v>
+        <v>7.348172881643928e-06</v>
       </c>
     </row>
     <row r="110">
@@ -3291,16 +3291,16 @@
         </is>
       </c>
       <c r="B110" s="18" t="n">
-        <v>1.13856777785522</v>
+        <v>1.216673817895112</v>
       </c>
       <c r="C110" s="18" t="n">
-        <v>0.8618856797131065</v>
+        <v>0.8729335050485126</v>
       </c>
       <c r="D110" s="18" t="n">
-        <v>1.504070221008524</v>
+        <v>1.695770835453501</v>
       </c>
       <c r="E110" s="18" t="n">
-        <v>0.3609326077121604</v>
+        <v>0.2469693411467394</v>
       </c>
     </row>
     <row r="111">
@@ -3310,16 +3310,16 @@
         </is>
       </c>
       <c r="B111" s="18" t="n">
-        <v>0.943447212008162</v>
+        <v>1.020994847965987</v>
       </c>
       <c r="C111" s="18" t="n">
-        <v>0.6965645840870646</v>
+        <v>0.7013716672980215</v>
       </c>
       <c r="D111" s="18" t="n">
-        <v>1.277832181222007</v>
+        <v>1.486274008741997</v>
       </c>
       <c r="E111" s="18" t="n">
-        <v>0.7068478015651112</v>
+        <v>0.9136372115503152</v>
       </c>
     </row>
     <row r="112">
@@ -3329,16 +3329,16 @@
         </is>
       </c>
       <c r="B112" s="18" t="n">
-        <v>3.808166948585998</v>
+        <v>5.473082896141038</v>
       </c>
       <c r="C112" s="18" t="n">
-        <v>2.109123989508763</v>
+        <v>2.875502680800064</v>
       </c>
       <c r="D112" s="18" t="n">
-        <v>6.875904679117745</v>
+        <v>10.41718256360559</v>
       </c>
       <c r="E112" s="18" t="n">
-        <v>9.190604927806135e-06</v>
+        <v>2.261652120766744e-07</v>
       </c>
     </row>
     <row r="113">
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B113" s="18" t="n">
-        <v>0.438566612240775</v>
+        <v>0.544529545374156</v>
       </c>
       <c r="C113" s="18" t="n">
-        <v>0.1827794459634378</v>
+        <v>0.1889320027093498</v>
       </c>
       <c r="D113" s="18" t="n">
-        <v>1.052310189247565</v>
+        <v>1.569413447871694</v>
       </c>
       <c r="E113" s="18" t="n">
-        <v>0.06492367142555358</v>
+        <v>0.2603973157795424</v>
       </c>
     </row>
     <row r="114">
@@ -3367,16 +3367,16 @@
         </is>
       </c>
       <c r="B114" s="18" t="n">
-        <v>1.000000000019095</v>
+        <v>1.000000000024621</v>
       </c>
       <c r="C114" s="18" t="n">
-        <v>0.999999976997356</v>
+        <v>0.9999997801726078</v>
       </c>
       <c r="D114" s="18" t="n">
-        <v>1.000000023040834</v>
+        <v>1.000000219876684</v>
       </c>
       <c r="E114" s="18" t="n">
-        <v>0.9987029356673804</v>
+        <v>0.9998248653140258</v>
       </c>
     </row>
     <row r="115">
@@ -3386,16 +3386,16 @@
         </is>
       </c>
       <c r="B115" s="18" t="n">
-        <v>0.7037503491326083</v>
+        <v>0.62398625728541</v>
       </c>
       <c r="C115" s="18" t="n">
-        <v>0.4401584663917282</v>
+        <v>0.3491820003457491</v>
       </c>
       <c r="D115" s="18" t="n">
-        <v>1.125196018525512</v>
+        <v>1.115059908287148</v>
       </c>
       <c r="E115" s="18" t="n">
-        <v>0.1422888195966267</v>
+        <v>0.1113227995094537</v>
       </c>
     </row>
     <row r="116">
@@ -3405,16 +3405,16 @@
         </is>
       </c>
       <c r="B116" s="18" t="n">
-        <v>9.864189297542628</v>
+        <v>8.444678684466759</v>
       </c>
       <c r="C116" s="18" t="n">
-        <v>5.76426281161917</v>
+        <v>4.711661480659275</v>
       </c>
       <c r="D116" s="18" t="n">
-        <v>16.88025575475497</v>
+        <v>15.13533991705807</v>
       </c>
       <c r="E116" s="18" t="n">
-        <v>6.796049567736419e-17</v>
+        <v>7.690923638873345e-13</v>
       </c>
     </row>
     <row r="117">
@@ -3424,16 +3424,16 @@
         </is>
       </c>
       <c r="B117" s="18" t="n">
-        <v>2.319868377516864</v>
+        <v>2.07563477744881</v>
       </c>
       <c r="C117" s="18" t="n">
-        <v>0.992554406728174</v>
+        <v>0.7835929804545526</v>
       </c>
       <c r="D117" s="18" t="n">
-        <v>5.422160490670828</v>
+        <v>5.498083618431347</v>
       </c>
       <c r="E117" s="18" t="n">
-        <v>0.05205111302128768</v>
+        <v>0.1417503031121662</v>
       </c>
     </row>
     <row r="118">
@@ -3443,16 +3443,16 @@
         </is>
       </c>
       <c r="B118" s="18" t="n">
-        <v>1.380089245863183</v>
+        <v>5.110341067442643e-10</v>
       </c>
       <c r="C118" s="18" t="n">
-        <v>0.2649504785633153</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D118" s="18" t="n">
-        <v>7.188688002660296</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E118" s="18" t="n">
-        <v>0.7020294572537096</v>
+        <v>0.9992068606804133</v>
       </c>
     </row>
     <row r="119">
@@ -3462,16 +3462,16 @@
         </is>
       </c>
       <c r="B119" s="18" t="n">
-        <v>1.293567200842359</v>
+        <v>0.7947248234314505</v>
       </c>
       <c r="C119" s="18" t="n">
-        <v>0.8606279796575607</v>
+        <v>0.4903705689806253</v>
       </c>
       <c r="D119" s="18" t="n">
-        <v>1.944296656217174</v>
+        <v>1.287980121423446</v>
       </c>
       <c r="E119" s="18" t="n">
-        <v>0.2156968498185113</v>
+        <v>0.3509959780772471</v>
       </c>
     </row>
     <row r="120">
@@ -3481,16 +3481,16 @@
         </is>
       </c>
       <c r="B120" s="18" t="n">
-        <v>3.963714889943167</v>
+        <v>1.670310921380069</v>
       </c>
       <c r="C120" s="18" t="n">
-        <v>1.904675470628327</v>
+        <v>0.6941457581391319</v>
       </c>
       <c r="D120" s="18" t="n">
-        <v>8.248668064998137</v>
+        <v>4.019240255189072</v>
       </c>
       <c r="E120" s="18" t="n">
-        <v>0.0002304235725128495</v>
+        <v>0.2521735144254335</v>
       </c>
     </row>
     <row r="121">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="B121" s="18" t="n">
-        <v>4.723656745618966e-09</v>
+        <v>7.115052682665255e-10</v>
       </c>
       <c r="C121" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3509,7 +3509,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E121" s="18" t="n">
-        <v>0.9987029188869393</v>
+        <v>0.9994737706654728</v>
       </c>
     </row>
     <row r="122">
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="B122" s="18" t="n">
-        <v>1.000552665897017</v>
+        <v>0.6295945767595302</v>
       </c>
       <c r="C122" s="18" t="n">
-        <v>0.4939565760187717</v>
+        <v>0.2558030784235007</v>
       </c>
       <c r="D122" s="18" t="n">
-        <v>2.026707783308432</v>
+        <v>1.549587806088715</v>
       </c>
       <c r="E122" s="18" t="n">
-        <v>0.9987759138531196</v>
+        <v>0.3140085578793721</v>
       </c>
     </row>
     <row r="123">
@@ -3538,16 +3538,16 @@
         </is>
       </c>
       <c r="B123" s="18" t="n">
-        <v>1.158570994669663</v>
+        <v>1.828222147349385</v>
       </c>
       <c r="C123" s="18" t="n">
-        <v>0.7672208324234059</v>
+        <v>1.133187767426392</v>
       </c>
       <c r="D123" s="18" t="n">
-        <v>1.749544189839053</v>
+        <v>2.949551977294801</v>
       </c>
       <c r="E123" s="18" t="n">
-        <v>0.483981349819412</v>
+        <v>0.01342401970071077</v>
       </c>
     </row>
     <row r="124">
@@ -3557,16 +3557,16 @@
         </is>
       </c>
       <c r="B124" s="18" t="n">
-        <v>1.69185912693773</v>
+        <v>2.923501446329919</v>
       </c>
       <c r="C124" s="18" t="n">
-        <v>1.028703517240609</v>
+        <v>1.692126857382446</v>
       </c>
       <c r="D124" s="18" t="n">
-        <v>2.782519217082641</v>
+        <v>5.050957420482223</v>
       </c>
       <c r="E124" s="18" t="n">
-        <v>0.03831712044985667</v>
+        <v>0.000120386828779751</v>
       </c>
     </row>
     <row r="125">
@@ -3576,16 +3576,16 @@
         </is>
       </c>
       <c r="B125" s="18" t="n">
-        <v>1.717888752018898</v>
+        <v>2.641595145431568</v>
       </c>
       <c r="C125" s="18" t="n">
-        <v>0.950862391653214</v>
+        <v>1.33047912968084</v>
       </c>
       <c r="D125" s="18" t="n">
-        <v>3.103647583728759</v>
+        <v>5.244745863876529</v>
       </c>
       <c r="E125" s="18" t="n">
-        <v>0.07297249397204733</v>
+        <v>0.005503883917163984</v>
       </c>
     </row>
     <row r="126">
@@ -3595,16 +3595,16 @@
         </is>
       </c>
       <c r="B126" s="18" t="n">
-        <v>0.6566244968823475</v>
+        <v>1.258483241342104</v>
       </c>
       <c r="C126" s="18" t="n">
-        <v>0.1871601344235027</v>
+        <v>0.3506019892518297</v>
       </c>
       <c r="D126" s="18" t="n">
-        <v>2.303672901465138</v>
+        <v>4.517316265428645</v>
       </c>
       <c r="E126" s="18" t="n">
-        <v>0.511276715996507</v>
+        <v>0.7243981688057398</v>
       </c>
     </row>
     <row r="127">
@@ -3614,16 +3614,16 @@
         </is>
       </c>
       <c r="B127" s="18" t="n">
-        <v>1.086433313008164</v>
+        <v>0.9315528133273752</v>
       </c>
       <c r="C127" s="18" t="n">
-        <v>1.003522359126627</v>
+        <v>0.8473139378031018</v>
       </c>
       <c r="D127" s="18" t="n">
-        <v>1.176194364658853</v>
+        <v>1.024166610864607</v>
       </c>
       <c r="E127" s="18" t="n">
-        <v>0.04067997878349369</v>
+        <v>0.1426014608895745</v>
       </c>
     </row>
     <row r="128">
@@ -3633,16 +3633,16 @@
         </is>
       </c>
       <c r="B128" s="18" t="n">
-        <v>1.080494405034959</v>
+        <v>1.038195618451682</v>
       </c>
       <c r="C128" s="18" t="n">
-        <v>1.02047785588654</v>
+        <v>0.9702186126052279</v>
       </c>
       <c r="D128" s="18" t="n">
-        <v>1.144040659557096</v>
+        <v>1.110935337838996</v>
       </c>
       <c r="E128" s="18" t="n">
-        <v>0.007926432924495779</v>
+        <v>0.2779634572785756</v>
       </c>
     </row>
     <row r="129">
@@ -3668,11 +3668,11 @@
         <is>
           <t>{
   "n_obs": 2521,
-  "n_events": 138,
-  "llf": -465.43619265721696,
-  "aic": 972.8723853144339,
-  "pseudo_r2_mcfadden": 0.13049510541536558,
-  "lr_vs_null_chi2": 139.70512507337696,
+  "n_events": 188,
+  "llf": -580.6068941804726,
+  "aic": 1203.2137883609453,
+  "pseudo_r2_mcfadden": 0.1323359469785419,
+  "lr_vs_null_chi2": 177.10809361314568,
   "lr_vs_null_pvalue": 0.0,
   "n": 2525
 }</t>
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="B132" s="18" t="n">
-        <v>0.02908836568246988</v>
+        <v>0.04363130864346525</v>
       </c>
       <c r="C132" s="18" t="n">
-        <v>0.01422363206737047</v>
+        <v>0.02340113623837687</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.05948783082052238</v>
+        <v>0.08135037010806993</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>3.295407773829771e-22</v>
+        <v>6.626898695130678e-23</v>
       </c>
     </row>
     <row r="133">
@@ -3709,16 +3709,16 @@
         </is>
       </c>
       <c r="B133" s="18" t="n">
-        <v>0.6967038672593778</v>
+        <v>0.8367753662236633</v>
       </c>
       <c r="C133" s="18" t="n">
-        <v>0.2953856544843342</v>
+        <v>0.3919872181799608</v>
       </c>
       <c r="D133" s="18" t="n">
-        <v>1.643262871047503</v>
+        <v>1.786264911314757</v>
       </c>
       <c r="E133" s="18" t="n">
-        <v>0.409103046803036</v>
+        <v>0.6451048254172587</v>
       </c>
     </row>
     <row r="134">
@@ -3728,16 +3728,16 @@
         </is>
       </c>
       <c r="B134" s="18" t="n">
-        <v>1.56075483239178</v>
+        <v>1.75622057749488</v>
       </c>
       <c r="C134" s="18" t="n">
-        <v>1.047720718607233</v>
+        <v>1.240656534484457</v>
       </c>
       <c r="D134" s="18" t="n">
-        <v>2.325004749426435</v>
+        <v>2.486031090061608</v>
       </c>
       <c r="E134" s="18" t="n">
-        <v>0.02858136422021448</v>
+        <v>0.001492512891929718</v>
       </c>
     </row>
     <row r="135">
@@ -3747,16 +3747,16 @@
         </is>
       </c>
       <c r="B135" s="18" t="n">
-        <v>1.458627255653701</v>
+        <v>1.243982323774845</v>
       </c>
       <c r="C135" s="18" t="n">
-        <v>0.9838836891875408</v>
+        <v>0.8754086433034645</v>
       </c>
       <c r="D135" s="18" t="n">
-        <v>2.162444092037694</v>
+        <v>1.767736740666173</v>
       </c>
       <c r="E135" s="18" t="n">
-        <v>0.06023258661637108</v>
+        <v>0.2233198104369601</v>
       </c>
     </row>
     <row r="136">
@@ -3766,16 +3766,16 @@
         </is>
       </c>
       <c r="B136" s="18" t="n">
-        <v>0.9574647974563437</v>
+        <v>1.046461229658687</v>
       </c>
       <c r="C136" s="18" t="n">
-        <v>0.602114387491521</v>
+        <v>0.6991150899697461</v>
       </c>
       <c r="D136" s="18" t="n">
-        <v>1.522532690486534</v>
+        <v>1.566381731548892</v>
       </c>
       <c r="E136" s="18" t="n">
-        <v>0.854274615306685</v>
+        <v>0.8253453914381443</v>
       </c>
     </row>
     <row r="137">
@@ -3785,16 +3785,16 @@
         </is>
       </c>
       <c r="B137" s="18" t="n">
-        <v>4.109223330412473</v>
+        <v>5.530902207001015</v>
       </c>
       <c r="C137" s="18" t="n">
-        <v>1.887696337379918</v>
+        <v>2.744222804289304</v>
       </c>
       <c r="D137" s="18" t="n">
-        <v>8.94514443072088</v>
+        <v>11.1473744681351</v>
       </c>
       <c r="E137" s="18" t="n">
-        <v>0.0003696831296258759</v>
+        <v>1.726415487561163e-06</v>
       </c>
     </row>
     <row r="138">
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="B138" s="18" t="n">
-        <v>0.4068359110860293</v>
+        <v>0.4514993853613486</v>
       </c>
       <c r="C138" s="18" t="n">
-        <v>0.09281764416320884</v>
+        <v>0.1329739035102636</v>
       </c>
       <c r="D138" s="18" t="n">
-        <v>1.783232703667421</v>
+        <v>1.533020311507523</v>
       </c>
       <c r="E138" s="18" t="n">
-        <v>0.2329486047848915</v>
+        <v>0.2023266960036824</v>
       </c>
     </row>
     <row r="139">
@@ -3823,16 +3823,16 @@
         </is>
       </c>
       <c r="B139" s="18" t="n">
-        <v>1.000000000034585</v>
+        <v>0.999999999854895</v>
       </c>
       <c r="C139" s="18" t="n">
-        <v>0.9999999298307514</v>
+        <v>0.9999997325923143</v>
       </c>
       <c r="D139" s="18" t="n">
-        <v>1.000000070238424</v>
+        <v>1.000000267117547</v>
       </c>
       <c r="E139" s="18" t="n">
-        <v>0.9992295924674709</v>
+        <v>0.99915095199866</v>
       </c>
     </row>
     <row r="140">
@@ -3842,16 +3842,16 @@
         </is>
       </c>
       <c r="B140" s="18" t="n">
-        <v>0.3686023654622728</v>
+        <v>0.4738408423987575</v>
       </c>
       <c r="C140" s="18" t="n">
-        <v>0.1625998523490924</v>
+        <v>0.2481105493357377</v>
       </c>
       <c r="D140" s="18" t="n">
-        <v>0.83559549323995</v>
+        <v>0.9049399331317497</v>
       </c>
       <c r="E140" s="18" t="n">
-        <v>0.01684402024437861</v>
+        <v>0.02366324443146435</v>
       </c>
     </row>
     <row r="141">
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="B141" s="18" t="n">
-        <v>7.264690280466549</v>
+        <v>6.910574375749285</v>
       </c>
       <c r="C141" s="18" t="n">
-        <v>3.809578983992684</v>
+        <v>3.823468293839909</v>
       </c>
       <c r="D141" s="18" t="n">
-        <v>13.85342713535048</v>
+        <v>12.49024041331888</v>
       </c>
       <c r="E141" s="18" t="n">
-        <v>1.732410226682796e-09</v>
+        <v>1.543709985989811e-10</v>
       </c>
     </row>
     <row r="142">
@@ -3880,16 +3880,16 @@
         </is>
       </c>
       <c r="B142" s="18" t="n">
-        <v>1.526244356792841</v>
+        <v>1.12729182712519</v>
       </c>
       <c r="C142" s="18" t="n">
-        <v>0.4834428215446275</v>
+        <v>0.372215865716208</v>
       </c>
       <c r="D142" s="18" t="n">
-        <v>4.818401955373661</v>
+        <v>3.414112563573922</v>
       </c>
       <c r="E142" s="18" t="n">
-        <v>0.4710124921846449</v>
+        <v>0.8321618368320125</v>
       </c>
     </row>
     <row r="143">
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="B143" s="18" t="n">
-        <v>1.342942866592801e-09</v>
+        <v>8.547062639071912e-10</v>
       </c>
       <c r="C143" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3908,7 +3908,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E143" s="18" t="n">
-        <v>0.9990038688346223</v>
+        <v>0.9989577186999676</v>
       </c>
     </row>
     <row r="144">
@@ -3918,16 +3918,16 @@
         </is>
       </c>
       <c r="B144" s="18" t="n">
-        <v>0.7976062383549249</v>
+        <v>0.6931726148542389</v>
       </c>
       <c r="C144" s="18" t="n">
-        <v>0.4449690053260308</v>
+        <v>0.4149129396065503</v>
       </c>
       <c r="D144" s="18" t="n">
-        <v>1.429707920884432</v>
+        <v>1.158046009458022</v>
       </c>
       <c r="E144" s="18" t="n">
-        <v>0.4475795226531398</v>
+        <v>0.1616383777105939</v>
       </c>
     </row>
     <row r="145">
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="B145" s="18" t="n">
-        <v>2.298546506418883</v>
+        <v>1.75659119782004</v>
       </c>
       <c r="C145" s="18" t="n">
-        <v>0.8733351751023075</v>
+        <v>0.7105742574998318</v>
       </c>
       <c r="D145" s="18" t="n">
-        <v>6.049585763623382</v>
+        <v>4.342421082232316</v>
       </c>
       <c r="E145" s="18" t="n">
-        <v>0.09186168903436234</v>
+        <v>0.2224542073301841</v>
       </c>
     </row>
     <row r="146">
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="B146" s="18" t="n">
-        <v>2.696103367404128e-09</v>
+        <v>1.778887478333027e-09</v>
       </c>
       <c r="C146" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3965,7 +3965,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E146" s="18" t="n">
-        <v>0.9993452656452344</v>
+        <v>0.9993308193721876</v>
       </c>
     </row>
     <row r="147">
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="B147" s="18" t="n">
-        <v>0.9198714516263979</v>
+        <v>0.7211873930185499</v>
       </c>
       <c r="C147" s="18" t="n">
-        <v>0.3407862767436721</v>
+        <v>0.2908392318501625</v>
       </c>
       <c r="D147" s="18" t="n">
-        <v>2.482974066921457</v>
+        <v>1.78831188811848</v>
       </c>
       <c r="E147" s="18" t="n">
-        <v>0.8690570239934933</v>
+        <v>0.4805388967759936</v>
       </c>
     </row>
     <row r="148">
@@ -3994,16 +3994,16 @@
         </is>
       </c>
       <c r="B148" s="18" t="n">
-        <v>1.670515128410172</v>
+        <v>1.750492570098143</v>
       </c>
       <c r="C148" s="18" t="n">
-        <v>0.9483483889786684</v>
+        <v>1.060749396389155</v>
       </c>
       <c r="D148" s="18" t="n">
-        <v>2.942611414411361</v>
+        <v>2.888735311469023</v>
       </c>
       <c r="E148" s="18" t="n">
-        <v>0.07567162892133317</v>
+        <v>0.02847213972373774</v>
       </c>
     </row>
     <row r="149">
@@ -4013,16 +4013,16 @@
         </is>
       </c>
       <c r="B149" s="18" t="n">
-        <v>2.017062696856311</v>
+        <v>2.111799843108331</v>
       </c>
       <c r="C149" s="18" t="n">
-        <v>1.007396366826732</v>
+        <v>1.155935454318834</v>
       </c>
       <c r="D149" s="18" t="n">
-        <v>4.03867043501957</v>
+        <v>3.858086159300625</v>
       </c>
       <c r="E149" s="18" t="n">
-        <v>0.04761736256326053</v>
+        <v>0.01504635624762385</v>
       </c>
     </row>
     <row r="150">
@@ -4032,16 +4032,16 @@
         </is>
       </c>
       <c r="B150" s="18" t="n">
-        <v>2.226052214747696</v>
+        <v>2.399736053179221</v>
       </c>
       <c r="C150" s="18" t="n">
-        <v>0.9737306036417397</v>
+        <v>1.167875214211356</v>
       </c>
       <c r="D150" s="18" t="n">
-        <v>5.088993243357385</v>
+        <v>4.930949004527807</v>
       </c>
       <c r="E150" s="18" t="n">
-        <v>0.0578460779069714</v>
+        <v>0.01720460371182364</v>
       </c>
     </row>
     <row r="151">
@@ -4051,16 +4051,16 @@
         </is>
       </c>
       <c r="B151" s="18" t="n">
-        <v>1.374306357101369</v>
+        <v>1.596500572743153</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>0.2865455654617833</v>
+        <v>0.4240292548313608</v>
       </c>
       <c r="D151" s="18" t="n">
-        <v>6.591335518054409</v>
+        <v>6.010939221122599</v>
       </c>
       <c r="E151" s="18" t="n">
-        <v>0.6910149479343543</v>
+        <v>0.4891893343829928</v>
       </c>
     </row>
     <row r="152">
@@ -4070,16 +4070,16 @@
         </is>
       </c>
       <c r="B152" s="18" t="n">
-        <v>0.9674994576527555</v>
+        <v>0.9430109003645007</v>
       </c>
       <c r="C152" s="18" t="n">
-        <v>0.8626119829159001</v>
+        <v>0.8532657096965484</v>
       </c>
       <c r="D152" s="18" t="n">
-        <v>1.085140502447247</v>
+        <v>1.042195353804294</v>
       </c>
       <c r="E152" s="18" t="n">
-        <v>0.5725223452727237</v>
+        <v>0.2501529542629989</v>
       </c>
     </row>
     <row r="153">
@@ -4089,16 +4089,16 @@
         </is>
       </c>
       <c r="B153" s="18" t="n">
-        <v>1.073737581618053</v>
+        <v>1.077816640081945</v>
       </c>
       <c r="C153" s="18" t="n">
-        <v>0.9875127997683897</v>
+        <v>1.000062832099851</v>
       </c>
       <c r="D153" s="18" t="n">
-        <v>1.167491089178173</v>
+        <v>1.161615722882444</v>
       </c>
       <c r="E153" s="18" t="n">
-        <v>0.09576197272368855</v>
+        <v>0.04980806252637921</v>
       </c>
     </row>
     <row r="154">
@@ -4123,14 +4123,14 @@
       <c r="A156" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 2937,
-  "n_events": 78,
-  "llf": -311.58207763500735,
-  "aic": 665.1641552700147,
-  "pseudo_r2_mcfadden": 0.1348168172870341,
-  "lr_vs_null_chi2": 97.10430084577683,
-  "lr_vs_null_pvalue": 4.138800413500121e-12,
-  "n": 2943
+  "n_obs": 3717,
+  "n_events": 193,
+  "llf": -651.0944143756712,
+  "aic": 1344.1888287513425,
+  "pseudo_r2_mcfadden": 0.14229297228102877,
+  "lr_vs_null_chi2": 216.0321799005842,
+  "lr_vs_null_pvalue": 0.0,
+  "n": 3723
 }</t>
         </is>
       </c>
@@ -4146,16 +4146,16 @@
         </is>
       </c>
       <c r="B157" s="18" t="n">
-        <v>0.006502386128745978</v>
+        <v>0.03100129671872217</v>
       </c>
       <c r="C157" s="18" t="n">
-        <v>0.002483292138222196</v>
+        <v>0.01694356078479456</v>
       </c>
       <c r="D157" s="18" t="n">
-        <v>0.01702619869669356</v>
+        <v>0.05672245701179554</v>
       </c>
       <c r="E157" s="18" t="n">
-        <v>1.144884845538399e-24</v>
+        <v>1.855879669272762e-29</v>
       </c>
     </row>
     <row r="158">
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="B158" s="18" t="n">
-        <v>1.039491980508763</v>
+        <v>0.7150318147426775</v>
       </c>
       <c r="C158" s="18" t="n">
-        <v>0.3413370167749367</v>
+        <v>0.3414272777287525</v>
       </c>
       <c r="D158" s="18" t="n">
-        <v>3.165620851061973</v>
+        <v>1.497450641598667</v>
       </c>
       <c r="E158" s="18" t="n">
-        <v>0.945651543906166</v>
+        <v>0.3737956944075218</v>
       </c>
     </row>
     <row r="159">
@@ -4184,16 +4184,16 @@
         </is>
       </c>
       <c r="B159" s="18" t="n">
-        <v>2.506147697411602</v>
+        <v>2.072147125881193</v>
       </c>
       <c r="C159" s="18" t="n">
-        <v>1.454459174816054</v>
+        <v>1.475059846025695</v>
       </c>
       <c r="D159" s="18" t="n">
-        <v>4.318289842707896</v>
+        <v>2.910928477150679</v>
       </c>
       <c r="E159" s="18" t="n">
-        <v>0.0009348131726604907</v>
+        <v>2.652668493025389e-05</v>
       </c>
     </row>
     <row r="160">
@@ -4203,16 +4203,16 @@
         </is>
       </c>
       <c r="B160" s="18" t="n">
-        <v>1.432107419559419</v>
+        <v>1.231457338257394</v>
       </c>
       <c r="C160" s="18" t="n">
-        <v>0.8590537645802639</v>
+        <v>0.8736264681971518</v>
       </c>
       <c r="D160" s="18" t="n">
-        <v>2.387431084897498</v>
+        <v>1.735853057517208</v>
       </c>
       <c r="E160" s="18" t="n">
-        <v>0.1684089568398195</v>
+        <v>0.234581073474619</v>
       </c>
     </row>
     <row r="161">
@@ -4222,16 +4222,16 @@
         </is>
       </c>
       <c r="B161" s="18" t="n">
-        <v>0.934908197130936</v>
+        <v>1.043205914738665</v>
       </c>
       <c r="C161" s="18" t="n">
-        <v>0.5124098854763671</v>
+        <v>0.705177134727242</v>
       </c>
       <c r="D161" s="18" t="n">
-        <v>1.705769856976987</v>
+        <v>1.543269806906989</v>
       </c>
       <c r="E161" s="18" t="n">
-        <v>0.8263529696478267</v>
+        <v>0.8323391879185403</v>
       </c>
     </row>
     <row r="162">
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="B162" s="18" t="n">
-        <v>4.270051806130786</v>
+        <v>6.098413824737721</v>
       </c>
       <c r="C162" s="18" t="n">
-        <v>1.489743097647362</v>
+        <v>3.134312628284531</v>
       </c>
       <c r="D162" s="18" t="n">
-        <v>12.23925283213953</v>
+        <v>11.8656482579746</v>
       </c>
       <c r="E162" s="18" t="n">
-        <v>0.006894966928026045</v>
+        <v>1.015799091084381e-07</v>
       </c>
     </row>
     <row r="163">
@@ -4260,16 +4260,16 @@
         </is>
       </c>
       <c r="B163" s="18" t="n">
-        <v>0.5892028459037046</v>
+        <v>0.4348271502381356</v>
       </c>
       <c r="C163" s="18" t="n">
-        <v>0.128231971474948</v>
+        <v>0.1301058082141819</v>
       </c>
       <c r="D163" s="18" t="n">
-        <v>2.707281106481682</v>
+        <v>1.453237585465523</v>
       </c>
       <c r="E163" s="18" t="n">
-        <v>0.4965713353907472</v>
+        <v>0.176124338010709</v>
       </c>
     </row>
     <row r="164">
@@ -4279,16 +4279,16 @@
         </is>
       </c>
       <c r="B164" s="18" t="n">
-        <v>1.000000000017794</v>
+        <v>0.9999999999186785</v>
       </c>
       <c r="C164" s="18" t="n">
-        <v>0.9999998264468912</v>
+        <v>0.9999998288546924</v>
       </c>
       <c r="D164" s="18" t="n">
-        <v>1.000000173588727</v>
+        <v>1.000000170982694</v>
       </c>
       <c r="E164" s="18" t="n">
-        <v>0.9998396795404492</v>
+        <v>0.9992565788374325</v>
       </c>
     </row>
     <row r="165">
@@ -4298,16 +4298,16 @@
         </is>
       </c>
       <c r="B165" s="18" t="n">
-        <v>0.2273963112968245</v>
+        <v>0.5167956980295385</v>
       </c>
       <c r="C165" s="18" t="n">
-        <v>0.06313252446005879</v>
+        <v>0.2725848475576154</v>
       </c>
       <c r="D165" s="18" t="n">
-        <v>0.8190561494830829</v>
+        <v>0.9797969178950294</v>
       </c>
       <c r="E165" s="18" t="n">
-        <v>0.02349721362966558</v>
+        <v>0.0431249442048128</v>
       </c>
     </row>
     <row r="166">
@@ -4317,16 +4317,16 @@
         </is>
       </c>
       <c r="B166" s="18" t="n">
-        <v>5.51106952524079</v>
+        <v>8.600413345423584</v>
       </c>
       <c r="C166" s="18" t="n">
-        <v>2.427593499139769</v>
+        <v>4.757220482490345</v>
       </c>
       <c r="D166" s="18" t="n">
-        <v>12.51110917985247</v>
+        <v>15.54838796822367</v>
       </c>
       <c r="E166" s="18" t="n">
-        <v>4.499699787636308e-05</v>
+        <v>1.061092590082541e-12</v>
       </c>
     </row>
     <row r="167">
@@ -4336,16 +4336,16 @@
         </is>
       </c>
       <c r="B167" s="18" t="n">
-        <v>0.8047511377402732</v>
+        <v>1.734462027176505</v>
       </c>
       <c r="C167" s="18" t="n">
-        <v>0.1473111243650157</v>
+        <v>0.6175440705272582</v>
       </c>
       <c r="D167" s="18" t="n">
-        <v>4.396303378212933</v>
+        <v>4.871487991373149</v>
       </c>
       <c r="E167" s="18" t="n">
-        <v>0.8020175877862454</v>
+        <v>0.2959454935688725</v>
       </c>
     </row>
     <row r="168">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="B168" s="18" t="n">
-        <v>3.627304354786253e-09</v>
+        <v>5.056238745370455e-10</v>
       </c>
       <c r="C168" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4364,7 +4364,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E168" s="18" t="n">
-        <v>0.9994078977176027</v>
+        <v>0.9991996755193954</v>
       </c>
     </row>
     <row r="169">
@@ -4374,16 +4374,16 @@
         </is>
       </c>
       <c r="B169" s="18" t="n">
-        <v>0.6544769775633407</v>
+        <v>0.7434836808352291</v>
       </c>
       <c r="C169" s="18" t="n">
-        <v>0.3039646223368073</v>
+        <v>0.4469066364251899</v>
       </c>
       <c r="D169" s="18" t="n">
-        <v>1.409177524895723</v>
+        <v>1.23687575572808</v>
       </c>
       <c r="E169" s="18" t="n">
-        <v>0.2786430202448137</v>
+        <v>0.2537193514613728</v>
       </c>
     </row>
     <row r="170">
@@ -4393,16 +4393,16 @@
         </is>
       </c>
       <c r="B170" s="18" t="n">
-        <v>1.422492904658987</v>
+        <v>1.821561298414603</v>
       </c>
       <c r="C170" s="18" t="n">
-        <v>0.2864644973892301</v>
+        <v>0.7498929489128719</v>
       </c>
       <c r="D170" s="18" t="n">
-        <v>7.063653898639225</v>
+        <v>4.424745650285363</v>
       </c>
       <c r="E170" s="18" t="n">
-        <v>0.6664624974393076</v>
+        <v>0.1853894168502391</v>
       </c>
     </row>
     <row r="171">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="B171" s="18" t="n">
-        <v>2.604428285762068e-09</v>
+        <v>7.709877016853058e-10</v>
       </c>
       <c r="C171" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4421,7 +4421,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E171" s="18" t="n">
-        <v>0.9992422617613105</v>
+        <v>0.9994745498615001</v>
       </c>
     </row>
     <row r="172">
@@ -4431,16 +4431,16 @@
         </is>
       </c>
       <c r="B172" s="18" t="n">
-        <v>0.5566285153286287</v>
+        <v>0.6693454840649947</v>
       </c>
       <c r="C172" s="18" t="n">
-        <v>0.1528545047597947</v>
+        <v>0.2693990584096177</v>
       </c>
       <c r="D172" s="18" t="n">
-        <v>2.026994916269222</v>
+        <v>1.663047301215836</v>
       </c>
       <c r="E172" s="18" t="n">
-        <v>0.3742920992143629</v>
+        <v>0.3872830685344942</v>
       </c>
     </row>
     <row r="173">
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="B173" s="18" t="n">
-        <v>2.663589003054468</v>
+        <v>1.816074625029992</v>
       </c>
       <c r="C173" s="18" t="n">
-        <v>1.268853652465288</v>
+        <v>1.104607899864972</v>
       </c>
       <c r="D173" s="18" t="n">
-        <v>5.591429999360614</v>
+        <v>2.98578983916464</v>
       </c>
       <c r="E173" s="18" t="n">
-        <v>0.009616984338207917</v>
+        <v>0.0186644495147789</v>
       </c>
     </row>
     <row r="174">
@@ -4469,16 +4469,16 @@
         </is>
       </c>
       <c r="B174" s="18" t="n">
-        <v>3.113416766669969</v>
+        <v>2.371076262941582</v>
       </c>
       <c r="C174" s="18" t="n">
-        <v>1.246049058850452</v>
+        <v>1.304690715213044</v>
       </c>
       <c r="D174" s="18" t="n">
-        <v>7.779279550938662</v>
+        <v>4.309069252299383</v>
       </c>
       <c r="E174" s="18" t="n">
-        <v>0.01506626457807376</v>
+        <v>0.004617347076342188</v>
       </c>
     </row>
     <row r="175">
@@ -4488,16 +4488,16 @@
         </is>
       </c>
       <c r="B175" s="18" t="n">
-        <v>4.092504815044145</v>
+        <v>2.773688972599852</v>
       </c>
       <c r="C175" s="18" t="n">
-        <v>1.4044538520001</v>
+        <v>1.36362772124516</v>
       </c>
       <c r="D175" s="18" t="n">
-        <v>11.92534424488752</v>
+        <v>5.641826135433098</v>
       </c>
       <c r="E175" s="18" t="n">
-        <v>0.009811629327635359</v>
+        <v>0.004861092716051891</v>
       </c>
     </row>
     <row r="176">
@@ -4507,16 +4507,16 @@
         </is>
       </c>
       <c r="B176" s="18" t="n">
-        <v>2.712979000475439</v>
+        <v>1.363877952718846</v>
       </c>
       <c r="C176" s="18" t="n">
-        <v>0.5624202234570175</v>
+        <v>0.3739360326313018</v>
       </c>
       <c r="D176" s="18" t="n">
-        <v>13.08675390756679</v>
+        <v>4.974548873568054</v>
       </c>
       <c r="E176" s="18" t="n">
-        <v>0.2138186518143934</v>
+        <v>0.6383227355345196</v>
       </c>
     </row>
     <row r="177">
@@ -4526,16 +4526,16 @@
         </is>
       </c>
       <c r="B177" s="18" t="n">
-        <v>1.082385853805393</v>
+        <v>0.9335220944450449</v>
       </c>
       <c r="C177" s="18" t="n">
-        <v>0.9306294844737771</v>
+        <v>0.8462624530058837</v>
       </c>
       <c r="D177" s="18" t="n">
-        <v>1.258888909134966</v>
+        <v>1.029779234233619</v>
       </c>
       <c r="E177" s="18" t="n">
-        <v>0.3043411616052959</v>
+        <v>0.169474659107431</v>
       </c>
     </row>
     <row r="178">
@@ -4545,16 +4545,16 @@
         </is>
       </c>
       <c r="B178" s="18" t="n">
-        <v>1.037916303799494</v>
+        <v>1.044178307246225</v>
       </c>
       <c r="C178" s="18" t="n">
-        <v>0.9399201287406921</v>
+        <v>0.974356721352632</v>
       </c>
       <c r="D178" s="18" t="n">
-        <v>1.146129570749946</v>
+        <v>1.119003249456721</v>
       </c>
       <c r="E178" s="18" t="n">
-        <v>0.4620549727048879</v>
+        <v>0.2208481672060447</v>
       </c>
     </row>
     <row r="179">
@@ -4580,11 +4580,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -514.3309410872571,
-  "aic": 1068.6618821745142,
-  "pseudo_r2_mcfadden": 0.13503753184707556,
-  "lr_vs_null_chi2": 160.59420701876616,
+  "n_events": 193,
+  "llf": -659.833331011966,
+  "aic": 1359.666662023932,
+  "pseudo_r2_mcfadden": 0.13277867633378282,
+  "lr_vs_null_chi2": 202.05175749668342,
   "lr_vs_null_pvalue": 0.0
 }</t>
         </is>
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="B182" s="18" t="n">
-        <v>0.01558270619948315</v>
+        <v>0.02527058313800203</v>
       </c>
       <c r="C182" s="18" t="n">
-        <v>0.007958222128147119</v>
+        <v>0.01426522477669402</v>
       </c>
       <c r="D182" s="18" t="n">
-        <v>0.03051193201061674</v>
+        <v>0.04476637291954885</v>
       </c>
       <c r="E182" s="18" t="n">
-        <v>6.598402949008738e-34</v>
+        <v>1.928487978383358e-36</v>
       </c>
     </row>
     <row r="183">
@@ -4620,16 +4620,16 @@
         </is>
       </c>
       <c r="B183" s="18" t="n">
-        <v>0.4561132506767139</v>
+        <v>0.6039166233799963</v>
       </c>
       <c r="C183" s="18" t="n">
-        <v>0.1934735465322265</v>
+        <v>0.2889105819236581</v>
       </c>
       <c r="D183" s="18" t="n">
-        <v>1.075285490816318</v>
+        <v>1.26238120309165</v>
       </c>
       <c r="E183" s="18" t="n">
-        <v>0.07280117755237232</v>
+        <v>0.1800514146595602</v>
       </c>
     </row>
     <row r="184">
@@ -4639,16 +4639,16 @@
         </is>
       </c>
       <c r="B184" s="18" t="n">
-        <v>1.775640143294263</v>
+        <v>2.069652404189313</v>
       </c>
       <c r="C184" s="18" t="n">
-        <v>1.198689496902142</v>
+        <v>1.476685616213492</v>
       </c>
       <c r="D184" s="18" t="n">
-        <v>2.630287431921552</v>
+        <v>2.900726483102225</v>
       </c>
       <c r="E184" s="18" t="n">
-        <v>0.004184044109714271</v>
+        <v>2.409536762635444e-05</v>
       </c>
     </row>
     <row r="185">
@@ -4658,16 +4658,16 @@
         </is>
       </c>
       <c r="B185" s="18" t="n">
-        <v>1.322052159491932</v>
+        <v>1.164320594150314</v>
       </c>
       <c r="C185" s="18" t="n">
-        <v>0.8953467408035691</v>
+        <v>0.8277340060898324</v>
       </c>
       <c r="D185" s="18" t="n">
-        <v>1.952117356063215</v>
+        <v>1.637775464084793</v>
       </c>
       <c r="E185" s="18" t="n">
-        <v>0.1603090431560963</v>
+        <v>0.3821586862064008</v>
       </c>
     </row>
     <row r="186">
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="B186" s="18" t="n">
-        <v>0.5284257222228992</v>
+        <v>0.6567404076767659</v>
       </c>
       <c r="C186" s="18" t="n">
-        <v>0.2341764352175759</v>
+        <v>0.3455271301133249</v>
       </c>
       <c r="D186" s="18" t="n">
-        <v>1.192407526604261</v>
+        <v>1.248260774585155</v>
       </c>
       <c r="E186" s="18" t="n">
-        <v>0.1244991954150533</v>
+        <v>0.1994190645217789</v>
       </c>
     </row>
     <row r="187">
@@ -4696,16 +4696,16 @@
         </is>
       </c>
       <c r="B187" s="18" t="n">
-        <v>7.562267570680389</v>
+        <v>7.436080604949479</v>
       </c>
       <c r="C187" s="18" t="n">
-        <v>3.887523607210341</v>
+        <v>4.077585818484178</v>
       </c>
       <c r="D187" s="18" t="n">
-        <v>14.71062213088447</v>
+        <v>13.56079239648267</v>
       </c>
       <c r="E187" s="18" t="n">
-        <v>2.532466925013516e-09</v>
+        <v>5.958038260080889e-11</v>
       </c>
     </row>
     <row r="188">
@@ -4715,16 +4715,16 @@
         </is>
       </c>
       <c r="B188" s="18" t="n">
-        <v>2.19807968652546</v>
+        <v>2.010418509520878</v>
       </c>
       <c r="C188" s="18" t="n">
-        <v>0.6958696997203222</v>
+        <v>0.7091941804292959</v>
       </c>
       <c r="D188" s="18" t="n">
-        <v>6.943188229431055</v>
+        <v>5.699119782649007</v>
       </c>
       <c r="E188" s="18" t="n">
-        <v>0.1795680857507178</v>
+        <v>0.1889819111102734</v>
       </c>
     </row>
     <row r="189">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="B189" s="18" t="n">
-        <v>9.103951323747511e-10</v>
+        <v>6.590067645738035e-10</v>
       </c>
       <c r="C189" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4743,7 +4743,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E189" s="18" t="n">
-        <v>0.9992449015870003</v>
+        <v>0.9992343727220721</v>
       </c>
     </row>
     <row r="190">
@@ -4753,16 +4753,16 @@
         </is>
       </c>
       <c r="B190" s="18" t="n">
-        <v>0.7894421567339874</v>
+        <v>0.6935195757366641</v>
       </c>
       <c r="C190" s="18" t="n">
-        <v>0.4387083777085533</v>
+        <v>0.4171511104288705</v>
       </c>
       <c r="D190" s="18" t="n">
-        <v>1.420576744132368</v>
+        <v>1.152986028097782</v>
       </c>
       <c r="E190" s="18" t="n">
-        <v>0.4302504600248325</v>
+        <v>0.1582188256733409</v>
       </c>
     </row>
     <row r="191">
@@ -4772,16 +4772,16 @@
         </is>
       </c>
       <c r="B191" s="18" t="n">
-        <v>1.719414031921572</v>
+        <v>1.306259139061344</v>
       </c>
       <c r="C191" s="18" t="n">
-        <v>0.6455881769315357</v>
+        <v>0.5304357610650219</v>
       </c>
       <c r="D191" s="18" t="n">
-        <v>4.57936610180877</v>
+        <v>3.216813540164239</v>
       </c>
       <c r="E191" s="18" t="n">
-        <v>0.2781807357901862</v>
+        <v>0.56121989692881</v>
       </c>
     </row>
     <row r="192">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="B192" s="18" t="n">
-        <v>1.439361522774956e-09</v>
+        <v>9.34662820712118e-10</v>
       </c>
       <c r="C192" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4800,7 +4800,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E192" s="18" t="n">
-        <v>0.9994934671243836</v>
+        <v>0.9994812248496244</v>
       </c>
     </row>
     <row r="193">
@@ -4810,16 +4810,16 @@
         </is>
       </c>
       <c r="B193" s="18" t="n">
-        <v>0.9463750321896648</v>
+        <v>0.7295399806870587</v>
       </c>
       <c r="C193" s="18" t="n">
-        <v>0.356253989721381</v>
+        <v>0.2997925295712148</v>
       </c>
       <c r="D193" s="18" t="n">
-        <v>2.514008902054514</v>
+        <v>1.775323034840482</v>
       </c>
       <c r="E193" s="18" t="n">
-        <v>0.9119575645804074</v>
+        <v>0.4870712439830762</v>
       </c>
     </row>
     <row r="194">
@@ -4829,16 +4829,16 @@
         </is>
       </c>
       <c r="B194" s="18" t="n">
-        <v>1.493459267068766</v>
+        <v>1.557823600479261</v>
       </c>
       <c r="C194" s="18" t="n">
-        <v>0.853248480403083</v>
+        <v>0.9541886495043181</v>
       </c>
       <c r="D194" s="18" t="n">
-        <v>2.614034051768721</v>
+        <v>2.543327644350883</v>
       </c>
       <c r="E194" s="18" t="n">
-        <v>0.16022666156398</v>
+        <v>0.0763178709251582</v>
       </c>
     </row>
     <row r="195">
@@ -4848,16 +4848,16 @@
         </is>
       </c>
       <c r="B195" s="18" t="n">
-        <v>2.050143865099995</v>
+        <v>2.105749074656395</v>
       </c>
       <c r="C195" s="18" t="n">
-        <v>1.027023712293629</v>
+        <v>1.160750223888297</v>
       </c>
       <c r="D195" s="18" t="n">
-        <v>4.092495448055898</v>
+        <v>3.820097618041022</v>
       </c>
       <c r="E195" s="18" t="n">
-        <v>0.04179352348710282</v>
+        <v>0.01426583045112131</v>
       </c>
     </row>
     <row r="196">
@@ -4867,16 +4867,16 @@
         </is>
       </c>
       <c r="B196" s="18" t="n">
-        <v>2.265299968370812</v>
+        <v>2.549493737205072</v>
       </c>
       <c r="C196" s="18" t="n">
-        <v>0.9984223640147872</v>
+        <v>1.265842431421196</v>
       </c>
       <c r="D196" s="18" t="n">
-        <v>5.139692510558389</v>
+        <v>5.13485577249156</v>
       </c>
       <c r="E196" s="18" t="n">
-        <v>0.05044314669462652</v>
+        <v>0.00879633214983817</v>
       </c>
     </row>
     <row r="197">
@@ -4886,16 +4886,16 @@
         </is>
       </c>
       <c r="B197" s="18" t="n">
-        <v>0.9375532466402631</v>
+        <v>1.073131678980225</v>
       </c>
       <c r="C197" s="18" t="n">
-        <v>0.2041948671644215</v>
+        <v>0.2999893107247148</v>
       </c>
       <c r="D197" s="18" t="n">
-        <v>4.304741360505924</v>
+        <v>3.838842116236913</v>
       </c>
       <c r="E197" s="18" t="n">
-        <v>0.9339176039757167</v>
+        <v>0.9135719530365902</v>
       </c>
     </row>
     <row r="198">
@@ -4905,16 +4905,16 @@
         </is>
       </c>
       <c r="B198" s="18" t="n">
-        <v>0.9804731615872894</v>
+        <v>0.9548960230641651</v>
       </c>
       <c r="C198" s="18" t="n">
-        <v>0.8739526713807532</v>
+        <v>0.8651420681624363</v>
       </c>
       <c r="D198" s="18" t="n">
-        <v>1.099976751686311</v>
+        <v>1.053961480338692</v>
       </c>
       <c r="E198" s="18" t="n">
-        <v>0.7368219511609637</v>
+        <v>0.3594508049613295</v>
       </c>
     </row>
     <row r="199">
@@ -4924,16 +4924,16 @@
         </is>
       </c>
       <c r="B199" s="18" t="n">
-        <v>1.035860268228134</v>
+        <v>1.033054487912812</v>
       </c>
       <c r="C199" s="18" t="n">
-        <v>0.9576991842918305</v>
+        <v>0.9641189520244976</v>
       </c>
       <c r="D199" s="18" t="n">
-        <v>1.120400343754177</v>
+        <v>1.10691898832177</v>
       </c>
       <c r="E199" s="18" t="n">
-        <v>0.3787584860491637</v>
+        <v>0.3560447049649573</v>
       </c>
     </row>
     <row r="200">
@@ -4943,16 +4943,16 @@
         </is>
       </c>
       <c r="B200" s="18" t="n">
-        <v>1.697450756056022</v>
+        <v>1.800179828941329</v>
       </c>
       <c r="C200" s="18" t="n">
-        <v>1.109168728788741</v>
+        <v>1.247354508266999</v>
       </c>
       <c r="D200" s="18" t="n">
-        <v>2.597746397323791</v>
+        <v>2.59801635785932</v>
       </c>
       <c r="E200" s="18" t="n">
-        <v>0.01480133540652497</v>
+        <v>0.001684910862556366</v>
       </c>
     </row>
     <row r="201">
@@ -4962,16 +4962,16 @@
         </is>
       </c>
       <c r="B201" s="18" t="n">
-        <v>1.852318989337811</v>
+        <v>1.655559000418064</v>
       </c>
       <c r="C201" s="18" t="n">
-        <v>1.161468867415143</v>
+        <v>1.096379543961563</v>
       </c>
       <c r="D201" s="18" t="n">
-        <v>2.954091783706055</v>
+        <v>2.499933183687115</v>
       </c>
       <c r="E201" s="18" t="n">
-        <v>0.009639067461523189</v>
+        <v>0.01650482846874887</v>
       </c>
     </row>
     <row r="202">
@@ -4997,11 +4997,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -516.6771864168462,
-  "aic": 1061.3543728336924,
-  "pseudo_r2_mcfadden": 0.13109179576733743,
-  "lr_vs_null_chi2": 155.9017163595879,
+  "n_events": 193,
+  "llf": -658.3184800480203,
+  "aic": 1344.6369600960406,
+  "pseudo_r2_mcfadden": 0.13476965041218425,
+  "lr_vs_null_chi2": 205.08145942457486,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + lvi_pooled"
 }</t>
@@ -5019,16 +5019,16 @@
         </is>
       </c>
       <c r="B205" s="18" t="n">
-        <v>0.02021087491374202</v>
+        <v>0.03025297803333175</v>
       </c>
       <c r="C205" s="18" t="n">
-        <v>0.01007384412305393</v>
+        <v>0.01660684821435115</v>
       </c>
       <c r="D205" s="18" t="n">
-        <v>0.04054851949159344</v>
+        <v>0.05511236497569284</v>
       </c>
       <c r="E205" s="18" t="n">
-        <v>4.639862840916524e-28</v>
+        <v>2.916536869114584e-30</v>
       </c>
     </row>
     <row r="206">
@@ -5038,16 +5038,16 @@
         </is>
       </c>
       <c r="B206" s="18" t="n">
-        <v>0.4989896103159526</v>
+        <v>0.6100869727686163</v>
       </c>
       <c r="C206" s="18" t="n">
-        <v>0.2155895438926278</v>
+        <v>0.2939203669109388</v>
       </c>
       <c r="D206" s="18" t="n">
-        <v>1.154929068949993</v>
+        <v>1.266350196326331</v>
       </c>
       <c r="E206" s="18" t="n">
-        <v>0.1044692101109805</v>
+        <v>0.1847691787131558</v>
       </c>
     </row>
     <row r="207">
@@ -5057,16 +5057,16 @@
         </is>
       </c>
       <c r="B207" s="18" t="n">
-        <v>1.785223429482205</v>
+        <v>2.026213731383377</v>
       </c>
       <c r="C207" s="18" t="n">
-        <v>1.208688057254049</v>
+        <v>1.447493115419733</v>
       </c>
       <c r="D207" s="18" t="n">
-        <v>2.636761961901589</v>
+        <v>2.836311994517537</v>
       </c>
       <c r="E207" s="18" t="n">
-        <v>0.003585891927572049</v>
+        <v>3.869593260788055e-05</v>
       </c>
     </row>
     <row r="208">
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="B208" s="18" t="n">
-        <v>1.450582494586029</v>
+        <v>1.266110506409792</v>
       </c>
       <c r="C208" s="18" t="n">
-        <v>0.9837675594159128</v>
+        <v>0.9004487312533399</v>
       </c>
       <c r="D208" s="18" t="n">
-        <v>2.138909291589912</v>
+        <v>1.780263282963356</v>
       </c>
       <c r="E208" s="18" t="n">
-        <v>0.06046819558825995</v>
+        <v>0.1748079559961424</v>
       </c>
     </row>
     <row r="209">
@@ -5095,16 +5095,16 @@
         </is>
       </c>
       <c r="B209" s="18" t="n">
-        <v>0.9586351885531019</v>
+        <v>1.032497406626194</v>
       </c>
       <c r="C209" s="18" t="n">
-        <v>0.610242777146131</v>
+        <v>0.6993979467630532</v>
       </c>
       <c r="D209" s="18" t="n">
-        <v>1.505927573661685</v>
+        <v>1.52424081257845</v>
       </c>
       <c r="E209" s="18" t="n">
-        <v>0.8545453785793127</v>
+        <v>0.8721568293672328</v>
       </c>
     </row>
     <row r="210">
@@ -5114,16 +5114,16 @@
         </is>
       </c>
       <c r="B210" s="18" t="n">
-        <v>3.754784499347146</v>
+        <v>4.8616189778203</v>
       </c>
       <c r="C210" s="18" t="n">
-        <v>1.793322837679357</v>
+        <v>2.543858438456445</v>
       </c>
       <c r="D210" s="18" t="n">
-        <v>7.86161104978822</v>
+        <v>9.291137717491813</v>
       </c>
       <c r="E210" s="18" t="n">
-        <v>0.0004496119807850188</v>
+        <v>1.706762192734391e-06</v>
       </c>
     </row>
     <row r="211">
@@ -5133,16 +5133,16 @@
         </is>
       </c>
       <c r="B211" s="18" t="n">
-        <v>0.4118148680669103</v>
+        <v>0.4508168072162796</v>
       </c>
       <c r="C211" s="18" t="n">
-        <v>0.09551164632551803</v>
+        <v>0.1350495814512362</v>
       </c>
       <c r="D211" s="18" t="n">
-        <v>1.775610536363005</v>
+        <v>1.504897619709135</v>
       </c>
       <c r="E211" s="18" t="n">
-        <v>0.2340824456473869</v>
+        <v>0.1951845416816871</v>
       </c>
     </row>
     <row r="212">
@@ -5152,16 +5152,16 @@
         </is>
       </c>
       <c r="B212" s="18" t="n">
-        <v>1.000000000018248</v>
+        <v>1.00000000000287</v>
       </c>
       <c r="C212" s="18" t="n">
-        <v>0.9999999758030332</v>
+        <v>0.9999999962907928</v>
       </c>
       <c r="D212" s="18" t="n">
-        <v>1.000000024233463</v>
+        <v>1.000000003714948</v>
       </c>
       <c r="E212" s="18" t="n">
-        <v>0.9988215530075235</v>
+        <v>0.9987907893319894</v>
       </c>
     </row>
     <row r="213">
@@ -5171,16 +5171,16 @@
         </is>
       </c>
       <c r="B213" s="18" t="n">
-        <v>0.4717581387369703</v>
+        <v>0.6410302260070506</v>
       </c>
       <c r="C213" s="18" t="n">
-        <v>0.2189528681764926</v>
+        <v>0.3525111555782744</v>
       </c>
       <c r="D213" s="18" t="n">
-        <v>1.016455017548223</v>
+        <v>1.165692898372422</v>
       </c>
       <c r="E213" s="18" t="n">
-        <v>0.05507415145671912</v>
+        <v>0.1449888259107431</v>
       </c>
     </row>
     <row r="214">
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="B214" s="18" t="n">
-        <v>9.820140285363935</v>
+        <v>9.934817167934103</v>
       </c>
       <c r="C214" s="18" t="n">
-        <v>5.395221760316805</v>
+        <v>5.700357140920815</v>
       </c>
       <c r="D214" s="18" t="n">
-        <v>17.87417820960246</v>
+        <v>17.31480847958492</v>
       </c>
       <c r="E214" s="18" t="n">
-        <v>7.674314786086407e-14</v>
+        <v>5.456889374497295e-16</v>
       </c>
     </row>
     <row r="215">
@@ -5209,16 +5209,16 @@
         </is>
       </c>
       <c r="B215" s="18" t="n">
-        <v>2.552818777147546</v>
+        <v>2.514656937541992</v>
       </c>
       <c r="C215" s="18" t="n">
-        <v>0.8931136058738796</v>
+        <v>0.9573967322699311</v>
       </c>
       <c r="D215" s="18" t="n">
-        <v>7.296813827598732</v>
+        <v>6.604889384294668</v>
       </c>
       <c r="E215" s="18" t="n">
-        <v>0.08029011518904536</v>
+        <v>0.06126210402319419</v>
       </c>
     </row>
     <row r="216">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="B216" s="18" t="n">
-        <v>2.775542565041556e-09</v>
+        <v>2.079588031683173e-09</v>
       </c>
       <c r="C216" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5237,7 +5237,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E216" s="18" t="n">
-        <v>0.9988215334418707</v>
+        <v>0.9987907977574263</v>
       </c>
     </row>
     <row r="217">
@@ -5247,16 +5247,16 @@
         </is>
       </c>
       <c r="B217" s="18" t="n">
-        <v>0.9497976034238312</v>
+        <v>0.9274469143388928</v>
       </c>
       <c r="C217" s="18" t="n">
-        <v>0.8480634082206614</v>
+        <v>0.8412896803931682</v>
       </c>
       <c r="D217" s="18" t="n">
-        <v>1.063735893713891</v>
+        <v>1.02242758821759</v>
       </c>
       <c r="E217" s="18" t="n">
-        <v>0.3729002445685481</v>
+        <v>0.130000650396566</v>
       </c>
     </row>
     <row r="218">
@@ -5266,16 +5266,16 @@
         </is>
       </c>
       <c r="B218" s="18" t="n">
-        <v>1.055658601574149</v>
+        <v>1.049947220941366</v>
       </c>
       <c r="C218" s="18" t="n">
-        <v>0.9768026587729248</v>
+        <v>0.9800331789921888</v>
       </c>
       <c r="D218" s="18" t="n">
-        <v>1.140880476797057</v>
+        <v>1.124848821849209</v>
       </c>
       <c r="E218" s="18" t="n">
-        <v>0.1714903283776938</v>
+        <v>0.1656542344117218</v>
       </c>
     </row>
     <row r="219">
@@ -5285,16 +5285,16 @@
         </is>
       </c>
       <c r="B219" s="18" t="n">
-        <v>1.798068443931121</v>
+        <v>1.720509958843602</v>
       </c>
       <c r="C219" s="18" t="n">
-        <v>1.205773676339642</v>
+        <v>1.220585872810284</v>
       </c>
       <c r="D219" s="18" t="n">
-        <v>2.681307605649036</v>
+        <v>2.425191528445709</v>
       </c>
       <c r="E219" s="18" t="n">
-        <v>0.004004853466394623</v>
+        <v>0.001948210925390039</v>
       </c>
     </row>
     <row r="220">
@@ -5320,11 +5320,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -514.0770137496083,
-  "aic": 1064.1540274992167,
-  "pseudo_r2_mcfadden": 0.13546456743672897,
-  "lr_vs_null_chi2": 161.10206169406365,
+  "n_events": 193,
+  "llf": -655.2695391328182,
+  "aic": 1346.5390782656364,
+  "pseudo_r2_mcfadden": 0.13877688443930813,
+  "lr_vs_null_chi2": 211.17934125497914,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + vasc_ord",
   "ordering_note": "vasc_ord: missing=0 indeterminate=1 focal=2 present_ungraded=3 extensive=4; single linear coefficient"
@@ -5343,16 +5343,16 @@
         </is>
       </c>
       <c r="B223" s="18" t="n">
-        <v>0.02021578303280577</v>
+        <v>0.0310329232926618</v>
       </c>
       <c r="C223" s="18" t="n">
-        <v>0.01004315881694209</v>
+        <v>0.01700584905003968</v>
       </c>
       <c r="D223" s="18" t="n">
-        <v>0.04069216578951911</v>
+        <v>0.05663006447102293</v>
       </c>
       <c r="E223" s="18" t="n">
-        <v>8.275750841787124e-28</v>
+        <v>1.095477234483102e-29</v>
       </c>
     </row>
     <row r="224">
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="B224" s="18" t="n">
-        <v>0.5076149945951489</v>
+        <v>0.6516466888724859</v>
       </c>
       <c r="C224" s="18" t="n">
-        <v>0.2165706734857281</v>
+        <v>0.3118733891252518</v>
       </c>
       <c r="D224" s="18" t="n">
-        <v>1.18978705006804</v>
+        <v>1.361589099696906</v>
       </c>
       <c r="E224" s="18" t="n">
-        <v>0.1187320275647996</v>
+        <v>0.2546890503963902</v>
       </c>
     </row>
     <row r="225">
@@ -5381,16 +5381,16 @@
         </is>
       </c>
       <c r="B225" s="18" t="n">
-        <v>1.779513087702089</v>
+        <v>2.053998392318718</v>
       </c>
       <c r="C225" s="18" t="n">
-        <v>1.200855012945103</v>
+        <v>1.463498219969417</v>
       </c>
       <c r="D225" s="18" t="n">
-        <v>2.637010126257256</v>
+        <v>2.882756766001424</v>
       </c>
       <c r="E225" s="18" t="n">
-        <v>0.004077829649028575</v>
+        <v>3.154192884648393e-05</v>
       </c>
     </row>
     <row r="226">
@@ -5400,16 +5400,16 @@
         </is>
       </c>
       <c r="B226" s="18" t="n">
-        <v>1.408371982916116</v>
+        <v>1.237984291844038</v>
       </c>
       <c r="C226" s="18" t="n">
-        <v>0.953130914675545</v>
+        <v>0.8786333237186766</v>
       </c>
       <c r="D226" s="18" t="n">
-        <v>2.081048481087491</v>
+        <v>1.744305690986174</v>
       </c>
       <c r="E226" s="18" t="n">
-        <v>0.08561568676498361</v>
+        <v>0.2223345115583454</v>
       </c>
     </row>
     <row r="227">
@@ -5419,16 +5419,16 @@
         </is>
       </c>
       <c r="B227" s="18" t="n">
-        <v>0.9556421948568171</v>
+        <v>1.048277827184413</v>
       </c>
       <c r="C227" s="18" t="n">
-        <v>0.6069274813015293</v>
+        <v>0.7090494987740202</v>
       </c>
       <c r="D227" s="18" t="n">
-        <v>1.504713549355726</v>
+        <v>1.549802101075453</v>
       </c>
       <c r="E227" s="18" t="n">
-        <v>0.8446998873950671</v>
+        <v>0.8131573774532923</v>
       </c>
     </row>
     <row r="228">
@@ -5438,16 +5438,16 @@
         </is>
       </c>
       <c r="B228" s="18" t="n">
-        <v>4.066874901013498</v>
+        <v>5.607479803852337</v>
       </c>
       <c r="C228" s="18" t="n">
-        <v>1.917534829722514</v>
+        <v>2.897030599142081</v>
       </c>
       <c r="D228" s="18" t="n">
-        <v>8.625382550619419</v>
+        <v>10.8538134736732</v>
       </c>
       <c r="E228" s="18" t="n">
-        <v>0.0002550181368398688</v>
+        <v>3.108510895633969e-07</v>
       </c>
     </row>
     <row r="229">
@@ -5457,16 +5457,16 @@
         </is>
       </c>
       <c r="B229" s="18" t="n">
-        <v>0.4003701459361586</v>
+        <v>0.4408698434693836</v>
       </c>
       <c r="C229" s="18" t="n">
-        <v>0.09287256622299864</v>
+        <v>0.1321339597547841</v>
       </c>
       <c r="D229" s="18" t="n">
-        <v>1.725980666584032</v>
+        <v>1.470978537549515</v>
       </c>
       <c r="E229" s="18" t="n">
-        <v>0.2195039942711231</v>
+        <v>0.1827919881318931</v>
       </c>
     </row>
     <row r="230">
@@ -5476,16 +5476,16 @@
         </is>
       </c>
       <c r="B230" s="18" t="n">
-        <v>0.9999999999846505</v>
+        <v>0.9999999999845147</v>
       </c>
       <c r="C230" s="18" t="n">
-        <v>0.9999999731459508</v>
+        <v>0.9999999673726164</v>
       </c>
       <c r="D230" s="18" t="n">
-        <v>1.000000026823351</v>
+        <v>1.000000032596414</v>
       </c>
       <c r="E230" s="18" t="n">
-        <v>0.9991056245847534</v>
+        <v>0.9992574412369173</v>
       </c>
     </row>
     <row r="231">
@@ -5495,16 +5495,16 @@
         </is>
       </c>
       <c r="B231" s="18" t="n">
-        <v>0.4380380453631006</v>
+        <v>0.5601886579708687</v>
       </c>
       <c r="C231" s="18" t="n">
-        <v>0.1979211564198055</v>
+        <v>0.3000321848980259</v>
       </c>
       <c r="D231" s="18" t="n">
-        <v>0.9694634603818689</v>
+        <v>1.045925565038499</v>
       </c>
       <c r="E231" s="18" t="n">
-        <v>0.04170265716477226</v>
+        <v>0.06890924580773959</v>
       </c>
     </row>
     <row r="232">
@@ -5514,16 +5514,16 @@
         </is>
       </c>
       <c r="B232" s="18" t="n">
-        <v>9.240682230034183</v>
+        <v>8.538198152334786</v>
       </c>
       <c r="C232" s="18" t="n">
-        <v>4.816939662489342</v>
+        <v>4.734088457488871</v>
       </c>
       <c r="D232" s="18" t="n">
-        <v>17.7270661580886</v>
+        <v>15.39912664141522</v>
       </c>
       <c r="E232" s="18" t="n">
-        <v>2.235779085816864e-11</v>
+        <v>1.025604706093417e-12</v>
       </c>
     </row>
     <row r="233">
@@ -5533,16 +5533,16 @@
         </is>
       </c>
       <c r="B233" s="18" t="n">
-        <v>1.999491236306955</v>
+        <v>1.889803257984597</v>
       </c>
       <c r="C233" s="18" t="n">
-        <v>0.6687322678615855</v>
+        <v>0.6939863194425195</v>
       </c>
       <c r="D233" s="18" t="n">
-        <v>5.978424245703988</v>
+        <v>5.146148063492195</v>
       </c>
       <c r="E233" s="18" t="n">
-        <v>0.2150033636246419</v>
+        <v>0.2130390031427415</v>
       </c>
     </row>
     <row r="234">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="B234" s="18" t="n">
-        <v>8.759297856899323e-10</v>
+        <v>5.571351989603471e-10</v>
       </c>
       <c r="C234" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5561,7 +5561,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E234" s="18" t="n">
-        <v>0.9992348976467678</v>
+        <v>0.9992027278318458</v>
       </c>
     </row>
     <row r="235">
@@ -5571,16 +5571,16 @@
         </is>
       </c>
       <c r="B235" s="18" t="n">
-        <v>0.8685151775231311</v>
+        <v>0.7108018192563973</v>
       </c>
       <c r="C235" s="18" t="n">
-        <v>0.4892619510418473</v>
+        <v>0.4319874013665285</v>
       </c>
       <c r="D235" s="18" t="n">
-        <v>1.541747957268637</v>
+        <v>1.169569354707925</v>
       </c>
       <c r="E235" s="18" t="n">
-        <v>0.6301983911821567</v>
+        <v>0.1791119409393991</v>
       </c>
     </row>
     <row r="236">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="B236" s="18" t="n">
-        <v>2.389099544200493</v>
+        <v>1.689910845125026</v>
       </c>
       <c r="C236" s="18" t="n">
-        <v>0.9315880517442137</v>
+        <v>0.7057421444646111</v>
       </c>
       <c r="D236" s="18" t="n">
-        <v>6.126953454815452</v>
+        <v>4.046518529281882</v>
       </c>
       <c r="E236" s="18" t="n">
-        <v>0.06991113841276111</v>
+        <v>0.2389161269620909</v>
       </c>
     </row>
     <row r="237">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="B237" s="18" t="n">
-        <v>1.231945232294593e-09</v>
+        <v>8.179354549635147e-10</v>
       </c>
       <c r="C237" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5618,7 +5618,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E237" s="18" t="n">
-        <v>0.9994855173405885</v>
+        <v>0.9994744478317581</v>
       </c>
     </row>
     <row r="238">
@@ -5628,16 +5628,16 @@
         </is>
       </c>
       <c r="B238" s="18" t="n">
-        <v>0.8528192223852246</v>
+        <v>0.6376847424345509</v>
       </c>
       <c r="C238" s="18" t="n">
-        <v>0.3220682522275967</v>
+        <v>0.2622746690768858</v>
       </c>
       <c r="D238" s="18" t="n">
-        <v>2.258218936636375</v>
+        <v>1.550442641544664</v>
       </c>
       <c r="E238" s="18" t="n">
-        <v>0.7486332890558433</v>
+        <v>0.3209418693855892</v>
       </c>
     </row>
     <row r="239">
@@ -5647,16 +5647,16 @@
         </is>
       </c>
       <c r="B239" s="18" t="n">
-        <v>0.9595608500498828</v>
+        <v>0.9340056427801126</v>
       </c>
       <c r="C239" s="18" t="n">
-        <v>0.8563476739647635</v>
+        <v>0.8469066842184035</v>
       </c>
       <c r="D239" s="18" t="n">
-        <v>1.075214019891576</v>
+        <v>1.030062174500588</v>
       </c>
       <c r="E239" s="18" t="n">
-        <v>0.4771107034485673</v>
+        <v>0.1716447937098534</v>
       </c>
     </row>
     <row r="240">
@@ -5666,16 +5666,16 @@
         </is>
       </c>
       <c r="B240" s="18" t="n">
-        <v>1.055286575123502</v>
+        <v>1.048812125162017</v>
       </c>
       <c r="C240" s="18" t="n">
-        <v>0.9765435966192685</v>
+        <v>0.9790429640640671</v>
       </c>
       <c r="D240" s="18" t="n">
-        <v>1.140378944156929</v>
+        <v>1.123553219074952</v>
       </c>
       <c r="E240" s="18" t="n">
-        <v>0.1738108311663651</v>
+        <v>0.1748030732518505</v>
       </c>
     </row>
     <row r="241">
@@ -5685,16 +5685,16 @@
         </is>
       </c>
       <c r="B241" s="18" t="n">
-        <v>1.231242209331056</v>
+        <v>1.263153318005346</v>
       </c>
       <c r="C241" s="18" t="n">
-        <v>1.045468583210665</v>
+        <v>1.097227866956414</v>
       </c>
       <c r="D241" s="18" t="n">
-        <v>1.450026717572774</v>
+        <v>1.454170416956149</v>
       </c>
       <c r="E241" s="18" t="n">
-        <v>0.01267394131018268</v>
+        <v>0.001148573816578156</v>
       </c>
     </row>
     <row r="242">
@@ -5720,11 +5720,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -513.1710224690692,
-  "aic": 1068.3420449381383,
-  "pseudo_r2_mcfadden": 0.13698819433050213,
-  "lr_vs_null_chi2": 162.91404425514202,
+  "n_events": 193,
+  "llf": -654.0326151062296,
+  "aic": 1350.0652302124593,
+  "pseudo_r2_mcfadden": 0.14040257814284918,
+  "lr_vs_null_chi2": 213.65318930815624,
   "lr_vs_null_pvalue": 0.0,
   "n": 3756,
   "n_removed": 0
@@ -5743,16 +5743,16 @@
         </is>
       </c>
       <c r="B245" s="18" t="n">
-        <v>0.01988594511462632</v>
+        <v>0.03052220194197974</v>
       </c>
       <c r="C245" s="18" t="n">
-        <v>0.009863719699586729</v>
+        <v>0.01669454927553033</v>
       </c>
       <c r="D245" s="18" t="n">
-        <v>0.04009144877854741</v>
+        <v>0.05580293280229319</v>
       </c>
       <c r="E245" s="18" t="n">
-        <v>6.536582072092165e-28</v>
+        <v>8.856417170795826e-30</v>
       </c>
     </row>
     <row r="246">
@@ -5762,16 +5762,16 @@
         </is>
       </c>
       <c r="B246" s="18" t="n">
-        <v>0.5206463545221203</v>
+        <v>0.6669255032178935</v>
       </c>
       <c r="C246" s="18" t="n">
-        <v>0.2208502401334555</v>
+        <v>0.3177659954934816</v>
       </c>
       <c r="D246" s="18" t="n">
-        <v>1.227404716940174</v>
+        <v>1.399739535225268</v>
       </c>
       <c r="E246" s="18" t="n">
-        <v>0.1357850626236052</v>
+        <v>0.2842080600304258</v>
       </c>
     </row>
     <row r="247">
@@ -5781,16 +5781,16 @@
         </is>
       </c>
       <c r="B247" s="18" t="n">
-        <v>1.803142473049089</v>
+        <v>2.076021874744788</v>
       </c>
       <c r="C247" s="18" t="n">
-        <v>1.216513912993913</v>
+        <v>1.47858360953565</v>
       </c>
       <c r="D247" s="18" t="n">
-        <v>2.672655646092765</v>
+        <v>2.914861761366597</v>
       </c>
       <c r="E247" s="18" t="n">
-        <v>0.003324166076161661</v>
+        <v>2.458209087953318e-05</v>
       </c>
     </row>
     <row r="248">
@@ -5800,16 +5800,16 @@
         </is>
       </c>
       <c r="B248" s="18" t="n">
-        <v>1.415612656293561</v>
+        <v>1.243365865671108</v>
       </c>
       <c r="C248" s="18" t="n">
-        <v>0.9581423942358214</v>
+        <v>0.8826065421803896</v>
       </c>
       <c r="D248" s="18" t="n">
-        <v>2.091504566246435</v>
+        <v>1.751583069050145</v>
       </c>
       <c r="E248" s="18" t="n">
-        <v>0.08094065547071054</v>
+        <v>0.2128480394355131</v>
       </c>
     </row>
     <row r="249">
@@ -5819,16 +5819,16 @@
         </is>
       </c>
       <c r="B249" s="18" t="n">
-        <v>0.9499944309815264</v>
+        <v>1.041542433253086</v>
       </c>
       <c r="C249" s="18" t="n">
-        <v>0.6030069709102068</v>
+        <v>0.7041041255179393</v>
       </c>
       <c r="D249" s="18" t="n">
-        <v>1.496648401151407</v>
+        <v>1.540696327363191</v>
       </c>
       <c r="E249" s="18" t="n">
-        <v>0.8249314914809625</v>
+        <v>0.8385463175879454</v>
       </c>
     </row>
     <row r="250">
@@ -5838,16 +5838,16 @@
         </is>
       </c>
       <c r="B250" s="18" t="n">
-        <v>4.064670487927986</v>
+        <v>5.589610780216073</v>
       </c>
       <c r="C250" s="18" t="n">
-        <v>1.916630062128165</v>
+        <v>2.888512518705153</v>
       </c>
       <c r="D250" s="18" t="n">
-        <v>8.620101761884987</v>
+        <v>10.81655297388619</v>
       </c>
       <c r="E250" s="18" t="n">
-        <v>0.0002560862557023006</v>
+        <v>3.235499429458743e-07</v>
       </c>
     </row>
     <row r="251">
@@ -5857,16 +5857,16 @@
         </is>
       </c>
       <c r="B251" s="18" t="n">
-        <v>0.4032548237157987</v>
+        <v>0.4437282968749986</v>
       </c>
       <c r="C251" s="18" t="n">
-        <v>0.09349528866863414</v>
+        <v>0.1329051128210752</v>
       </c>
       <c r="D251" s="18" t="n">
-        <v>1.739279648907206</v>
+        <v>1.481468976386622</v>
       </c>
       <c r="E251" s="18" t="n">
-        <v>0.223298329848848</v>
+        <v>0.1865048194220119</v>
       </c>
     </row>
     <row r="252">
@@ -5876,16 +5876,16 @@
         </is>
       </c>
       <c r="B252" s="18" t="n">
-        <v>1.000000000008999</v>
+        <v>1.000000000181017</v>
       </c>
       <c r="C252" s="18" t="n">
-        <v>0.9999999520573437</v>
+        <v>0.999999567207104</v>
       </c>
       <c r="D252" s="18" t="n">
-        <v>1.000000047960657</v>
+        <v>1.000000433155118</v>
       </c>
       <c r="E252" s="18" t="n">
-        <v>0.9997065048579439</v>
+        <v>0.9993461969791613</v>
       </c>
     </row>
     <row r="253">
@@ -5895,16 +5895,16 @@
         </is>
       </c>
       <c r="B253" s="18" t="n">
-        <v>0.4025658212119982</v>
+        <v>0.5113539780108236</v>
       </c>
       <c r="C253" s="18" t="n">
-        <v>0.1790133646743275</v>
+        <v>0.2699812706456613</v>
       </c>
       <c r="D253" s="18" t="n">
-        <v>0.9052912932110907</v>
+        <v>0.9685223356500121</v>
       </c>
       <c r="E253" s="18" t="n">
-        <v>0.02776413268177263</v>
+        <v>0.03957954869899567</v>
       </c>
     </row>
     <row r="254">
@@ -5914,16 +5914,16 @@
         </is>
       </c>
       <c r="B254" s="18" t="n">
-        <v>9.263262405819614</v>
+        <v>8.57905103879509</v>
       </c>
       <c r="C254" s="18" t="n">
-        <v>4.810900420995365</v>
+        <v>4.741888142926279</v>
       </c>
       <c r="D254" s="18" t="n">
-        <v>17.83616846954348</v>
+        <v>15.52126800714273</v>
       </c>
       <c r="E254" s="18" t="n">
-        <v>2.75126119173499e-11</v>
+        <v>1.201350488743744e-12</v>
       </c>
     </row>
     <row r="255">
@@ -5933,16 +5933,16 @@
         </is>
       </c>
       <c r="B255" s="18" t="n">
-        <v>1.865793604816147</v>
+        <v>1.715255922337146</v>
       </c>
       <c r="C255" s="18" t="n">
-        <v>0.5997323531271797</v>
+        <v>0.6113741691283806</v>
       </c>
       <c r="D255" s="18" t="n">
-        <v>5.804565582665188</v>
+        <v>4.812278679204144</v>
       </c>
       <c r="E255" s="18" t="n">
-        <v>0.2814594132836409</v>
+        <v>0.3053064560865795</v>
       </c>
     </row>
     <row r="256">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B256" s="18" t="n">
-        <v>8.234027685038964e-10</v>
+        <v>5.16727771697659e-10</v>
       </c>
       <c r="C256" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5961,7 +5961,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E256" s="18" t="n">
-        <v>0.9992368963210904</v>
+        <v>0.9992030750468766</v>
       </c>
     </row>
     <row r="257">
@@ -5971,16 +5971,16 @@
         </is>
       </c>
       <c r="B257" s="18" t="n">
-        <v>0.8900578758120717</v>
+        <v>0.7384752852970617</v>
       </c>
       <c r="C257" s="18" t="n">
-        <v>0.4972517251809985</v>
+        <v>0.4452543797335514</v>
       </c>
       <c r="D257" s="18" t="n">
-        <v>1.593162943792175</v>
+        <v>1.224795918506005</v>
       </c>
       <c r="E257" s="18" t="n">
-        <v>0.6949870010775352</v>
+        <v>0.2402193969427563</v>
       </c>
     </row>
     <row r="258">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="B258" s="18" t="n">
-        <v>2.471075365116653</v>
+        <v>1.757893717879382</v>
       </c>
       <c r="C258" s="18" t="n">
-        <v>0.9552563654630083</v>
+        <v>0.7279395352184567</v>
       </c>
       <c r="D258" s="18" t="n">
-        <v>6.392224831840555</v>
+        <v>4.245119510417058</v>
       </c>
       <c r="E258" s="18" t="n">
-        <v>0.06210208227991102</v>
+        <v>0.2098197201769865</v>
       </c>
     </row>
     <row r="259">
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="B259" s="18" t="n">
-        <v>1.149473450125798e-09</v>
+        <v>7.668397975541751e-10</v>
       </c>
       <c r="C259" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -6018,7 +6018,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E259" s="18" t="n">
-        <v>0.9994853005338252</v>
+        <v>0.999474226098751</v>
       </c>
     </row>
     <row r="260">
@@ -6028,16 +6028,16 @@
         </is>
       </c>
       <c r="B260" s="18" t="n">
-        <v>0.8994143043047927</v>
+        <v>0.6744064518387922</v>
       </c>
       <c r="C260" s="18" t="n">
-        <v>0.3327371250746836</v>
+        <v>0.2721746782092361</v>
       </c>
       <c r="D260" s="18" t="n">
-        <v>2.431186753226002</v>
+        <v>1.671074125169499</v>
       </c>
       <c r="E260" s="18" t="n">
-        <v>0.8344867055868811</v>
+        <v>0.3948394123437013</v>
       </c>
     </row>
     <row r="261">
@@ -6047,16 +6047,16 @@
         </is>
       </c>
       <c r="B261" s="18" t="n">
-        <v>1.730704538765684</v>
+        <v>1.823942570144014</v>
       </c>
       <c r="C261" s="18" t="n">
-        <v>0.9825439306168026</v>
+        <v>1.112341481819554</v>
       </c>
       <c r="D261" s="18" t="n">
-        <v>3.048553970125065</v>
+        <v>2.990778060116638</v>
       </c>
       <c r="E261" s="18" t="n">
-        <v>0.05756478400617536</v>
+        <v>0.01722257193913048</v>
       </c>
     </row>
     <row r="262">
@@ -6066,16 +6066,16 @@
         </is>
       </c>
       <c r="B262" s="18" t="n">
-        <v>2.295459213080084</v>
+        <v>2.39090079920365</v>
       </c>
       <c r="C262" s="18" t="n">
-        <v>1.149102116321473</v>
+        <v>1.317147438489974</v>
       </c>
       <c r="D262" s="18" t="n">
-        <v>4.585434944443309</v>
+        <v>4.339989939308657</v>
       </c>
       <c r="E262" s="18" t="n">
-        <v>0.01859114256048034</v>
+        <v>0.004162942684026138</v>
       </c>
     </row>
     <row r="263">
@@ -6085,16 +6085,16 @@
         </is>
       </c>
       <c r="B263" s="18" t="n">
-        <v>2.426078408991356</v>
+        <v>2.788892715938317</v>
       </c>
       <c r="C263" s="18" t="n">
-        <v>1.060571024699771</v>
+        <v>1.376348027128713</v>
       </c>
       <c r="D263" s="18" t="n">
-        <v>5.549705120635568</v>
+        <v>5.651130693477159</v>
       </c>
       <c r="E263" s="18" t="n">
-        <v>0.03579426143389187</v>
+        <v>0.004420333345359666</v>
       </c>
     </row>
     <row r="264">
@@ -6104,16 +6104,16 @@
         </is>
       </c>
       <c r="B264" s="18" t="n">
-        <v>1.12362744109839</v>
+        <v>1.304747414145783</v>
       </c>
       <c r="C264" s="18" t="n">
-        <v>0.2422511546911795</v>
+        <v>0.3606986337620886</v>
       </c>
       <c r="D264" s="18" t="n">
-        <v>5.211692914317758</v>
+        <v>4.719634773673588</v>
       </c>
       <c r="E264" s="18" t="n">
-        <v>0.8816355286876525</v>
+        <v>0.6851050284367951</v>
       </c>
     </row>
     <row r="265">
@@ -6123,16 +6123,16 @@
         </is>
       </c>
       <c r="B265" s="18" t="n">
-        <v>0.9590876471583448</v>
+        <v>0.9342008179855855</v>
       </c>
       <c r="C265" s="18" t="n">
-        <v>0.855857777736727</v>
+        <v>0.84698924688341</v>
       </c>
       <c r="D265" s="18" t="n">
-        <v>1.074768657666727</v>
+        <v>1.030392264761622</v>
       </c>
       <c r="E265" s="18" t="n">
-        <v>0.472169331137781</v>
+        <v>0.1734490646119403</v>
       </c>
     </row>
     <row r="266">
@@ -6142,16 +6142,16 @@
         </is>
       </c>
       <c r="B266" s="18" t="n">
-        <v>1.05396825090431</v>
+        <v>1.047101558155796</v>
       </c>
       <c r="C266" s="18" t="n">
-        <v>0.9751068751851638</v>
+        <v>0.9772115482993279</v>
       </c>
       <c r="D266" s="18" t="n">
-        <v>1.139207508616274</v>
+        <v>1.121990090068454</v>
       </c>
       <c r="E266" s="18" t="n">
-        <v>0.1852806869483926</v>
+        <v>0.1915859030131092</v>
       </c>
     </row>
     <row r="267">
@@ -6177,14 +6177,14 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": NaN,
-  "aic": NaN,
-  "pseudo_r2_mcfadden": NaN,
-  "lr_vs_null_chi2": NaN,
-  "lr_vs_null_pvalue": NaN,
+  "n_events": 193,
+  "llf": -636.3735895956061,
+  "aic": 1330.7471791912121,
+  "pseudo_r2_mcfadden": 0.16361189897920558,
+  "lr_vs_null_chi2": 248.97124032940337,
+  "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing')) + C(multifocal_flag_path_fac, Treatment(reference='missing')) + C(bilateral_disease_fac, Treatment(reference='missing')) + C(margin_involved_fac, Treatment(reference='missing')) + C(aggressive_variant_fac, Treatment(reference='missing')) + C(braf_positive_fac, Treatment(reference='missing')) + C(surg_tt_fac, Treatment(reference='missing'))",
-  "change_note": "coefficient strengthened vs primary"
+  "change_note": "coefficient attenuated vs primary"
 }</t>
         </is>
       </c>
@@ -6200,16 +6200,16 @@
         </is>
       </c>
       <c r="B270" s="18" t="n">
-        <v/>
+        <v>0.2569000145316158</v>
       </c>
       <c r="C270" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>0.1527709823249613</v>
       </c>
       <c r="D270" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>0.4320036204647814</v>
       </c>
       <c r="E270" s="18" t="n">
-        <v>0</v>
+        <v>2.974723093457755e-07</v>
       </c>
     </row>
     <row r="271">
@@ -6219,16 +6219,16 @@
         </is>
       </c>
       <c r="B271" s="18" t="n">
-        <v>9.566859474348441</v>
+        <v>1.507918166655319</v>
       </c>
       <c r="C271" s="18" t="n">
-        <v>2.19544726900292</v>
+        <v>0.5259457685579816</v>
       </c>
       <c r="D271" s="18" t="n">
-        <v>41.6884529608845</v>
+        <v>4.323292121093409</v>
       </c>
       <c r="E271" s="18" t="n">
-        <v>0.002637599206829688</v>
+        <v>0.4446949206287111</v>
       </c>
     </row>
     <row r="272">
@@ -6238,16 +6238,16 @@
         </is>
       </c>
       <c r="B272" s="18" t="n">
-        <v>2.29546265773934</v>
+        <v>1.821599442885074</v>
       </c>
       <c r="C272" s="18" t="n">
-        <v>1.55586487136481</v>
+        <v>1.284888858634383</v>
       </c>
       <c r="D272" s="18" t="n">
-        <v>3.386636532550312</v>
+        <v>2.582499262890268</v>
       </c>
       <c r="E272" s="18" t="n">
-        <v>2.818176436054717e-05</v>
+        <v>0.000758385662750599</v>
       </c>
     </row>
     <row r="273">
@@ -6257,16 +6257,16 @@
         </is>
       </c>
       <c r="B273" s="18" t="n">
-        <v>0.6912449663046616</v>
+        <v>1.268180975101935</v>
       </c>
       <c r="C273" s="18" t="n">
-        <v>0.4825044372105628</v>
+        <v>0.8969462903129783</v>
       </c>
       <c r="D273" s="18" t="n">
-        <v>0.9902905892511291</v>
+        <v>1.793064983912585</v>
       </c>
       <c r="E273" s="18" t="n">
-        <v>0.04409812311690399</v>
+        <v>0.1787893148851736</v>
       </c>
     </row>
     <row r="274">
@@ -6276,16 +6276,16 @@
         </is>
       </c>
       <c r="B274" s="18" t="n">
-        <v>1.497968965085737</v>
+        <v>1.008000416455425</v>
       </c>
       <c r="C274" s="18" t="n">
-        <v>0.9852593910305401</v>
+        <v>0.679174845213538</v>
       </c>
       <c r="D274" s="18" t="n">
-        <v>2.277482499317259</v>
+        <v>1.496028374335408</v>
       </c>
       <c r="E274" s="18" t="n">
-        <v>0.05869222054010568</v>
+        <v>0.9684478417405459</v>
       </c>
     </row>
     <row r="275">
@@ -6295,16 +6295,16 @@
         </is>
       </c>
       <c r="B275" s="18" t="n">
-        <v>5.306026032138532</v>
+        <v>4.692219568614115</v>
       </c>
       <c r="C275" s="18" t="n">
-        <v>2.533842630983727</v>
+        <v>2.405243540331351</v>
       </c>
       <c r="D275" s="18" t="n">
-        <v>11.11115264597212</v>
+        <v>9.153719409657844</v>
       </c>
       <c r="E275" s="18" t="n">
-        <v>9.624444710793545e-06</v>
+        <v>5.785514248232934e-06</v>
       </c>
     </row>
     <row r="276">
@@ -6314,16 +6314,16 @@
         </is>
       </c>
       <c r="B276" s="18" t="n">
-        <v>2.256366810322605</v>
+        <v>0.5465064056350517</v>
       </c>
       <c r="C276" s="18" t="n">
-        <v>0.4986396611817037</v>
+        <v>0.1610008209546971</v>
       </c>
       <c r="D276" s="18" t="n">
-        <v>10.21016092193714</v>
+        <v>1.855079058784328</v>
       </c>
       <c r="E276" s="18" t="n">
-        <v>0.2907365587578151</v>
+        <v>0.3325541551006228</v>
       </c>
     </row>
     <row r="277">
@@ -6333,16 +6333,16 @@
         </is>
       </c>
       <c r="B277" s="18" t="n">
-        <v/>
+        <v>0.9999999999155477</v>
       </c>
       <c r="C277" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>0.9999997104503192</v>
       </c>
       <c r="D277" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>1.00000028938086</v>
       </c>
       <c r="E277" s="18" t="n">
-        <v>0</v>
+        <v>0.9995437496511856</v>
       </c>
     </row>
     <row r="278">
@@ -6352,16 +6352,16 @@
         </is>
       </c>
       <c r="B278" s="18" t="n">
-        <v>0.2252896970771125</v>
+        <v>0.6241988240191877</v>
       </c>
       <c r="C278" s="18" t="n">
-        <v>0.1189964905513792</v>
+        <v>0.3227216797610402</v>
       </c>
       <c r="D278" s="18" t="n">
-        <v>0.4265289452984532</v>
+        <v>1.207307089487867</v>
       </c>
       <c r="E278" s="18" t="n">
-        <v>4.731047691394981e-06</v>
+        <v>0.1614433749243808</v>
       </c>
     </row>
     <row r="279">
@@ -6371,16 +6371,16 @@
         </is>
       </c>
       <c r="B279" s="18" t="n">
-        <v>0.7539075925248735</v>
+        <v>9.017693660266431</v>
       </c>
       <c r="C279" s="18" t="n">
-        <v>0.3839612134344813</v>
+        <v>4.862700985386842</v>
       </c>
       <c r="D279" s="18" t="n">
-        <v>1.480297066942252</v>
+        <v>16.7229692294025</v>
       </c>
       <c r="E279" s="18" t="n">
-        <v>0.4118915915140042</v>
+        <v>2.968161437026701e-12</v>
       </c>
     </row>
     <row r="280">
@@ -6390,16 +6390,16 @@
         </is>
       </c>
       <c r="B280" s="18" t="n">
-        <v>0.264603078845361</v>
+        <v>2.188323971289851</v>
       </c>
       <c r="C280" s="18" t="n">
-        <v>0.07115848445717535</v>
+        <v>0.7602702563666991</v>
       </c>
       <c r="D280" s="18" t="n">
-        <v>0.9839274946416358</v>
+        <v>6.298762529797082</v>
       </c>
       <c r="E280" s="18" t="n">
-        <v>0.04723967879253103</v>
+        <v>0.1465440080869578</v>
       </c>
     </row>
     <row r="281">
@@ -6409,16 +6409,16 @@
         </is>
       </c>
       <c r="B281" s="18" t="n">
-        <v>0</v>
+        <v>5.821868636193188e-10</v>
       </c>
       <c r="C281" s="18" t="n">
         <v>1.388794386496402e-11</v>
       </c>
       <c r="D281" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E281" s="18" t="n">
-        <v>0</v>
+        <v>0.9992088105883246</v>
       </c>
     </row>
     <row r="282">
@@ -6428,16 +6428,16 @@
         </is>
       </c>
       <c r="B282" s="18" t="n">
-        <v>0.1303617132381301</v>
+        <v>0.6497784646596605</v>
       </c>
       <c r="C282" s="18" t="n">
-        <v>0.07475424793141351</v>
+        <v>0.3880027269369928</v>
       </c>
       <c r="D282" s="18" t="n">
-        <v>0.2273339207956784</v>
+        <v>1.088167746831398</v>
       </c>
       <c r="E282" s="18" t="n">
-        <v>6.928584456567677e-13</v>
+        <v>0.1012587521982251</v>
       </c>
     </row>
     <row r="283">
@@ -6447,16 +6447,16 @@
         </is>
       </c>
       <c r="B283" s="18" t="n">
-        <v>0.4952774713184976</v>
+        <v>1.482568729461025</v>
       </c>
       <c r="C283" s="18" t="n">
-        <v>0.1976737690025077</v>
+        <v>0.6042450457358023</v>
       </c>
       <c r="D283" s="18" t="n">
-        <v>1.240932344404954</v>
+        <v>3.637613668638545</v>
       </c>
       <c r="E283" s="18" t="n">
-        <v>0.1337855914636944</v>
+        <v>0.3898549103105284</v>
       </c>
     </row>
     <row r="284">
@@ -6466,16 +6466,16 @@
         </is>
       </c>
       <c r="B284" s="18" t="n">
-        <v>0</v>
+        <v>4.792562307739752e-10</v>
       </c>
       <c r="C284" s="18" t="n">
         <v>1.388794386496402e-11</v>
       </c>
       <c r="D284" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E284" s="18" t="n">
-        <v>0</v>
+        <v>0.9994648160034991</v>
       </c>
     </row>
     <row r="285">
@@ -6485,16 +6485,16 @@
         </is>
       </c>
       <c r="B285" s="18" t="n">
-        <v>0.08341118776417443</v>
+        <v>0.680769187345277</v>
       </c>
       <c r="C285" s="18" t="n">
-        <v>0.04059879472489226</v>
+        <v>0.2729344970609212</v>
       </c>
       <c r="D285" s="18" t="n">
-        <v>0.1713702658262554</v>
+        <v>1.698014327354537</v>
       </c>
       <c r="E285" s="18" t="n">
-        <v>1.36675980089849e-11</v>
+        <v>0.4096040552189486</v>
       </c>
     </row>
     <row r="286">
@@ -6504,16 +6504,16 @@
         </is>
       </c>
       <c r="B286" s="18" t="n">
-        <v>3.551298771423097</v>
+        <v>1.677730182811396</v>
       </c>
       <c r="C286" s="18" t="n">
-        <v>2.131151312621032</v>
+        <v>1.018781501161789</v>
       </c>
       <c r="D286" s="18" t="n">
-        <v>5.917797994549931</v>
+        <v>2.762887393524979</v>
       </c>
       <c r="E286" s="18" t="n">
-        <v>1.149435934562752e-06</v>
+        <v>0.04204507706803557</v>
       </c>
     </row>
     <row r="287">
@@ -6523,16 +6523,16 @@
         </is>
       </c>
       <c r="B287" s="18" t="n">
-        <v>4.390515583668303</v>
+        <v>2.088299313337765</v>
       </c>
       <c r="C287" s="18" t="n">
-        <v>2.496536986363427</v>
+        <v>1.139555207597329</v>
       </c>
       <c r="D287" s="18" t="n">
-        <v>7.721346487445179</v>
+        <v>3.826926499929586</v>
       </c>
       <c r="E287" s="18" t="n">
-        <v>2.801881081155815e-07</v>
+        <v>0.01718700007875044</v>
       </c>
     </row>
     <row r="288">
@@ -6542,16 +6542,16 @@
         </is>
       </c>
       <c r="B288" s="18" t="n">
-        <v>22.3188938421767</v>
+        <v>2.329701490577631</v>
       </c>
       <c r="C288" s="18" t="n">
-        <v>6.549408078278536</v>
+        <v>1.113565733332385</v>
       </c>
       <c r="D288" s="18" t="n">
-        <v>76.05771642027284</v>
+        <v>4.873990706374939</v>
       </c>
       <c r="E288" s="18" t="n">
-        <v>6.894530850778762e-07</v>
+        <v>0.02473145160901895</v>
       </c>
     </row>
     <row r="289">
@@ -6561,16 +6561,16 @@
         </is>
       </c>
       <c r="B289" s="18" t="n">
-        <v>0.6455599885333275</v>
+        <v>1.174904493076838</v>
       </c>
       <c r="C289" s="18" t="n">
-        <v>0.2196326385359816</v>
+        <v>0.3130135013985568</v>
       </c>
       <c r="D289" s="18" t="n">
-        <v>1.897476174639116</v>
+        <v>4.410035227504427</v>
       </c>
       <c r="E289" s="18" t="n">
-        <v>0.4262820968788209</v>
+        <v>0.8112250937714095</v>
       </c>
     </row>
     <row r="290">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="B290" s="18" t="n">
-        <v/>
+        <v>0.3829991502059606</v>
       </c>
       <c r="C290" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>0.283645282180823</v>
       </c>
       <c r="D290" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>0.5171542002414643</v>
       </c>
       <c r="E290" s="18" t="n">
-        <v>0</v>
+        <v>3.761064347255035e-10</v>
       </c>
     </row>
     <row r="291">
@@ -6599,16 +6599,16 @@
         </is>
       </c>
       <c r="B291" s="18" t="n">
-        <v/>
+        <v>0.6707587064464695</v>
       </c>
       <c r="C291" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>0.489761450607343</v>
       </c>
       <c r="D291" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>0.9186456829458667</v>
       </c>
       <c r="E291" s="18" t="n">
-        <v>0</v>
+        <v>0.0128177199070952</v>
       </c>
     </row>
     <row r="292">
@@ -6618,16 +6618,16 @@
         </is>
       </c>
       <c r="B292" s="18" t="n">
-        <v>2.307827736181179</v>
+        <v>1.478428736465799</v>
       </c>
       <c r="C292" s="18" t="n">
-        <v>1.430673041212053</v>
+        <v>0.9654875475687518</v>
       </c>
       <c r="D292" s="18" t="n">
-        <v>3.722771525333944</v>
+        <v>2.263883707575434</v>
       </c>
       <c r="E292" s="18" t="n">
-        <v>0.0006080798228158872</v>
+        <v>0.07211188680654161</v>
       </c>
     </row>
     <row r="293">
@@ -6637,16 +6637,16 @@
         </is>
       </c>
       <c r="B293" s="18" t="n">
-        <v>0.7736593315791253</v>
+        <v>1.341403969539692</v>
       </c>
       <c r="C293" s="18" t="n">
-        <v>0.4946242197756848</v>
+        <v>0.9053618078824965</v>
       </c>
       <c r="D293" s="18" t="n">
-        <v>1.210108072772709</v>
+        <v>1.987453627743899</v>
       </c>
       <c r="E293" s="18" t="n">
-        <v>0.260851412479539</v>
+        <v>0.1431097626596375</v>
       </c>
     </row>
     <row r="294">
@@ -6656,16 +6656,16 @@
         </is>
       </c>
       <c r="B294" s="18" t="n">
-        <v>4.028541636128907</v>
+        <v>1.619269540817887</v>
       </c>
       <c r="C294" s="18" t="n">
-        <v>0.6450510481737461</v>
+        <v>0.4806606887660818</v>
       </c>
       <c r="D294" s="18" t="n">
-        <v>25.15947809087633</v>
+        <v>5.455061974283086</v>
       </c>
       <c r="E294" s="18" t="n">
-        <v>0.1359953804871079</v>
+        <v>0.4367052344178606</v>
       </c>
     </row>
     <row r="295">
@@ -6675,16 +6675,16 @@
         </is>
       </c>
       <c r="B295" s="18" t="n">
-        <v>5.275466559648033</v>
+        <v>2.805997122414412</v>
       </c>
       <c r="C295" s="18" t="n">
-        <v>0.8407768791334691</v>
+        <v>0.8247482160722029</v>
       </c>
       <c r="D295" s="18" t="n">
-        <v>33.10099042048788</v>
+        <v>9.546695218688003</v>
       </c>
       <c r="E295" s="18" t="n">
-        <v>0.07591846768007322</v>
+        <v>0.09862749066643212</v>
       </c>
     </row>
     <row r="296">
@@ -6694,16 +6694,16 @@
         </is>
       </c>
       <c r="B296" s="18" t="n">
-        <v>0</v>
+        <v>0.5619147415812717</v>
       </c>
       <c r="C296" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.3104866771069246</v>
       </c>
       <c r="D296" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>1.016945975745075</v>
       </c>
       <c r="E296" s="18" t="n">
-        <v>0</v>
+        <v>0.05685244078067574</v>
       </c>
     </row>
     <row r="297">
@@ -6713,16 +6713,16 @@
         </is>
       </c>
       <c r="B297" s="18" t="n">
-        <v>0</v>
+        <v>0.4571868213529854</v>
       </c>
       <c r="C297" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.2035136855745858</v>
       </c>
       <c r="D297" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>1.027055202841594</v>
       </c>
       <c r="E297" s="18" t="n">
-        <v>0</v>
+        <v>0.05805041142654126</v>
       </c>
     </row>
     <row r="298">
@@ -6732,16 +6732,16 @@
         </is>
       </c>
       <c r="B298" s="18" t="n">
-        <v>0</v>
+        <v>0.4288235052548739</v>
       </c>
       <c r="C298" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.3072307692955564</v>
       </c>
       <c r="D298" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.5985390040220055</v>
       </c>
       <c r="E298" s="18" t="n">
-        <v>0</v>
+        <v>6.461859568288532e-07</v>
       </c>
     </row>
     <row r="299">
@@ -6751,16 +6751,16 @@
         </is>
       </c>
       <c r="B299" s="18" t="n">
-        <v>0</v>
+        <v>0.5990810004455327</v>
       </c>
       <c r="C299" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.4014782918454663</v>
       </c>
       <c r="D299" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.8939413472272231</v>
       </c>
       <c r="E299" s="18" t="n">
-        <v>0</v>
+        <v>0.01210789915536751</v>
       </c>
     </row>
     <row r="300">
@@ -6770,16 +6770,16 @@
         </is>
       </c>
       <c r="B300" s="18" t="n">
-        <v>0.2313671471307593</v>
+        <v>0.4247494045818319</v>
       </c>
       <c r="C300" s="18" t="n">
-        <v>0.1423300268385204</v>
+        <v>0.3043453849425314</v>
       </c>
       <c r="D300" s="18" t="n">
-        <v>0.3761030469850145</v>
+        <v>0.5927872266789502</v>
       </c>
       <c r="E300" s="18" t="n">
-        <v>3.530492534718155e-09</v>
+        <v>4.78723974833185e-07</v>
       </c>
     </row>
     <row r="301">
@@ -6789,16 +6789,16 @@
         </is>
       </c>
       <c r="B301" s="18" t="n">
-        <v>0.4000424768799858</v>
+        <v>0.6048272504128508</v>
       </c>
       <c r="C301" s="18" t="n">
-        <v>0.2559077152348334</v>
+        <v>0.4356655661971757</v>
       </c>
       <c r="D301" s="18" t="n">
-        <v>0.6253581810201344</v>
+        <v>0.8396715995599398</v>
       </c>
       <c r="E301" s="18" t="n">
-        <v>5.834303600896217e-05</v>
+        <v>0.00266514129187637</v>
       </c>
     </row>
     <row r="302">
@@ -6808,16 +6808,16 @@
         </is>
       </c>
       <c r="B302" s="18" t="n">
-        <v>1.035280496242129</v>
+        <v>0.9203801264734032</v>
       </c>
       <c r="C302" s="18" t="n">
-        <v>0.926772833328028</v>
+        <v>0.8316485171553893</v>
       </c>
       <c r="D302" s="18" t="n">
-        <v>1.156492365071287</v>
+        <v>1.018578834367021</v>
       </c>
       <c r="E302" s="18" t="n">
-        <v>0.5393641394215409</v>
+        <v>0.108699269417467</v>
       </c>
     </row>
     <row r="303">
@@ -6827,16 +6827,16 @@
         </is>
       </c>
       <c r="B303" s="18" t="n">
-        <v>1.130102514626227</v>
+        <v>1.048882343825277</v>
       </c>
       <c r="C303" s="18" t="n">
-        <v>1.043695576027466</v>
+        <v>0.9757344109651043</v>
       </c>
       <c r="D303" s="18" t="n">
-        <v>1.22366303249609</v>
+        <v>1.12751396161199</v>
       </c>
       <c r="E303" s="18" t="n">
-        <v>0.002579891430286264</v>
+        <v>0.1956829844783866</v>
       </c>
     </row>
     <row r="304">
@@ -6883,16 +6883,16 @@
         </is>
       </c>
       <c r="B307" s="18" t="n">
-        <v>0.212146578965095</v>
+        <v>0.2121465789650938</v>
       </c>
       <c r="C307" s="18" t="n">
-        <v>0.1447620495987545</v>
+        <v>0.1447620495987536</v>
       </c>
       <c r="D307" s="18" t="n">
-        <v>0.3108975804870097</v>
+        <v>0.3108975804870083</v>
       </c>
       <c r="E307" s="18" t="n">
-        <v>1.845469936715135e-15</v>
+        <v>1.845469936715041e-15</v>
       </c>
     </row>
     <row r="308">
@@ -6902,16 +6902,16 @@
         </is>
       </c>
       <c r="B308" s="18" t="n">
-        <v>0.1481709302516656</v>
+        <v>0.1481709302516655</v>
       </c>
       <c r="C308" s="18" t="n">
-        <v>0.07281506778999984</v>
+        <v>0.0728150677899998</v>
       </c>
       <c r="D308" s="18" t="n">
-        <v>0.3015121078368224</v>
+        <v>0.301512107836822</v>
       </c>
       <c r="E308" s="18" t="n">
-        <v>1.38218575447334e-07</v>
+        <v>1.382185754473308e-07</v>
       </c>
     </row>
     <row r="309">
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="B310" s="18" t="n">
-        <v>1.000927484046317</v>
+        <v>1.000927484046316</v>
       </c>
       <c r="C310" s="18" t="n">
-        <v>0.7871210841082442</v>
+        <v>0.7871210841082436</v>
       </c>
       <c r="D310" s="18" t="n">
-        <v>1.272810306503637</v>
+        <v>1.272810306503635</v>
       </c>
       <c r="E310" s="18" t="n">
-        <v>0.9939669776747871</v>
+        <v>0.9939669776747947</v>
       </c>
     </row>
     <row r="311">
@@ -6959,16 +6959,16 @@
         </is>
       </c>
       <c r="B311" s="18" t="n">
-        <v>0.8684486853414537</v>
+        <v>0.868448685341453</v>
       </c>
       <c r="C311" s="18" t="n">
-        <v>0.6845751774163163</v>
+        <v>0.6845751774163154</v>
       </c>
       <c r="D311" s="18" t="n">
         <v>1.101709708373839</v>
       </c>
       <c r="E311" s="18" t="n">
-        <v>0.2452437467003608</v>
+        <v>0.2452437467003592</v>
       </c>
     </row>
     <row r="312">
@@ -6978,16 +6978,16 @@
         </is>
       </c>
       <c r="B312" s="18" t="n">
-        <v>2.773620309514966</v>
+        <v>2.773620309514969</v>
       </c>
       <c r="C312" s="18" t="n">
-        <v>1.54981593010447</v>
+        <v>1.549815930104473</v>
       </c>
       <c r="D312" s="18" t="n">
-        <v>4.96379568174611</v>
+        <v>4.963795681746108</v>
       </c>
       <c r="E312" s="18" t="n">
-        <v>0.0005916727631447649</v>
+        <v>0.0005916727631447432</v>
       </c>
     </row>
     <row r="313">
@@ -6997,16 +6997,16 @@
         </is>
       </c>
       <c r="B313" s="18" t="n">
-        <v>0.6926461139556238</v>
+        <v>0.6926461139556217</v>
       </c>
       <c r="C313" s="18" t="n">
-        <v>0.3940886371243369</v>
+        <v>0.394088637124336</v>
       </c>
       <c r="D313" s="18" t="n">
-        <v>1.217387648318469</v>
+        <v>1.217387648318464</v>
       </c>
       <c r="E313" s="18" t="n">
-        <v>0.2018441278021943</v>
+        <v>0.20184412780219</v>
       </c>
     </row>
     <row r="314">
@@ -7016,16 +7016,16 @@
         </is>
       </c>
       <c r="B314" s="18" t="n">
-        <v>1.000000000055106</v>
+        <v>1.000000000027197</v>
       </c>
       <c r="C314" s="18" t="n">
-        <v>0.9999999365258215</v>
+        <v>0.999999968673107</v>
       </c>
       <c r="D314" s="18" t="n">
-        <v>1.000000063584395</v>
+        <v>1.000000031381287</v>
       </c>
       <c r="E314" s="18" t="n">
-        <v>0.9986435126981521</v>
+        <v>0.998643529701507</v>
       </c>
     </row>
     <row r="315">
@@ -7038,13 +7038,13 @@
         <v>1.071424148750146</v>
       </c>
       <c r="C315" s="18" t="n">
-        <v>0.7691735683880992</v>
+        <v>0.7691735683880994</v>
       </c>
       <c r="D315" s="18" t="n">
         <v>1.492445598372094</v>
       </c>
       <c r="E315" s="18" t="n">
-        <v>0.6832889925151042</v>
+        <v>0.6832889925151044</v>
       </c>
     </row>
     <row r="316">
@@ -7054,16 +7054,16 @@
         </is>
       </c>
       <c r="B316" s="18" t="n">
-        <v>15.11279260106002</v>
+        <v>15.11279260106012</v>
       </c>
       <c r="C316" s="18" t="n">
-        <v>8.440112611810473</v>
+        <v>8.440112611810511</v>
       </c>
       <c r="D316" s="18" t="n">
-        <v>27.06083564371561</v>
+        <v>27.06083564371585</v>
       </c>
       <c r="E316" s="18" t="n">
-        <v>6.457500862693175e-20</v>
+        <v>6.457500862694149e-20</v>
       </c>
     </row>
     <row r="317">
@@ -7073,16 +7073,16 @@
         </is>
       </c>
       <c r="B317" s="18" t="n">
-        <v>1.321481870785391</v>
+        <v>1.321481870785394</v>
       </c>
       <c r="C317" s="18" t="n">
-        <v>0.561728102537477</v>
+        <v>0.561728102537479</v>
       </c>
       <c r="D317" s="18" t="n">
-        <v>3.108824940261817</v>
+        <v>3.108824940261825</v>
       </c>
       <c r="E317" s="18" t="n">
-        <v>0.5230598484323501</v>
+        <v>0.5230598484323455</v>
       </c>
     </row>
     <row r="318">
@@ -7092,16 +7092,16 @@
         </is>
       </c>
       <c r="B318" s="18" t="n">
-        <v>0.3479305781815193</v>
+        <v>0.3479305781815146</v>
       </c>
       <c r="C318" s="18" t="n">
-        <v>0.04221587777756942</v>
+        <v>0.04221587777756792</v>
       </c>
       <c r="D318" s="18" t="n">
-        <v>2.867539267371266</v>
+        <v>2.86753926737129</v>
       </c>
       <c r="E318" s="18" t="n">
-        <v>0.326568227525325</v>
+        <v>0.3265682275253238</v>
       </c>
     </row>
     <row r="319">
@@ -7111,16 +7111,16 @@
         </is>
       </c>
       <c r="B319" s="18" t="n">
-        <v>0.5839324058902094</v>
+        <v>0.5839324058902089</v>
       </c>
       <c r="C319" s="18" t="n">
-        <v>0.406001884937935</v>
+        <v>0.4060018849379343</v>
       </c>
       <c r="D319" s="18" t="n">
         <v>0.8398410630552934</v>
       </c>
       <c r="E319" s="18" t="n">
-        <v>0.003716508413346156</v>
+        <v>0.003716508413346185</v>
       </c>
     </row>
     <row r="320">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="B320" s="18" t="n">
-        <v>1.251285385774945</v>
+        <v>1.251285385774938</v>
       </c>
       <c r="C320" s="18" t="n">
-        <v>0.6170159457505981</v>
+        <v>0.6170159457505956</v>
       </c>
       <c r="D320" s="18" t="n">
-        <v>2.537560216129041</v>
+        <v>2.537560216129026</v>
       </c>
       <c r="E320" s="18" t="n">
-        <v>0.5343195291870233</v>
+        <v>0.5343195291870322</v>
       </c>
     </row>
     <row r="321">
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="B321" s="18" t="n">
-        <v>2.014726184509153e-09</v>
+        <v>2.01472617828268e-09</v>
       </c>
       <c r="C321" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -7158,7 +7158,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E321" s="18" t="n">
-        <v>0.9986435259041617</v>
+        <v>0.9986435259058022</v>
       </c>
     </row>
     <row r="322">
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="B322" s="18" t="n">
-        <v>0.7729013050052419</v>
+        <v>0.7729013050052385</v>
       </c>
       <c r="C322" s="18" t="n">
-        <v>0.4448679420783686</v>
+        <v>0.4448679420783668</v>
       </c>
       <c r="D322" s="18" t="n">
-        <v>1.342817431366118</v>
+        <v>1.342817431366112</v>
       </c>
       <c r="E322" s="18" t="n">
-        <v>0.3606933796774029</v>
+        <v>0.3606933796773942</v>
       </c>
     </row>
     <row r="323">
@@ -7187,16 +7187,16 @@
         </is>
       </c>
       <c r="B323" s="18" t="n">
-        <v>1.947800313575633</v>
+        <v>1.947800313575637</v>
       </c>
       <c r="C323" s="18" t="n">
-        <v>1.379229957871423</v>
+        <v>1.379229957871424</v>
       </c>
       <c r="D323" s="18" t="n">
-        <v>2.750756710230203</v>
+        <v>2.750756710230211</v>
       </c>
       <c r="E323" s="18" t="n">
-        <v>0.0001533139669903153</v>
+        <v>0.0001533139669903146</v>
       </c>
     </row>
     <row r="324">
@@ -7206,16 +7206,16 @@
         </is>
       </c>
       <c r="B324" s="18" t="n">
-        <v>2.102017488094825</v>
+        <v>2.102017488094829</v>
       </c>
       <c r="C324" s="18" t="n">
-        <v>1.416008527883011</v>
+        <v>1.416008527883012</v>
       </c>
       <c r="D324" s="18" t="n">
-        <v>3.120374936485924</v>
+        <v>3.120374936485933</v>
       </c>
       <c r="E324" s="18" t="n">
-        <v>0.0002280835182906435</v>
+        <v>0.0002280835182906418</v>
       </c>
     </row>
     <row r="325">
@@ -7225,16 +7225,16 @@
         </is>
       </c>
       <c r="B325" s="18" t="n">
-        <v>1.925961533572608</v>
+        <v>1.92596153357261</v>
       </c>
       <c r="C325" s="18" t="n">
         <v>1.164609708115182</v>
       </c>
       <c r="D325" s="18" t="n">
-        <v>3.18503941960485</v>
+        <v>3.185039419604856</v>
       </c>
       <c r="E325" s="18" t="n">
-        <v>0.01065859349159797</v>
+        <v>0.010658593491598</v>
       </c>
     </row>
     <row r="326">
@@ -7244,16 +7244,16 @@
         </is>
       </c>
       <c r="B326" s="18" t="n">
-        <v>0.8286562662072178</v>
+        <v>0.8286562662072231</v>
       </c>
       <c r="C326" s="18" t="n">
-        <v>0.2932358696188969</v>
+        <v>0.2932358696188989</v>
       </c>
       <c r="D326" s="18" t="n">
-        <v>2.341702631458142</v>
+        <v>2.341702631458156</v>
       </c>
       <c r="E326" s="18" t="n">
-        <v>0.722884606305379</v>
+        <v>0.722884606305388</v>
       </c>
     </row>
     <row r="327">
@@ -7266,13 +7266,13 @@
         <v>0.8209842993608983</v>
       </c>
       <c r="C327" s="18" t="n">
-        <v>0.7675122378997299</v>
+        <v>0.7675122378997297</v>
       </c>
       <c r="D327" s="18" t="n">
-        <v>0.8781817233840128</v>
+        <v>0.8781817233840129</v>
       </c>
       <c r="E327" s="18" t="n">
-        <v>9.451936694501723e-09</v>
+        <v>9.451936694502102e-09</v>
       </c>
     </row>
     <row r="328">
@@ -7288,10 +7288,10 @@
         <v>1.07592686808832</v>
       </c>
       <c r="D328" s="18" t="n">
-        <v>1.190883108567977</v>
+        <v>1.190883108567978</v>
       </c>
       <c r="E328" s="18" t="n">
-        <v>1.70207304021339e-06</v>
+        <v>1.702073040213375e-06</v>
       </c>
     </row>
     <row r="329"/>
@@ -7309,58 +7309,58 @@
   {
     "stratum": "N0",
     "n": 1115,
-    "events": 29,
-    "gross_or": 1.6456763294087677,
+    "events": 39,
+    "gross_or": 1.740487686615032,
     "gross_ci": [
-      0.7230984843626904,
-      3.7453412498343943
+      0.8528797712492094,
+      3.5518457458799224
     ],
-    "gross_p": 0.23512401713133046,
-    "noneg_or": 1.8260044626521557,
+    "gross_p": 0.12783408907872904,
+    "noneg_or": 2.8330706750819927,
     "noneg_ci": [
-      0.18779197285420438,
-      17.755243991255288
+      0.505507240440091,
+      15.877694339297511
     ],
-    "noneg_p": 0.6038644472897621
+    "noneg_p": 0.23633444494411338
   },
   {
     "stratum": "N1a",
     "n": 2372,
-    "events": 92,
-    "gross_or": 1.9512850044893069,
+    "events": 128,
+    "gross_or": 2.166171497313047,
     "gross_ci": [
-      1.2099148754955278,
-      3.1469264870269864
+      1.4363522901951746,
+      3.2668162175825604
     ],
-    "gross_p": 0.006118067426024094,
-    "noneg_or": 0.7178066325740177,
+    "gross_p": 0.0002265759946471743,
+    "noneg_or": 0.7282490109442497,
     "noneg_ci": [
-      0.2568789836007096,
-      2.0057941468973777
+      0.30249724388588256,
+      1.7532279472316505
     ],
-    "noneg_p": 0.527135184857842
+    "noneg_p": 0.47929846452204217
   },
   {
     "stratum": "N1b",
     "n": 76,
-    "events": 16,
-    "gross_or": 1.2412076938293504,
+    "events": 23,
+    "gross_or": 3.776898980170589,
     "gross_ci": [
-      0.07204442242452236,
-      21.383980707669448
+      0.5865487191236326,
+      24.320172291445875
     ],
-    "gross_p": 0.8817250858670661,
-    "noneg_or": 0.044672950756756896,
+    "gross_p": 0.16195778052707288,
+    "noneg_or": 0.15109828304029313,
     "noneg_ci": [
-      0.0010542234750577223,
-      1.8930260770434428
+      0.008687683131828751,
+      2.62793782775992
     ],
-    "noneg_p": 0.10392614431984892
+    "noneg_p": 0.19466430889482844
   },
   {
     "stratum": "Nx",
     "n": 193,
-    "events": 2,
+    "events": 3,
     "note": "skipped_sparse_events_for_stable_GLMs"
   },
   {
@@ -7386,13 +7386,13 @@
         <is>
           <t>{
   "n_obs": 192,
-  "n_events": 29,
-  "llf": -54.05824166134959,
-  "aic": 130.1164833226992,
-  "pseudo_r2_mcfadden": 0.3367595502439821,
-  "lr_vs_null_chi2": 54.89601593374893,
-  "lr_vs_null_pvalue": 3.302489481882276e-08,
-  "events": 29,
+  "n_events": 19,
+  "llf": -44.26887111171082,
+  "aic": 110.53774222342165,
+  "pseudo_r2_mcfadden": 0.2857016703325118,
+  "lr_vs_null_chi2": 35.41290773069025,
+  "lr_vs_null_pvalue": 0.00010613916145962854,
+  "events": 19,
   "formula": "y_comp ~ tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + central_pos_flag + lateral_pos_flag + rai_received_flag + ge2 + days_per_100"
 }</t>
         </is>
@@ -7405,16 +7405,16 @@
         </is>
       </c>
       <c r="B335" s="18" t="n">
-        <v>0.01652051389901656</v>
+        <v>0.02411789512997224</v>
       </c>
       <c r="C335" s="18" t="n">
-        <v>0.002047122854006331</v>
+        <v>0.003095426568018558</v>
       </c>
       <c r="D335" s="18" t="n">
-        <v>0.1333224232016488</v>
+        <v>0.187913637335186</v>
       </c>
       <c r="E335" s="18" t="n">
-        <v>0.000117522055073025</v>
+        <v>0.0003766088038290857</v>
       </c>
     </row>
     <row r="336">
@@ -7424,16 +7424,16 @@
         </is>
       </c>
       <c r="B336" s="18" t="n">
-        <v>0.913704174617744</v>
+        <v>0.8040871828013445</v>
       </c>
       <c r="C336" s="18" t="n">
-        <v>0.1031825134962474</v>
+        <v>0.08807263284511103</v>
       </c>
       <c r="D336" s="18" t="n">
-        <v>8.091054292297843</v>
+        <v>7.341170312036306</v>
       </c>
       <c r="E336" s="18" t="n">
-        <v>0.9353609862144719</v>
+        <v>0.8467687891007277</v>
       </c>
     </row>
     <row r="337">
@@ -7443,16 +7443,16 @@
         </is>
       </c>
       <c r="B337" s="18" t="n">
-        <v>2.030051996958292</v>
+        <v>1.215463783755382</v>
       </c>
       <c r="C337" s="18" t="n">
-        <v>0.1045557549793954</v>
+        <v>0.05425189302773018</v>
       </c>
       <c r="D337" s="18" t="n">
-        <v>39.41544022293645</v>
+        <v>27.23134857000878</v>
       </c>
       <c r="E337" s="18" t="n">
-        <v>0.6398709470246327</v>
+        <v>0.9021064666247514</v>
       </c>
     </row>
     <row r="338">
@@ -7462,16 +7462,16 @@
         </is>
       </c>
       <c r="B338" s="18" t="n">
-        <v>1.796187301528384</v>
+        <v>1.094107558560965</v>
       </c>
       <c r="C338" s="18" t="n">
-        <v>0.1911136343597706</v>
+        <v>0.1059296698753412</v>
       </c>
       <c r="D338" s="18" t="n">
-        <v>16.88152094945954</v>
+        <v>11.30062381114711</v>
       </c>
       <c r="E338" s="18" t="n">
-        <v>0.6084256719305801</v>
+        <v>0.9398200139471643</v>
       </c>
     </row>
     <row r="339">
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="B339" s="18" t="n">
-        <v>3.03582939339014e-09</v>
+        <v>3.674513475945357e-09</v>
       </c>
       <c r="C339" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -7490,7 +7490,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E339" s="18" t="n">
-        <v>0.9991222694924362</v>
+        <v>0.9991500083918476</v>
       </c>
     </row>
     <row r="340">
@@ -7500,16 +7500,16 @@
         </is>
       </c>
       <c r="B340" s="18" t="n">
-        <v>1.055587646281052</v>
+        <v>0.9516299292814673</v>
       </c>
       <c r="C340" s="18" t="n">
-        <v>0.9083864295117887</v>
+        <v>0.7675933343346527</v>
       </c>
       <c r="D340" s="18" t="n">
-        <v>1.226642365826659</v>
+        <v>1.179790758721506</v>
       </c>
       <c r="E340" s="18" t="n">
-        <v>0.4801874233652026</v>
+        <v>0.6511648987738741</v>
       </c>
     </row>
     <row r="341">
@@ -7519,16 +7519,16 @@
         </is>
       </c>
       <c r="B341" s="18" t="n">
-        <v>1.369218027004348</v>
+        <v>1.376884772637383</v>
       </c>
       <c r="C341" s="18" t="n">
-        <v>0.4144862618993688</v>
+        <v>0.357345754615485</v>
       </c>
       <c r="D341" s="18" t="n">
-        <v>4.523088405590737</v>
+        <v>5.305258709903101</v>
       </c>
       <c r="E341" s="18" t="n">
-        <v>0.6062625723199894</v>
+        <v>0.6421354769371461</v>
       </c>
     </row>
     <row r="342">
@@ -7538,16 +7538,16 @@
         </is>
       </c>
       <c r="B342" s="18" t="n">
-        <v>4.796367595255656</v>
+        <v>2.524185711263298</v>
       </c>
       <c r="C342" s="18" t="n">
-        <v>1.294072005033074</v>
+        <v>0.6101216624634135</v>
       </c>
       <c r="D342" s="18" t="n">
-        <v>17.77732770614303</v>
+        <v>10.44302128073985</v>
       </c>
       <c r="E342" s="18" t="n">
-        <v>0.01899421120183582</v>
+        <v>0.2012525917948234</v>
       </c>
     </row>
     <row r="343">
@@ -7557,16 +7557,16 @@
         </is>
       </c>
       <c r="B343" s="18" t="n">
-        <v>15.91850505630191</v>
+        <v>8.843888533396331</v>
       </c>
       <c r="C343" s="18" t="n">
-        <v>5.601241949901261</v>
+        <v>2.771343352101149</v>
       </c>
       <c r="D343" s="18" t="n">
-        <v>45.23975316438104</v>
+        <v>28.22254569497472</v>
       </c>
       <c r="E343" s="18" t="n">
-        <v>2.068165598651782e-07</v>
+        <v>0.0002317142156747089</v>
       </c>
     </row>
     <row r="344">
@@ -7576,16 +7576,16 @@
         </is>
       </c>
       <c r="B344" s="18" t="n">
-        <v>3.311015683449587</v>
+        <v>3.308184753372749</v>
       </c>
       <c r="C344" s="18" t="n">
-        <v>0.7158630096050408</v>
+        <v>0.6587459583166945</v>
       </c>
       <c r="D344" s="18" t="n">
-        <v>15.31413791319878</v>
+        <v>16.61351576321401</v>
       </c>
       <c r="E344" s="18" t="n">
-        <v>0.1254763905358091</v>
+        <v>0.1462195968306</v>
       </c>
     </row>
     <row r="345">
@@ -7595,16 +7595,16 @@
         </is>
       </c>
       <c r="B345" s="18" t="n">
-        <v>1.03165389352651</v>
+        <v>1.088031671121559</v>
       </c>
       <c r="C345" s="18" t="n">
-        <v>0.8966012325738687</v>
+        <v>0.9466969428212387</v>
       </c>
       <c r="D345" s="18" t="n">
-        <v>1.187049177897179</v>
+        <v>1.250466610608996</v>
       </c>
       <c r="E345" s="18" t="n">
-        <v>0.6633289121046686</v>
+        <v>0.2346731667026427</v>
       </c>
     </row>
     <row r="346"/>
@@ -7620,13 +7620,13 @@
         <is>
           <t>{
   "n_obs": 171,
-  "n_events": 11,
-  "llf": -27.093819271894194,
-  "aic": 72.18763854378838,
-  "pseudo_r2_mcfadden": 0.3362580704014553,
-  "lr_vs_null_chi2": 27.451980903732498,
-  "lr_vs_null_pvalue": 0.0005904940071913556,
-  "events": 11,
+  "n_events": 17,
+  "llf": -43.72348369239609,
+  "aic": 105.44696738479217,
+  "pseudo_r2_mcfadden": 0.21032757118954393,
+  "lr_vs_null_chi2": 23.29131369780839,
+  "lr_vs_null_pvalue": 0.0030096903863037205,
+  "events": 17,
   "formula": "y_pp ~ tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + central_pos_flag + lateral_pos_flag + ge2 + days_per_100"
 }</t>
         </is>
@@ -7639,16 +7639,16 @@
         </is>
       </c>
       <c r="B349" s="18" t="n">
-        <v>0.0141302155278802</v>
+        <v>0.04922383763851679</v>
       </c>
       <c r="C349" s="18" t="n">
-        <v>0.001068060180277024</v>
+        <v>0.008558428624978697</v>
       </c>
       <c r="D349" s="18" t="n">
-        <v>0.1869398321848868</v>
+        <v>0.2831111057924016</v>
       </c>
       <c r="E349" s="18" t="n">
-        <v>0.001226273475024953</v>
+        <v>0.0007416006127659506</v>
       </c>
     </row>
     <row r="350">
@@ -7658,16 +7658,16 @@
         </is>
       </c>
       <c r="B350" s="18" t="n">
-        <v>0.5689880035875429</v>
+        <v>0.6101636481989928</v>
       </c>
       <c r="C350" s="18" t="n">
-        <v>0.03005726534141087</v>
+        <v>0.07575595587047168</v>
       </c>
       <c r="D350" s="18" t="n">
-        <v>10.77101807330757</v>
+        <v>4.914460827608937</v>
       </c>
       <c r="E350" s="18" t="n">
-        <v>0.7070453614462651</v>
+        <v>0.6425530500487189</v>
       </c>
     </row>
     <row r="351">
@@ -7677,16 +7677,16 @@
         </is>
       </c>
       <c r="B351" s="18" t="n">
-        <v>0.4799986868471424</v>
+        <v>2.760569677045763</v>
       </c>
       <c r="C351" s="18" t="n">
-        <v>0.001897303751580639</v>
+        <v>0.1496531861902959</v>
       </c>
       <c r="D351" s="18" t="n">
-        <v>121.4348199032636</v>
+        <v>50.9227042592609</v>
       </c>
       <c r="E351" s="18" t="n">
-        <v>0.7948794393251364</v>
+        <v>0.4947450252775966</v>
       </c>
     </row>
     <row r="352">
@@ -7696,16 +7696,16 @@
         </is>
       </c>
       <c r="B352" s="18" t="n">
-        <v>0.6528464689608989</v>
+        <v>0.2889497250519529</v>
       </c>
       <c r="C352" s="18" t="n">
-        <v>0.02841986932470973</v>
+        <v>0.0201071220311442</v>
       </c>
       <c r="D352" s="18" t="n">
-        <v>14.99684981535598</v>
+        <v>4.152356736000177</v>
       </c>
       <c r="E352" s="18" t="n">
-        <v>0.7897371772286215</v>
+        <v>0.3612440745991894</v>
       </c>
     </row>
     <row r="353">
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="B353" s="18" t="n">
-        <v>0.999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C353" s="18" t="n">
-        <v>0.9999999999999976</v>
+        <v>0.9999999999999988</v>
       </c>
       <c r="D353" s="18" t="n">
-        <v>1</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="E353" s="18" t="n">
-        <v>0.2046645190177655</v>
+        <v>0.7463453472040671</v>
       </c>
     </row>
     <row r="354">
@@ -7734,16 +7734,16 @@
         </is>
       </c>
       <c r="B354" s="18" t="n">
-        <v>0.9161328106597633</v>
+        <v>0.9869548136095684</v>
       </c>
       <c r="C354" s="18" t="n">
-        <v>0.6771543318825252</v>
+        <v>0.8140775973964304</v>
       </c>
       <c r="D354" s="18" t="n">
-        <v>1.239450576110265</v>
+        <v>1.196544171246554</v>
       </c>
       <c r="E354" s="18" t="n">
-        <v>0.570043804339301</v>
+        <v>0.8936812272882472</v>
       </c>
     </row>
     <row r="355">
@@ -7753,16 +7753,16 @@
         </is>
       </c>
       <c r="B355" s="18" t="n">
-        <v>2.746920567150562</v>
+        <v>1.63226533864375</v>
       </c>
       <c r="C355" s="18" t="n">
-        <v>0.5191680013353919</v>
+        <v>0.4313154498324233</v>
       </c>
       <c r="D355" s="18" t="n">
-        <v>14.53397085880913</v>
+        <v>6.177126594405416</v>
       </c>
       <c r="E355" s="18" t="n">
-        <v>0.2345290624516252</v>
+        <v>0.4705611936807946</v>
       </c>
     </row>
     <row r="356">
@@ -7772,16 +7772,16 @@
         </is>
       </c>
       <c r="B356" s="18" t="n">
-        <v>4.769593548838071</v>
+        <v>2.689750688613711</v>
       </c>
       <c r="C356" s="18" t="n">
-        <v>0.7207462802354853</v>
+        <v>0.6788461432656692</v>
       </c>
       <c r="D356" s="18" t="n">
-        <v>31.56314953673447</v>
+        <v>10.65743517683444</v>
       </c>
       <c r="E356" s="18" t="n">
-        <v>0.1051624795233538</v>
+        <v>0.1589728430816552</v>
       </c>
     </row>
     <row r="357">
@@ -7791,16 +7791,16 @@
         </is>
       </c>
       <c r="B357" s="18" t="n">
-        <v>11.56308962388756</v>
+        <v>4.729983405246534</v>
       </c>
       <c r="C357" s="18" t="n">
-        <v>1.588019908436881</v>
+        <v>0.9399959378094223</v>
       </c>
       <c r="D357" s="18" t="n">
-        <v>84.19607395329493</v>
+        <v>23.80089329539583</v>
       </c>
       <c r="E357" s="18" t="n">
-        <v>0.01566868583656481</v>
+        <v>0.05944280025238249</v>
       </c>
     </row>
     <row r="358">
@@ -7810,16 +7810,16 @@
         </is>
       </c>
       <c r="B358" s="18" t="n">
-        <v>1.088665125354509</v>
+        <v>1.099003722075374</v>
       </c>
       <c r="C358" s="18" t="n">
-        <v>0.9371042249758984</v>
+        <v>0.9508170949000114</v>
       </c>
       <c r="D358" s="18" t="n">
-        <v>1.264738460861843</v>
+        <v>1.27028551296981</v>
       </c>
       <c r="E358" s="18" t="n">
-        <v>0.2667118841834583</v>
+        <v>0.2014294484859358</v>
       </c>
     </row>
     <row r="359"/>
@@ -7834,21 +7834,21 @@
       <c r="A361" s="18" t="inlineStr">
         <is>
           <t>{
-  "n": 2018,
-  "events": 75,
-  "coef_table_path": "/sessions/wonderful-trusting-babbage/mnt/THyroid 2026/data/m044/m044_cox_primary_summary.csv",
+  "n": 2511,
+  "events": 178,
+  "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 2.336985915027275,
-    "hr_ci_low": 1.3452598047553705,
-    "hr_ci_high": 4.059812942994324,
-    "p": 0.002590885019965145,
+    "hr": 0.9102808635560813,
+    "hr_ci_low": 0.47913333888681914,
+    "hr_ci_high": 1.7293959390960676,
+    "p": 0.7740508906797761,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 1.636551906943798,
-    "hr_ci_low": 0.5754754163628808,
-    "hr_ci_high": 4.654068736852017,
-    "p": 0.3556144639726626,
+    "hr": 2.443225068198415,
+    "hr_ci_low": 0.6478494195146004,
+    "hr_ci_high": 9.214099070036475,
+    "p": 0.18716625998772768,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -7862,16 +7862,16 @@
         </is>
       </c>
       <c r="B362" s="18" t="n">
-        <v>2.336985915027275</v>
+        <v>0.9102808635560812</v>
       </c>
       <c r="C362" s="18" t="n">
-        <v>1.34525980475537</v>
+        <v>0.4791333388868191</v>
       </c>
       <c r="D362" s="18" t="n">
-        <v>4.059812942994324</v>
+        <v>1.729395939096068</v>
       </c>
       <c r="E362" s="18" t="n">
-        <v>0.0025908850199651</v>
+        <v>0.7740508906797761</v>
       </c>
     </row>
     <row r="363">
@@ -7881,16 +7881,16 @@
         </is>
       </c>
       <c r="B363" s="18" t="n">
-        <v>1.636551906943798</v>
+        <v>2.443225068198415</v>
       </c>
       <c r="C363" s="18" t="n">
-        <v>0.5754754163628808</v>
+        <v>0.6478494195146004</v>
       </c>
       <c r="D363" s="18" t="n">
-        <v>4.654068736852017</v>
+        <v>9.214099070036475</v>
       </c>
       <c r="E363" s="18" t="n">
-        <v>0.3556144639726626</v>
+        <v>0.1871662599877276</v>
       </c>
     </row>
     <row r="364">
@@ -7900,16 +7900,16 @@
         </is>
       </c>
       <c r="B364" s="18" t="n">
-        <v>1.158617020926911</v>
+        <v>0.936808739475723</v>
       </c>
       <c r="C364" s="18" t="n">
-        <v>0.9999632083001412</v>
+        <v>0.7873212832297154</v>
       </c>
       <c r="D364" s="18" t="n">
-        <v>1.342442791933829</v>
+        <v>1.114679144399598</v>
       </c>
       <c r="E364" s="18" t="n">
-        <v>0.0500572658919229</v>
+        <v>0.4617635228405863</v>
       </c>
     </row>
     <row r="365">
@@ -7919,16 +7919,16 @@
         </is>
       </c>
       <c r="B365" s="18" t="n">
-        <v>1.321970007016732</v>
+        <v>1.292591248233988</v>
       </c>
       <c r="C365" s="18" t="n">
-        <v>0.8046282650464567</v>
+        <v>0.7674327357304391</v>
       </c>
       <c r="D365" s="18" t="n">
-        <v>2.171940479061987</v>
+        <v>2.177118667502301</v>
       </c>
       <c r="E365" s="18" t="n">
-        <v>0.2705226219105535</v>
+        <v>0.3346248968410373</v>
       </c>
     </row>
     <row r="366">
@@ -7938,16 +7938,16 @@
         </is>
       </c>
       <c r="B366" s="18" t="n">
-        <v>1.043016202186432</v>
+        <v>0.9684720408602407</v>
       </c>
       <c r="C366" s="18" t="n">
-        <v>0.9397772649081764</v>
+        <v>0.8403166642816156</v>
       </c>
       <c r="D366" s="18" t="n">
-        <v>1.157596420604731</v>
+        <v>1.116172192931388</v>
       </c>
       <c r="E366" s="18" t="n">
-        <v>0.4283730261365804</v>
+        <v>0.658229676744901</v>
       </c>
     </row>
     <row r="367">
@@ -7957,16 +7957,16 @@
         </is>
       </c>
       <c r="B367" s="18" t="n">
-        <v>0.8260676260869618</v>
+        <v>0.6913177685676808</v>
       </c>
       <c r="C367" s="18" t="n">
-        <v>0.4531774800447916</v>
+        <v>0.3652127171363888</v>
       </c>
       <c r="D367" s="18" t="n">
-        <v>1.505784715519187</v>
+        <v>1.308607928236294</v>
       </c>
       <c r="E367" s="18" t="n">
-        <v>0.532778396109143</v>
+        <v>0.2568575144361521</v>
       </c>
     </row>
     <row r="368">
@@ -7976,16 +7976,16 @@
         </is>
       </c>
       <c r="B368" s="18" t="n">
-        <v>3.588078269865834</v>
+        <v>1.669305268165391e-120</v>
       </c>
       <c r="C368" s="18" t="n">
-        <v>1.319050158960855</v>
+        <v>1.265014436368057e-131</v>
       </c>
       <c r="D368" s="18" t="n">
-        <v>9.760285143990089</v>
+        <v>2.202804962704766e-109</v>
       </c>
       <c r="E368" s="18" t="n">
-        <v>0.0123382677681206</v>
+        <v>6.351843715822425e-99</v>
       </c>
     </row>
     <row r="369">
@@ -7995,16 +7995,16 @@
         </is>
       </c>
       <c r="B369" s="18" t="n">
-        <v>0.4819838004331586</v>
+        <v>0.0926611428602198</v>
       </c>
       <c r="C369" s="18" t="n">
-        <v>0.1073871454994997</v>
+        <v>0.0025158197320641</v>
       </c>
       <c r="D369" s="18" t="n">
-        <v>2.163279252832669</v>
+        <v>3.412838879802226</v>
       </c>
       <c r="E369" s="18" t="n">
-        <v>0.3407356845310225</v>
+        <v>0.1960721582196949</v>
       </c>
     </row>
     <row r="370">
@@ -8014,16 +8014,16 @@
         </is>
       </c>
       <c r="B370" s="18" t="n">
-        <v>0.2287495351664525</v>
+        <v>0.8226508028771761</v>
       </c>
       <c r="C370" s="18" t="n">
-        <v>0.0649027164141687</v>
+        <v>0.3030914664962339</v>
       </c>
       <c r="D370" s="18" t="n">
-        <v>0.8062274235943206</v>
+        <v>2.232838658566692</v>
       </c>
       <c r="E370" s="18" t="n">
-        <v>0.0217286742916431</v>
+        <v>0.7015663976844336</v>
       </c>
     </row>
     <row r="371">
@@ -8033,16 +8033,16 @@
         </is>
       </c>
       <c r="B371" s="18" t="n">
-        <v>0.0183491637677193</v>
+        <v>0.0009814849519229</v>
       </c>
       <c r="C371" s="18" t="n">
-        <v>1.54062852975256e-40</v>
+        <v>1.593797932419506e-33</v>
       </c>
       <c r="D371" s="18" t="n">
-        <v>2.185418512460364e+36</v>
+        <v>6.044133269697347e+26</v>
       </c>
       <c r="E371" s="18" t="n">
-        <v>0.9287794170456518</v>
+        <v>0.8431110258271137</v>
       </c>
     </row>
     <row r="372">
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="B372" s="18" t="n">
-        <v>3.514639213512396</v>
+        <v>4.525643291271133</v>
       </c>
       <c r="C372" s="18" t="n">
-        <v>1.630572377118862</v>
+        <v>1.182715803554595</v>
       </c>
       <c r="D372" s="18" t="n">
-        <v>7.575676476861211</v>
+        <v>17.31730238005733</v>
       </c>
       <c r="E372" s="18" t="n">
-        <v>0.0013378954753054</v>
+        <v>0.0274497615896922</v>
       </c>
     </row>
     <row r="373">
@@ -8071,16 +8071,16 @@
         </is>
       </c>
       <c r="B373" s="18" t="n">
-        <v>0.8842763523212637</v>
+        <v>82.59421045665907</v>
       </c>
       <c r="C373" s="18" t="n">
-        <v>0.1720132653217445</v>
+        <v>36.94479353587479</v>
       </c>
       <c r="D373" s="18" t="n">
-        <v>4.545839332867734</v>
+        <v>184.6485782721904</v>
       </c>
       <c r="E373" s="18" t="n">
-        <v>0.8829491431072735</v>
+        <v>5.719938258257363e-27</v>
       </c>
     </row>
     <row r="374">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="B374" s="18" t="n">
-        <v>1.715137670866464</v>
+        <v>168.1113399897766</v>
       </c>
       <c r="C374" s="18" t="n">
-        <v>0.3739472067674566</v>
+        <v>65.31641294157042</v>
       </c>
       <c r="D374" s="18" t="n">
-        <v>7.866611053079929</v>
+        <v>432.6848545470469</v>
       </c>
       <c r="E374" s="18" t="n">
-        <v>0.4875453004907298</v>
+        <v>2.296010445246175e-26</v>
       </c>
     </row>
     <row r="375">
@@ -8109,16 +8109,16 @@
         </is>
       </c>
       <c r="B375" s="18" t="n">
-        <v>0.0146152307833709</v>
+        <v>6.799822934266519e-05</v>
       </c>
       <c r="C375" s="18" t="n">
-        <v>3.395802415754482e-21</v>
+        <v>2.377172731334699e-47</v>
       </c>
       <c r="D375" s="18" t="n">
-        <v>6.290265000701886e+16</v>
+        <v>1.945066562807834e+38</v>
       </c>
       <c r="E375" s="18" t="n">
-        <v>0.8469346263911736</v>
+        <v>0.8474374497066779</v>
       </c>
     </row>
     <row r="376">
@@ -8128,16 +8128,16 @@
         </is>
       </c>
       <c r="B376" s="18" t="n">
-        <v>0.7453082295694787</v>
+        <v>0.3712996489567189</v>
       </c>
       <c r="C376" s="18" t="n">
-        <v>0.2180992952431064</v>
+        <v>0.0250670217806946</v>
       </c>
       <c r="D376" s="18" t="n">
-        <v>2.546933296803252</v>
+        <v>5.499792935974478</v>
       </c>
       <c r="E376" s="18" t="n">
-        <v>0.6391763731419102</v>
+        <v>0.4712743001833367</v>
       </c>
     </row>
     <row r="377">
@@ -8147,16 +8147,16 @@
         </is>
       </c>
       <c r="B377" s="18" t="n">
-        <v>0.6928470999855146</v>
+        <v>0.2729965144346066</v>
       </c>
       <c r="C377" s="18" t="n">
-        <v>0.3233685924842587</v>
+        <v>0.0591620977775801</v>
       </c>
       <c r="D377" s="18" t="n">
-        <v>1.484488955066672</v>
+        <v>1.259710180893667</v>
       </c>
       <c r="E377" s="18" t="n">
-        <v>0.3452653955510506</v>
+        <v>0.096104351105412</v>
       </c>
     </row>
     <row r="378">
@@ -8166,16 +8166,16 @@
         </is>
       </c>
       <c r="B378" s="18" t="n">
-        <v>3.689087017780135</v>
+        <v>1.838452428514997</v>
       </c>
       <c r="C378" s="18" t="n">
-        <v>1.366352867441817</v>
+        <v>0.6299890245754654</v>
       </c>
       <c r="D378" s="18" t="n">
-        <v>9.960357495523354</v>
+        <v>5.365025738647318</v>
       </c>
       <c r="E378" s="18" t="n">
-        <v>0.009997242803493799</v>
+        <v>0.2651185955914953</v>
       </c>
     </row>
     <row r="379">
@@ -8185,16 +8185,16 @@
         </is>
       </c>
       <c r="B379" s="18" t="n">
-        <v>2.304421327650905</v>
+        <v>0.7805127177967276</v>
       </c>
       <c r="C379" s="18" t="n">
-        <v>0.9679050526160936</v>
+        <v>0.2417986199502257</v>
       </c>
       <c r="D379" s="18" t="n">
-        <v>5.486444812927989</v>
+        <v>2.519452355715835</v>
       </c>
       <c r="E379" s="18" t="n">
-        <v>0.059260229946666</v>
+        <v>0.6785346416122111</v>
       </c>
     </row>
     <row r="380">
@@ -8204,16 +8204,16 @@
         </is>
       </c>
       <c r="B380" s="18" t="n">
-        <v>3.343470790546604</v>
+        <v>2.227850675343217</v>
       </c>
       <c r="C380" s="18" t="n">
-        <v>0.7644174376741791</v>
+        <v>0.1778621678789783</v>
       </c>
       <c r="D380" s="18" t="n">
-        <v>14.62394285673415</v>
+        <v>27.90542075819289</v>
       </c>
       <c r="E380" s="18" t="n">
-        <v>0.1089007013777374</v>
+        <v>0.5345343965720899</v>
       </c>
     </row>
     <row r="381">
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="B381" s="18" t="n">
-        <v>2.254406466216466</v>
+        <v>1.479844528005039</v>
       </c>
       <c r="C381" s="18" t="n">
-        <v>1.102378435740078</v>
+        <v>0.5348540887333044</v>
       </c>
       <c r="D381" s="18" t="n">
-        <v>4.610348270742973</v>
+        <v>4.094462159301975</v>
       </c>
       <c r="E381" s="18" t="n">
-        <v>0.0259476670977792</v>
+        <v>0.4503549791478004</v>
       </c>
     </row>
     <row r="382">
@@ -8246,21 +8246,21 @@
       <c r="A383" s="18" t="inlineStr">
         <is>
           <t>{
-  "n": 2018,
-  "events": 75,
-  "coef_table_path": "/sessions/wonderful-trusting-babbage/mnt/THyroid 2026/data/m044/m044_cox_primary_with_rai_summary.csv",
+  "n": 2511,
+  "events": 178,
+  "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_with_rai_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 2.1448815550829625,
-    "hr_ci_low": 1.223313350048504,
-    "hr_ci_high": 3.76070193720415,
-    "p": 0.007733002062061849,
+    "hr": 0.6195366880806339,
+    "hr_ci_low": 0.2885784687778236,
+    "hr_ci_high": 1.3300566376399614,
+    "p": 0.2193486452707155,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 1.7561721454500336,
-    "hr_ci_low": 0.6191617969177373,
-    "hr_ci_high": 4.9811545541210736,
-    "p": 0.289733851232417,
+    "hr": 5.165307958844581,
+    "hr_ci_low": 0.6348162961236556,
+    "hr_ci_high": 42.028546640375005,
+    "p": 0.12475550364321643,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -8274,16 +8274,16 @@
         </is>
       </c>
       <c r="B384" s="18" t="n">
-        <v>2.144881555082963</v>
+        <v>0.6195366880806339</v>
       </c>
       <c r="C384" s="18" t="n">
-        <v>1.223313350048504</v>
+        <v>0.2885784687778236</v>
       </c>
       <c r="D384" s="18" t="n">
-        <v>3.76070193720415</v>
+        <v>1.330056637639961</v>
       </c>
       <c r="E384" s="18" t="n">
-        <v>0.0077330020620618</v>
+        <v>0.2193486452707155</v>
       </c>
     </row>
     <row r="385">
@@ -8293,16 +8293,16 @@
         </is>
       </c>
       <c r="B385" s="18" t="n">
-        <v>1.756172145450034</v>
+        <v>5.165307958844581</v>
       </c>
       <c r="C385" s="18" t="n">
-        <v>0.6191617969177373</v>
+        <v>0.6348162961236556</v>
       </c>
       <c r="D385" s="18" t="n">
-        <v>4.981154554121074</v>
+        <v>42.028546640375</v>
       </c>
       <c r="E385" s="18" t="n">
-        <v>0.289733851232417</v>
+        <v>0.1247555036432164</v>
       </c>
     </row>
     <row r="386">
@@ -8312,16 +8312,16 @@
         </is>
       </c>
       <c r="B386" s="18" t="n">
-        <v>1.17877590028441</v>
+        <v>0.7862597071903951</v>
       </c>
       <c r="C386" s="18" t="n">
-        <v>1.015244981136063</v>
+        <v>0.6238653960942784</v>
       </c>
       <c r="D386" s="18" t="n">
-        <v>1.368647616003432</v>
+        <v>0.9909258167248997</v>
       </c>
       <c r="E386" s="18" t="n">
-        <v>0.0308871739770638</v>
+        <v>0.0416310821738029</v>
       </c>
     </row>
     <row r="387">
@@ -8331,16 +8331,16 @@
         </is>
       </c>
       <c r="B387" s="18" t="n">
-        <v>1.351644613992799</v>
+        <v>1.797323120587958</v>
       </c>
       <c r="C387" s="18" t="n">
-        <v>0.822674961649924</v>
+        <v>0.8653448635461843</v>
       </c>
       <c r="D387" s="18" t="n">
-        <v>2.220735099159575</v>
+        <v>3.733043941073358</v>
       </c>
       <c r="E387" s="18" t="n">
-        <v>0.2342632235265654</v>
+        <v>0.1159160466304021</v>
       </c>
     </row>
     <row r="388">
@@ -8350,16 +8350,16 @@
         </is>
       </c>
       <c r="B388" s="18" t="n">
-        <v>1.044204056762613</v>
+        <v>1.068630419767369</v>
       </c>
       <c r="C388" s="18" t="n">
-        <v>0.9404854035297732</v>
+        <v>0.9630936387125496</v>
       </c>
       <c r="D388" s="18" t="n">
-        <v>1.159361015138797</v>
+        <v>1.185732028693238</v>
       </c>
       <c r="E388" s="18" t="n">
-        <v>0.4177166289184747</v>
+        <v>0.210877979077011</v>
       </c>
     </row>
     <row r="389">
@@ -8369,16 +8369,16 @@
         </is>
       </c>
       <c r="B389" s="18" t="n">
-        <v>0.8153820803804008</v>
+        <v>118.1323653991867</v>
       </c>
       <c r="C389" s="18" t="n">
-        <v>0.4469217868053021</v>
+        <v>12.10257479144966</v>
       </c>
       <c r="D389" s="18" t="n">
-        <v>1.487615857257606</v>
+        <v>1153.081554568554</v>
       </c>
       <c r="E389" s="18" t="n">
-        <v>0.5058601450053162</v>
+        <v>4.044786956070582e-05</v>
       </c>
     </row>
     <row r="390">
@@ -8388,16 +8388,16 @@
         </is>
       </c>
       <c r="B390" s="18" t="n">
-        <v>3.103797084173702</v>
+        <v>2.159390070958419e-100</v>
       </c>
       <c r="C390" s="18" t="n">
-        <v>1.123755759637267</v>
+        <v>1.636405075577344e-111</v>
       </c>
       <c r="D390" s="18" t="n">
-        <v>8.572642459990375</v>
+        <v>2.849517853584423e-89</v>
       </c>
       <c r="E390" s="18" t="n">
-        <v>0.0288847828622335</v>
+        <v>4.49095631820043e-69</v>
       </c>
     </row>
     <row r="391">
@@ -8407,16 +8407,16 @@
         </is>
       </c>
       <c r="B391" s="18" t="n">
-        <v>0.4795134452400518</v>
+        <v>0.5174942401844203</v>
       </c>
       <c r="C391" s="18" t="n">
-        <v>0.1064045541050051</v>
+        <v>1.00833663938705e-06</v>
       </c>
       <c r="D391" s="18" t="n">
-        <v>2.160933299331108</v>
+        <v>265586.1923125609</v>
       </c>
       <c r="E391" s="18" t="n">
-        <v>0.3386494524908222</v>
+        <v>0.9217757881419042</v>
       </c>
     </row>
     <row r="392">
@@ -8426,16 +8426,16 @@
         </is>
       </c>
       <c r="B392" s="18" t="n">
-        <v>0.2336321355555458</v>
+        <v>5.28000955338478</v>
       </c>
       <c r="C392" s="18" t="n">
-        <v>0.0662312278521124</v>
+        <v>1.734006595622719</v>
       </c>
       <c r="D392" s="18" t="n">
-        <v>0.8241425764614446</v>
+        <v>16.07750567628192</v>
       </c>
       <c r="E392" s="18" t="n">
-        <v>0.0237791434100633</v>
+        <v>0.0034023415240864</v>
       </c>
     </row>
     <row r="393">
@@ -8445,16 +8445,16 @@
         </is>
       </c>
       <c r="B393" s="18" t="n">
-        <v>0.0148850604299784</v>
+        <v>0.0007538458202525999</v>
       </c>
       <c r="C393" s="18" t="n">
-        <v>7.402660545770863e-40</v>
+        <v>7.87370023106309e-34</v>
       </c>
       <c r="D393" s="18" t="n">
-        <v>2.993045846613774e+35</v>
+        <v>7.217489922596581e+26</v>
       </c>
       <c r="E393" s="18" t="n">
-        <v>0.9235158846632326</v>
+        <v>0.8382422392940119</v>
       </c>
     </row>
     <row r="394">
@@ -8464,16 +8464,16 @@
         </is>
       </c>
       <c r="B394" s="18" t="n">
-        <v>3.41760281481349</v>
+        <v>0.2141299452268806</v>
       </c>
       <c r="C394" s="18" t="n">
-        <v>1.587604175234166</v>
+        <v>0.008271310808961501</v>
       </c>
       <c r="D394" s="18" t="n">
-        <v>7.357003201442403</v>
+        <v>5.543454296650193</v>
       </c>
       <c r="E394" s="18" t="n">
-        <v>0.0016804957078762</v>
+        <v>0.3532282666818117</v>
       </c>
     </row>
     <row r="395">
@@ -8483,16 +8483,16 @@
         </is>
       </c>
       <c r="B395" s="18" t="n">
-        <v>0.947832373839374</v>
+        <v>1879.319965286519</v>
       </c>
       <c r="C395" s="18" t="n">
-        <v>0.1868224435604146</v>
+        <v>708.118289554257</v>
       </c>
       <c r="D395" s="18" t="n">
-        <v>4.808770251457839</v>
+        <v>4987.646250667713</v>
       </c>
       <c r="E395" s="18" t="n">
-        <v>0.9484441605720668</v>
+        <v>9.092997502793388e-52</v>
       </c>
     </row>
     <row r="396">
@@ -8502,16 +8502,16 @@
         </is>
       </c>
       <c r="B396" s="18" t="n">
-        <v>1.538214247890503</v>
+        <v>1.503034356645002</v>
       </c>
       <c r="C396" s="18" t="n">
-        <v>0.938007178498022</v>
+        <v>0.9162695004306858</v>
       </c>
       <c r="D396" s="18" t="n">
-        <v>2.522478640517499</v>
+        <v>2.465554376952824</v>
       </c>
       <c r="E396" s="18" t="n">
-        <v>0.0879394102750914</v>
+        <v>0.1065977172144751</v>
       </c>
     </row>
     <row r="397">
@@ -8521,16 +8521,16 @@
         </is>
       </c>
       <c r="B397" s="18" t="n">
-        <v>1.728581031556823</v>
+        <v>0.09762202898769851</v>
       </c>
       <c r="C397" s="18" t="n">
-        <v>0.3783747100406025</v>
+        <v>0.0156870030163558</v>
       </c>
       <c r="D397" s="18" t="n">
-        <v>7.896913571040239</v>
+        <v>0.6075131453559768</v>
       </c>
       <c r="E397" s="18" t="n">
-        <v>0.4801246285767078</v>
+        <v>0.0126225496879036</v>
       </c>
     </row>
     <row r="398">
@@ -8540,16 +8540,16 @@
         </is>
       </c>
       <c r="B398" s="18" t="n">
-        <v>0.0169759177456617</v>
+        <v>3.183808411155286e-05</v>
       </c>
       <c r="C398" s="18" t="n">
-        <v>2.104095110674241e-21</v>
+        <v>8.276780346535801e-48</v>
       </c>
       <c r="D398" s="18" t="n">
-        <v>1.369623368475615e+17</v>
+        <v>1.224707624769307e+38</v>
       </c>
       <c r="E398" s="18" t="n">
-        <v>0.854402766556741</v>
+        <v>0.836029126257533</v>
       </c>
     </row>
     <row r="399">
@@ -8559,16 +8559,16 @@
         </is>
       </c>
       <c r="B399" s="18" t="n">
-        <v>0.7411259167422364</v>
+        <v>4.352903403823486</v>
       </c>
       <c r="C399" s="18" t="n">
-        <v>0.2164486557617133</v>
+        <v>2.086236680262511</v>
       </c>
       <c r="D399" s="18" t="n">
-        <v>2.537634722350527</v>
+        <v>9.082271547748787</v>
       </c>
       <c r="E399" s="18" t="n">
-        <v>0.6333184372976182</v>
+        <v>8.869250150454874e-05</v>
       </c>
     </row>
     <row r="400">
@@ -8578,16 +8578,16 @@
         </is>
       </c>
       <c r="B400" s="18" t="n">
-        <v>0.6626635950125541</v>
+        <v>1.256411627150506</v>
       </c>
       <c r="C400" s="18" t="n">
-        <v>0.3069980350935224</v>
+        <v>0.6555007012144456</v>
       </c>
       <c r="D400" s="18" t="n">
-        <v>1.430377363885049</v>
+        <v>2.408189913320256</v>
       </c>
       <c r="E400" s="18" t="n">
-        <v>0.2945531493272398</v>
+        <v>0.4916877121378405</v>
       </c>
     </row>
     <row r="401">
@@ -8597,16 +8597,16 @@
         </is>
       </c>
       <c r="B401" s="18" t="n">
-        <v>3.61448888220602</v>
+        <v>2.286425471636428</v>
       </c>
       <c r="C401" s="18" t="n">
-        <v>1.346833172214342</v>
+        <v>0.8913158978824999</v>
       </c>
       <c r="D401" s="18" t="n">
-        <v>9.700184216662407</v>
+        <v>5.865194876213264</v>
       </c>
       <c r="E401" s="18" t="n">
-        <v>0.0107375727030134</v>
+        <v>0.08532621888335901</v>
       </c>
     </row>
     <row r="402">
@@ -8616,16 +8616,16 @@
         </is>
       </c>
       <c r="B402" s="18" t="n">
-        <v>2.23915037115549</v>
+        <v>0.1766024486089431</v>
       </c>
       <c r="C402" s="18" t="n">
-        <v>0.945989067674685</v>
+        <v>0.0327714753260228</v>
       </c>
       <c r="D402" s="18" t="n">
-        <v>5.300055313503851</v>
+        <v>0.951694256801084</v>
       </c>
       <c r="E402" s="18" t="n">
-        <v>0.0667043809638897</v>
+        <v>0.0436352966560586</v>
       </c>
     </row>
     <row r="403">
@@ -8635,16 +8635,16 @@
         </is>
       </c>
       <c r="B403" s="18" t="n">
-        <v>3.090185909833739</v>
+        <v>0.0629578538984947</v>
       </c>
       <c r="C403" s="18" t="n">
-        <v>0.7041375675163155</v>
+        <v>1.631278642615491e-09</v>
       </c>
       <c r="D403" s="18" t="n">
-        <v>13.56162403181777</v>
+        <v>2429806.449956992</v>
       </c>
       <c r="E403" s="18" t="n">
-        <v>0.1348847104905889</v>
+        <v>0.7563607739507602</v>
       </c>
     </row>
     <row r="404">
@@ -8654,16 +8654,16 @@
         </is>
       </c>
       <c r="B404" s="18" t="n">
-        <v>2.270670195340033</v>
+        <v>0.521537506501187</v>
       </c>
       <c r="C404" s="18" t="n">
-        <v>1.107888128350439</v>
+        <v>0.1897718262966125</v>
       </c>
       <c r="D404" s="18" t="n">
-        <v>4.653848167578393</v>
+        <v>1.433307440812309</v>
       </c>
       <c r="E404" s="18" t="n">
-        <v>0.0251044927096119</v>
+        <v>0.2069289207676676</v>
       </c>
     </row>
   </sheetData>
@@ -8679,7 +8679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="70" customWidth="1" style="18" min="1" max="1"/>
@@ -8695,6 +8695,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="19">
       <c r="A3" s="22" t="inlineStr">
         <is>
@@ -9105,196 +9106,336 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="25"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>S4 pooled-LVI artifact check</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>OR pooled=1.5960394763510433 p=0.01732708403608204</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT QA: within ±0.5 ppt</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OR pooled=1.720509958843602 p=0.001948210925390039</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 5.35% expected 4.1% (n=318)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>OR pooled=1.5960394763510433 p=0.01732708403608204</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 11.34% expected 7.0% (n=344)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT QA: within ±0.5 ppt</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 3.73% expected 2.6% (n=268)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 11.61% expected 8.6% (n=336)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>OR pooled=1.5960394763510433 p=0.01732708403608204</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.51% expected 2.7% (n=712)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT QA: within ±0.5 ppt</t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.27% expected 2.3% (n=642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 1.69% expected 1.1% (n=947)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>OR pooled=1.5960394763510433 p=0.01732708403608204</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 6.69% expected 5.6% (n=269)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT QA: within ±0.5 ppt</t>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 18.18% expected 11.4% (n=44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 9.3% expected 7.0% (n=43)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>OR pooled=1.7980684439311188 p=0.004004853466394754</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT QA: within ±0.5 ppt</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 7.55% expected 3.8% (n=53)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>OR pooled=1.7980684439311188 p=0.004004853466394754</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>Strict-DTC Cox/KM inclusion flow</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT QA: within ±0.5 ppt</t>
-        </is>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>excluded_at_step</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>cum_excluded_from_cohort</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>path_proven_events_final_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4128</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>OR pooled=1.7980684439311188 p=0.004004853466394754</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
-        </is>
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Strict-DTC histology (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3789</v>
+      </c>
+      <c r="D44" t="n">
+        <v>339</v>
+      </c>
+      <c r="E44" t="n">
+        <v>339</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT QA: within ±0.5 ppt</t>
-        </is>
+      <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D45" t="n">
+        <v>33</v>
+      </c>
+      <c r="E45" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sex known female/male (same frame as primary logistic/Cox categoricals)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>372</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
+      <c r="A47" t="n">
+        <v>4</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OR pooled=1.7980684439311208 p=0.004004853466394623</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
-        </is>
+          <t>Positive analytic follow-up (followup_years &gt; 0)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1603</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT QA: within ±0.5 ppt</t>
-        </is>
+      <c r="A48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Known surgery date (CPM surg_first_date; mig_258/mig_254 lineage)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>6</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Finite positive Cox time_days (path-proven TTE if event else censor at FU×365.25)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2515</v>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tumor size known (cm; Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2511</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Age at surgery known (Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2511</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>9</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Final Cox PH + Kaplan–Meier rows (lifelines sample; aligns Figure 6)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2511</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1617</v>
+      </c>
+      <c r="F52" t="n">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -11047,16 +11188,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0141302155278802</v>
+        <v>0.04922383763851679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001068060180277024</v>
+        <v>0.008558428624978697</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1869398321848868</v>
+        <v>0.2831111057924016</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001226273475024953</v>
+        <v>0.0007416006127659506</v>
       </c>
     </row>
     <row r="5">
@@ -11066,16 +11207,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5689880035875429</v>
+        <v>0.6101636481989928</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03005726534141087</v>
+        <v>0.07575595587047168</v>
       </c>
       <c r="D5" t="n">
-        <v>10.77101807330757</v>
+        <v>4.914460827608937</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7070453614462651</v>
+        <v>0.6425530500487189</v>
       </c>
     </row>
     <row r="6">
@@ -11085,16 +11226,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4799986868471424</v>
+        <v>2.760569677045763</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001897303751580639</v>
+        <v>0.1496531861902959</v>
       </c>
       <c r="D6" t="n">
-        <v>121.4348199032636</v>
+        <v>50.9227042592609</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7948794393251364</v>
+        <v>0.4947450252775966</v>
       </c>
     </row>
     <row r="7">
@@ -11104,16 +11245,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6528464689608989</v>
+        <v>0.2889497250519529</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02841986932470973</v>
+        <v>0.0201071220311442</v>
       </c>
       <c r="D7" t="n">
-        <v>14.99684981535598</v>
+        <v>4.152356736000177</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7897371772286215</v>
+        <v>0.3612440745991894</v>
       </c>
     </row>
     <row r="8">
@@ -11123,16 +11264,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9999999999999976</v>
+        <v>0.9999999999999988</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2046645190177655</v>
+        <v>0.7463453472040671</v>
       </c>
     </row>
     <row r="9">
@@ -11142,16 +11283,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9161328106597633</v>
+        <v>0.9869548136095684</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6771543318825252</v>
+        <v>0.8140775973964304</v>
       </c>
       <c r="D9" t="n">
-        <v>1.239450576110265</v>
+        <v>1.196544171246554</v>
       </c>
       <c r="E9" t="n">
-        <v>0.570043804339301</v>
+        <v>0.8936812272882472</v>
       </c>
     </row>
     <row r="10">
@@ -11161,16 +11302,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.746920567150562</v>
+        <v>1.63226533864375</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5191680013353919</v>
+        <v>0.4313154498324233</v>
       </c>
       <c r="D10" t="n">
-        <v>14.53397085880913</v>
+        <v>6.177126594405416</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2345290624516252</v>
+        <v>0.4705611936807946</v>
       </c>
     </row>
     <row r="11">
@@ -11180,16 +11321,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.769593548838071</v>
+        <v>2.689750688613711</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7207462802354853</v>
+        <v>0.6788461432656692</v>
       </c>
       <c r="D11" t="n">
-        <v>31.56314953673447</v>
+        <v>10.65743517683444</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1051624795233538</v>
+        <v>0.1589728430816552</v>
       </c>
     </row>
     <row r="12">
@@ -11199,16 +11340,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11.56308962388756</v>
+        <v>4.729983405246534</v>
       </c>
       <c r="C12" t="n">
-        <v>1.588019908436881</v>
+        <v>0.9399959378094223</v>
       </c>
       <c r="D12" t="n">
-        <v>84.19607395329493</v>
+        <v>23.80089329539583</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01566868583656481</v>
+        <v>0.05944280025238249</v>
       </c>
     </row>
     <row r="13">
@@ -11218,16 +11359,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.088665125354509</v>
+        <v>1.099003722075374</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9371042249758984</v>
+        <v>0.9508170949000114</v>
       </c>
       <c r="D13" t="n">
-        <v>1.264738460861843</v>
+        <v>1.27028551296981</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2667118841834583</v>
+        <v>0.2014294484859358</v>
       </c>
     </row>
   </sheetData>
@@ -11966,7 +12107,7 @@
       </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
-          <t>Person-years</t>
+          <t>Person-years (FU&gt;0)</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
@@ -12000,37 +12141,37 @@
         <v>2576</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="E5" s="28" t="n">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="H5" s="28" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>3.61%</t>
         </is>
       </c>
       <c r="I5" s="28" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J5" s="28" t="n">
         <v>8137.3</v>
       </c>
       <c r="K5" s="28" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="L5" s="28" t="n">
         <v>1.78</v>
@@ -12054,37 +12195,37 @@
         <v>1266</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="D6" s="28" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>8.29%</t>
         </is>
       </c>
       <c r="E6" s="28" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>7.11%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="G6" s="28" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="H6" s="28" t="inlineStr">
         <is>
-          <t>12.88%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="I6" s="28" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>4138.3</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>1.76</v>
+        <v>2.49</v>
       </c>
       <c r="L6" s="28" t="n">
         <v>3.94</v>
@@ -12108,37 +12249,37 @@
         <v>192</v>
       </c>
       <c r="C7" s="28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>9.38%</t>
         </is>
       </c>
       <c r="E7" s="28" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>8.85%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>15.10%</t>
+          <t>9.90%</t>
         </is>
       </c>
       <c r="I7" s="28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7" s="28" t="n">
         <v>700.8</v>
       </c>
       <c r="K7" s="28" t="n">
-        <v>1.71</v>
+        <v>2.43</v>
       </c>
       <c r="L7" s="28" t="n">
         <v>4.14</v>
@@ -12263,7 +12404,7 @@
     <row r="11" ht="15" customHeight="1" s="19">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>Notes: Person-years use all follow-up time (incl zero-FU). Restricted to FU&gt;0 in Supp Table S3.</t>
+          <t>Notes: Col J sums follow-up years among patients with FU&gt;0 only (PY-rate denominator). Col K = 100 × (path-proven events among FU&gt;0) / col J. Path-proven n and Path-proven % include all patients (zero-FU retained in denominator for proportions).</t>
         </is>
       </c>
     </row>
@@ -12351,16 +12492,16 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>0.5206463545221203</v>
+        <v>0.6669255032178935</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>0.2208502401334555</v>
+        <v>0.3177659954934816</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>1.227404716940174</v>
+        <v>1.399739535225268</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>0.1357850626236052</v>
+        <v>0.2842080600304258</v>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
@@ -12375,16 +12516,16 @@
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>1.803142473049089</v>
+        <v>2.076021874744788</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>1.216513912993913</v>
+        <v>1.47858360953565</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>2.672655646092765</v>
+        <v>2.914861761366597</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>0.003324166076161661</v>
+        <v>2.458209087953318e-05</v>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
@@ -12399,16 +12540,16 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>0.9590876471583448</v>
+        <v>0.9342008179855855</v>
       </c>
       <c r="C7" s="28" t="n">
-        <v>0.855857777736727</v>
+        <v>0.84698924688341</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>1.074768657666727</v>
+        <v>1.030392264761622</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>0.472169331137781</v>
+        <v>0.1734490646119403</v>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
@@ -12423,16 +12564,16 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>1.415612656293561</v>
+        <v>1.243365865671108</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>0.9581423942358214</v>
+        <v>0.8826065421803896</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>2.091504566246435</v>
+        <v>1.751583069050145</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>0.08094065547071054</v>
+        <v>0.2128480394355131</v>
       </c>
       <c r="F8" s="28" t="n"/>
     </row>
@@ -12443,16 +12584,16 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>1.05396825090431</v>
+        <v>1.047101558155796</v>
       </c>
       <c r="C9" s="28" t="n">
-        <v>0.9751068751851638</v>
+        <v>0.9772115482993279</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>1.139207508616274</v>
+        <v>1.121990090068454</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>0.1852806869483926</v>
+        <v>0.1915859030131092</v>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
@@ -12467,16 +12608,16 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>0.9499944309815264</v>
+        <v>1.041542433253086</v>
       </c>
       <c r="C10" s="28" t="n">
-        <v>0.6030069709102068</v>
+        <v>0.7041041255179393</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>1.496648401151407</v>
+        <v>1.540696327363191</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>0.8249314914809625</v>
+        <v>0.8385463175879454</v>
       </c>
       <c r="F10" s="28" t="n"/>
     </row>
@@ -12487,16 +12628,16 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>4.064670487927986</v>
+        <v>5.589610780216073</v>
       </c>
       <c r="C11" s="28" t="n">
-        <v>1.916630062128165</v>
+        <v>2.888512518705153</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>8.620101761884987</v>
+        <v>10.81655297388619</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>0.0002560862557023006</v>
+        <v>3.235499429458743e-07</v>
       </c>
       <c r="F11" s="28" t="n"/>
     </row>
@@ -12507,16 +12648,16 @@
         </is>
       </c>
       <c r="B12" s="28" t="n">
-        <v>0.4032548237157987</v>
+        <v>0.4437282968749986</v>
       </c>
       <c r="C12" s="28" t="n">
-        <v>0.09349528866863414</v>
+        <v>0.1329051128210752</v>
       </c>
       <c r="D12" s="28" t="n">
-        <v>1.739279648907206</v>
+        <v>1.481468976386622</v>
       </c>
       <c r="E12" s="28" t="n">
-        <v>0.223298329848848</v>
+        <v>0.1865048194220119</v>
       </c>
       <c r="F12" s="28" t="n"/>
     </row>
@@ -12527,16 +12668,16 @@
         </is>
       </c>
       <c r="B13" s="28" t="n">
-        <v>1.000000000008999</v>
+        <v>1.000000000181017</v>
       </c>
       <c r="C13" s="28" t="n">
-        <v>0.9999999520573437</v>
+        <v>0.999999567207104</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>1.000000047960657</v>
+        <v>1.000000433155118</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>0.9997065048579439</v>
+        <v>0.9993461969791613</v>
       </c>
       <c r="F13" s="28" t="n"/>
     </row>
@@ -12547,16 +12688,16 @@
         </is>
       </c>
       <c r="B14" s="28" t="n">
-        <v>0.4025658212119982</v>
+        <v>0.5113539780108236</v>
       </c>
       <c r="C14" s="28" t="n">
-        <v>0.1790133646743275</v>
+        <v>0.2699812706456613</v>
       </c>
       <c r="D14" s="28" t="n">
-        <v>0.9052912932110907</v>
+        <v>0.9685223356500121</v>
       </c>
       <c r="E14" s="28" t="n">
-        <v>0.02776413268177263</v>
+        <v>0.03957954869899567</v>
       </c>
       <c r="F14" s="28" t="n"/>
     </row>
@@ -12567,16 +12708,16 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>9.263262405819614</v>
+        <v>8.57905103879509</v>
       </c>
       <c r="C15" s="28" t="n">
-        <v>4.810900420995365</v>
+        <v>4.741888142926279</v>
       </c>
       <c r="D15" s="28" t="n">
-        <v>17.83616846954348</v>
+        <v>15.52126800714273</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>2.75126119173499e-11</v>
+        <v>1.201350488743744e-12</v>
       </c>
       <c r="F15" s="28" t="n"/>
     </row>
@@ -12587,16 +12728,16 @@
         </is>
       </c>
       <c r="B16" s="28" t="n">
-        <v>1.865793604816147</v>
+        <v>1.715255922337146</v>
       </c>
       <c r="C16" s="28" t="n">
-        <v>0.5997323531271797</v>
+        <v>0.6113741691283806</v>
       </c>
       <c r="D16" s="28" t="n">
-        <v>5.804565582665188</v>
+        <v>4.812278679204144</v>
       </c>
       <c r="E16" s="28" t="n">
-        <v>0.2814594132836409</v>
+        <v>0.3053064560865795</v>
       </c>
       <c r="F16" s="28" t="n"/>
     </row>
@@ -12607,7 +12748,7 @@
         </is>
       </c>
       <c r="B17" s="28" t="n">
-        <v>8.234027685038964e-10</v>
+        <v>5.16727771697659e-10</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>1.388794386496402e-11</v>
@@ -12616,7 +12757,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>0.9992368963210904</v>
+        <v>0.9992030750468766</v>
       </c>
       <c r="F17" s="28" t="n"/>
     </row>
@@ -12627,16 +12768,16 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>0.8900578758120717</v>
+        <v>0.7384752852970617</v>
       </c>
       <c r="C18" s="28" t="n">
-        <v>0.4972517251809985</v>
+        <v>0.4452543797335514</v>
       </c>
       <c r="D18" s="28" t="n">
-        <v>1.593162943792175</v>
+        <v>1.224795918506005</v>
       </c>
       <c r="E18" s="28" t="n">
-        <v>0.6949870010775352</v>
+        <v>0.2402193969427563</v>
       </c>
       <c r="F18" s="28" t="n"/>
     </row>
@@ -12647,16 +12788,16 @@
         </is>
       </c>
       <c r="B19" s="28" t="n">
-        <v>2.471075365116653</v>
+        <v>1.757893717879382</v>
       </c>
       <c r="C19" s="28" t="n">
-        <v>0.9552563654630083</v>
+        <v>0.7279395352184567</v>
       </c>
       <c r="D19" s="28" t="n">
-        <v>6.392224831840555</v>
+        <v>4.245119510417058</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>0.06210208227991102</v>
+        <v>0.2098197201769865</v>
       </c>
       <c r="F19" s="28" t="n"/>
     </row>
@@ -12667,7 +12808,7 @@
         </is>
       </c>
       <c r="B20" s="28" t="n">
-        <v>1.149473450125798e-09</v>
+        <v>7.668397975541751e-10</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>1.388794386496402e-11</v>
@@ -12676,7 +12817,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>0.9994853005338252</v>
+        <v>0.999474226098751</v>
       </c>
       <c r="F20" s="28" t="n"/>
     </row>
@@ -12687,16 +12828,16 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>0.8994143043047927</v>
+        <v>0.6744064518387922</v>
       </c>
       <c r="C21" s="28" t="n">
-        <v>0.3327371250746836</v>
+        <v>0.2721746782092361</v>
       </c>
       <c r="D21" s="28" t="n">
-        <v>2.431186753226002</v>
+        <v>1.671074125169499</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>0.8344867055868811</v>
+        <v>0.3948394123437013</v>
       </c>
       <c r="F21" s="28" t="n"/>
     </row>
@@ -12707,16 +12848,16 @@
         </is>
       </c>
       <c r="B22" s="28" t="n">
-        <v>1.730704538765684</v>
+        <v>1.823942570144014</v>
       </c>
       <c r="C22" s="28" t="n">
-        <v>0.9825439306168026</v>
+        <v>1.112341481819554</v>
       </c>
       <c r="D22" s="28" t="n">
-        <v>3.048553970125065</v>
+        <v>2.990778060116638</v>
       </c>
       <c r="E22" s="28" t="n">
-        <v>0.05756478400617536</v>
+        <v>0.01722257193913048</v>
       </c>
       <c r="F22" s="28" t="n"/>
     </row>
@@ -12727,16 +12868,16 @@
         </is>
       </c>
       <c r="B23" s="28" t="n">
-        <v>2.295459213080084</v>
+        <v>2.39090079920365</v>
       </c>
       <c r="C23" s="28" t="n">
-        <v>1.149102116321473</v>
+        <v>1.317147438489974</v>
       </c>
       <c r="D23" s="28" t="n">
-        <v>4.585434944443309</v>
+        <v>4.339989939308657</v>
       </c>
       <c r="E23" s="28" t="n">
-        <v>0.01859114256048034</v>
+        <v>0.004162942684026138</v>
       </c>
       <c r="F23" s="28" t="n"/>
     </row>
@@ -12747,16 +12888,16 @@
         </is>
       </c>
       <c r="B24" s="28" t="n">
-        <v>2.426078408991356</v>
+        <v>2.788892715938317</v>
       </c>
       <c r="C24" s="28" t="n">
-        <v>1.060571024699771</v>
+        <v>1.376348027128713</v>
       </c>
       <c r="D24" s="28" t="n">
-        <v>5.549705120635568</v>
+        <v>5.651130693477159</v>
       </c>
       <c r="E24" s="28" t="n">
-        <v>0.03579426143389187</v>
+        <v>0.004420333345359666</v>
       </c>
       <c r="F24" s="28" t="n"/>
     </row>
@@ -12767,16 +12908,16 @@
         </is>
       </c>
       <c r="B25" s="18" t="n">
-        <v>1.12362744109839</v>
+        <v>1.304747414145783</v>
       </c>
       <c r="C25" s="18" t="n">
-        <v>0.2422511546911795</v>
+        <v>0.3606986337620886</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>5.211692914317758</v>
+        <v>4.719634773673588</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>0.8816355286876525</v>
+        <v>0.6851050284367951</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="19">
@@ -12793,16 +12934,16 @@
         </is>
       </c>
       <c r="B27" s="18" t="n">
-        <v>1.393944822862145</v>
+        <v>1.590964961232916</v>
       </c>
       <c r="C27" s="18" t="n">
-        <v>0.9410113793459456</v>
+        <v>1.134847190953743</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>2.06488700544166</v>
+        <v>2.23040558063471</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>0.0975811859505394</v>
+        <v>0.007063602444180204</v>
       </c>
     </row>
     <row r="28">
@@ -12812,16 +12953,16 @@
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>1.025049938589364</v>
+        <v>1.224487779211359</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.4683176194958099</v>
+        <v>0.6249861848359756</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>2.243621279364356</v>
+        <v>2.39904554343304</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>0.9506396590407828</v>
+        <v>0.5550575699205013</v>
       </c>
     </row>
     <row r="29">
@@ -12831,16 +12972,16 @@
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>1.399180970657792</v>
+        <v>1.588785874419103</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>0.931990309061838</v>
+        <v>1.117522728799781</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>2.100566250116434</v>
+        <v>2.258782295609063</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>0.1051856235318305</v>
+        <v>0.009911220692569871</v>
       </c>
     </row>
     <row r="30">
@@ -12850,16 +12991,16 @@
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>0.5247295914671026</v>
+        <v>0.6605652523227008</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>0.2195589178881915</v>
+        <v>0.3089484868535126</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>1.254064953542208</v>
+        <v>1.412359895399152</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>0.1468679320291499</v>
+        <v>0.2848553724927133</v>
       </c>
     </row>
     <row r="31">
@@ -12869,16 +13010,16 @@
         </is>
       </c>
       <c r="B31" s="18" t="n">
-        <v>4.045155914882562</v>
+        <v>4.413484571074677</v>
       </c>
       <c r="C31" s="18" t="n">
-        <v>2.780534009197913</v>
+        <v>3.192075222553084</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>5.884943799133611</v>
+        <v>6.102251576494701</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>2.739210328395703e-13</v>
+        <v>2.675251785808035e-19</v>
       </c>
     </row>
     <row r="32"/>
@@ -12890,7 +13031,7 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>LR χ²=6.30, df=6, p=0.3909</t>
+          <t>LR χ²=3.70, df=6, p=0.7177</t>
         </is>
       </c>
     </row>
@@ -12902,16 +13043,16 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>1.645676329408768</v>
+        <v>1.740487686615032</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>0.7230984843626904</v>
+        <v>0.8528797712492094</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>3.745341249834394</v>
+        <v>3.551845745879922</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.2351240171313305</v>
+        <v>0.127834089078729</v>
       </c>
     </row>
     <row r="36">
@@ -12921,16 +13062,16 @@
         </is>
       </c>
       <c r="B36" s="18" t="n">
-        <v>1.951285004489307</v>
+        <v>2.166171497313047</v>
       </c>
       <c r="C36" s="18" t="n">
-        <v>1.209914875495528</v>
+        <v>1.436352290195175</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>3.146926487026986</v>
+        <v>3.26681621758256</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.006118067426024094</v>
+        <v>0.0002265759946471743</v>
       </c>
     </row>
     <row r="37">
@@ -12940,16 +13081,16 @@
         </is>
       </c>
       <c r="B37" s="18" t="n">
-        <v>1.24120769382935</v>
+        <v>3.776898980170589</v>
       </c>
       <c r="C37" s="18" t="n">
-        <v>0.07204442242452236</v>
+        <v>0.5865487191236326</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>21.38398070766945</v>
+        <v>24.32017229144587</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>0.8817250858670661</v>
+        <v>0.1619577805270729</v>
       </c>
     </row>
     <row r="38">

--- a/M044_submission_package_v1_0/04_tables.xlsx
+++ b/M044_submission_package_v1_0/04_tables.xlsx
@@ -2273,12 +2273,12 @@
       <c r="A53" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 4028,
-  "n_events": 203,
-  "llf": -668.4548944332049,
-  "aic": 1380.9097888664098,
-  "pseudo_r2_mcfadden": 0.16924339565274382,
-  "lr_vs_null_chi2": 272.3579339184719,
+  "n_obs": 3963,
+  "n_events": 202,
+  "llf": -664.8694686549093,
+  "aic": 1373.7389373098185,
+  "pseudo_r2_mcfadden": 0.16717101382841393,
+  "lr_vs_null_chi2": 266.91410838023035,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + rai_received_flag + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "label": "full cohort sensitivity \u2014 includes non-DTC histologies (RAI covariate)"
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="B54" s="18" t="n">
-        <v>0.01820768988501063</v>
+        <v>0.01881692303623327</v>
       </c>
       <c r="C54" s="18" t="n">
-        <v>0.009912962075123204</v>
+        <v>0.01023808127512506</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>0.03344307871213138</v>
+        <v>0.03458427248588151</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>3.775467573871243e-38</v>
+        <v>1.772547926417216e-37</v>
       </c>
     </row>
     <row r="55">
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="B55" s="18" t="n">
-        <v>1.224487779211359</v>
+        <v>1.234036811889456</v>
       </c>
       <c r="C55" s="18" t="n">
-        <v>0.6249861848359756</v>
+        <v>0.6296290952169418</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>2.39904554343304</v>
+        <v>2.418641172504247</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.5550575699205013</v>
+        <v>0.5402052351946247</v>
       </c>
     </row>
     <row r="56">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="B56" s="18" t="n">
-        <v>1.590964961232916</v>
+        <v>1.605347833573521</v>
       </c>
       <c r="C56" s="18" t="n">
-        <v>1.134847190953743</v>
+        <v>1.144503489899247</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>2.23040558063471</v>
+        <v>2.251755184238075</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>0.007063602444180204</v>
+        <v>0.006110978617229343</v>
       </c>
     </row>
     <row r="57">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B57" s="18" t="n">
-        <v>1.285465042605963</v>
+        <v>1.30074903442832</v>
       </c>
       <c r="C57" s="18" t="n">
-        <v>0.9203333460739046</v>
+        <v>0.9308559060649149</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>1.795458550764341</v>
+        <v>1.817626164847276</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>0.140751701646049</v>
+        <v>0.1234997267822623</v>
       </c>
     </row>
     <row r="58">
@@ -2373,16 +2373,16 @@
         </is>
       </c>
       <c r="B58" s="18" t="n">
-        <v>1.246981532406513</v>
+        <v>1.230139271573314</v>
       </c>
       <c r="C58" s="18" t="n">
-        <v>0.8471999299335975</v>
+        <v>0.8353077310506075</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1.83541438947566</v>
+        <v>1.81159897270871</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>0.2630612138995111</v>
+        <v>0.2942819158437429</v>
       </c>
     </row>
     <row r="59">
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B59" s="18" t="n">
-        <v>5.235949933040403</v>
+        <v>5.185237994209519</v>
       </c>
       <c r="C59" s="18" t="n">
-        <v>2.713948858097169</v>
+        <v>2.689349157916357</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>10.1015800719721</v>
+        <v>9.997472056557029</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>7.902637423371317e-07</v>
+        <v>8.950254840615399e-07</v>
       </c>
     </row>
     <row r="60">
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="B60" s="18" t="n">
-        <v>0.4856241442953312</v>
+        <v>0.4818062924969674</v>
       </c>
       <c r="C60" s="18" t="n">
-        <v>0.1440922993926894</v>
+        <v>0.1429702388002312</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>1.636664905179087</v>
+        <v>1.623675706480655</v>
       </c>
       <c r="E60" s="18" t="n">
-        <v>0.243929361824139</v>
+        <v>0.2387859210607071</v>
       </c>
     </row>
     <row r="61">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B61" s="18" t="n">
-        <v>2.087527512272552e-09</v>
+        <v>1.275475206682042e-09</v>
       </c>
       <c r="C61" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2439,7 +2439,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>0.9988791109878108</v>
+        <v>0.9992146353933082</v>
       </c>
     </row>
     <row r="62">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B62" s="18" t="n">
-        <v>0.6797721604528594</v>
+        <v>0.6703448943879612</v>
       </c>
       <c r="C62" s="18" t="n">
-        <v>0.3781808465470493</v>
+        <v>0.3661342037083442</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>1.221876238169718</v>
+        <v>1.22731575712047</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0.196988782715572</v>
+        <v>0.19491739581879</v>
       </c>
     </row>
     <row r="63">
@@ -2468,16 +2468,16 @@
         </is>
       </c>
       <c r="B63" s="18" t="n">
-        <v>1.802192782210647</v>
+        <v>1.778439644995289</v>
       </c>
       <c r="C63" s="18" t="n">
-        <v>0.8581125686501837</v>
+        <v>0.8471264195793732</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>3.784933286038587</v>
+        <v>3.733619325037023</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.1197602232866131</v>
+        <v>0.1281294442203</v>
       </c>
     </row>
     <row r="64">
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="B64" s="18" t="n">
-        <v>3.319979904968426</v>
+        <v>3.333027731194698</v>
       </c>
       <c r="C64" s="18" t="n">
-        <v>1.984907808615645</v>
+        <v>1.991611142896396</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>5.553037033534335</v>
+        <v>5.577933170607278</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>4.826342779005567e-06</v>
+        <v>4.600306701175059e-06</v>
       </c>
     </row>
     <row r="65">
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="B65" s="18" t="n">
-        <v>0.6883312598936068</v>
+        <v>0.6877617653898112</v>
       </c>
       <c r="C65" s="18" t="n">
-        <v>0.4232788864596663</v>
+        <v>0.4227728699706244</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>1.119356382997544</v>
+        <v>1.118842479095161</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>0.1322037264095022</v>
+        <v>0.1316410384497489</v>
       </c>
     </row>
     <row r="66">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B66" s="18" t="n">
-        <v>1.474355572683133</v>
+        <v>1.468070655857398</v>
       </c>
       <c r="C66" s="18" t="n">
-        <v>0.6089309908457249</v>
+        <v>0.6064738063648494</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>3.569738422547343</v>
+        <v>3.55370904393685</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>0.3895236467276599</v>
+        <v>0.3946399821179301</v>
       </c>
     </row>
     <row r="67">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B67" s="18" t="n">
-        <v>1.519426391063587e-09</v>
+        <v>1.500093204321947e-09</v>
       </c>
       <c r="C67" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2553,7 +2553,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.9994983792860411</v>
+        <v>0.9994978399243757</v>
       </c>
     </row>
     <row r="68">
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="B68" s="18" t="n">
-        <v>0.7729909728052788</v>
+        <v>0.7778941343935867</v>
       </c>
       <c r="C68" s="18" t="n">
-        <v>0.3310228843539463</v>
+        <v>0.3328212674043152</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>1.805056605692428</v>
+        <v>1.8181508923492</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>0.5517965668261866</v>
+        <v>0.5620235742756428</v>
       </c>
     </row>
     <row r="69">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="B69" s="18" t="n">
-        <v>1.767254545007356</v>
+        <v>1.77562931311392</v>
       </c>
       <c r="C69" s="18" t="n">
-        <v>1.097064020587842</v>
+        <v>1.101148072875106</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>2.846860865217009</v>
+        <v>2.863247491645033</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>0.0192438176112148</v>
+        <v>0.01851225008280269</v>
       </c>
     </row>
     <row r="70">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="B70" s="18" t="n">
-        <v>1.895292977177866</v>
+        <v>1.91641428573758</v>
       </c>
       <c r="C70" s="18" t="n">
-        <v>1.066053509139101</v>
+        <v>1.075665388581756</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>3.369563946410716</v>
+        <v>3.414299422073429</v>
       </c>
       <c r="E70" s="18" t="n">
-        <v>0.0294181865662252</v>
+        <v>0.02727883903234741</v>
       </c>
     </row>
     <row r="71">
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="B71" s="18" t="n">
-        <v>1.889931828279741</v>
+        <v>1.90470910031505</v>
       </c>
       <c r="C71" s="18" t="n">
-        <v>0.9813552951043095</v>
+        <v>0.9868548096287644</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>3.639703513461096</v>
+        <v>3.676241653205013</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>0.05695218216704147</v>
+        <v>0.05479188168837221</v>
       </c>
     </row>
     <row r="72">
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="B72" s="18" t="n">
-        <v>1.175760709576873</v>
+        <v>1.178180598970277</v>
       </c>
       <c r="C72" s="18" t="n">
-        <v>0.3201459619406088</v>
+        <v>0.3209764511859936</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>4.318071787646562</v>
+        <v>4.324645994000363</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>0.8072723661594022</v>
+        <v>0.8047955297569923</v>
       </c>
     </row>
     <row r="73">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B73" s="18" t="n">
-        <v>0.9373124632003611</v>
+        <v>0.9334958671328363</v>
       </c>
       <c r="C73" s="18" t="n">
-        <v>0.8513049699952649</v>
+        <v>0.8475742387320844</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>1.032009308809292</v>
+        <v>1.028127677945551</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0.1873899203736279</v>
+        <v>0.1624428836647294</v>
       </c>
     </row>
     <row r="74">
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="B74" s="18" t="n">
-        <v>1.061823647341721</v>
+        <v>1.059716424637732</v>
       </c>
       <c r="C74" s="18" t="n">
-        <v>0.9914338598591365</v>
+        <v>0.9891913739424952</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>1.137210966563384</v>
+        <v>1.135269605284955</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>0.08650398849992604</v>
+        <v>0.09880338997329706</v>
       </c>
     </row>
     <row r="75">
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="B75" s="18" t="n">
-        <v>4.741474162290238</v>
+        <v>4.648297307741951</v>
       </c>
       <c r="C75" s="18" t="n">
-        <v>3.458823434089347</v>
+        <v>3.388276890214176</v>
       </c>
       <c r="D75" s="18" t="n">
-        <v>6.499775909372186</v>
+        <v>6.376889658446803</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>4.009029942074579e-22</v>
+        <v>1.65661107990849e-21</v>
       </c>
     </row>
     <row r="76">
@@ -7385,13 +7385,13 @@
       <c r="A334" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 192,
+  "n_obs": 190,
   "n_events": 19,
-  "llf": -44.26887111171082,
-  "aic": 110.53774222342165,
-  "pseudo_r2_mcfadden": 0.2857016703325118,
-  "lr_vs_null_chi2": 35.41290773069025,
-  "lr_vs_null_pvalue": 0.00010613916145962854,
+  "llf": -44.268871112647304,
+  "aic": 110.53774222529461,
+  "pseudo_r2_mcfadden": 0.2832781856985851,
+  "lr_vs_null_chi2": 34.993787663455734,
+  "lr_vs_null_pvalue": 0.0001251704165162737,
   "events": 19,
   "formula": "y_comp ~ tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + central_pos_flag + lateral_pos_flag + rai_received_flag + ge2 + days_per_100"
 }</t>
@@ -7405,16 +7405,16 @@
         </is>
       </c>
       <c r="B335" s="18" t="n">
-        <v>0.02411789512997224</v>
+        <v>0.02411789512997222</v>
       </c>
       <c r="C335" s="18" t="n">
-        <v>0.003095426568018558</v>
+        <v>0.003095426568054629</v>
       </c>
       <c r="D335" s="18" t="n">
-        <v>0.187913637335186</v>
+        <v>0.1879136373329959</v>
       </c>
       <c r="E335" s="18" t="n">
-        <v>0.0003766088038290857</v>
+        <v>0.0003766088038001654</v>
       </c>
     </row>
     <row r="336">
@@ -7424,16 +7424,16 @@
         </is>
       </c>
       <c r="B336" s="18" t="n">
-        <v>0.8040871828013445</v>
+        <v>0.8040871828013403</v>
       </c>
       <c r="C336" s="18" t="n">
-        <v>0.08807263284511103</v>
+        <v>0.08807263284518131</v>
       </c>
       <c r="D336" s="18" t="n">
-        <v>7.341170312036306</v>
+        <v>7.34117031203037</v>
       </c>
       <c r="E336" s="18" t="n">
-        <v>0.8467687891007277</v>
+        <v>0.8467687891006692</v>
       </c>
     </row>
     <row r="337">
@@ -7443,16 +7443,16 @@
         </is>
       </c>
       <c r="B337" s="18" t="n">
-        <v>1.215463783755382</v>
+        <v>1.215463783755397</v>
       </c>
       <c r="C337" s="18" t="n">
-        <v>0.05425189302773018</v>
+        <v>0.05425189302784397</v>
       </c>
       <c r="D337" s="18" t="n">
-        <v>27.23134857000878</v>
+        <v>27.23134856995235</v>
       </c>
       <c r="E337" s="18" t="n">
-        <v>0.9021064666247514</v>
+        <v>0.90210646662468</v>
       </c>
     </row>
     <row r="338">
@@ -7462,16 +7462,16 @@
         </is>
       </c>
       <c r="B338" s="18" t="n">
-        <v>1.094107558560965</v>
+        <v>1.094107558560973</v>
       </c>
       <c r="C338" s="18" t="n">
-        <v>0.1059296698753412</v>
+        <v>0.1059296698756102</v>
       </c>
       <c r="D338" s="18" t="n">
-        <v>11.30062381114711</v>
+        <v>11.3006238111186</v>
       </c>
       <c r="E338" s="18" t="n">
-        <v>0.9398200139471643</v>
+        <v>0.9398200139470939</v>
       </c>
     </row>
     <row r="339">
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="B339" s="18" t="n">
-        <v>3.674513475945357e-09</v>
+        <v>7.731246178897265e-09</v>
       </c>
       <c r="C339" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -7490,7 +7490,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E339" s="18" t="n">
-        <v>0.9991500083918476</v>
+        <v>0.9988893345361833</v>
       </c>
     </row>
     <row r="340">
@@ -7500,16 +7500,16 @@
         </is>
       </c>
       <c r="B340" s="18" t="n">
-        <v>0.9516299292814673</v>
+        <v>0.9516299292814678</v>
       </c>
       <c r="C340" s="18" t="n">
-        <v>0.7675933343346527</v>
+        <v>0.7675933343348874</v>
       </c>
       <c r="D340" s="18" t="n">
-        <v>1.179790758721506</v>
+        <v>1.179790758721146</v>
       </c>
       <c r="E340" s="18" t="n">
-        <v>0.6511648987738741</v>
+        <v>0.6511648987734149</v>
       </c>
     </row>
     <row r="341">
@@ -7519,16 +7519,16 @@
         </is>
       </c>
       <c r="B341" s="18" t="n">
-        <v>1.376884772637383</v>
+        <v>1.376884772637402</v>
       </c>
       <c r="C341" s="18" t="n">
-        <v>0.357345754615485</v>
+        <v>0.3573457546158765</v>
       </c>
       <c r="D341" s="18" t="n">
-        <v>5.305258709903101</v>
+        <v>5.305258709897432</v>
       </c>
       <c r="E341" s="18" t="n">
-        <v>0.6421354769371461</v>
+        <v>0.642135476936865</v>
       </c>
     </row>
     <row r="342">
@@ -7538,16 +7538,16 @@
         </is>
       </c>
       <c r="B342" s="18" t="n">
-        <v>2.524185711263298</v>
+        <v>2.524185711263305</v>
       </c>
       <c r="C342" s="18" t="n">
-        <v>0.6101216624634135</v>
+        <v>0.6101216624634787</v>
       </c>
       <c r="D342" s="18" t="n">
-        <v>10.44302128073985</v>
+        <v>10.44302128073879</v>
       </c>
       <c r="E342" s="18" t="n">
-        <v>0.2012525917948234</v>
+        <v>0.2012525917947889</v>
       </c>
     </row>
     <row r="343">
@@ -7557,16 +7557,16 @@
         </is>
       </c>
       <c r="B343" s="18" t="n">
-        <v>8.843888533396331</v>
+        <v>8.843888533396296</v>
       </c>
       <c r="C343" s="18" t="n">
-        <v>2.771343352101149</v>
+        <v>2.771343352277366</v>
       </c>
       <c r="D343" s="18" t="n">
-        <v>28.22254569497472</v>
+        <v>28.22254569317995</v>
       </c>
       <c r="E343" s="18" t="n">
-        <v>0.0002317142156747089</v>
+        <v>0.0002317142154913127</v>
       </c>
     </row>
     <row r="344">
@@ -7576,16 +7576,16 @@
         </is>
       </c>
       <c r="B344" s="18" t="n">
-        <v>3.308184753372749</v>
+        <v>3.308184753372745</v>
       </c>
       <c r="C344" s="18" t="n">
-        <v>0.6587459583166945</v>
+        <v>0.6587459583168344</v>
       </c>
       <c r="D344" s="18" t="n">
-        <v>16.61351576321401</v>
+        <v>16.61351576321043</v>
       </c>
       <c r="E344" s="18" t="n">
-        <v>0.1462195968306</v>
+        <v>0.1462195968305471</v>
       </c>
     </row>
     <row r="345">
@@ -7598,13 +7598,13 @@
         <v>1.088031671121559</v>
       </c>
       <c r="C345" s="18" t="n">
-        <v>0.9466969428212387</v>
+        <v>0.9466969428213032</v>
       </c>
       <c r="D345" s="18" t="n">
-        <v>1.250466610608996</v>
+        <v>1.25046661060891</v>
       </c>
       <c r="E345" s="18" t="n">
-        <v>0.2346731667026427</v>
+        <v>0.2346731667024146</v>
       </c>
     </row>
     <row r="346"/>
@@ -7838,17 +7838,17 @@
   "events": 178,
   "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 0.9102808635560813,
-    "hr_ci_low": 0.47913333888681914,
-    "hr_ci_high": 1.7293959390960676,
-    "p": 0.7740508906797761,
+    "hr": 0.9103037356162789,
+    "hr_ci_low": 0.47923951497127887,
+    "hr_ci_high": 1.729099678115261,
+    "p": 0.7740423569506414,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 2.443225068198415,
-    "hr_ci_low": 0.6478494195146004,
-    "hr_ci_high": 9.214099070036475,
-    "p": 0.18716625998772768,
+    "hr": 2.443341372260798,
+    "hr_ci_low": 0.6480998157458978,
+    "hr_ci_high": 9.21141607567116,
+    "p": 0.18703020836101486,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -7862,16 +7862,16 @@
         </is>
       </c>
       <c r="B362" s="18" t="n">
-        <v>0.9102808635560812</v>
+        <v>0.9103037356162788</v>
       </c>
       <c r="C362" s="18" t="n">
-        <v>0.4791333388868191</v>
+        <v>0.4792395149712788</v>
       </c>
       <c r="D362" s="18" t="n">
-        <v>1.729395939096068</v>
+        <v>1.729099678115261</v>
       </c>
       <c r="E362" s="18" t="n">
-        <v>0.7740508906797761</v>
+        <v>0.7740423569506414</v>
       </c>
     </row>
     <row r="363">
@@ -7881,16 +7881,16 @@
         </is>
       </c>
       <c r="B363" s="18" t="n">
-        <v>2.443225068198415</v>
+        <v>2.443341372260798</v>
       </c>
       <c r="C363" s="18" t="n">
-        <v>0.6478494195146004</v>
+        <v>0.6480998157458978</v>
       </c>
       <c r="D363" s="18" t="n">
-        <v>9.214099070036475</v>
+        <v>9.21141607567116</v>
       </c>
       <c r="E363" s="18" t="n">
-        <v>0.1871662599877276</v>
+        <v>0.1870302083610148</v>
       </c>
     </row>
     <row r="364">
@@ -7900,16 +7900,16 @@
         </is>
       </c>
       <c r="B364" s="18" t="n">
-        <v>0.936808739475723</v>
+        <v>0.936808656010379</v>
       </c>
       <c r="C364" s="18" t="n">
-        <v>0.7873212832297154</v>
+        <v>0.7873572846824738</v>
       </c>
       <c r="D364" s="18" t="n">
-        <v>1.114679144399598</v>
+        <v>1.114627977729191</v>
       </c>
       <c r="E364" s="18" t="n">
-        <v>0.4617635228405863</v>
+        <v>0.4616448505866697</v>
       </c>
     </row>
     <row r="365">
@@ -7919,16 +7919,16 @@
         </is>
       </c>
       <c r="B365" s="18" t="n">
-        <v>1.292591248233988</v>
+        <v>1.292464933823215</v>
       </c>
       <c r="C365" s="18" t="n">
-        <v>0.7674327357304391</v>
+        <v>0.7674325569331557</v>
       </c>
       <c r="D365" s="18" t="n">
-        <v>2.177118667502301</v>
+        <v>2.176693691284387</v>
       </c>
       <c r="E365" s="18" t="n">
-        <v>0.3346248968410373</v>
+        <v>0.3347185829241387</v>
       </c>
     </row>
     <row r="366">
@@ -7938,16 +7938,16 @@
         </is>
       </c>
       <c r="B366" s="18" t="n">
-        <v>0.9684720408602407</v>
+        <v>0.9684746094521792</v>
       </c>
       <c r="C366" s="18" t="n">
-        <v>0.8403166642816156</v>
+        <v>0.8403511120544364</v>
       </c>
       <c r="D366" s="18" t="n">
-        <v>1.116172192931388</v>
+        <v>1.116132359080871</v>
       </c>
       <c r="E366" s="18" t="n">
-        <v>0.658229676744901</v>
+        <v>0.6581697063897802</v>
       </c>
     </row>
     <row r="367">
@@ -7957,16 +7957,16 @@
         </is>
       </c>
       <c r="B367" s="18" t="n">
-        <v>0.6913177685676808</v>
+        <v>0.6912735971194832</v>
       </c>
       <c r="C367" s="18" t="n">
-        <v>0.3652127171363888</v>
+        <v>0.3652516338182929</v>
       </c>
       <c r="D367" s="18" t="n">
-        <v>1.308607928236294</v>
+        <v>1.308301296503542</v>
       </c>
       <c r="E367" s="18" t="n">
-        <v>0.2568575144361521</v>
+        <v>0.2566481166469044</v>
       </c>
     </row>
     <row r="368">
@@ -7976,16 +7976,16 @@
         </is>
       </c>
       <c r="B368" s="18" t="n">
-        <v>1.669305268165391e-120</v>
+        <v>1.735444020336766e-120</v>
       </c>
       <c r="C368" s="18" t="n">
-        <v>1.265014436368057e-131</v>
+        <v>1.315134973274594e-131</v>
       </c>
       <c r="D368" s="18" t="n">
-        <v>2.202804962704766e-109</v>
+        <v>2.290081253199094e-109</v>
       </c>
       <c r="E368" s="18" t="n">
-        <v>6.351843715822425e-99</v>
+        <v>6.764359580967242e-99</v>
       </c>
     </row>
     <row r="369">
@@ -7995,16 +7995,16 @@
         </is>
       </c>
       <c r="B369" s="18" t="n">
-        <v>0.0926611428602198</v>
+        <v>0.0926517228106373</v>
       </c>
       <c r="C369" s="18" t="n">
-        <v>0.0025158197320641</v>
+        <v>0.0025175244798904</v>
       </c>
       <c r="D369" s="18" t="n">
-        <v>3.412838879802226</v>
+        <v>3.409834465702075</v>
       </c>
       <c r="E369" s="18" t="n">
-        <v>0.1960721582196949</v>
+        <v>0.195956430476354</v>
       </c>
     </row>
     <row r="370">
@@ -8014,16 +8014,16 @@
         </is>
       </c>
       <c r="B370" s="18" t="n">
-        <v>0.8226508028771761</v>
+        <v>0.8224286004197328</v>
       </c>
       <c r="C370" s="18" t="n">
-        <v>0.3030914664962339</v>
+        <v>0.3030537526080663</v>
       </c>
       <c r="D370" s="18" t="n">
-        <v>2.232838658566692</v>
+        <v>2.231910335930145</v>
       </c>
       <c r="E370" s="18" t="n">
-        <v>0.7015663976844336</v>
+        <v>0.7011317863804092</v>
       </c>
     </row>
     <row r="371">
@@ -8033,16 +8033,16 @@
         </is>
       </c>
       <c r="B371" s="18" t="n">
-        <v>0.0009814849519229</v>
+        <v>0.0009815781044031999</v>
       </c>
       <c r="C371" s="18" t="n">
-        <v>1.593797932419506e-33</v>
+        <v>1.596000780572613e-33</v>
       </c>
       <c r="D371" s="18" t="n">
-        <v>6.044133269697347e+26</v>
+        <v>6.036936740709404e+26</v>
       </c>
       <c r="E371" s="18" t="n">
-        <v>0.8431110258271137</v>
+        <v>0.8431102437330177</v>
       </c>
     </row>
     <row r="372">
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="B372" s="18" t="n">
-        <v>4.525643291271133</v>
+        <v>4.524320048617943</v>
       </c>
       <c r="C372" s="18" t="n">
-        <v>1.182715803554595</v>
+        <v>1.18278999739249</v>
       </c>
       <c r="D372" s="18" t="n">
-        <v>17.31730238005733</v>
+        <v>17.30609148492299</v>
       </c>
       <c r="E372" s="18" t="n">
-        <v>0.0274497615896922</v>
+        <v>0.0274387810476094</v>
       </c>
     </row>
     <row r="373">
@@ -8071,16 +8071,16 @@
         </is>
       </c>
       <c r="B373" s="18" t="n">
-        <v>82.59421045665907</v>
+        <v>82.52812661832206</v>
       </c>
       <c r="C373" s="18" t="n">
-        <v>36.94479353587479</v>
+        <v>36.92243205135421</v>
       </c>
       <c r="D373" s="18" t="n">
-        <v>184.6485782721904</v>
+        <v>184.4648714812922</v>
       </c>
       <c r="E373" s="18" t="n">
-        <v>5.719938258257363e-27</v>
+        <v>5.679377375479022e-27</v>
       </c>
     </row>
     <row r="374">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="B374" s="18" t="n">
-        <v>168.1113399897766</v>
+        <v>167.9575168918756</v>
       </c>
       <c r="C374" s="18" t="n">
-        <v>65.31641294157042</v>
+        <v>65.27575447295933</v>
       </c>
       <c r="D374" s="18" t="n">
-        <v>432.6848545470469</v>
+        <v>432.1624117293142</v>
       </c>
       <c r="E374" s="18" t="n">
-        <v>2.296010445246175e-26</v>
+        <v>2.26199839463582e-26</v>
       </c>
     </row>
     <row r="375">
@@ -8109,16 +8109,16 @@
         </is>
       </c>
       <c r="B375" s="18" t="n">
-        <v>6.799822934266519e-05</v>
+        <v>6.800892356123554e-05</v>
       </c>
       <c r="C375" s="18" t="n">
-        <v>2.377172731334699e-47</v>
+        <v>2.378212457213654e-47</v>
       </c>
       <c r="D375" s="18" t="n">
-        <v>1.945066562807834e+38</v>
+        <v>1.94482779279398e+38</v>
       </c>
       <c r="E375" s="18" t="n">
-        <v>0.8474374497066779</v>
+        <v>0.8474394875745951</v>
       </c>
     </row>
     <row r="376">
@@ -8128,16 +8128,16 @@
         </is>
       </c>
       <c r="B376" s="18" t="n">
-        <v>0.3712996489567189</v>
+        <v>0.3712374815082589</v>
       </c>
       <c r="C376" s="18" t="n">
-        <v>0.0250670217806946</v>
+        <v>0.0250800268175174</v>
       </c>
       <c r="D376" s="18" t="n">
-        <v>5.499792935974478</v>
+        <v>5.495100490894795</v>
       </c>
       <c r="E376" s="18" t="n">
-        <v>0.4712743001833367</v>
+        <v>0.4710864563016359</v>
       </c>
     </row>
     <row r="377">
@@ -8147,16 +8147,16 @@
         </is>
       </c>
       <c r="B377" s="18" t="n">
-        <v>0.2729965144346066</v>
+        <v>0.2729954301672874</v>
       </c>
       <c r="C377" s="18" t="n">
-        <v>0.0591620977775801</v>
+        <v>0.0591887523669318</v>
       </c>
       <c r="D377" s="18" t="n">
-        <v>1.259710180893667</v>
+        <v>1.259132891164969</v>
       </c>
       <c r="E377" s="18" t="n">
-        <v>0.096104351105412</v>
+        <v>0.0960045354923339</v>
       </c>
     </row>
     <row r="378">
@@ -8166,16 +8166,16 @@
         </is>
       </c>
       <c r="B378" s="18" t="n">
-        <v>1.838452428514997</v>
+        <v>1.838518534199694</v>
       </c>
       <c r="C378" s="18" t="n">
-        <v>0.6299890245754654</v>
+        <v>0.6301882818520425</v>
       </c>
       <c r="D378" s="18" t="n">
-        <v>5.365025738647318</v>
+        <v>5.363715095847168</v>
       </c>
       <c r="E378" s="18" t="n">
-        <v>0.2651185955914953</v>
+        <v>0.2649653065047122</v>
       </c>
     </row>
     <row r="379">
@@ -8185,16 +8185,16 @@
         </is>
       </c>
       <c r="B379" s="18" t="n">
-        <v>0.7805127177967276</v>
+        <v>0.7805629636388375</v>
       </c>
       <c r="C379" s="18" t="n">
-        <v>0.2417986199502257</v>
+        <v>0.2418644301979245</v>
       </c>
       <c r="D379" s="18" t="n">
-        <v>2.519452355715835</v>
+        <v>2.519091127645579</v>
       </c>
       <c r="E379" s="18" t="n">
-        <v>0.6785346416122111</v>
+        <v>0.6785596777827072</v>
       </c>
     </row>
     <row r="380">
@@ -8204,16 +8204,16 @@
         </is>
       </c>
       <c r="B380" s="18" t="n">
-        <v>2.227850675343217</v>
+        <v>2.227525371486014</v>
       </c>
       <c r="C380" s="18" t="n">
-        <v>0.1778621678789783</v>
+        <v>0.1779417025391863</v>
       </c>
       <c r="D380" s="18" t="n">
-        <v>27.90542075819289</v>
+        <v>27.88480277421873</v>
       </c>
       <c r="E380" s="18" t="n">
-        <v>0.5345343965720899</v>
+        <v>0.534513006589991</v>
       </c>
     </row>
     <row r="381">
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="B381" s="18" t="n">
-        <v>1.479844528005039</v>
+        <v>1.479952097268279</v>
       </c>
       <c r="C381" s="18" t="n">
-        <v>0.5348540887333044</v>
+        <v>0.5350423956356825</v>
       </c>
       <c r="D381" s="18" t="n">
-        <v>4.094462159301975</v>
+        <v>4.093616184576434</v>
       </c>
       <c r="E381" s="18" t="n">
-        <v>0.4503549791478004</v>
+        <v>0.4501466216197959</v>
       </c>
     </row>
     <row r="382">
@@ -8250,17 +8250,17 @@
   "events": 178,
   "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_with_rai_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 0.6195366880806339,
-    "hr_ci_low": 0.2885784687778236,
-    "hr_ci_high": 1.3300566376399614,
-    "p": 0.2193486452707155,
+    "hr": 0.6195679029743909,
+    "hr_ci_low": 0.2887910192490381,
+    "hr_ci_high": 1.3292116472121316,
+    "p": 0.218983236437501,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 5.165307958844581,
-    "hr_ci_low": 0.6348162961236556,
-    "hr_ci_high": 42.028546640375005,
-    "p": 0.12475550364321643,
+    "hr": 5.167153773864532,
+    "hr_ci_low": 0.6368362954626577,
+    "hr_ci_high": 41.92518283425644,
+    "p": 0.12416666927802668,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -8274,16 +8274,16 @@
         </is>
       </c>
       <c r="B384" s="18" t="n">
-        <v>0.6195366880806339</v>
+        <v>0.6195679029743909</v>
       </c>
       <c r="C384" s="18" t="n">
-        <v>0.2885784687778236</v>
+        <v>0.2887910192490381</v>
       </c>
       <c r="D384" s="18" t="n">
-        <v>1.330056637639961</v>
+        <v>1.329211647212132</v>
       </c>
       <c r="E384" s="18" t="n">
-        <v>0.2193486452707155</v>
+        <v>0.218983236437501</v>
       </c>
     </row>
     <row r="385">
@@ -8293,16 +8293,16 @@
         </is>
       </c>
       <c r="B385" s="18" t="n">
-        <v>5.165307958844581</v>
+        <v>5.167153773864532</v>
       </c>
       <c r="C385" s="18" t="n">
-        <v>0.6348162961236556</v>
+        <v>0.6368362954626577</v>
       </c>
       <c r="D385" s="18" t="n">
-        <v>42.028546640375</v>
+        <v>41.92518283425644</v>
       </c>
       <c r="E385" s="18" t="n">
-        <v>0.1247555036432164</v>
+        <v>0.1241666692780266</v>
       </c>
     </row>
     <row r="386">
@@ -8312,16 +8312,16 @@
         </is>
       </c>
       <c r="B386" s="18" t="n">
-        <v>0.7862597071903951</v>
+        <v>0.7863070086627305</v>
       </c>
       <c r="C386" s="18" t="n">
-        <v>0.6238653960942784</v>
+        <v>0.6240342904607402</v>
       </c>
       <c r="D386" s="18" t="n">
-        <v>0.9909258167248997</v>
+        <v>0.9907768232025208</v>
       </c>
       <c r="E386" s="18" t="n">
-        <v>0.0416310821738029</v>
+        <v>0.0414964955672526</v>
       </c>
     </row>
     <row r="387">
@@ -8331,16 +8331,16 @@
         </is>
       </c>
       <c r="B387" s="18" t="n">
-        <v>1.797323120587958</v>
+        <v>1.797606236232786</v>
       </c>
       <c r="C387" s="18" t="n">
-        <v>0.8653448635461843</v>
+        <v>0.8660663278899774</v>
       </c>
       <c r="D387" s="18" t="n">
-        <v>3.733043941073358</v>
+        <v>3.73110935788917</v>
       </c>
       <c r="E387" s="18" t="n">
-        <v>0.1159160466304021</v>
+        <v>0.1154812929439595</v>
       </c>
     </row>
     <row r="388">
@@ -8350,16 +8350,16 @@
         </is>
       </c>
       <c r="B388" s="18" t="n">
-        <v>1.068630419767369</v>
+        <v>1.068541698187198</v>
       </c>
       <c r="C388" s="18" t="n">
-        <v>0.9630936387125496</v>
+        <v>0.9630806915513695</v>
       </c>
       <c r="D388" s="18" t="n">
-        <v>1.185732028693238</v>
+        <v>1.185551087028392</v>
       </c>
       <c r="E388" s="18" t="n">
-        <v>0.210877979077011</v>
+        <v>0.2111437289383263</v>
       </c>
     </row>
     <row r="389">
@@ -8369,16 +8369,16 @@
         </is>
       </c>
       <c r="B389" s="18" t="n">
-        <v>118.1323653991867</v>
+        <v>117.6132179872576</v>
       </c>
       <c r="C389" s="18" t="n">
-        <v>12.10257479144966</v>
+        <v>12.10022176593432</v>
       </c>
       <c r="D389" s="18" t="n">
-        <v>1153.081554568554</v>
+        <v>1143.191365654286</v>
       </c>
       <c r="E389" s="18" t="n">
-        <v>4.044786956070582e-05</v>
+        <v>3.978763320899973e-05</v>
       </c>
     </row>
     <row r="390">
@@ -8388,16 +8388,16 @@
         </is>
       </c>
       <c r="B390" s="18" t="n">
-        <v>2.159390070958419e-100</v>
+        <v>2.121731602928528e-100</v>
       </c>
       <c r="C390" s="18" t="n">
-        <v>1.636405075577344e-111</v>
+        <v>1.607867152276966e-111</v>
       </c>
       <c r="D390" s="18" t="n">
-        <v>2.849517853584423e-89</v>
+        <v>2.799823970836494e-89</v>
       </c>
       <c r="E390" s="18" t="n">
-        <v>4.49095631820043e-69</v>
+        <v>4.385630028864638e-69</v>
       </c>
     </row>
     <row r="391">
@@ -8407,16 +8407,16 @@
         </is>
       </c>
       <c r="B391" s="18" t="n">
-        <v>0.5174942401844203</v>
+        <v>0.51667350299869</v>
       </c>
       <c r="C391" s="18" t="n">
-        <v>1.00833663938705e-06</v>
+        <v>1.022602544094179e-06</v>
       </c>
       <c r="D391" s="18" t="n">
-        <v>265586.1923125609</v>
+        <v>261051.0899299618</v>
       </c>
       <c r="E391" s="18" t="n">
-        <v>0.9217757881419042</v>
+        <v>0.9214948614902508</v>
       </c>
     </row>
     <row r="392">
@@ -8426,16 +8426,16 @@
         </is>
       </c>
       <c r="B392" s="18" t="n">
-        <v>5.28000955338478</v>
+        <v>5.275814328773673</v>
       </c>
       <c r="C392" s="18" t="n">
-        <v>1.734006595622719</v>
+        <v>1.734829405598675</v>
       </c>
       <c r="D392" s="18" t="n">
-        <v>16.07750567628192</v>
+        <v>16.04435383782778</v>
       </c>
       <c r="E392" s="18" t="n">
-        <v>0.0034023415240864</v>
+        <v>0.0033811494546532</v>
       </c>
     </row>
     <row r="393">
@@ -8445,16 +8445,16 @@
         </is>
       </c>
       <c r="B393" s="18" t="n">
-        <v>0.0007538458202525999</v>
+        <v>0.0007539449476274</v>
       </c>
       <c r="C393" s="18" t="n">
-        <v>7.87370023106309e-34</v>
+        <v>7.885724289615266e-34</v>
       </c>
       <c r="D393" s="18" t="n">
-        <v>7.217489922596581e+26</v>
+        <v>7.208380145898187e+26</v>
       </c>
       <c r="E393" s="18" t="n">
-        <v>0.8382422392940119</v>
+        <v>0.838241934116758</v>
       </c>
     </row>
     <row r="394">
@@ -8464,16 +8464,16 @@
         </is>
       </c>
       <c r="B394" s="18" t="n">
-        <v>0.2141299452268806</v>
+        <v>0.2147113890850175</v>
       </c>
       <c r="C394" s="18" t="n">
-        <v>0.008271310808961501</v>
+        <v>0.0083525840177399</v>
       </c>
       <c r="D394" s="18" t="n">
-        <v>5.543454296650193</v>
+        <v>5.519367480159952</v>
       </c>
       <c r="E394" s="18" t="n">
-        <v>0.3532282666818117</v>
+        <v>0.3530294384880128</v>
       </c>
     </row>
     <row r="395">
@@ -8483,16 +8483,16 @@
         </is>
       </c>
       <c r="B395" s="18" t="n">
-        <v>1879.319965286519</v>
+        <v>1872.628714966891</v>
       </c>
       <c r="C395" s="18" t="n">
-        <v>708.118289554257</v>
+        <v>706.3861810513191</v>
       </c>
       <c r="D395" s="18" t="n">
-        <v>4987.646250667713</v>
+        <v>4964.335937177381</v>
       </c>
       <c r="E395" s="18" t="n">
-        <v>9.092997502793388e-52</v>
+        <v>7.788175008546828e-52</v>
       </c>
     </row>
     <row r="396">
@@ -8502,16 +8502,16 @@
         </is>
       </c>
       <c r="B396" s="18" t="n">
-        <v>1.503034356645002</v>
+        <v>1.503991751504678</v>
       </c>
       <c r="C396" s="18" t="n">
-        <v>0.9162695004306858</v>
+        <v>0.9170436666850992</v>
       </c>
       <c r="D396" s="18" t="n">
-        <v>2.465554376952824</v>
+        <v>2.46661230077591</v>
       </c>
       <c r="E396" s="18" t="n">
-        <v>0.1065977172144751</v>
+        <v>0.1059049444034784</v>
       </c>
     </row>
     <row r="397">
@@ -8521,16 +8521,16 @@
         </is>
       </c>
       <c r="B397" s="18" t="n">
-        <v>0.09762202898769851</v>
+        <v>0.0996147536797593</v>
       </c>
       <c r="C397" s="18" t="n">
-        <v>0.0156870030163558</v>
+        <v>0.0162759499609488</v>
       </c>
       <c r="D397" s="18" t="n">
-        <v>0.6075131453559768</v>
+        <v>0.6096786469906684</v>
       </c>
       <c r="E397" s="18" t="n">
-        <v>0.0126225496879036</v>
+        <v>0.0125848832600914</v>
       </c>
     </row>
     <row r="398">
@@ -8540,16 +8540,16 @@
         </is>
       </c>
       <c r="B398" s="18" t="n">
-        <v>3.183808411155286e-05</v>
+        <v>3.184477097328247e-05</v>
       </c>
       <c r="C398" s="18" t="n">
-        <v>8.276780346535801e-48</v>
+        <v>8.278552790267166e-48</v>
       </c>
       <c r="D398" s="18" t="n">
-        <v>1.224707624769307e+38</v>
+        <v>1.224959801588808e+38</v>
       </c>
       <c r="E398" s="18" t="n">
-        <v>0.836029126257533</v>
+        <v>0.8360323977225377</v>
       </c>
     </row>
     <row r="399">
@@ -8559,16 +8559,16 @@
         </is>
       </c>
       <c r="B399" s="18" t="n">
-        <v>4.352903403823486</v>
+        <v>4.349421678705429</v>
       </c>
       <c r="C399" s="18" t="n">
-        <v>2.086236680262511</v>
+        <v>2.085509217147165</v>
       </c>
       <c r="D399" s="18" t="n">
-        <v>9.082271547748787</v>
+        <v>9.070911211349411</v>
       </c>
       <c r="E399" s="18" t="n">
-        <v>8.869250150454874e-05</v>
+        <v>8.859188475476247e-05</v>
       </c>
     </row>
     <row r="400">
@@ -8578,16 +8578,16 @@
         </is>
       </c>
       <c r="B400" s="18" t="n">
-        <v>1.256411627150506</v>
+        <v>1.255370520701112</v>
       </c>
       <c r="C400" s="18" t="n">
-        <v>0.6555007012144456</v>
+        <v>0.6551809314904289</v>
       </c>
       <c r="D400" s="18" t="n">
-        <v>2.408189913320256</v>
+        <v>2.405373948628728</v>
       </c>
       <c r="E400" s="18" t="n">
-        <v>0.4916877121378405</v>
+        <v>0.4930353877669128</v>
       </c>
     </row>
     <row r="401">
@@ -8597,16 +8597,16 @@
         </is>
       </c>
       <c r="B401" s="18" t="n">
-        <v>2.286425471636428</v>
+        <v>2.286744666806819</v>
       </c>
       <c r="C401" s="18" t="n">
-        <v>0.8913158978824999</v>
+        <v>0.8921604001332837</v>
       </c>
       <c r="D401" s="18" t="n">
-        <v>5.865194876213264</v>
+        <v>5.861279171759041</v>
       </c>
       <c r="E401" s="18" t="n">
-        <v>0.08532621888335901</v>
+        <v>0.0850058938994806</v>
       </c>
     </row>
     <row r="402">
@@ -8616,16 +8616,16 @@
         </is>
       </c>
       <c r="B402" s="18" t="n">
-        <v>0.1766024486089431</v>
+        <v>0.1767500360564004</v>
       </c>
       <c r="C402" s="18" t="n">
-        <v>0.0327714753260228</v>
+        <v>0.0328444541491056</v>
       </c>
       <c r="D402" s="18" t="n">
-        <v>0.951694256801084</v>
+        <v>0.9511674361861652</v>
       </c>
       <c r="E402" s="18" t="n">
-        <v>0.0436352966560586</v>
+        <v>0.0435631735366287</v>
       </c>
     </row>
     <row r="403">
@@ -8635,16 +8635,16 @@
         </is>
       </c>
       <c r="B403" s="18" t="n">
-        <v>0.0629578538984947</v>
+        <v>0.0630401414450845</v>
       </c>
       <c r="C403" s="18" t="n">
-        <v>1.631278642615491e-09</v>
+        <v>1.682742170756617e-09</v>
       </c>
       <c r="D403" s="18" t="n">
-        <v>2429806.449956992</v>
+        <v>2361656.766246844</v>
       </c>
       <c r="E403" s="18" t="n">
-        <v>0.7563607739507602</v>
+        <v>0.7560698860865616</v>
       </c>
     </row>
     <row r="404">
@@ -8654,16 +8654,16 @@
         </is>
       </c>
       <c r="B404" s="18" t="n">
-        <v>0.521537506501187</v>
+        <v>0.5213933439270377</v>
       </c>
       <c r="C404" s="18" t="n">
-        <v>0.1897718262966125</v>
+        <v>0.1898912323532288</v>
       </c>
       <c r="D404" s="18" t="n">
-        <v>1.433307440812309</v>
+        <v>1.431614381151262</v>
       </c>
       <c r="E404" s="18" t="n">
-        <v>0.2069289207676676</v>
+        <v>0.2063294534311404</v>
       </c>
     </row>
   </sheetData>
@@ -8679,7 +8679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="70" customWidth="1" style="18" min="1" max="1"/>
@@ -9107,322 +9107,304 @@
       </c>
     </row>
     <row r="25"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>OR pooled=1.720509958843602 p=0.001948210925390039</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 5.35% expected 4.1% (n=318)</t>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OR pooled=1.720509958843602 p=0.001948210925390039</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 11.34% expected 7.0% (n=344)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 5.35% expected 4.1% (n=318)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 3.73% expected 2.6% (n=268)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 11.44% expected 7.0% (n=341)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 11.61% expected 8.6% (n=336)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 3.75% expected 2.6% (n=267)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.51% expected 2.7% (n=712)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 11.61% expected 8.6% (n=336)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.27% expected 2.3% (n=642)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.56% expected 2.7% (n=702)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 1.69% expected 1.1% (n=947)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.2% expected 2.3% (n=625)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 6.69% expected 5.6% (n=269)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 1.73% expected 1.1% (n=924)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 18.18% expected 11.4% (n=44)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 6.92% expected 5.6% (n=260)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 9.3% expected 7.0% (n=43)</t>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 18.18% expected 11.4% (n=44)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 7.55% expected 3.8% (n=53)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 9.3% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 7.84% expected 3.8% (n=51)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>Strict-DTC Cox/KM inclusion flow</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>excluded_at_step</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>cum_excluded_from_cohort</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>path_proven_events_final_only</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>0</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>4128</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Strict-DTC histology (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list)</t>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3789</v>
+        <v>4012</v>
       </c>
       <c r="D44" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+          <t>Strict-DTC histology (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3756</v>
+        <v>3789</v>
       </c>
       <c r="D45" t="n">
-        <v>33</v>
+        <v>223</v>
       </c>
       <c r="E45" t="n">
-        <v>372</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sex known female/male (same frame as primary logistic/Cox categoricals)</t>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>3756</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E46" t="n">
-        <v>372</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Positive analytic follow-up (followup_years &gt; 0)</t>
+          <t>Sex known female/male (same frame as primary logistic/Cox categoricals)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2525</v>
+        <v>3756</v>
       </c>
       <c r="D47" t="n">
-        <v>1231</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1603</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Known surgery date (CPM surg_first_date; mig_258/mig_254 lineage)</t>
+          <t>Positive analytic follow-up (followup_years &gt; 0)</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2525</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1231</v>
       </c>
       <c r="E48" t="n">
-        <v>1603</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Finite positive Cox time_days (path-proven TTE if event else censor at FU×365.25)</t>
+          <t>Known surgery date (CPM surg_first_date; mig_258/mig_254 lineage)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2515</v>
+        <v>2525</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1613</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tumor size known (cm; Cox covariate complete-case)</t>
+          <t>Finite positive Cox time_days (path-proven TTE if event else censor at FU×365.25)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>1617</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Age at surgery known (Cox covariate complete-case)</t>
+          <t>Tumor size known (cm; Cox covariate complete-case)</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2511</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>1617</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Final Cox PH + Kaplan–Meier rows (lifelines sample; aligns Figure 6)</t>
+          <t>Age at surgery known (Cox covariate complete-case)</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -9432,9 +9414,28 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1617</v>
-      </c>
-      <c r="F52" t="n">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>9</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Final Cox PH + Kaplan–Meier rows (lifelines sample; aligns Figure 6)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2511</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1501</v>
+      </c>
+      <c r="F53" t="n">
         <v>178</v>
       </c>
     </row>
@@ -12138,37 +12139,37 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>2576</v>
+        <v>2517</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="E5" s="28" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H5" s="28" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="I5" s="28" t="n">
         <v>2</v>
       </c>
       <c r="J5" s="28" t="n">
-        <v>8137.3</v>
+        <v>8050.9</v>
       </c>
       <c r="K5" s="28" t="n">
         <v>0.96</v>
@@ -12192,37 +12193,37 @@
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="C6" s="28" t="n">
         <v>105</v>
       </c>
       <c r="D6" s="28" t="inlineStr">
         <is>
-          <t>8.29%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="E6" s="28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="G6" s="28" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H6" s="28" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>8.87%</t>
         </is>
       </c>
       <c r="I6" s="28" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>4138.3</v>
+        <v>4135.6</v>
       </c>
       <c r="K6" s="28" t="n">
         <v>2.49</v>
@@ -12246,14 +12247,14 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C7" s="28" t="n">
         <v>18</v>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>9.38%</t>
+          <t>9.47%</t>
         </is>
       </c>
       <c r="E7" s="28" t="n">
@@ -12261,7 +12262,7 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="G7" s="28" t="n">
@@ -12269,7 +12270,7 @@
       </c>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>9.90%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="I7" s="28" t="n">
@@ -12354,7 +12355,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>0</v>
@@ -12365,26 +12366,26 @@
         </is>
       </c>
       <c r="E9" s="28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="28" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="I9" s="28" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="28" t="n">
-        <v>99.3</v>
+        <v>35.5</v>
       </c>
       <c r="K9" s="28" t="n">
         <v>0</v>
@@ -12934,16 +12935,16 @@
         </is>
       </c>
       <c r="B27" s="18" t="n">
-        <v>1.590964961232916</v>
+        <v>1.605347833573521</v>
       </c>
       <c r="C27" s="18" t="n">
-        <v>1.134847190953743</v>
+        <v>1.144503489899247</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>2.23040558063471</v>
+        <v>2.251755184238075</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>0.007063602444180204</v>
+        <v>0.006110978617229343</v>
       </c>
     </row>
     <row r="28">
@@ -12953,16 +12954,16 @@
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>1.224487779211359</v>
+        <v>1.234036811889456</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.6249861848359756</v>
+        <v>0.6296290952169418</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>2.39904554343304</v>
+        <v>2.418641172504247</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>0.5550575699205013</v>
+        <v>0.5402052351946247</v>
       </c>
     </row>
     <row r="29">

--- a/M044_submission_package_v1_0/04_tables.xlsx
+++ b/M044_submission_package_v1_0/04_tables.xlsx
@@ -1367,12 +1367,12 @@
       <c r="A2" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 193,
-  "llf": -654.0326151062296,
-  "aic": 1350.0652302124593,
-  "pseudo_r2_mcfadden": 0.14040257814284918,
-  "lr_vs_null_chi2": 213.65318930815624,
+  "n_obs": 3614,
+  "n_events": 136,
+  "llf": -495.05342883144544,
+  "aic": 1032.106857662891,
+  "pseudo_r2_mcfadden": 0.14597151217994864,
+  "lr_vs_null_chi2": 169.23018060170625,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "label": "strict-DTC primary \u2014 without RAI covariate"
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="B3" s="18" t="n">
-        <v>0.03052220194197974</v>
+        <v>0.01952818235876326</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>0.01669454927553033</v>
+        <v>0.009576002857726848</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>0.05580293280229319</v>
+        <v>0.03982349545033839</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>8.856417170795826e-30</v>
+        <v>2.607262166249015e-27</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="19">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>0.6669255032178935</v>
+        <v>0.5524765530770338</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>0.3177659954934816</v>
+        <v>0.2305492981731137</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>1.399739535225268</v>
+        <v>1.323926570666421</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>0.2842080600304258</v>
+        <v>0.183297870332655</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="19">
@@ -1425,16 +1425,16 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>2.076021874744788</v>
+        <v>1.720081707216226</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>1.47858360953565</v>
+        <v>1.154912102130645</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>2.914861761366597</v>
+        <v>2.561823600290921</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>2.458209087953318e-05</v>
+        <v>0.007616872842289187</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="19">
@@ -1444,16 +1444,16 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>1.243365865671108</v>
+        <v>1.4650883599481</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>0.8826065421803896</v>
+        <v>0.9878422186406968</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>1.751583069050145</v>
+        <v>2.172901564593024</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0.2128480394355131</v>
+        <v>0.05754647417412548</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="19">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>1.041542433253086</v>
+        <v>0.9358545641585758</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>0.7041041255179393</v>
+        <v>0.589211285748405</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>1.540696327363191</v>
+        <v>1.48643413057505</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0.8385463175879454</v>
+        <v>0.7788356451782399</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="19">
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>5.589610780216073</v>
+        <v>3.963807382165004</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>2.888512518705153</v>
+        <v>1.836332193384906</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>10.81655297388619</v>
+        <v>8.556060292089263</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>3.235499429458743e-07</v>
+        <v>0.0004512797412887346</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="19">
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>0.4437282968749986</v>
+        <v>0.3212734795521583</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>0.1329051128210752</v>
+        <v>0.04281602105476547</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>1.481468976386622</v>
+        <v>2.410701557987555</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>0.1865048194220119</v>
+        <v>0.2694885897248011</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="19">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>1.000000000181017</v>
+        <v>1.000000000021757</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>0.999999567207104</v>
+        <v>0.9999999223249101</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>1.000000433155118</v>
+        <v>1.000000077718611</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>0.9993461969791613</v>
+        <v>0.9995620828278956</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="19">
@@ -1539,16 +1539,16 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>0.5113539780108236</v>
+        <v>0.3890162634245708</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>0.2699812706456613</v>
+        <v>0.1725341866318366</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>0.9685223356500121</v>
+        <v>0.8771227092039422</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0.03957954869899567</v>
+        <v>0.02284436960335355</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="19">
@@ -1558,16 +1558,16 @@
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>8.57905103879509</v>
+        <v>8.037808447340625</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>4.741888142926279</v>
+        <v>4.156117229943009</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>15.52126800714273</v>
+        <v>15.54488506019024</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>1.201350488743744e-12</v>
+        <v>5.896019029138317e-10</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="19">
@@ -1577,16 +1577,16 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>1.715255922337146</v>
+        <v>1.842180788706986</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>0.6113741691283806</v>
+        <v>0.5932306073819177</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>4.812278679204144</v>
+        <v>5.720591648596947</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>0.3053064560865795</v>
+        <v>0.2906203332201726</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="19">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>5.16727771697659e-10</v>
+        <v>1.82521779930501e-09</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -1605,7 +1605,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>0.9992030750468766</v>
+        <v>0.9988564339892622</v>
       </c>
     </row>
     <row r="15">
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>0.7384752852970617</v>
+        <v>0.7049729669721491</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>0.4452543797335514</v>
+        <v>0.3996192564872628</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1.224795918506005</v>
+        <v>1.243650990520662</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.2402193969427563</v>
+        <v>0.2274016006370255</v>
       </c>
     </row>
     <row r="16">
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>1.757893717879382</v>
+        <v>1.960800196196869</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>0.7279395352184567</v>
+        <v>0.7711608720824789</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>4.245119510417058</v>
+        <v>4.985648972338509</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>0.2098197201769865</v>
+        <v>0.1573031701081236</v>
       </c>
     </row>
     <row r="17">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>7.668397975541751e-10</v>
+        <v>2.501109593889407e-09</v>
       </c>
       <c r="C17" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -1662,7 +1662,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0.999474226098751</v>
+        <v>0.9991855474853423</v>
       </c>
     </row>
     <row r="18">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>0.6744064518387922</v>
+        <v>0.7422833948819164</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>0.2721746782092361</v>
+        <v>0.276135190157902</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1.671074125169499</v>
+        <v>1.995343795198121</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>0.3948394123437013</v>
+        <v>0.5547156582209726</v>
       </c>
     </row>
     <row r="19">
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>1.823942570144014</v>
+        <v>2.75396182855841</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>1.112341481819554</v>
+        <v>1.611105036455845</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>2.990778060116638</v>
+        <v>4.707517872230699</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>0.01722257193913048</v>
+        <v>0.0002126425680882026</v>
       </c>
     </row>
     <row r="20">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>2.39090079920365</v>
+        <v>2.803176034744242</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>1.317147438489974</v>
+        <v>1.407722482750835</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>4.339989939308657</v>
+        <v>5.581921137189987</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0.004162942684026138</v>
+        <v>0.003356295661775941</v>
       </c>
     </row>
     <row r="21">
@@ -1729,16 +1729,16 @@
         </is>
       </c>
       <c r="B21" s="18" t="n">
-        <v>2.788892715938317</v>
+        <v>3.049893524544781</v>
       </c>
       <c r="C21" s="18" t="n">
-        <v>1.376348027128713</v>
+        <v>1.343814584395691</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>5.651130693477159</v>
+        <v>6.921974667541801</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>0.004420333345359666</v>
+        <v>0.007661210246188071</v>
       </c>
     </row>
     <row r="22">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>1.304747414145783</v>
+        <v>1.570591164182373</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>0.3606986337620886</v>
+        <v>0.3406980676503913</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>4.719634773673588</v>
+        <v>7.240301132376875</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>0.6851050284367951</v>
+        <v>0.5625910155522527</v>
       </c>
     </row>
     <row r="23">
@@ -1767,16 +1767,16 @@
         </is>
       </c>
       <c r="B23" s="18" t="n">
-        <v>0.9342008179855855</v>
+        <v>0.952926479401809</v>
       </c>
       <c r="C23" s="18" t="n">
-        <v>0.84698924688341</v>
+        <v>0.8491424738889585</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1.030392264761622</v>
+        <v>1.069395187578232</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>0.1734490646119403</v>
+        <v>0.4124644185366982</v>
       </c>
     </row>
     <row r="24">
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="B24" s="18" t="n">
-        <v>1.047101558155796</v>
+        <v>1.043402510286877</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>0.9772115482993279</v>
+        <v>0.9634033389088166</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1.121990090068454</v>
+        <v>1.130044659909568</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>0.1915859030131092</v>
+        <v>0.2965259820827366</v>
       </c>
     </row>
     <row r="25"/>
@@ -1810,12 +1810,12 @@
       <c r="A27" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 193,
-  "llf": -615.6138897275603,
-  "aic": 1275.2277794551205,
-  "pseudo_r2_mcfadden": 0.1908964472921395,
-  "lr_vs_null_chi2": 290.490640065495,
+  "n_obs": 3614,
+  "n_events": 136,
+  "llf": -470.60708396812936,
+  "aic": 985.2141679362587,
+  "pseudo_r2_mcfadden": 0.1881444852782802,
+  "lr_vs_null_chi2": 218.12287032833842,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + rai_received_flag + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))"
 }</t>
@@ -1829,16 +1829,16 @@
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>0.01852597376749012</v>
+        <v>0.01262252463343087</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.009880024697097232</v>
+        <v>0.006063799493112474</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>0.03473793988941832</v>
+        <v>0.026275296256504</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>1.683886297117039e-35</v>
+        <v>1.456701538581204e-31</v>
       </c>
     </row>
     <row r="29">
@@ -1848,16 +1848,16 @@
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>0.6605652523227008</v>
+        <v>0.5061923590587584</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>0.3089484868535126</v>
+        <v>0.2068132293429193</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>1.412359895399152</v>
+        <v>1.238947359332667</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>0.2848553724927133</v>
+        <v>0.1360131450792832</v>
       </c>
     </row>
     <row r="30">
@@ -1867,16 +1867,16 @@
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>1.588785874419103</v>
+        <v>1.333785302808943</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>1.117522728799781</v>
+        <v>0.8841108708522141</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>2.258782295609063</v>
+        <v>2.012172107186446</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>0.009911220692569871</v>
+        <v>0.1697964367673447</v>
       </c>
     </row>
     <row r="31">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="B31" s="18" t="n">
-        <v>1.327158313740222</v>
+        <v>1.561055714946559</v>
       </c>
       <c r="C31" s="18" t="n">
-        <v>0.9351044686229039</v>
+        <v>1.045843375077862</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>1.88358546967877</v>
+        <v>2.330076379731226</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>0.1131084878470058</v>
+        <v>0.02930936885766519</v>
       </c>
     </row>
     <row r="32">
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="B32" s="18" t="n">
-        <v>0.990583944558754</v>
+        <v>0.8875204431385577</v>
       </c>
       <c r="C32" s="18" t="n">
-        <v>0.6655851393719214</v>
+        <v>0.5559465151507302</v>
       </c>
       <c r="D32" s="18" t="n">
-        <v>1.474276532290883</v>
+        <v>1.416849490953819</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>0.9628057759983004</v>
+        <v>0.6170894241288438</v>
       </c>
     </row>
     <row r="33">
@@ -1924,16 +1924,16 @@
         </is>
       </c>
       <c r="B33" s="18" t="n">
-        <v>4.604586434968516</v>
+        <v>3.107939055974312</v>
       </c>
       <c r="C33" s="18" t="n">
-        <v>2.283886415442775</v>
+        <v>1.381816086735962</v>
       </c>
       <c r="D33" s="18" t="n">
-        <v>9.283393470767507</v>
+        <v>6.990282765101576</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>1.967841372061901e-05</v>
+        <v>0.006107513914765714</v>
       </c>
     </row>
     <row r="34">
@@ -1943,16 +1943,16 @@
         </is>
       </c>
       <c r="B34" s="18" t="n">
-        <v>0.4506894604405457</v>
+        <v>0.3124294620844387</v>
       </c>
       <c r="C34" s="18" t="n">
-        <v>0.1317159434817318</v>
+        <v>0.0407808597922712</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>1.542113918656794</v>
+        <v>2.393577998982533</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>0.2041484951130681</v>
+        <v>0.2627827542574714</v>
       </c>
     </row>
     <row r="35">
@@ -1962,16 +1962,16 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>0.9999999999279252</v>
+        <v>1.000000000005883</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>0.999999874087424</v>
+        <v>0.9999999798370514</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>1.000000125768442</v>
+        <v>1.000000020174715</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.9991043239232837</v>
+        <v>0.9995438661153807</v>
       </c>
     </row>
     <row r="36">
@@ -1981,16 +1981,16 @@
         </is>
       </c>
       <c r="B36" s="18" t="n">
-        <v>0.5182946546370739</v>
+        <v>0.4079127281985936</v>
       </c>
       <c r="C36" s="18" t="n">
-        <v>0.2701503346559783</v>
+        <v>0.179382340978378</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>0.9943698547234768</v>
+        <v>0.9275873696311949</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.04804753128137115</v>
+        <v>0.0324117192429491</v>
       </c>
     </row>
     <row r="37">
@@ -2000,16 +2000,16 @@
         </is>
       </c>
       <c r="B37" s="18" t="n">
-        <v>7.235365489821646</v>
+        <v>6.844895739784269</v>
       </c>
       <c r="C37" s="18" t="n">
-        <v>3.912752753308382</v>
+        <v>3.465270500842163</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>13.3794586757463</v>
+        <v>13.52061770563951</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>2.798472448423662e-10</v>
+        <v>3.054042451266067e-08</v>
       </c>
     </row>
     <row r="38">
@@ -2019,16 +2019,16 @@
         </is>
       </c>
       <c r="B38" s="18" t="n">
-        <v>1.77940635884233</v>
+        <v>1.994331652899053</v>
       </c>
       <c r="C38" s="18" t="n">
-        <v>0.6231982024830175</v>
+        <v>0.6383207707089228</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>5.080706230013237</v>
+        <v>6.230971831510029</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>0.2816799942444455</v>
+        <v>0.2349775032751991</v>
       </c>
     </row>
     <row r="39">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="B39" s="18" t="n">
-        <v>7.100757734654775e-10</v>
+        <v>2.54328714061616e-09</v>
       </c>
       <c r="C39" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2047,7 +2047,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>0.9992245316664904</v>
+        <v>0.9988841721187859</v>
       </c>
     </row>
     <row r="40">
@@ -2057,16 +2057,16 @@
         </is>
       </c>
       <c r="B40" s="18" t="n">
-        <v>0.7203248889034003</v>
+        <v>0.7336591562565389</v>
       </c>
       <c r="C40" s="18" t="n">
-        <v>0.4268775794085984</v>
+        <v>0.4115772315933248</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>1.215495895316268</v>
+        <v>1.307787983011901</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>0.219105558193422</v>
+        <v>0.2936611686425746</v>
       </c>
     </row>
     <row r="41">
@@ -2076,16 +2076,16 @@
         </is>
       </c>
       <c r="B41" s="18" t="n">
-        <v>1.698928214493524</v>
+        <v>2.056843536553713</v>
       </c>
       <c r="C41" s="18" t="n">
-        <v>0.6880356978898791</v>
+        <v>0.7977081697504216</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>4.195068783282983</v>
+        <v>5.303449926038002</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>0.2504733611055728</v>
+        <v>0.1356238239552236</v>
       </c>
     </row>
     <row r="42">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="B42" s="18" t="n">
-        <v>1.201370520861789e-09</v>
+        <v>4.14742413698274e-09</v>
       </c>
       <c r="C42" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2104,7 +2104,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>0.9994877572298072</v>
+        <v>0.9992089224389097</v>
       </c>
     </row>
     <row r="43">
@@ -2114,16 +2114,16 @@
         </is>
       </c>
       <c r="B43" s="18" t="n">
-        <v>0.7132757540808904</v>
+        <v>0.8205510589367143</v>
       </c>
       <c r="C43" s="18" t="n">
-        <v>0.2849891561050739</v>
+        <v>0.3035070334061876</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>1.785198806554187</v>
+        <v>2.218413302538104</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0.4703804923977388</v>
+        <v>0.6967171003890162</v>
       </c>
     </row>
     <row r="44">
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="B44" s="18" t="n">
-        <v>1.841779165835708</v>
+        <v>2.45676587539576</v>
       </c>
       <c r="C44" s="18" t="n">
-        <v>1.101608279690727</v>
+        <v>1.426091004611495</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>3.079271060543237</v>
+        <v>4.232337590652834</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0.01985927502901846</v>
+        <v>0.001199609869948601</v>
       </c>
     </row>
     <row r="45">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B45" s="18" t="n">
-        <v>2.062891729377959</v>
+        <v>2.228298303497014</v>
       </c>
       <c r="C45" s="18" t="n">
-        <v>1.130608886225852</v>
+        <v>1.11639746136052</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>3.763920785499557</v>
+        <v>4.447621480002822</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0.01827203960239072</v>
+        <v>0.02307359599385974</v>
       </c>
     </row>
     <row r="46">
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="B46" s="18" t="n">
-        <v>2.729766659902919</v>
+        <v>2.666092275609191</v>
       </c>
       <c r="C46" s="18" t="n">
-        <v>1.325706536412232</v>
+        <v>1.156572643922758</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>5.620871446922123</v>
+        <v>6.145786051064259</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>0.0064290669584959</v>
+        <v>0.02137260931670504</v>
       </c>
     </row>
     <row r="47">
@@ -2190,16 +2190,16 @@
         </is>
       </c>
       <c r="B47" s="18" t="n">
-        <v>1.145187691339581</v>
+        <v>1.250638812059367</v>
       </c>
       <c r="C47" s="18" t="n">
-        <v>0.2935567622878745</v>
+        <v>0.2518498959937396</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>4.46746597889511</v>
+        <v>6.210435116749637</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>0.8452404506108612</v>
+        <v>0.7844448947793462</v>
       </c>
     </row>
     <row r="48">
@@ -2209,16 +2209,16 @@
         </is>
       </c>
       <c r="B48" s="18" t="n">
-        <v>0.9675883940055234</v>
+        <v>0.9811449749857665</v>
       </c>
       <c r="C48" s="18" t="n">
-        <v>0.8753594456019949</v>
+        <v>0.8729889735303565</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1.069534697909535</v>
+        <v>1.102700596603064</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>0.5191419700053839</v>
+        <v>0.7494040744134413</v>
       </c>
     </row>
     <row r="49">
@@ -2228,16 +2228,16 @@
         </is>
       </c>
       <c r="B49" s="18" t="n">
-        <v>1.058002054934856</v>
+        <v>1.059742021646132</v>
       </c>
       <c r="C49" s="18" t="n">
-        <v>0.9851955209249599</v>
+        <v>0.9767817322507805</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>1.136189035040931</v>
+        <v>1.149748316704081</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>0.1211542894693701</v>
+        <v>0.1629755276094143</v>
       </c>
     </row>
     <row r="50">
@@ -2247,16 +2247,16 @@
         </is>
       </c>
       <c r="B50" s="18" t="n">
-        <v>4.413484571074677</v>
+        <v>4.027195014478223</v>
       </c>
       <c r="C50" s="18" t="n">
-        <v>3.192075222553084</v>
+        <v>2.750179223887142</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>6.102251576494701</v>
+        <v>5.897179188822129</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>2.675251785808035e-19</v>
+        <v>8.14297521841454e-13</v>
       </c>
     </row>
     <row r="51">
@@ -2273,12 +2273,12 @@
       <c r="A53" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3963,
-  "n_events": 202,
-  "llf": -664.8694686549093,
-  "aic": 1373.7389373098185,
-  "pseudo_r2_mcfadden": 0.16717101382841393,
-  "lr_vs_null_chi2": 266.91410838023035,
+  "n_obs": 3823,
+  "n_events": 140,
+  "llf": -502.0174748405145,
+  "aic": 1048.034949681029,
+  "pseudo_r2_mcfadden": 0.16418059673591667,
+  "lr_vs_null_chi2": 197.2232955332147,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + rai_received_flag + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "label": "full cohort sensitivity \u2014 includes non-DTC histologies (RAI covariate)"
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="B54" s="18" t="n">
-        <v>0.01881692303623327</v>
+        <v>0.0135430755303895</v>
       </c>
       <c r="C54" s="18" t="n">
-        <v>0.01023808127512506</v>
+        <v>0.006632160066787393</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>0.03458427248588151</v>
+        <v>0.02765537818369948</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>1.772547926417216e-37</v>
+        <v>3.474793939724354e-32</v>
       </c>
     </row>
     <row r="55">
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="B55" s="18" t="n">
-        <v>1.234036811889456</v>
+        <v>0.9942646397911438</v>
       </c>
       <c r="C55" s="18" t="n">
-        <v>0.6296290952169418</v>
+        <v>0.443867186878169</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>2.418641172504247</v>
+        <v>2.227157589394752</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.5402052351946247</v>
+        <v>0.9888470288982417</v>
       </c>
     </row>
     <row r="56">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="B56" s="18" t="n">
-        <v>1.605347833573521</v>
+        <v>1.35550179769246</v>
       </c>
       <c r="C56" s="18" t="n">
-        <v>1.144503489899247</v>
+        <v>0.9096029584447941</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>2.251755184238075</v>
+        <v>2.019985870196581</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>0.006110978617229343</v>
+        <v>0.135057119508862</v>
       </c>
     </row>
     <row r="57">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B57" s="18" t="n">
-        <v>1.30074903442832</v>
+        <v>1.478518418547712</v>
       </c>
       <c r="C57" s="18" t="n">
-        <v>0.9308559060649149</v>
+        <v>1.003250282757113</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>1.817626164847276</v>
+        <v>2.17893456055378</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>0.1234997267822623</v>
+        <v>0.04811349156661142</v>
       </c>
     </row>
     <row r="58">
@@ -2373,16 +2373,16 @@
         </is>
       </c>
       <c r="B58" s="18" t="n">
-        <v>1.230139271573314</v>
+        <v>1.085737986732571</v>
       </c>
       <c r="C58" s="18" t="n">
-        <v>0.8353077310506075</v>
+        <v>0.6888210746986508</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1.81159897270871</v>
+        <v>1.711368915868052</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>0.2942819158437429</v>
+        <v>0.7231007765351796</v>
       </c>
     </row>
     <row r="59">
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B59" s="18" t="n">
-        <v>5.185237994209519</v>
+        <v>3.444690492100065</v>
       </c>
       <c r="C59" s="18" t="n">
-        <v>2.689349157916357</v>
+        <v>1.599004722299348</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>9.997472056557029</v>
+        <v>7.420798963808929</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>8.950254840615399e-07</v>
+        <v>0.00158476331705517</v>
       </c>
     </row>
     <row r="60">
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="B60" s="18" t="n">
-        <v>0.4818062924969674</v>
+        <v>0.3128902105474966</v>
       </c>
       <c r="C60" s="18" t="n">
-        <v>0.1429702388002312</v>
+        <v>0.04140432840778841</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>1.623675706480655</v>
+        <v>2.364493945952789</v>
       </c>
       <c r="E60" s="18" t="n">
-        <v>0.2387859210607071</v>
+        <v>0.2601675923054678</v>
       </c>
     </row>
     <row r="61">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B61" s="18" t="n">
-        <v>1.275475206682042e-09</v>
+        <v>1.803201101665717e-09</v>
       </c>
       <c r="C61" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2439,7 +2439,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>0.9992146353933082</v>
+        <v>0.9992236464479791</v>
       </c>
     </row>
     <row r="62">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B62" s="18" t="n">
-        <v>0.6703448943879612</v>
+        <v>0.5014723501102751</v>
       </c>
       <c r="C62" s="18" t="n">
-        <v>0.3661342037083442</v>
+        <v>0.2319194610209431</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>1.22731575712047</v>
+        <v>1.084318309546319</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0.19491739581879</v>
+        <v>0.07939300576332722</v>
       </c>
     </row>
     <row r="63">
@@ -2468,16 +2468,16 @@
         </is>
       </c>
       <c r="B63" s="18" t="n">
-        <v>1.778439644995289</v>
+        <v>0.9719062304039024</v>
       </c>
       <c r="C63" s="18" t="n">
-        <v>0.8471264195793732</v>
+        <v>0.3385858583369234</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>3.733619325037023</v>
+        <v>2.789843986212678</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.1281294442203</v>
+        <v>0.9577594799276866</v>
       </c>
     </row>
     <row r="64">
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="B64" s="18" t="n">
-        <v>3.333027731194698</v>
+        <v>3.171212778000964</v>
       </c>
       <c r="C64" s="18" t="n">
-        <v>1.991611142896396</v>
+        <v>1.761886589320364</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>5.577933170607278</v>
+        <v>5.707853470430155</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>4.600306701175059e-06</v>
+        <v>0.0001187218258347868</v>
       </c>
     </row>
     <row r="65">
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="B65" s="18" t="n">
-        <v>0.6877617653898112</v>
+        <v>0.6232572713278857</v>
       </c>
       <c r="C65" s="18" t="n">
-        <v>0.4227728699706244</v>
+        <v>0.3605127763907263</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>1.118842479095161</v>
+        <v>1.07749198281416</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>0.1316410384497489</v>
+        <v>0.09050396410395635</v>
       </c>
     </row>
     <row r="66">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B66" s="18" t="n">
-        <v>1.468070655857398</v>
+        <v>1.678545586915365</v>
       </c>
       <c r="C66" s="18" t="n">
-        <v>0.6064738063648494</v>
+        <v>0.6647988588401412</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>3.55370904393685</v>
+        <v>4.238146997226648</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>0.3946399821179301</v>
+        <v>0.2730758771134385</v>
       </c>
     </row>
     <row r="67">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B67" s="18" t="n">
-        <v>1.500093204321947e-09</v>
+        <v>1.729678004208316e-09</v>
       </c>
       <c r="C67" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2553,7 +2553,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.9994978399243757</v>
+        <v>0.9995012381532452</v>
       </c>
     </row>
     <row r="68">
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="B68" s="18" t="n">
-        <v>0.7778941343935867</v>
+        <v>0.7208857103312178</v>
       </c>
       <c r="C68" s="18" t="n">
-        <v>0.3328212674043152</v>
+        <v>0.2699173392918572</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>1.8181508923492</v>
+        <v>1.925316130942692</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>0.5620235742756428</v>
+        <v>0.513781006507994</v>
       </c>
     </row>
     <row r="69">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="B69" s="18" t="n">
-        <v>1.77562931311392</v>
+        <v>2.564418967386722</v>
       </c>
       <c r="C69" s="18" t="n">
-        <v>1.101148072875106</v>
+        <v>1.529085540551802</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>2.863247491645033</v>
+        <v>4.300769620723512</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>0.01851225008280269</v>
+        <v>0.0003573791048447831</v>
       </c>
     </row>
     <row r="70">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="B70" s="18" t="n">
-        <v>1.91641428573758</v>
+        <v>2.052479601847642</v>
       </c>
       <c r="C70" s="18" t="n">
-        <v>1.075665388581756</v>
+        <v>1.040086994014109</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>3.414299422073429</v>
+        <v>4.05030784948313</v>
       </c>
       <c r="E70" s="18" t="n">
-        <v>0.02727883903234741</v>
+        <v>0.03814496816188444</v>
       </c>
     </row>
     <row r="71">
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="B71" s="18" t="n">
-        <v>1.90470910031505</v>
+        <v>2.047316380135611</v>
       </c>
       <c r="C71" s="18" t="n">
-        <v>0.9868548096287644</v>
+        <v>0.9407535521883862</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>3.676241653205013</v>
+        <v>4.455475454353889</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>0.05479188168837221</v>
+        <v>0.07091431929731469</v>
       </c>
     </row>
     <row r="72">
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="B72" s="18" t="n">
-        <v>1.178180598970277</v>
+        <v>1.41164357976955</v>
       </c>
       <c r="C72" s="18" t="n">
-        <v>0.3209764511859936</v>
+        <v>0.3026621180910943</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>4.324645994000363</v>
+        <v>6.584033736606648</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>0.8047955297569923</v>
+        <v>0.6608056318970386</v>
       </c>
     </row>
     <row r="73">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B73" s="18" t="n">
-        <v>0.9334958671328363</v>
+        <v>0.9448705893885451</v>
       </c>
       <c r="C73" s="18" t="n">
-        <v>0.8475742387320844</v>
+        <v>0.8435915621084616</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>1.028127677945551</v>
+        <v>1.0583088674572</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0.1624428836647294</v>
+        <v>0.3269453689068119</v>
       </c>
     </row>
     <row r="74">
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="B74" s="18" t="n">
-        <v>1.059716424637732</v>
+        <v>1.058867488613961</v>
       </c>
       <c r="C74" s="18" t="n">
-        <v>0.9891913739424952</v>
+        <v>0.977916591569387</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>1.135269605284955</v>
+        <v>1.146519414957777</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>0.09880338997329706</v>
+        <v>0.1586461308739907</v>
       </c>
     </row>
     <row r="75">
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="B75" s="18" t="n">
-        <v>4.648297307741951</v>
+        <v>4.338789645371109</v>
       </c>
       <c r="C75" s="18" t="n">
-        <v>3.388276890214176</v>
+        <v>2.986244142313403</v>
       </c>
       <c r="D75" s="18" t="n">
-        <v>6.376889658446803</v>
+        <v>6.303937216665751</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>1.65661107990849e-21</v>
+        <v>1.364197601897826e-14</v>
       </c>
     </row>
     <row r="76">
@@ -2722,9 +2722,9 @@
       <c r="A78" s="18" t="inlineStr">
         <is>
           <t>{
-  "lr_chi2": 3.6960718240545702,
+  "lr_chi2": 5.726023244916291,
   "df": 6,
-  "p_value": 0.7177264638482881,
+  "p_value": 0.4545701344004083,
   "formula_full": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) * C(ajcc8_n_fac, Treatment(reference='N0')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "formula_reduced": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + C(ajcc8_n_fac, Treatment(reference='N0')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))"
 }</t>
@@ -2757,13 +2757,13 @@
       <c r="A81" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 14,
-  "llf": -81.0638843247846,
-  "aic": 204.1277686495692,
-  "pseudo_r2_mcfadden": 0.12137881887901447,
-  "lr_vs_null_chi2": 22.39745352037565,
-  "lr_vs_null_pvalue": 0.31933887897609237
+  "n_obs": 3614,
+  "n_events": 159,
+  "llf": -602.2980193490433,
+  "aic": 1246.5960386980867,
+  "pseudo_r2_mcfadden": 0.07670816184236329,
+  "lr_vs_null_chi2": 100.07924263199902,
+  "lr_vs_null_pvalue": 1.2191359033408844e-12
 }</t>
         </is>
       </c>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="B82" s="18" t="n">
-        <v>0.001786923068411454</v>
+        <v>0.009300650533072809</v>
       </c>
       <c r="C82" s="18" t="n">
-        <v>0.0002115687708741055</v>
+        <v>0.004765276068941907</v>
       </c>
       <c r="D82" s="18" t="n">
-        <v>0.01509246397390598</v>
+        <v>0.0181525895009803</v>
       </c>
       <c r="E82" s="18" t="n">
-        <v>6.170743635778745e-09</v>
+        <v>8.883477767443412e-43</v>
       </c>
     </row>
     <row r="83">
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="B83" s="18" t="n">
-        <v>2.355604278444697</v>
+        <v>1.168222848918381</v>
       </c>
       <c r="C83" s="18" t="n">
-        <v>0.1946082032947651</v>
+        <v>0.5380643666381768</v>
       </c>
       <c r="D83" s="18" t="n">
-        <v>28.513040163175</v>
+        <v>2.53639658998773</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0.5006607963547791</v>
+        <v>0.6942576494008772</v>
       </c>
     </row>
     <row r="84">
@@ -2817,16 +2817,16 @@
         </is>
       </c>
       <c r="B84" s="18" t="n">
-        <v>2.375717141246138</v>
+        <v>1.395746559301482</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>0.7381737066014609</v>
+        <v>0.9677957167546896</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>7.645940087998728</v>
+        <v>2.012933539667356</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>0.1467995693644507</v>
+        <v>0.07430229897457914</v>
       </c>
     </row>
     <row r="85">
@@ -2836,16 +2836,16 @@
         </is>
       </c>
       <c r="B85" s="18" t="n">
-        <v>0.9193439069638312</v>
+        <v>0.8749512978544075</v>
       </c>
       <c r="C85" s="18" t="n">
-        <v>0.2684093137257994</v>
+        <v>0.6012692599677051</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>3.148896763451923</v>
+        <v>1.273206239843743</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>0.8934992612409755</v>
+        <v>0.4851966910547617</v>
       </c>
     </row>
     <row r="86">
@@ -2855,16 +2855,16 @@
         </is>
       </c>
       <c r="B86" s="18" t="n">
-        <v>0.8377688957101103</v>
+        <v>1.068844497903118</v>
       </c>
       <c r="C86" s="18" t="n">
-        <v>0.2386806653638656</v>
+        <v>0.715417731601632</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>2.940567982535855</v>
+        <v>1.596869227912722</v>
       </c>
       <c r="E86" s="18" t="n">
-        <v>0.7823100301725159</v>
+        <v>0.745154544984939</v>
       </c>
     </row>
     <row r="87">
@@ -2874,16 +2874,16 @@
         </is>
       </c>
       <c r="B87" s="18" t="n">
-        <v>2.691336535594656</v>
+        <v>2.577968922245357</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>0.2557976385597303</v>
+        <v>1.185325214246661</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>28.31649419678006</v>
+        <v>5.606835730974251</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>0.4096422478169726</v>
+        <v>0.01690181173262741</v>
       </c>
     </row>
     <row r="88">
@@ -2893,16 +2893,16 @@
         </is>
       </c>
       <c r="B88" s="18" t="n">
-        <v>1.767155055363416</v>
+        <v>0.4385447061099553</v>
       </c>
       <c r="C88" s="18" t="n">
-        <v>0.1811306545993918</v>
+        <v>0.1025306791990693</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>17.24079779098289</v>
+        <v>1.875745491587583</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>0.6242047862455105</v>
+        <v>0.2662812650482015</v>
       </c>
     </row>
     <row r="89">
@@ -2912,16 +2912,16 @@
         </is>
       </c>
       <c r="B89" s="18" t="n">
-        <v>0.9999999999960187</v>
+        <v>0.9999999999885172</v>
       </c>
       <c r="C89" s="18" t="n">
-        <v>0.9999997899039276</v>
+        <v>0.9999999853956553</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>1.000000210088154</v>
+        <v>1.000000014581379</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0.9999703654559708</v>
+        <v>0.9987694566287185</v>
       </c>
     </row>
     <row r="90">
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="B90" s="18" t="n">
-        <v>2.878946803441325</v>
+        <v>1.142804640909171</v>
       </c>
       <c r="C90" s="18" t="n">
-        <v>0.5889034971326118</v>
+        <v>0.6603470533494636</v>
       </c>
       <c r="D90" s="18" t="n">
-        <v>14.07418148712169</v>
+        <v>1.977751609035177</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>0.1915526072694045</v>
+        <v>0.6333569147488016</v>
       </c>
     </row>
     <row r="91">
@@ -2950,16 +2950,16 @@
         </is>
       </c>
       <c r="B91" s="18" t="n">
-        <v>2.380401768922977</v>
+        <v>4.417093761304089</v>
       </c>
       <c r="C91" s="18" t="n">
-        <v>0.1785689893148111</v>
+        <v>2.214304293113969</v>
       </c>
       <c r="D91" s="18" t="n">
-        <v>31.7317839073509</v>
+        <v>8.811217752151691</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>0.5116393020940575</v>
+        <v>2.484202387687913e-05</v>
       </c>
     </row>
     <row r="92">
@@ -2969,16 +2969,16 @@
         </is>
       </c>
       <c r="B92" s="18" t="n">
-        <v>9.117152013220499</v>
+        <v>2.324745027299013</v>
       </c>
       <c r="C92" s="18" t="n">
-        <v>0.6821678137134559</v>
+        <v>0.8095915202592705</v>
       </c>
       <c r="D92" s="18" t="n">
-        <v>121.8504584373226</v>
+        <v>6.675513893995242</v>
       </c>
       <c r="E92" s="18" t="n">
-        <v>0.09475729860505173</v>
+        <v>0.1169999063186704</v>
       </c>
     </row>
     <row r="93">
@@ -2988,16 +2988,16 @@
         </is>
       </c>
       <c r="B93" s="18" t="n">
-        <v>2.477532991957287e-09</v>
+        <v>3.54044146396748</v>
       </c>
       <c r="C93" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.6730225050979082</v>
       </c>
       <c r="D93" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>18.62452691378678</v>
       </c>
       <c r="E93" s="18" t="n">
-        <v>0.9997357907928893</v>
+        <v>0.1355685798226988</v>
       </c>
     </row>
     <row r="94">
@@ -3007,16 +3007,16 @@
         </is>
       </c>
       <c r="B94" s="18" t="n">
-        <v>2.100268075359052</v>
+        <v>1.673115507732209</v>
       </c>
       <c r="C94" s="18" t="n">
-        <v>0.4591337909409427</v>
+        <v>1.000993879271125</v>
       </c>
       <c r="D94" s="18" t="n">
-        <v>9.607495844146682</v>
+        <v>2.796536082970192</v>
       </c>
       <c r="E94" s="18" t="n">
-        <v>0.3387921663504317</v>
+        <v>0.04955860626358623</v>
       </c>
     </row>
     <row r="95">
@@ -3026,16 +3026,16 @@
         </is>
       </c>
       <c r="B95" s="18" t="n">
-        <v>2.011022141784835e-09</v>
+        <v>4.22676055552003</v>
       </c>
       <c r="C95" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>1.662300452518632</v>
       </c>
       <c r="D95" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>10.74745829890806</v>
       </c>
       <c r="E95" s="18" t="n">
-        <v>0.9994414708553463</v>
+        <v>0.002467621657066496</v>
       </c>
     </row>
     <row r="96">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="B96" s="18" t="n">
-        <v>1.976731211879618e-09</v>
+        <v>1.154358995676012e-08</v>
       </c>
       <c r="C96" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3054,7 +3054,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E96" s="18" t="n">
-        <v>0.9998126242745856</v>
+        <v>0.9987695265742892</v>
       </c>
     </row>
     <row r="97">
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="B97" s="18" t="n">
-        <v>2.968183959850206e-09</v>
+        <v>1.070180000062418</v>
       </c>
       <c r="C97" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.4107597392368807</v>
       </c>
       <c r="D97" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>2.788211996290912</v>
       </c>
       <c r="E97" s="18" t="n">
-        <v>0.9990297347742679</v>
+        <v>0.8895859331449321</v>
       </c>
     </row>
     <row r="98">
@@ -3083,16 +3083,16 @@
         </is>
       </c>
       <c r="B98" s="18" t="n">
-        <v>1.594915489366299</v>
+        <v>0.8968667395902873</v>
       </c>
       <c r="C98" s="18" t="n">
-        <v>0.2687277948110208</v>
+        <v>0.5358161462363483</v>
       </c>
       <c r="D98" s="18" t="n">
-        <v>9.465918551556614</v>
+        <v>1.501205132083692</v>
       </c>
       <c r="E98" s="18" t="n">
-        <v>0.6074164792059515</v>
+        <v>0.6787603222926568</v>
       </c>
     </row>
     <row r="99">
@@ -3102,16 +3102,16 @@
         </is>
       </c>
       <c r="B99" s="18" t="n">
-        <v>7.992098005631019</v>
+        <v>1.24491965433012</v>
       </c>
       <c r="C99" s="18" t="n">
-        <v>1.753182671062876</v>
+        <v>0.6575086881356208</v>
       </c>
       <c r="D99" s="18" t="n">
-        <v>36.43295794892131</v>
+        <v>2.357117059748647</v>
       </c>
       <c r="E99" s="18" t="n">
-        <v>0.007245923079154247</v>
+        <v>0.5011970747164538</v>
       </c>
     </row>
     <row r="100">
@@ -3121,16 +3121,16 @@
         </is>
       </c>
       <c r="B100" s="18" t="n">
-        <v>1.650396770245106</v>
+        <v>1.207049811420221</v>
       </c>
       <c r="C100" s="18" t="n">
-        <v>0.121632055434126</v>
+        <v>0.5747946913561099</v>
       </c>
       <c r="D100" s="18" t="n">
-        <v>22.39384584527266</v>
+        <v>2.534764619715211</v>
       </c>
       <c r="E100" s="18" t="n">
-        <v>0.7065032591764135</v>
+        <v>0.6191040294921268</v>
       </c>
     </row>
     <row r="101">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="B101" s="18" t="n">
-        <v>5.38394050011315e-09</v>
+        <v>0.4318643172446746</v>
       </c>
       <c r="C101" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.05669590885498776</v>
       </c>
       <c r="D101" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>3.289598707840472</v>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0.9994607925343963</v>
+        <v>0.4176458406455007</v>
       </c>
     </row>
     <row r="102">
@@ -3159,16 +3159,16 @@
         </is>
       </c>
       <c r="B102" s="18" t="n">
-        <v>0.9461255572965408</v>
+        <v>1.186615971029109</v>
       </c>
       <c r="C102" s="18" t="n">
-        <v>0.6711845132547247</v>
+        <v>1.068873296341741</v>
       </c>
       <c r="D102" s="18" t="n">
-        <v>1.333692229918847</v>
+        <v>1.31732869323285</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>0.751891675586252</v>
+        <v>0.001331142181322135</v>
       </c>
     </row>
     <row r="103">
@@ -3178,16 +3178,16 @@
         </is>
       </c>
       <c r="B103" s="18" t="n">
-        <v>0.8932782057804017</v>
+        <v>1.088922109736263</v>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.6529378085699872</v>
+        <v>1.014494997450041</v>
       </c>
       <c r="D103" s="18" t="n">
-        <v>1.222085690932574</v>
+        <v>1.168809470774021</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>0.4803384917184649</v>
+        <v>0.01835563554282874</v>
       </c>
     </row>
     <row r="104">
@@ -3212,12 +3212,12 @@
       <c r="A106" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 207,
-  "llf": -691.6903656209505,
-  "aic": 1425.380731241901,
-  "pseudo_r2_mcfadden": 0.13663363535423334,
-  "lr_vs_null_chi2": 218.92946740649404,
+  "n_obs": 3614,
+  "n_events": 295,
+  "llf": -895.5209957991765,
+  "aic": 1833.041991598353,
+  "pseudo_r2_mcfadden": 0.1239229797180239,
+  "lr_vs_null_chi2": 253.3467437914694,
   "lr_vs_null_pvalue": 0.0
 }</t>
         </is>
@@ -3234,16 +3234,16 @@
         </is>
       </c>
       <c r="B107" s="18" t="n">
-        <v>0.03297932471141883</v>
+        <v>0.02537840743611185</v>
       </c>
       <c r="C107" s="18" t="n">
-        <v>0.01842066428832918</v>
+        <v>0.01531657193033489</v>
       </c>
       <c r="D107" s="18" t="n">
-        <v>0.05904433419973331</v>
+        <v>0.04205011192600557</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>1.626547486868297e-30</v>
+        <v>3.901183992329421e-46</v>
       </c>
     </row>
     <row r="108">
@@ -3253,16 +3253,16 @@
         </is>
       </c>
       <c r="B108" s="18" t="n">
-        <v>0.7123964730954562</v>
+        <v>0.6475647500208774</v>
       </c>
       <c r="C108" s="18" t="n">
-        <v>0.3463188194251166</v>
+        <v>0.3390853494808016</v>
       </c>
       <c r="D108" s="18" t="n">
-        <v>1.465437932946586</v>
+        <v>1.236680104615796</v>
       </c>
       <c r="E108" s="18" t="n">
-        <v>0.3567825087481744</v>
+        <v>0.1880353708553849</v>
       </c>
     </row>
     <row r="109">
@@ -3272,16 +3272,16 @@
         </is>
       </c>
       <c r="B109" s="18" t="n">
-        <v>2.115753263314071</v>
+        <v>1.575700620707195</v>
       </c>
       <c r="C109" s="18" t="n">
-        <v>1.524694902902878</v>
+        <v>1.192128519127776</v>
       </c>
       <c r="D109" s="18" t="n">
-        <v>2.935939421520638</v>
+        <v>2.082688574478204</v>
       </c>
       <c r="E109" s="18" t="n">
-        <v>7.348172881643928e-06</v>
+        <v>0.001399704998066663</v>
       </c>
     </row>
     <row r="110">
@@ -3291,16 +3291,16 @@
         </is>
       </c>
       <c r="B110" s="18" t="n">
-        <v>1.216673817895112</v>
+        <v>1.126213643100072</v>
       </c>
       <c r="C110" s="18" t="n">
-        <v>0.8729335050485126</v>
+        <v>0.8491325416684106</v>
       </c>
       <c r="D110" s="18" t="n">
-        <v>1.695770835453501</v>
+        <v>1.493709294679268</v>
       </c>
       <c r="E110" s="18" t="n">
-        <v>0.2469693411467394</v>
+        <v>0.4094062824665267</v>
       </c>
     </row>
     <row r="111">
@@ -3310,16 +3310,16 @@
         </is>
       </c>
       <c r="B111" s="18" t="n">
-        <v>1.020994847965987</v>
+        <v>1.009335124208737</v>
       </c>
       <c r="C111" s="18" t="n">
-        <v>0.7013716672980215</v>
+        <v>0.7392911842065418</v>
       </c>
       <c r="D111" s="18" t="n">
-        <v>1.486274008741997</v>
+        <v>1.378019127950062</v>
       </c>
       <c r="E111" s="18" t="n">
-        <v>0.9136372115503152</v>
+        <v>0.9533571319559171</v>
       </c>
     </row>
     <row r="112">
@@ -3329,16 +3329,16 @@
         </is>
       </c>
       <c r="B112" s="18" t="n">
-        <v>5.473082896141038</v>
+        <v>4.12481661308883</v>
       </c>
       <c r="C112" s="18" t="n">
-        <v>2.875502680800064</v>
+        <v>2.26121541167682</v>
       </c>
       <c r="D112" s="18" t="n">
-        <v>10.41718256360559</v>
+        <v>7.524321656288675</v>
       </c>
       <c r="E112" s="18" t="n">
-        <v>2.261652120766744e-07</v>
+        <v>3.833064959609256e-06</v>
       </c>
     </row>
     <row r="113">
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B113" s="18" t="n">
-        <v>0.544529545374156</v>
+        <v>0.3751055626764683</v>
       </c>
       <c r="C113" s="18" t="n">
-        <v>0.1889320027093498</v>
+        <v>0.1137622077002997</v>
       </c>
       <c r="D113" s="18" t="n">
-        <v>1.569413447871694</v>
+        <v>1.236827115042522</v>
       </c>
       <c r="E113" s="18" t="n">
-        <v>0.2603973157795424</v>
+        <v>0.1072237732158858</v>
       </c>
     </row>
     <row r="114">
@@ -3367,16 +3367,16 @@
         </is>
       </c>
       <c r="B114" s="18" t="n">
-        <v>1.000000000024621</v>
+        <v>1.000000000008232</v>
       </c>
       <c r="C114" s="18" t="n">
-        <v>0.9999997801726078</v>
+        <v>0.9999999901117067</v>
       </c>
       <c r="D114" s="18" t="n">
-        <v>1.000000219876684</v>
+        <v>1.000000009904758</v>
       </c>
       <c r="E114" s="18" t="n">
-        <v>0.9998248653140258</v>
+        <v>0.9986991357678737</v>
       </c>
     </row>
     <row r="115">
@@ -3386,16 +3386,16 @@
         </is>
       </c>
       <c r="B115" s="18" t="n">
-        <v>0.62398625728541</v>
+        <v>0.7340531014966594</v>
       </c>
       <c r="C115" s="18" t="n">
-        <v>0.3491820003457491</v>
+        <v>0.4607920889429809</v>
       </c>
       <c r="D115" s="18" t="n">
-        <v>1.115059908287148</v>
+        <v>1.169364597931587</v>
       </c>
       <c r="E115" s="18" t="n">
-        <v>0.1113227995094537</v>
+        <v>0.1931266606421584</v>
       </c>
     </row>
     <row r="116">
@@ -3405,16 +3405,16 @@
         </is>
       </c>
       <c r="B116" s="18" t="n">
-        <v>8.444678684466759</v>
+        <v>8.777159293805354</v>
       </c>
       <c r="C116" s="18" t="n">
-        <v>4.711661480659275</v>
+        <v>5.122198576593606</v>
       </c>
       <c r="D116" s="18" t="n">
-        <v>15.13533991705807</v>
+        <v>15.04012859260648</v>
       </c>
       <c r="E116" s="18" t="n">
-        <v>7.690923638873345e-13</v>
+        <v>2.68121797500056e-15</v>
       </c>
     </row>
     <row r="117">
@@ -3424,16 +3424,16 @@
         </is>
       </c>
       <c r="B117" s="18" t="n">
-        <v>2.07563477744881</v>
+        <v>2.327537305679747</v>
       </c>
       <c r="C117" s="18" t="n">
-        <v>0.7835929804545526</v>
+        <v>0.999440581525299</v>
       </c>
       <c r="D117" s="18" t="n">
-        <v>5.498083618431347</v>
+        <v>5.420462216036005</v>
       </c>
       <c r="E117" s="18" t="n">
-        <v>0.1417503031121662</v>
+        <v>0.05015184112952711</v>
       </c>
     </row>
     <row r="118">
@@ -3443,16 +3443,16 @@
         </is>
       </c>
       <c r="B118" s="18" t="n">
-        <v>5.110341067442643e-10</v>
+        <v>1.312257137754052</v>
       </c>
       <c r="C118" s="18" t="n">
-        <v>1.388794386496402e-11</v>
+        <v>0.2498565549199225</v>
       </c>
       <c r="D118" s="18" t="n">
-        <v>72004899337.38588</v>
+        <v>6.89202969335087</v>
       </c>
       <c r="E118" s="18" t="n">
-        <v>0.9992068606804133</v>
+        <v>0.748118309062591</v>
       </c>
     </row>
     <row r="119">
@@ -3462,16 +3462,16 @@
         </is>
       </c>
       <c r="B119" s="18" t="n">
-        <v>0.7947248234314505</v>
+        <v>1.068404423156355</v>
       </c>
       <c r="C119" s="18" t="n">
-        <v>0.4903705689806253</v>
+        <v>0.7149666865554479</v>
       </c>
       <c r="D119" s="18" t="n">
-        <v>1.287980121423446</v>
+        <v>1.596561116601811</v>
       </c>
       <c r="E119" s="18" t="n">
-        <v>0.3509959780772471</v>
+        <v>0.7468099217074886</v>
       </c>
     </row>
     <row r="120">
@@ -3481,16 +3481,16 @@
         </is>
       </c>
       <c r="B120" s="18" t="n">
-        <v>1.670310921380069</v>
+        <v>3.256971322462449</v>
       </c>
       <c r="C120" s="18" t="n">
-        <v>0.6941457581391319</v>
+        <v>1.582429762705717</v>
       </c>
       <c r="D120" s="18" t="n">
-        <v>4.019240255189072</v>
+        <v>6.703527982945005</v>
       </c>
       <c r="E120" s="18" t="n">
-        <v>0.2521735144254335</v>
+        <v>0.001345201039770615</v>
       </c>
     </row>
     <row r="121">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="B121" s="18" t="n">
-        <v>7.115052682665255e-10</v>
+        <v>4.080325230299868e-09</v>
       </c>
       <c r="C121" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3509,7 +3509,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E121" s="18" t="n">
-        <v>0.9994737706654728</v>
+        <v>0.9986991395238715</v>
       </c>
     </row>
     <row r="122">
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="B122" s="18" t="n">
-        <v>0.6295945767595302</v>
+        <v>0.880915301692244</v>
       </c>
       <c r="C122" s="18" t="n">
-        <v>0.2558030784235007</v>
+        <v>0.4353081995751883</v>
       </c>
       <c r="D122" s="18" t="n">
-        <v>1.549587806088715</v>
+        <v>1.782672068922288</v>
       </c>
       <c r="E122" s="18" t="n">
-        <v>0.3140085578793721</v>
+        <v>0.7244298249564071</v>
       </c>
     </row>
     <row r="123">
@@ -3538,16 +3538,16 @@
         </is>
       </c>
       <c r="B123" s="18" t="n">
-        <v>1.828222147349385</v>
+        <v>1.641381879841034</v>
       </c>
       <c r="C123" s="18" t="n">
-        <v>1.133187767426392</v>
+        <v>1.109969569955745</v>
       </c>
       <c r="D123" s="18" t="n">
-        <v>2.949551977294801</v>
+        <v>2.427214716866431</v>
       </c>
       <c r="E123" s="18" t="n">
-        <v>0.01342401970071077</v>
+        <v>0.01303995235145484</v>
       </c>
     </row>
     <row r="124">
@@ -3557,16 +3557,16 @@
         </is>
       </c>
       <c r="B124" s="18" t="n">
-        <v>2.923501446329919</v>
+        <v>1.891918730205662</v>
       </c>
       <c r="C124" s="18" t="n">
-        <v>1.692126857382446</v>
+        <v>1.153645597580414</v>
       </c>
       <c r="D124" s="18" t="n">
-        <v>5.050957420482223</v>
+        <v>3.102648238948019</v>
       </c>
       <c r="E124" s="18" t="n">
-        <v>0.000120386828779751</v>
+        <v>0.01152806364780331</v>
       </c>
     </row>
     <row r="125">
@@ -3576,16 +3576,16 @@
         </is>
       </c>
       <c r="B125" s="18" t="n">
-        <v>2.641595145431568</v>
+        <v>1.970491621083926</v>
       </c>
       <c r="C125" s="18" t="n">
-        <v>1.33047912968084</v>
+        <v>1.095507301567392</v>
       </c>
       <c r="D125" s="18" t="n">
-        <v>5.244745863876529</v>
+        <v>3.544328023379313</v>
       </c>
       <c r="E125" s="18" t="n">
-        <v>0.005503883917163984</v>
+        <v>0.02354332651863262</v>
       </c>
     </row>
     <row r="126">
@@ -3595,16 +3595,16 @@
         </is>
       </c>
       <c r="B126" s="18" t="n">
-        <v>1.258483241342104</v>
+        <v>0.8329703384904631</v>
       </c>
       <c r="C126" s="18" t="n">
-        <v>0.3506019892518297</v>
+        <v>0.2378002954022271</v>
       </c>
       <c r="D126" s="18" t="n">
-        <v>4.517316265428645</v>
+        <v>2.917740634557759</v>
       </c>
       <c r="E126" s="18" t="n">
-        <v>0.7243981688057398</v>
+        <v>0.775075164062149</v>
       </c>
     </row>
     <row r="127">
@@ -3614,16 +3614,16 @@
         </is>
       </c>
       <c r="B127" s="18" t="n">
-        <v>0.9315528133273752</v>
+        <v>1.081365288203047</v>
       </c>
       <c r="C127" s="18" t="n">
-        <v>0.8473139378031018</v>
+        <v>0.997893573000454</v>
       </c>
       <c r="D127" s="18" t="n">
-        <v>1.024166610864607</v>
+        <v>1.171819238212417</v>
       </c>
       <c r="E127" s="18" t="n">
-        <v>0.1426014608895745</v>
+        <v>0.05632439971665872</v>
       </c>
     </row>
     <row r="128">
@@ -3633,16 +3633,16 @@
         </is>
       </c>
       <c r="B128" s="18" t="n">
-        <v>1.038195618451682</v>
+        <v>1.079231918226324</v>
       </c>
       <c r="C128" s="18" t="n">
-        <v>0.9702186126052279</v>
+        <v>1.018604435202758</v>
       </c>
       <c r="D128" s="18" t="n">
-        <v>1.110935337838996</v>
+        <v>1.143467957791312</v>
       </c>
       <c r="E128" s="18" t="n">
-        <v>0.2779634572785756</v>
+        <v>0.009741894528185325</v>
       </c>
     </row>
     <row r="129">
@@ -3667,14 +3667,14 @@
       <c r="A131" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 2521,
-  "n_events": 188,
-  "llf": -580.6068941804726,
-  "aic": 1203.2137883609453,
-  "pseudo_r2_mcfadden": 0.1323359469785419,
-  "lr_vs_null_chi2": 177.10809361314568,
+  "n_obs": 2434,
+  "n_events": 135,
+  "llf": -449.17652464245737,
+  "aic": 940.3530492849147,
+  "pseudo_r2_mcfadden": 0.13914289732977303,
+  "lr_vs_null_chi2": 145.20347885242882,
   "lr_vs_null_pvalue": 0.0,
-  "n": 2525
+  "n": 2437
 }</t>
         </is>
       </c>
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="B132" s="18" t="n">
-        <v>0.04363130864346525</v>
+        <v>0.02873659766900771</v>
       </c>
       <c r="C132" s="18" t="n">
-        <v>0.02340113623837687</v>
+        <v>0.01389028834508949</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.08135037010806993</v>
+        <v>0.05945103694570558</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>6.626898695130678e-23</v>
+        <v>1.071296206806243e-21</v>
       </c>
     </row>
     <row r="133">
@@ -3709,16 +3709,16 @@
         </is>
       </c>
       <c r="B133" s="18" t="n">
-        <v>0.8367753662236633</v>
+        <v>0.7454543437731723</v>
       </c>
       <c r="C133" s="18" t="n">
-        <v>0.3919872181799608</v>
+        <v>0.309548353022944</v>
       </c>
       <c r="D133" s="18" t="n">
-        <v>1.786264911314757</v>
+        <v>1.795203150730709</v>
       </c>
       <c r="E133" s="18" t="n">
-        <v>0.6451048254172587</v>
+        <v>0.5123977101180809</v>
       </c>
     </row>
     <row r="134">
@@ -3728,16 +3728,16 @@
         </is>
       </c>
       <c r="B134" s="18" t="n">
-        <v>1.75622057749488</v>
+        <v>1.495615179721825</v>
       </c>
       <c r="C134" s="18" t="n">
-        <v>1.240656534484457</v>
+        <v>0.9991042507685065</v>
       </c>
       <c r="D134" s="18" t="n">
-        <v>2.486031090061608</v>
+        <v>2.238870232104168</v>
       </c>
       <c r="E134" s="18" t="n">
-        <v>0.001492512891929718</v>
+        <v>0.05051107851712615</v>
       </c>
     </row>
     <row r="135">
@@ -3747,16 +3747,16 @@
         </is>
       </c>
       <c r="B135" s="18" t="n">
-        <v>1.243982323774845</v>
+        <v>1.510079955811967</v>
       </c>
       <c r="C135" s="18" t="n">
-        <v>0.8754086433034645</v>
+        <v>1.014676678321648</v>
       </c>
       <c r="D135" s="18" t="n">
-        <v>1.767736740666173</v>
+        <v>2.247357726519278</v>
       </c>
       <c r="E135" s="18" t="n">
-        <v>0.2233198104369601</v>
+        <v>0.04217511867409292</v>
       </c>
     </row>
     <row r="136">
@@ -3766,16 +3766,16 @@
         </is>
       </c>
       <c r="B136" s="18" t="n">
-        <v>1.046461229658687</v>
+        <v>0.9289711411373242</v>
       </c>
       <c r="C136" s="18" t="n">
-        <v>0.6991150899697461</v>
+        <v>0.5790921486935767</v>
       </c>
       <c r="D136" s="18" t="n">
-        <v>1.566381731548892</v>
+        <v>1.490241895029779</v>
       </c>
       <c r="E136" s="18" t="n">
-        <v>0.8253453914381443</v>
+        <v>0.7599511360127995</v>
       </c>
     </row>
     <row r="137">
@@ -3785,16 +3785,16 @@
         </is>
       </c>
       <c r="B137" s="18" t="n">
-        <v>5.530902207001015</v>
+        <v>3.982466338825456</v>
       </c>
       <c r="C137" s="18" t="n">
-        <v>2.744222804289304</v>
+        <v>1.796662385241804</v>
       </c>
       <c r="D137" s="18" t="n">
-        <v>11.1473744681351</v>
+        <v>8.827500519939541</v>
       </c>
       <c r="E137" s="18" t="n">
-        <v>1.726415487561163e-06</v>
+        <v>0.0006671501911252767</v>
       </c>
     </row>
     <row r="138">
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="B138" s="18" t="n">
-        <v>0.4514993853613486</v>
+        <v>0.3331743243218874</v>
       </c>
       <c r="C138" s="18" t="n">
-        <v>0.1329739035102636</v>
+        <v>0.04391289705223417</v>
       </c>
       <c r="D138" s="18" t="n">
-        <v>1.533020311507523</v>
+        <v>2.527848031873328</v>
       </c>
       <c r="E138" s="18" t="n">
-        <v>0.2023266960036824</v>
+        <v>0.2877705234461162</v>
       </c>
     </row>
     <row r="139">
@@ -3823,16 +3823,16 @@
         </is>
       </c>
       <c r="B139" s="18" t="n">
-        <v>0.999999999854895</v>
+        <v>1.000000000063747</v>
       </c>
       <c r="C139" s="18" t="n">
-        <v>0.9999997325923143</v>
+        <v>0.9999998862684186</v>
       </c>
       <c r="D139" s="18" t="n">
-        <v>1.000000267117547</v>
+        <v>1.000000113859089</v>
       </c>
       <c r="E139" s="18" t="n">
-        <v>0.99915095199866</v>
+        <v>0.999123953545058</v>
       </c>
     </row>
     <row r="140">
@@ -3842,16 +3842,16 @@
         </is>
       </c>
       <c r="B140" s="18" t="n">
-        <v>0.4738408423987575</v>
+        <v>0.3540087573750092</v>
       </c>
       <c r="C140" s="18" t="n">
-        <v>0.2481105493357377</v>
+        <v>0.1554778984945765</v>
       </c>
       <c r="D140" s="18" t="n">
-        <v>0.9049399331317497</v>
+        <v>0.8060451132388422</v>
       </c>
       <c r="E140" s="18" t="n">
-        <v>0.02366324443146435</v>
+        <v>0.0133773125704674</v>
       </c>
     </row>
     <row r="141">
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="B141" s="18" t="n">
-        <v>6.910574375749285</v>
+        <v>6.590415915839203</v>
       </c>
       <c r="C141" s="18" t="n">
-        <v>3.823468293839909</v>
+        <v>3.440602835153112</v>
       </c>
       <c r="D141" s="18" t="n">
-        <v>12.49024041331888</v>
+        <v>12.62382902786099</v>
       </c>
       <c r="E141" s="18" t="n">
-        <v>1.543709985989811e-10</v>
+        <v>1.300350047820422e-08</v>
       </c>
     </row>
     <row r="142">
@@ -3880,16 +3880,16 @@
         </is>
       </c>
       <c r="B142" s="18" t="n">
-        <v>1.12729182712519</v>
+        <v>1.481166595646278</v>
       </c>
       <c r="C142" s="18" t="n">
-        <v>0.372215865716208</v>
+        <v>0.4703513614694408</v>
       </c>
       <c r="D142" s="18" t="n">
-        <v>3.414112563573922</v>
+        <v>4.664288580359349</v>
       </c>
       <c r="E142" s="18" t="n">
-        <v>0.8321618368320125</v>
+        <v>0.5020955681505876</v>
       </c>
     </row>
     <row r="143">
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="B143" s="18" t="n">
-        <v>8.547062639071912e-10</v>
+        <v>1.235483546525378e-09</v>
       </c>
       <c r="C143" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3908,7 +3908,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E143" s="18" t="n">
-        <v>0.9989577186999676</v>
+        <v>0.9989964890967161</v>
       </c>
     </row>
     <row r="144">
@@ -3918,16 +3918,16 @@
         </is>
       </c>
       <c r="B144" s="18" t="n">
-        <v>0.6931726148542389</v>
+        <v>0.6451174629080526</v>
       </c>
       <c r="C144" s="18" t="n">
-        <v>0.4149129396065503</v>
+        <v>0.3650729045618365</v>
       </c>
       <c r="D144" s="18" t="n">
-        <v>1.158046009458022</v>
+        <v>1.139982002905478</v>
       </c>
       <c r="E144" s="18" t="n">
-        <v>0.1616383777105939</v>
+        <v>0.1313122487643803</v>
       </c>
     </row>
     <row r="145">
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="B145" s="18" t="n">
-        <v>1.75659119782004</v>
+        <v>1.840029631518581</v>
       </c>
       <c r="C145" s="18" t="n">
-        <v>0.7105742574998318</v>
+        <v>0.7120910548761145</v>
       </c>
       <c r="D145" s="18" t="n">
-        <v>4.342421082232316</v>
+        <v>4.754601285442957</v>
       </c>
       <c r="E145" s="18" t="n">
-        <v>0.2224542073301841</v>
+        <v>0.2080523296993451</v>
       </c>
     </row>
     <row r="146">
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="B146" s="18" t="n">
-        <v>1.778887478333027e-09</v>
+        <v>2.03916967908748e-09</v>
       </c>
       <c r="C146" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3965,7 +3965,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E146" s="18" t="n">
-        <v>0.9993308193721876</v>
+        <v>0.9993356750490124</v>
       </c>
     </row>
     <row r="147">
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="B147" s="18" t="n">
-        <v>0.7211873930185499</v>
+        <v>0.7584089130850494</v>
       </c>
       <c r="C147" s="18" t="n">
-        <v>0.2908392318501625</v>
+        <v>0.2817820623700151</v>
       </c>
       <c r="D147" s="18" t="n">
-        <v>1.78831188811848</v>
+        <v>2.041237382568225</v>
       </c>
       <c r="E147" s="18" t="n">
-        <v>0.4805388967759936</v>
+        <v>0.584090564922207</v>
       </c>
     </row>
     <row r="148">
@@ -3994,16 +3994,16 @@
         </is>
       </c>
       <c r="B148" s="18" t="n">
-        <v>1.750492570098143</v>
+        <v>2.59214065277174</v>
       </c>
       <c r="C148" s="18" t="n">
-        <v>1.060749396389155</v>
+        <v>1.515815680851988</v>
       </c>
       <c r="D148" s="18" t="n">
-        <v>2.888735311469023</v>
+        <v>4.432724406159513</v>
       </c>
       <c r="E148" s="18" t="n">
-        <v>0.02847213972373774</v>
+        <v>0.0005024304476387489</v>
       </c>
     </row>
     <row r="149">
@@ -4013,16 +4013,16 @@
         </is>
       </c>
       <c r="B149" s="18" t="n">
-        <v>2.111799843108331</v>
+        <v>2.506751951333646</v>
       </c>
       <c r="C149" s="18" t="n">
-        <v>1.155935454318834</v>
+        <v>1.249076476177774</v>
       </c>
       <c r="D149" s="18" t="n">
-        <v>3.858086159300625</v>
+        <v>5.030761098586816</v>
       </c>
       <c r="E149" s="18" t="n">
-        <v>0.01504635624762385</v>
+        <v>0.009717038490356433</v>
       </c>
     </row>
     <row r="150">
@@ -4032,16 +4032,16 @@
         </is>
       </c>
       <c r="B150" s="18" t="n">
-        <v>2.399736053179221</v>
+        <v>2.970223731957207</v>
       </c>
       <c r="C150" s="18" t="n">
-        <v>1.167875214211356</v>
+        <v>1.298498008382541</v>
       </c>
       <c r="D150" s="18" t="n">
-        <v>4.930949004527807</v>
+        <v>6.794179860830979</v>
       </c>
       <c r="E150" s="18" t="n">
-        <v>0.01720460371182364</v>
+        <v>0.009917337906614931</v>
       </c>
     </row>
     <row r="151">
@@ -4051,16 +4051,16 @@
         </is>
       </c>
       <c r="B151" s="18" t="n">
-        <v>1.596500572743153</v>
+        <v>1.778902956582448</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>0.4240292548313608</v>
+        <v>0.3694899866719728</v>
       </c>
       <c r="D151" s="18" t="n">
-        <v>6.010939221122599</v>
+        <v>8.564496584713032</v>
       </c>
       <c r="E151" s="18" t="n">
-        <v>0.4891893343829928</v>
+        <v>0.4725596422928534</v>
       </c>
     </row>
     <row r="152">
@@ -4070,16 +4070,16 @@
         </is>
       </c>
       <c r="B152" s="18" t="n">
-        <v>0.9430109003645007</v>
+        <v>0.9621951879233196</v>
       </c>
       <c r="C152" s="18" t="n">
-        <v>0.8532657096965484</v>
+        <v>0.856846250666813</v>
       </c>
       <c r="D152" s="18" t="n">
-        <v>1.042195353804294</v>
+        <v>1.080496738991742</v>
       </c>
       <c r="E152" s="18" t="n">
-        <v>0.2501529542629989</v>
+        <v>0.5148027028599738</v>
       </c>
     </row>
     <row r="153">
@@ -4089,16 +4089,16 @@
         </is>
       </c>
       <c r="B153" s="18" t="n">
-        <v>1.077816640081945</v>
+        <v>1.058225251336471</v>
       </c>
       <c r="C153" s="18" t="n">
-        <v>1.000062832099851</v>
+        <v>0.971595279415577</v>
       </c>
       <c r="D153" s="18" t="n">
-        <v>1.161615722882444</v>
+        <v>1.152579377742275</v>
       </c>
       <c r="E153" s="18" t="n">
-        <v>0.04980806252637921</v>
+        <v>0.1940477394853283</v>
       </c>
     </row>
     <row r="154">
@@ -4123,14 +4123,14 @@
       <c r="A156" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3717,
-  "n_events": 193,
-  "llf": -651.0944143756712,
-  "aic": 1344.1888287513425,
-  "pseudo_r2_mcfadden": 0.14229297228102877,
-  "lr_vs_null_chi2": 216.0321799005842,
+  "n_obs": 3581,
+  "n_events": 136,
+  "llf": -493.0043293715282,
+  "aic": 1028.0086587430565,
+  "pseudo_r2_mcfadden": 0.1476391139435388,
+  "lr_vs_null_chi2": 170.78850883338043,
   "lr_vs_null_pvalue": 0.0,
-  "n": 3723
+  "n": 3586
 }</t>
         </is>
       </c>
@@ -4146,16 +4146,16 @@
         </is>
       </c>
       <c r="B157" s="18" t="n">
-        <v>0.03100129671872217</v>
+        <v>0.01953506927865708</v>
       </c>
       <c r="C157" s="18" t="n">
-        <v>0.01694356078479456</v>
+        <v>0.009562664563447947</v>
       </c>
       <c r="D157" s="18" t="n">
-        <v>0.05672245701179554</v>
+        <v>0.03990717536831953</v>
       </c>
       <c r="E157" s="18" t="n">
-        <v>1.855879669272762e-29</v>
+        <v>3.516290784193386e-27</v>
       </c>
     </row>
     <row r="158">
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="B158" s="18" t="n">
-        <v>0.7150318147426775</v>
+        <v>0.6096255484173594</v>
       </c>
       <c r="C158" s="18" t="n">
-        <v>0.3414272777287525</v>
+        <v>0.2545718422536157</v>
       </c>
       <c r="D158" s="18" t="n">
-        <v>1.497450641598667</v>
+        <v>1.459875946974995</v>
       </c>
       <c r="E158" s="18" t="n">
-        <v>0.3737956944075218</v>
+        <v>0.2666607318643098</v>
       </c>
     </row>
     <row r="159">
@@ -4184,16 +4184,16 @@
         </is>
       </c>
       <c r="B159" s="18" t="n">
-        <v>2.072147125881193</v>
+        <v>1.716424067460524</v>
       </c>
       <c r="C159" s="18" t="n">
-        <v>1.475059846025695</v>
+        <v>1.15185209922663</v>
       </c>
       <c r="D159" s="18" t="n">
-        <v>2.910928477150679</v>
+        <v>2.557716899014892</v>
       </c>
       <c r="E159" s="18" t="n">
-        <v>2.652668493025389e-05</v>
+        <v>0.007939566197287787</v>
       </c>
     </row>
     <row r="160">
@@ -4203,16 +4203,16 @@
         </is>
       </c>
       <c r="B160" s="18" t="n">
-        <v>1.231457338257394</v>
+        <v>1.446326856295562</v>
       </c>
       <c r="C160" s="18" t="n">
-        <v>0.8736264681971518</v>
+        <v>0.9746403848079587</v>
       </c>
       <c r="D160" s="18" t="n">
-        <v>1.735853057517208</v>
+        <v>2.146290475798393</v>
       </c>
       <c r="E160" s="18" t="n">
-        <v>0.234581073474619</v>
+        <v>0.06688949410937578</v>
       </c>
     </row>
     <row r="161">
@@ -4222,16 +4222,16 @@
         </is>
       </c>
       <c r="B161" s="18" t="n">
-        <v>1.043205914738665</v>
+        <v>0.9368432096910522</v>
       </c>
       <c r="C161" s="18" t="n">
-        <v>0.705177134727242</v>
+        <v>0.5897413993936332</v>
       </c>
       <c r="D161" s="18" t="n">
-        <v>1.543269806906989</v>
+        <v>1.488237387517055</v>
       </c>
       <c r="E161" s="18" t="n">
-        <v>0.8323391879185403</v>
+        <v>0.7823403295620788</v>
       </c>
     </row>
     <row r="162">
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="B162" s="18" t="n">
-        <v>6.098413824737721</v>
+        <v>4.304107020932759</v>
       </c>
       <c r="C162" s="18" t="n">
-        <v>3.134312628284531</v>
+        <v>1.986813219808815</v>
       </c>
       <c r="D162" s="18" t="n">
-        <v>11.8656482579746</v>
+        <v>9.324146358068479</v>
       </c>
       <c r="E162" s="18" t="n">
-        <v>1.015799091084381e-07</v>
+        <v>0.0002150896403856845</v>
       </c>
     </row>
     <row r="163">
@@ -4260,16 +4260,16 @@
         </is>
       </c>
       <c r="B163" s="18" t="n">
-        <v>0.4348271502381356</v>
+        <v>0.3178202023962297</v>
       </c>
       <c r="C163" s="18" t="n">
-        <v>0.1301058082141819</v>
+        <v>0.0423525399707109</v>
       </c>
       <c r="D163" s="18" t="n">
-        <v>1.453237585465523</v>
+        <v>2.384973395244634</v>
       </c>
       <c r="E163" s="18" t="n">
-        <v>0.176124338010709</v>
+        <v>0.2649755002440306</v>
       </c>
     </row>
     <row r="164">
@@ -4279,16 +4279,16 @@
         </is>
       </c>
       <c r="B164" s="18" t="n">
-        <v>0.9999999999186785</v>
+        <v>1.000000000022869</v>
       </c>
       <c r="C164" s="18" t="n">
-        <v>0.9999998288546924</v>
+        <v>0.9999999631677073</v>
       </c>
       <c r="D164" s="18" t="n">
-        <v>1.000000170982694</v>
+        <v>1.000000036878032</v>
       </c>
       <c r="E164" s="18" t="n">
-        <v>0.9992565788374325</v>
+        <v>0.9990296223841052</v>
       </c>
     </row>
     <row r="165">
@@ -4298,16 +4298,16 @@
         </is>
       </c>
       <c r="B165" s="18" t="n">
-        <v>0.5167956980295385</v>
+        <v>0.3908098791584043</v>
       </c>
       <c r="C165" s="18" t="n">
-        <v>0.2725848475576154</v>
+        <v>0.173182058349294</v>
       </c>
       <c r="D165" s="18" t="n">
-        <v>0.9797969178950294</v>
+        <v>0.8819179255841729</v>
       </c>
       <c r="E165" s="18" t="n">
-        <v>0.0431249442048128</v>
+        <v>0.02366240100356966</v>
       </c>
     </row>
     <row r="166">
@@ -4317,16 +4317,16 @@
         </is>
       </c>
       <c r="B166" s="18" t="n">
-        <v>8.600413345423584</v>
+        <v>7.955380933271055</v>
       </c>
       <c r="C166" s="18" t="n">
-        <v>4.757220482490345</v>
+        <v>4.118706775327086</v>
       </c>
       <c r="D166" s="18" t="n">
-        <v>15.54838796822367</v>
+        <v>15.3660091008607</v>
       </c>
       <c r="E166" s="18" t="n">
-        <v>1.061092590082541e-12</v>
+        <v>6.641304148816224e-10</v>
       </c>
     </row>
     <row r="167">
@@ -4336,16 +4336,16 @@
         </is>
       </c>
       <c r="B167" s="18" t="n">
-        <v>1.734462027176505</v>
+        <v>1.856165459194713</v>
       </c>
       <c r="C167" s="18" t="n">
-        <v>0.6175440705272582</v>
+        <v>0.5971042525803348</v>
       </c>
       <c r="D167" s="18" t="n">
-        <v>4.871487991373149</v>
+        <v>5.770098265116576</v>
       </c>
       <c r="E167" s="18" t="n">
-        <v>0.2959454935688725</v>
+        <v>0.2851379017688556</v>
       </c>
     </row>
     <row r="168">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="B168" s="18" t="n">
-        <v>5.056238745370455e-10</v>
+        <v>1.789472038703356e-09</v>
       </c>
       <c r="C168" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4364,7 +4364,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E168" s="18" t="n">
-        <v>0.9991996755193954</v>
+        <v>0.9988519205336038</v>
       </c>
     </row>
     <row r="169">
@@ -4374,16 +4374,16 @@
         </is>
       </c>
       <c r="B169" s="18" t="n">
-        <v>0.7434836808352291</v>
+        <v>0.6955954957839608</v>
       </c>
       <c r="C169" s="18" t="n">
-        <v>0.4469066364251899</v>
+        <v>0.3927276018859978</v>
       </c>
       <c r="D169" s="18" t="n">
-        <v>1.23687575572808</v>
+        <v>1.232032307969504</v>
       </c>
       <c r="E169" s="18" t="n">
-        <v>0.2537193514613728</v>
+        <v>0.2133024724472922</v>
       </c>
     </row>
     <row r="170">
@@ -4393,16 +4393,16 @@
         </is>
       </c>
       <c r="B170" s="18" t="n">
-        <v>1.821561298414603</v>
+        <v>1.996776164266147</v>
       </c>
       <c r="C170" s="18" t="n">
-        <v>0.7498929489128719</v>
+        <v>0.7820694794448176</v>
       </c>
       <c r="D170" s="18" t="n">
-        <v>4.424745650285363</v>
+        <v>5.098159632839574</v>
       </c>
       <c r="E170" s="18" t="n">
-        <v>0.1853894168502391</v>
+        <v>0.1481832340284055</v>
       </c>
     </row>
     <row r="171">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="B171" s="18" t="n">
-        <v>7.709877016853058e-10</v>
+        <v>2.469497370580487e-09</v>
       </c>
       <c r="C171" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4421,7 +4421,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E171" s="18" t="n">
-        <v>0.9994745498615001</v>
+        <v>0.9991854837883326</v>
       </c>
     </row>
     <row r="172">
@@ -4431,16 +4431,16 @@
         </is>
       </c>
       <c r="B172" s="18" t="n">
-        <v>0.6693454840649947</v>
+        <v>0.7258599830592388</v>
       </c>
       <c r="C172" s="18" t="n">
-        <v>0.2693990584096177</v>
+        <v>0.2694100144389456</v>
       </c>
       <c r="D172" s="18" t="n">
-        <v>1.663047301215836</v>
+        <v>1.955653787050145</v>
       </c>
       <c r="E172" s="18" t="n">
-        <v>0.3872830685344942</v>
+        <v>0.5263461950935866</v>
       </c>
     </row>
     <row r="173">
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="B173" s="18" t="n">
-        <v>1.816074625029992</v>
+        <v>2.827357002169177</v>
       </c>
       <c r="C173" s="18" t="n">
-        <v>1.104607899864972</v>
+        <v>1.645451273659307</v>
       </c>
       <c r="D173" s="18" t="n">
-        <v>2.98578983916464</v>
+        <v>4.858209869647124</v>
       </c>
       <c r="E173" s="18" t="n">
-        <v>0.0186644495147789</v>
+        <v>0.0001678158387805632</v>
       </c>
     </row>
     <row r="174">
@@ -4469,16 +4469,16 @@
         </is>
       </c>
       <c r="B174" s="18" t="n">
-        <v>2.371076262941582</v>
+        <v>2.814978130955091</v>
       </c>
       <c r="C174" s="18" t="n">
-        <v>1.304690715213044</v>
+        <v>1.411454416006161</v>
       </c>
       <c r="D174" s="18" t="n">
-        <v>4.309069252299383</v>
+        <v>5.614139420936729</v>
       </c>
       <c r="E174" s="18" t="n">
-        <v>0.004617347076342188</v>
+        <v>0.003299162535870483</v>
       </c>
     </row>
     <row r="175">
@@ -4488,16 +4488,16 @@
         </is>
       </c>
       <c r="B175" s="18" t="n">
-        <v>2.773688972599852</v>
+        <v>3.072344152958648</v>
       </c>
       <c r="C175" s="18" t="n">
-        <v>1.36362772124516</v>
+        <v>1.347045123080388</v>
       </c>
       <c r="D175" s="18" t="n">
-        <v>5.641826135433098</v>
+        <v>7.007410837607017</v>
       </c>
       <c r="E175" s="18" t="n">
-        <v>0.004861092716051891</v>
+        <v>0.007627550624955167</v>
       </c>
     </row>
     <row r="176">
@@ -4507,16 +4507,16 @@
         </is>
       </c>
       <c r="B176" s="18" t="n">
-        <v>1.363877952718846</v>
+        <v>1.686266810201704</v>
       </c>
       <c r="C176" s="18" t="n">
-        <v>0.3739360326313018</v>
+        <v>0.3640462550103681</v>
       </c>
       <c r="D176" s="18" t="n">
-        <v>4.974548873568054</v>
+        <v>7.810808972906056</v>
       </c>
       <c r="E176" s="18" t="n">
-        <v>0.6383227355345196</v>
+        <v>0.5041017769530478</v>
       </c>
     </row>
     <row r="177">
@@ -4526,16 +4526,16 @@
         </is>
       </c>
       <c r="B177" s="18" t="n">
-        <v>0.9335220944450449</v>
+        <v>0.9547938394703017</v>
       </c>
       <c r="C177" s="18" t="n">
-        <v>0.8462624530058837</v>
+        <v>0.850665716200407</v>
       </c>
       <c r="D177" s="18" t="n">
-        <v>1.029779234233619</v>
+        <v>1.071668057768147</v>
       </c>
       <c r="E177" s="18" t="n">
-        <v>0.169474659107431</v>
+        <v>0.4323581517656722</v>
       </c>
     </row>
     <row r="178">
@@ -4545,16 +4545,16 @@
         </is>
       </c>
       <c r="B178" s="18" t="n">
-        <v>1.044178307246225</v>
+        <v>1.040102992495496</v>
       </c>
       <c r="C178" s="18" t="n">
-        <v>0.974356721352632</v>
+        <v>0.9602796047317756</v>
       </c>
       <c r="D178" s="18" t="n">
-        <v>1.119003249456721</v>
+        <v>1.126561711471793</v>
       </c>
       <c r="E178" s="18" t="n">
-        <v>0.2208481672060447</v>
+        <v>0.3344850994973525</v>
       </c>
     </row>
     <row r="179">
@@ -4579,12 +4579,12 @@
       <c r="A181" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 193,
-  "llf": -659.833331011966,
-  "aic": 1359.666662023932,
-  "pseudo_r2_mcfadden": 0.13277867633378282,
-  "lr_vs_null_chi2": 202.05175749668342,
+  "n_obs": 3614,
+  "n_events": 136,
+  "llf": -496.9290777116455,
+  "aic": 1033.858155423291,
+  "pseudo_r2_mcfadden": 0.14273578552187915,
+  "lr_vs_null_chi2": 165.47888284130613,
   "lr_vs_null_pvalue": 0.0
 }</t>
         </is>
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="B182" s="18" t="n">
-        <v>0.02527058313800203</v>
+        <v>0.01527566712342721</v>
       </c>
       <c r="C182" s="18" t="n">
-        <v>0.01426522477669402</v>
+        <v>0.007746898338719528</v>
       </c>
       <c r="D182" s="18" t="n">
-        <v>0.04476637291954885</v>
+        <v>0.03012121701655431</v>
       </c>
       <c r="E182" s="18" t="n">
-        <v>1.928487978383358e-36</v>
+        <v>1.509774706019216e-33</v>
       </c>
     </row>
     <row r="183">
@@ -4620,16 +4620,16 @@
         </is>
       </c>
       <c r="B183" s="18" t="n">
-        <v>0.6039166233799963</v>
+        <v>0.5031277284367919</v>
       </c>
       <c r="C183" s="18" t="n">
-        <v>0.2889105819236581</v>
+        <v>0.2098732173713009</v>
       </c>
       <c r="D183" s="18" t="n">
-        <v>1.26238120309165</v>
+        <v>1.206144901634226</v>
       </c>
       <c r="E183" s="18" t="n">
-        <v>0.1800514146595602</v>
+        <v>0.123605820230975</v>
       </c>
     </row>
     <row r="184">
@@ -4639,16 +4639,16 @@
         </is>
       </c>
       <c r="B184" s="18" t="n">
-        <v>2.069652404189313</v>
+        <v>1.684371421115171</v>
       </c>
       <c r="C184" s="18" t="n">
-        <v>1.476685616213492</v>
+        <v>1.131688651980055</v>
       </c>
       <c r="D184" s="18" t="n">
-        <v>2.900726483102225</v>
+        <v>2.506967865504004</v>
       </c>
       <c r="E184" s="18" t="n">
-        <v>2.409536762635444e-05</v>
+        <v>0.01017953779929671</v>
       </c>
     </row>
     <row r="185">
@@ -4658,16 +4658,16 @@
         </is>
       </c>
       <c r="B185" s="18" t="n">
-        <v>1.164320594150314</v>
+        <v>1.375834486329633</v>
       </c>
       <c r="C185" s="18" t="n">
-        <v>0.8277340060898324</v>
+        <v>0.9285388266972096</v>
       </c>
       <c r="D185" s="18" t="n">
-        <v>1.637775464084793</v>
+        <v>2.03860138030738</v>
       </c>
       <c r="E185" s="18" t="n">
-        <v>0.3821586862064008</v>
+        <v>0.1117469095721779</v>
       </c>
     </row>
     <row r="186">
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="B186" s="18" t="n">
-        <v>0.6567404076767659</v>
+        <v>0.5011833962713644</v>
       </c>
       <c r="C186" s="18" t="n">
-        <v>0.3455271301133249</v>
+        <v>0.2210249599493112</v>
       </c>
       <c r="D186" s="18" t="n">
-        <v>1.248260774585155</v>
+        <v>1.136454438248536</v>
       </c>
       <c r="E186" s="18" t="n">
-        <v>0.1994190645217789</v>
+        <v>0.0981805796384166</v>
       </c>
     </row>
     <row r="187">
@@ -4696,16 +4696,16 @@
         </is>
       </c>
       <c r="B187" s="18" t="n">
-        <v>7.436080604949479</v>
+        <v>6.867626636443525</v>
       </c>
       <c r="C187" s="18" t="n">
-        <v>4.077585818484178</v>
+        <v>3.536911224745978</v>
       </c>
       <c r="D187" s="18" t="n">
-        <v>13.56079239648267</v>
+        <v>13.33488250640952</v>
       </c>
       <c r="E187" s="18" t="n">
-        <v>5.958038260080889e-11</v>
+        <v>1.26132702817347e-08</v>
       </c>
     </row>
     <row r="188">
@@ -4715,16 +4715,16 @@
         </is>
       </c>
       <c r="B188" s="18" t="n">
-        <v>2.010418509520878</v>
+        <v>2.122372383439231</v>
       </c>
       <c r="C188" s="18" t="n">
-        <v>0.7091941804292959</v>
+        <v>0.6744496807369255</v>
       </c>
       <c r="D188" s="18" t="n">
-        <v>5.699119782649007</v>
+        <v>6.678725874795873</v>
       </c>
       <c r="E188" s="18" t="n">
-        <v>0.1889819111102734</v>
+        <v>0.1982362787754893</v>
       </c>
     </row>
     <row r="189">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="B189" s="18" t="n">
-        <v>6.590067645738035e-10</v>
+        <v>2.060937065358087e-09</v>
       </c>
       <c r="C189" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4743,7 +4743,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E189" s="18" t="n">
-        <v>0.9992343727220721</v>
+        <v>0.9988701752910393</v>
       </c>
     </row>
     <row r="190">
@@ -4753,16 +4753,16 @@
         </is>
       </c>
       <c r="B190" s="18" t="n">
-        <v>0.6935195757366641</v>
+        <v>0.6423922425664046</v>
       </c>
       <c r="C190" s="18" t="n">
-        <v>0.4171511104288705</v>
+        <v>0.3633293205897405</v>
       </c>
       <c r="D190" s="18" t="n">
-        <v>1.152986028097782</v>
+        <v>1.135795461372811</v>
       </c>
       <c r="E190" s="18" t="n">
-        <v>0.1582188256733409</v>
+        <v>0.1279992045728094</v>
       </c>
     </row>
     <row r="191">
@@ -4772,16 +4772,16 @@
         </is>
       </c>
       <c r="B191" s="18" t="n">
-        <v>1.306259139061344</v>
+        <v>1.401570231942669</v>
       </c>
       <c r="C191" s="18" t="n">
-        <v>0.5304357610650219</v>
+        <v>0.536698768747552</v>
       </c>
       <c r="D191" s="18" t="n">
-        <v>3.216813540164239</v>
+        <v>3.660152080564631</v>
       </c>
       <c r="E191" s="18" t="n">
-        <v>0.56121989692881</v>
+        <v>0.4906321884097089</v>
       </c>
     </row>
     <row r="192">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="B192" s="18" t="n">
-        <v>9.34662820712118e-10</v>
+        <v>3.069500713690255e-09</v>
       </c>
       <c r="C192" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4800,7 +4800,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E192" s="18" t="n">
-        <v>0.9994812248496244</v>
+        <v>0.9991966758540968</v>
       </c>
     </row>
     <row r="193">
@@ -4810,16 +4810,16 @@
         </is>
       </c>
       <c r="B193" s="18" t="n">
-        <v>0.7295399806870587</v>
+        <v>0.8021109116458051</v>
       </c>
       <c r="C193" s="18" t="n">
-        <v>0.2997925295712148</v>
+        <v>0.3030213527934861</v>
       </c>
       <c r="D193" s="18" t="n">
-        <v>1.775323034840482</v>
+        <v>2.123223029169629</v>
       </c>
       <c r="E193" s="18" t="n">
-        <v>0.4870712439830762</v>
+        <v>0.6570577871898373</v>
       </c>
     </row>
     <row r="194">
@@ -4829,16 +4829,16 @@
         </is>
       </c>
       <c r="B194" s="18" t="n">
-        <v>1.557823600479261</v>
+        <v>2.385775889093684</v>
       </c>
       <c r="C194" s="18" t="n">
-        <v>0.9541886495043181</v>
+        <v>1.395734922282749</v>
       </c>
       <c r="D194" s="18" t="n">
-        <v>2.543327644350883</v>
+        <v>4.078085675230874</v>
       </c>
       <c r="E194" s="18" t="n">
-        <v>0.0763178709251582</v>
+        <v>0.001478182032799388</v>
       </c>
     </row>
     <row r="195">
@@ -4848,16 +4848,16 @@
         </is>
       </c>
       <c r="B195" s="18" t="n">
-        <v>2.105749074656395</v>
+        <v>2.493939761356206</v>
       </c>
       <c r="C195" s="18" t="n">
-        <v>1.160750223888297</v>
+        <v>1.25024621199284</v>
       </c>
       <c r="D195" s="18" t="n">
-        <v>3.820097618041022</v>
+        <v>4.974808540598939</v>
       </c>
       <c r="E195" s="18" t="n">
-        <v>0.01426583045112131</v>
+        <v>0.009489735325845579</v>
       </c>
     </row>
     <row r="196">
@@ -4867,16 +4867,16 @@
         </is>
       </c>
       <c r="B196" s="18" t="n">
-        <v>2.549493737205072</v>
+        <v>2.991198022022297</v>
       </c>
       <c r="C196" s="18" t="n">
-        <v>1.265842431421196</v>
+        <v>1.324422895135984</v>
       </c>
       <c r="D196" s="18" t="n">
-        <v>5.13485577249156</v>
+        <v>6.755595693648479</v>
       </c>
       <c r="E196" s="18" t="n">
-        <v>0.00879633214983817</v>
+        <v>0.008390799930375519</v>
       </c>
     </row>
     <row r="197">
@@ -4886,16 +4886,16 @@
         </is>
       </c>
       <c r="B197" s="18" t="n">
-        <v>1.073131678980225</v>
+        <v>1.264927777174557</v>
       </c>
       <c r="C197" s="18" t="n">
-        <v>0.2999893107247148</v>
+        <v>0.2757093396250549</v>
       </c>
       <c r="D197" s="18" t="n">
-        <v>3.838842116236913</v>
+        <v>5.803366268417712</v>
       </c>
       <c r="E197" s="18" t="n">
-        <v>0.9135719530365902</v>
+        <v>0.7623782557603859</v>
       </c>
     </row>
     <row r="198">
@@ -4905,16 +4905,16 @@
         </is>
       </c>
       <c r="B198" s="18" t="n">
-        <v>0.9548960230641651</v>
+        <v>0.9758298459224014</v>
       </c>
       <c r="C198" s="18" t="n">
-        <v>0.8651420681624363</v>
+        <v>0.8689100552174756</v>
       </c>
       <c r="D198" s="18" t="n">
-        <v>1.053961480338692</v>
+        <v>1.095906167128662</v>
       </c>
       <c r="E198" s="18" t="n">
-        <v>0.3594508049613295</v>
+        <v>0.6794396321133429</v>
       </c>
     </row>
     <row r="199">
@@ -4924,16 +4924,16 @@
         </is>
       </c>
       <c r="B199" s="18" t="n">
-        <v>1.033054487912812</v>
+        <v>1.023118280864582</v>
       </c>
       <c r="C199" s="18" t="n">
-        <v>0.9641189520244976</v>
+        <v>0.9440806366616863</v>
       </c>
       <c r="D199" s="18" t="n">
-        <v>1.10691898832177</v>
+        <v>1.108772890778408</v>
       </c>
       <c r="E199" s="18" t="n">
-        <v>0.3560447049649573</v>
+        <v>0.5774165688516302</v>
       </c>
     </row>
     <row r="200">
@@ -4943,16 +4943,16 @@
         </is>
       </c>
       <c r="B200" s="18" t="n">
-        <v>1.800179828941329</v>
+        <v>1.632421667229149</v>
       </c>
       <c r="C200" s="18" t="n">
-        <v>1.247354508266999</v>
+        <v>1.062541514503287</v>
       </c>
       <c r="D200" s="18" t="n">
-        <v>2.59801635785932</v>
+        <v>2.50794953727989</v>
       </c>
       <c r="E200" s="18" t="n">
-        <v>0.001684910862556366</v>
+        <v>0.02529560500616445</v>
       </c>
     </row>
     <row r="201">
@@ -4962,16 +4962,16 @@
         </is>
       </c>
       <c r="B201" s="18" t="n">
-        <v>1.655559000418064</v>
+        <v>1.767989818112829</v>
       </c>
       <c r="C201" s="18" t="n">
-        <v>1.096379543961563</v>
+        <v>1.10146246559686</v>
       </c>
       <c r="D201" s="18" t="n">
-        <v>2.499933183687115</v>
+        <v>2.837852486654489</v>
       </c>
       <c r="E201" s="18" t="n">
-        <v>0.01650482846874887</v>
+        <v>0.01826350873942186</v>
       </c>
     </row>
     <row r="202">
@@ -4996,12 +4996,12 @@
       <c r="A204" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 193,
-  "llf": -658.3184800480203,
-  "aic": 1344.6369600960406,
-  "pseudo_r2_mcfadden": 0.13476965041218425,
-  "lr_vs_null_chi2": 205.08145942457486,
+  "n_obs": 3614,
+  "n_events": 136,
+  "llf": -500.11894238869394,
+  "aic": 1028.237884777388,
+  "pseudo_r2_mcfadden": 0.13723287382016502,
+  "lr_vs_null_chi2": 159.09915348720926,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + lvi_pooled"
 }</t>
@@ -5019,16 +5019,16 @@
         </is>
       </c>
       <c r="B205" s="18" t="n">
-        <v>0.03025297803333175</v>
+        <v>0.01992543195335608</v>
       </c>
       <c r="C205" s="18" t="n">
-        <v>0.01660684821435115</v>
+        <v>0.009840989174055141</v>
       </c>
       <c r="D205" s="18" t="n">
-        <v>0.05511236497569284</v>
+        <v>0.04034379385098172</v>
       </c>
       <c r="E205" s="18" t="n">
-        <v>2.916536869114584e-30</v>
+        <v>1.445691349906032e-27</v>
       </c>
     </row>
     <row r="206">
@@ -5038,16 +5038,16 @@
         </is>
       </c>
       <c r="B206" s="18" t="n">
-        <v>0.6100869727686163</v>
+        <v>0.4895256888370385</v>
       </c>
       <c r="C206" s="18" t="n">
-        <v>0.2939203669109388</v>
+        <v>0.2067918062003167</v>
       </c>
       <c r="D206" s="18" t="n">
-        <v>1.266350196326331</v>
+        <v>1.158824444906899</v>
       </c>
       <c r="E206" s="18" t="n">
-        <v>0.1847691787131558</v>
+        <v>0.1042278452778389</v>
       </c>
     </row>
     <row r="207">
@@ -5057,16 +5057,16 @@
         </is>
       </c>
       <c r="B207" s="18" t="n">
-        <v>2.026213731383377</v>
+        <v>1.711964390606363</v>
       </c>
       <c r="C207" s="18" t="n">
-        <v>1.447493115419733</v>
+        <v>1.154236802428198</v>
       </c>
       <c r="D207" s="18" t="n">
-        <v>2.836311994517537</v>
+        <v>2.53918612587865</v>
       </c>
       <c r="E207" s="18" t="n">
-        <v>3.869593260788055e-05</v>
+        <v>0.007514462507373454</v>
       </c>
     </row>
     <row r="208">
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="B208" s="18" t="n">
-        <v>1.266110506409792</v>
+        <v>1.512901057508101</v>
       </c>
       <c r="C208" s="18" t="n">
-        <v>0.9004487312533399</v>
+        <v>1.022562733807301</v>
       </c>
       <c r="D208" s="18" t="n">
-        <v>1.780263282963356</v>
+        <v>2.238365954611897</v>
       </c>
       <c r="E208" s="18" t="n">
-        <v>0.1748079559961424</v>
+        <v>0.03830254426886286</v>
       </c>
     </row>
     <row r="209">
@@ -5095,16 +5095,16 @@
         </is>
       </c>
       <c r="B209" s="18" t="n">
-        <v>1.032497406626194</v>
+        <v>0.9406145686508145</v>
       </c>
       <c r="C209" s="18" t="n">
-        <v>0.6993979467630532</v>
+        <v>0.5942649269512084</v>
       </c>
       <c r="D209" s="18" t="n">
-        <v>1.52424081257845</v>
+        <v>1.488823800013357</v>
       </c>
       <c r="E209" s="18" t="n">
-        <v>0.8721568293672328</v>
+        <v>0.7938587271365076</v>
       </c>
     </row>
     <row r="210">
@@ -5114,16 +5114,16 @@
         </is>
       </c>
       <c r="B210" s="18" t="n">
-        <v>4.8616189778203</v>
+        <v>3.499707186845904</v>
       </c>
       <c r="C210" s="18" t="n">
-        <v>2.543858438456445</v>
+        <v>1.64951899959648</v>
       </c>
       <c r="D210" s="18" t="n">
-        <v>9.291137717491813</v>
+        <v>7.425164788436553</v>
       </c>
       <c r="E210" s="18" t="n">
-        <v>1.706762192734391e-06</v>
+        <v>0.001098305664437754</v>
       </c>
     </row>
     <row r="211">
@@ -5133,16 +5133,16 @@
         </is>
       </c>
       <c r="B211" s="18" t="n">
-        <v>0.4508168072162796</v>
+        <v>0.3293284478329097</v>
       </c>
       <c r="C211" s="18" t="n">
-        <v>0.1350495814512362</v>
+        <v>0.04387892774827255</v>
       </c>
       <c r="D211" s="18" t="n">
-        <v>1.504897619709135</v>
+        <v>2.471738306237516</v>
       </c>
       <c r="E211" s="18" t="n">
-        <v>0.1951845416816871</v>
+        <v>0.2801288511192345</v>
       </c>
     </row>
     <row r="212">
@@ -5152,16 +5152,16 @@
         </is>
       </c>
       <c r="B212" s="18" t="n">
-        <v>1.00000000000287</v>
+        <v>1.000000000018336</v>
       </c>
       <c r="C212" s="18" t="n">
-        <v>0.9999999962907928</v>
+        <v>0.9999999743813285</v>
       </c>
       <c r="D212" s="18" t="n">
-        <v>1.000000003714948</v>
+        <v>1.000000025655343</v>
       </c>
       <c r="E212" s="18" t="n">
-        <v>0.9987907893319894</v>
+        <v>0.9988815560410259</v>
       </c>
     </row>
     <row r="213">
@@ -5171,16 +5171,16 @@
         </is>
       </c>
       <c r="B213" s="18" t="n">
-        <v>0.6410302260070506</v>
+        <v>0.4689236471139903</v>
       </c>
       <c r="C213" s="18" t="n">
-        <v>0.3525111555782744</v>
+        <v>0.2167906797705422</v>
       </c>
       <c r="D213" s="18" t="n">
-        <v>1.165692898372422</v>
+        <v>1.014293543686582</v>
       </c>
       <c r="E213" s="18" t="n">
-        <v>0.1449888259107431</v>
+        <v>0.05436595932389754</v>
       </c>
     </row>
     <row r="214">
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="B214" s="18" t="n">
-        <v>9.934817167934103</v>
+        <v>9.733340551157417</v>
       </c>
       <c r="C214" s="18" t="n">
-        <v>5.700357140920815</v>
+        <v>5.312213006118687</v>
       </c>
       <c r="D214" s="18" t="n">
-        <v>17.31480847958492</v>
+        <v>17.83398334661747</v>
       </c>
       <c r="E214" s="18" t="n">
-        <v>5.456889374497295e-16</v>
+        <v>1.76830787859118e-13</v>
       </c>
     </row>
     <row r="215">
@@ -5209,16 +5209,16 @@
         </is>
       </c>
       <c r="B215" s="18" t="n">
-        <v>2.514656937541992</v>
+        <v>2.451774509909193</v>
       </c>
       <c r="C215" s="18" t="n">
-        <v>0.9573967322699311</v>
+        <v>0.8568892893732978</v>
       </c>
       <c r="D215" s="18" t="n">
-        <v>6.604889384294668</v>
+        <v>7.015139904288994</v>
       </c>
       <c r="E215" s="18" t="n">
-        <v>0.06126210402319419</v>
+        <v>0.09452152049549552</v>
       </c>
     </row>
     <row r="216">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="B216" s="18" t="n">
-        <v>2.079588031683173e-09</v>
+        <v>2.423214341170981e-09</v>
       </c>
       <c r="C216" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5237,7 +5237,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E216" s="18" t="n">
-        <v>0.9987907977574263</v>
+        <v>0.9988815654612542</v>
       </c>
     </row>
     <row r="217">
@@ -5247,16 +5247,16 @@
         </is>
       </c>
       <c r="B217" s="18" t="n">
-        <v>0.9274469143388928</v>
+        <v>0.9422875150726806</v>
       </c>
       <c r="C217" s="18" t="n">
-        <v>0.8412896803931682</v>
+        <v>0.8402566208060509</v>
       </c>
       <c r="D217" s="18" t="n">
-        <v>1.02242758821759</v>
+        <v>1.056707842670834</v>
       </c>
       <c r="E217" s="18" t="n">
-        <v>0.130000650396566</v>
+        <v>0.3093262250001674</v>
       </c>
     </row>
     <row r="218">
@@ -5266,16 +5266,16 @@
         </is>
       </c>
       <c r="B218" s="18" t="n">
-        <v>1.049947220941366</v>
+        <v>1.045268765276583</v>
       </c>
       <c r="C218" s="18" t="n">
-        <v>0.9800331789921888</v>
+        <v>0.96547708833076</v>
       </c>
       <c r="D218" s="18" t="n">
-        <v>1.124848821849209</v>
+        <v>1.131654810733868</v>
       </c>
       <c r="E218" s="18" t="n">
-        <v>0.1656542344117218</v>
+        <v>0.2744837519527811</v>
       </c>
     </row>
     <row r="219">
@@ -5285,16 +5285,16 @@
         </is>
       </c>
       <c r="B219" s="18" t="n">
-        <v>1.720509958843602</v>
+        <v>2.183267567544981</v>
       </c>
       <c r="C219" s="18" t="n">
-        <v>1.220585872810284</v>
+        <v>1.459667658911839</v>
       </c>
       <c r="D219" s="18" t="n">
-        <v>2.425191528445709</v>
+        <v>3.265577093793564</v>
       </c>
       <c r="E219" s="18" t="n">
-        <v>0.001948210925390039</v>
+        <v>0.0001440425701642091</v>
       </c>
     </row>
     <row r="220">
@@ -5319,12 +5319,12 @@
       <c r="A222" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 193,
-  "llf": -655.2695391328182,
-  "aic": 1346.5390782656364,
-  "pseudo_r2_mcfadden": 0.13877688443930813,
-  "lr_vs_null_chi2": 211.17934125497914,
+  "n_obs": 3614,
+  "n_events": 136,
+  "llf": -495.9148552036097,
+  "aic": 1027.8297104072194,
+  "pseudo_r2_mcfadden": 0.14448544498165794,
+  "lr_vs_null_chi2": 167.50732785737773,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + vasc_ord",
   "ordering_note": "vasc_ord: missing=0 indeterminate=1 focal=2 present_ungraded=3 extensive=4; single linear coefficient"
@@ -5343,16 +5343,16 @@
         </is>
       </c>
       <c r="B223" s="18" t="n">
-        <v>0.0310329232926618</v>
+        <v>0.02012786654194628</v>
       </c>
       <c r="C223" s="18" t="n">
-        <v>0.01700584905003968</v>
+        <v>0.009895425460777516</v>
       </c>
       <c r="D223" s="18" t="n">
-        <v>0.05663006447102293</v>
+        <v>0.0409412423079955</v>
       </c>
       <c r="E223" s="18" t="n">
-        <v>1.095477234483102e-29</v>
+        <v>4.227983511766281e-27</v>
       </c>
     </row>
     <row r="224">
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="B224" s="18" t="n">
-        <v>0.6516466888724859</v>
+        <v>0.5211431639720989</v>
       </c>
       <c r="C224" s="18" t="n">
-        <v>0.3118733891252518</v>
+        <v>0.2182519942802325</v>
       </c>
       <c r="D224" s="18" t="n">
-        <v>1.361589099696906</v>
+        <v>1.244388158974309</v>
       </c>
       <c r="E224" s="18" t="n">
-        <v>0.2546890503963902</v>
+        <v>0.1422108068237348</v>
       </c>
     </row>
     <row r="225">
@@ -5381,16 +5381,16 @@
         </is>
       </c>
       <c r="B225" s="18" t="n">
-        <v>2.053998392318718</v>
+        <v>1.703819982100868</v>
       </c>
       <c r="C225" s="18" t="n">
-        <v>1.463498219969417</v>
+        <v>1.144178731257892</v>
       </c>
       <c r="D225" s="18" t="n">
-        <v>2.882756766001424</v>
+        <v>2.537193230479549</v>
       </c>
       <c r="E225" s="18" t="n">
-        <v>3.154192884648393e-05</v>
+        <v>0.008717825481080608</v>
       </c>
     </row>
     <row r="226">
@@ -5400,16 +5400,16 @@
         </is>
       </c>
       <c r="B226" s="18" t="n">
-        <v>1.237984291844038</v>
+        <v>1.467786362242134</v>
       </c>
       <c r="C226" s="18" t="n">
-        <v>0.8786333237186766</v>
+        <v>0.98952195924245</v>
       </c>
       <c r="D226" s="18" t="n">
-        <v>1.744305690986174</v>
+        <v>2.17720969712824</v>
       </c>
       <c r="E226" s="18" t="n">
-        <v>0.2223345115583454</v>
+        <v>0.05644241145559879</v>
       </c>
     </row>
     <row r="227">
@@ -5419,16 +5419,16 @@
         </is>
       </c>
       <c r="B227" s="18" t="n">
-        <v>1.048277827184413</v>
+        <v>0.9466588932446808</v>
       </c>
       <c r="C227" s="18" t="n">
-        <v>0.7090494987740202</v>
+        <v>0.596345916123369</v>
       </c>
       <c r="D227" s="18" t="n">
-        <v>1.549802101075453</v>
+        <v>1.502757101088038</v>
       </c>
       <c r="E227" s="18" t="n">
-        <v>0.8131573774532923</v>
+        <v>0.8161566724648637</v>
       </c>
     </row>
     <row r="228">
@@ -5438,16 +5438,16 @@
         </is>
       </c>
       <c r="B228" s="18" t="n">
-        <v>5.607479803852337</v>
+        <v>3.969002013774726</v>
       </c>
       <c r="C228" s="18" t="n">
-        <v>2.897030599142081</v>
+        <v>1.837857357296977</v>
       </c>
       <c r="D228" s="18" t="n">
-        <v>10.8538134736732</v>
+        <v>8.571381735803735</v>
       </c>
       <c r="E228" s="18" t="n">
-        <v>3.108510895633969e-07</v>
+        <v>0.000449333929135112</v>
       </c>
     </row>
     <row r="229">
@@ -5457,16 +5457,16 @@
         </is>
       </c>
       <c r="B229" s="18" t="n">
-        <v>0.4408698434693836</v>
+        <v>0.3246369056383784</v>
       </c>
       <c r="C229" s="18" t="n">
-        <v>0.1321339597547841</v>
+        <v>0.04329761492685272</v>
       </c>
       <c r="D229" s="18" t="n">
-        <v>1.470978537549515</v>
+        <v>2.434062954287585</v>
       </c>
       <c r="E229" s="18" t="n">
-        <v>0.1827919881318931</v>
+        <v>0.2737220369605666</v>
       </c>
     </row>
     <row r="230">
@@ -5476,16 +5476,16 @@
         </is>
       </c>
       <c r="B230" s="18" t="n">
-        <v>0.9999999999845147</v>
+        <v>1.000000000025699</v>
       </c>
       <c r="C230" s="18" t="n">
-        <v>0.9999999673726164</v>
+        <v>0.9999999458338172</v>
       </c>
       <c r="D230" s="18" t="n">
-        <v>1.000000032596414</v>
+        <v>1.000000054217583</v>
       </c>
       <c r="E230" s="18" t="n">
-        <v>0.9992574412369173</v>
+        <v>0.9992584050426551</v>
       </c>
     </row>
     <row r="231">
@@ -5495,16 +5495,16 @@
         </is>
       </c>
       <c r="B231" s="18" t="n">
-        <v>0.5601886579708687</v>
+        <v>0.3983931993655788</v>
       </c>
       <c r="C231" s="18" t="n">
-        <v>0.3000321848980259</v>
+        <v>0.178985445716229</v>
       </c>
       <c r="D231" s="18" t="n">
-        <v>1.045925565038499</v>
+        <v>0.8867600416649444</v>
       </c>
       <c r="E231" s="18" t="n">
-        <v>0.06890924580773959</v>
+        <v>0.02417403115141011</v>
       </c>
     </row>
     <row r="232">
@@ -5514,16 +5514,16 @@
         </is>
       </c>
       <c r="B232" s="18" t="n">
-        <v>8.538198152334786</v>
+        <v>8.308574567851533</v>
       </c>
       <c r="C232" s="18" t="n">
-        <v>4.734088457488871</v>
+        <v>4.310776119139011</v>
       </c>
       <c r="D232" s="18" t="n">
-        <v>15.39912664141522</v>
+        <v>16.01391708631277</v>
       </c>
       <c r="E232" s="18" t="n">
-        <v>1.025604706093417e-12</v>
+        <v>2.544037177304162e-10</v>
       </c>
     </row>
     <row r="233">
@@ -5533,16 +5533,16 @@
         </is>
       </c>
       <c r="B233" s="18" t="n">
-        <v>1.889803257984597</v>
+        <v>1.706501062335775</v>
       </c>
       <c r="C233" s="18" t="n">
-        <v>0.6939863194425195</v>
+        <v>0.5719494843670719</v>
       </c>
       <c r="D233" s="18" t="n">
-        <v>5.146148063492195</v>
+        <v>5.091613779450737</v>
       </c>
       <c r="E233" s="18" t="n">
-        <v>0.2130390031427415</v>
+        <v>0.3379448016479434</v>
       </c>
     </row>
     <row r="234">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="B234" s="18" t="n">
-        <v>5.571351989603471e-10</v>
+        <v>1.753958207220768e-09</v>
       </c>
       <c r="C234" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5561,7 +5561,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E234" s="18" t="n">
-        <v>0.9992027278318458</v>
+        <v>0.9988414059572132</v>
       </c>
     </row>
     <row r="235">
@@ -5571,16 +5571,16 @@
         </is>
       </c>
       <c r="B235" s="18" t="n">
-        <v>0.7108018192563973</v>
+        <v>0.7257466666851908</v>
       </c>
       <c r="C235" s="18" t="n">
-        <v>0.4319874013665285</v>
+        <v>0.4154642195664209</v>
       </c>
       <c r="D235" s="18" t="n">
-        <v>1.169569354707925</v>
+        <v>1.267758327671006</v>
       </c>
       <c r="E235" s="18" t="n">
-        <v>0.1791119409393991</v>
+        <v>0.2600236910573237</v>
       </c>
     </row>
     <row r="236">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="B236" s="18" t="n">
-        <v>1.689910845125026</v>
+        <v>1.952724097983555</v>
       </c>
       <c r="C236" s="18" t="n">
-        <v>0.7057421444646111</v>
+        <v>0.7722683444213446</v>
       </c>
       <c r="D236" s="18" t="n">
-        <v>4.046518529281882</v>
+        <v>4.937573099286936</v>
       </c>
       <c r="E236" s="18" t="n">
-        <v>0.2389161269620909</v>
+        <v>0.1573737546041553</v>
       </c>
     </row>
     <row r="237">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="B237" s="18" t="n">
-        <v>8.179354549635147e-10</v>
+        <v>2.596124099606013e-09</v>
       </c>
       <c r="C237" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5618,7 +5618,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E237" s="18" t="n">
-        <v>0.9994744478317581</v>
+        <v>0.9991782423206655</v>
       </c>
     </row>
     <row r="238">
@@ -5628,16 +5628,16 @@
         </is>
       </c>
       <c r="B238" s="18" t="n">
-        <v>0.6376847424345509</v>
+        <v>0.7639982196735575</v>
       </c>
       <c r="C238" s="18" t="n">
-        <v>0.2622746690768858</v>
+        <v>0.288977097157377</v>
       </c>
       <c r="D238" s="18" t="n">
-        <v>1.550442641544664</v>
+        <v>2.019860000692325</v>
       </c>
       <c r="E238" s="18" t="n">
-        <v>0.3209418693855892</v>
+        <v>0.5873508014224229</v>
       </c>
     </row>
     <row r="239">
@@ -5647,16 +5647,16 @@
         </is>
       </c>
       <c r="B239" s="18" t="n">
-        <v>0.9340056427801126</v>
+        <v>0.9526378060281556</v>
       </c>
       <c r="C239" s="18" t="n">
-        <v>0.8469066842184035</v>
+        <v>0.8489278355454744</v>
       </c>
       <c r="D239" s="18" t="n">
-        <v>1.030062174500588</v>
+        <v>1.069017590748472</v>
       </c>
       <c r="E239" s="18" t="n">
-        <v>0.1716447937098534</v>
+        <v>0.4093299563928872</v>
       </c>
     </row>
     <row r="240">
@@ -5666,16 +5666,16 @@
         </is>
       </c>
       <c r="B240" s="18" t="n">
-        <v>1.048812125162017</v>
+        <v>1.042839790474807</v>
       </c>
       <c r="C240" s="18" t="n">
-        <v>0.9790429640640671</v>
+        <v>0.9631674814129527</v>
       </c>
       <c r="D240" s="18" t="n">
-        <v>1.123553219074952</v>
+        <v>1.129102518081456</v>
       </c>
       <c r="E240" s="18" t="n">
-        <v>0.1748030732518505</v>
+        <v>0.3009126190072691</v>
       </c>
     </row>
     <row r="241">
@@ -5685,16 +5685,16 @@
         </is>
       </c>
       <c r="B241" s="18" t="n">
-        <v>1.263153318005346</v>
+        <v>1.375353569045601</v>
       </c>
       <c r="C241" s="18" t="n">
-        <v>1.097227866956414</v>
+        <v>1.176105101827849</v>
       </c>
       <c r="D241" s="18" t="n">
-        <v>1.454170416956149</v>
+        <v>1.608357481781721</v>
       </c>
       <c r="E241" s="18" t="n">
-        <v>0.001148573816578156</v>
+        <v>6.568933530444733e-05</v>
       </c>
     </row>
     <row r="242">
@@ -5719,14 +5719,14 @@
       <c r="A244" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 193,
-  "llf": -654.0326151062296,
-  "aic": 1350.0652302124593,
-  "pseudo_r2_mcfadden": 0.14040257814284918,
-  "lr_vs_null_chi2": 213.65318930815624,
+  "n_obs": 3614,
+  "n_events": 136,
+  "llf": -495.05342883144544,
+  "aic": 1032.106857662891,
+  "pseudo_r2_mcfadden": 0.14597151217994864,
+  "lr_vs_null_chi2": 169.23018060170625,
   "lr_vs_null_pvalue": 0.0,
-  "n": 3756,
+  "n": 3619,
   "n_removed": 0
 }</t>
         </is>
@@ -5743,16 +5743,16 @@
         </is>
       </c>
       <c r="B245" s="18" t="n">
-        <v>0.03052220194197974</v>
+        <v>0.01952818235876326</v>
       </c>
       <c r="C245" s="18" t="n">
-        <v>0.01669454927553033</v>
+        <v>0.009576002857726848</v>
       </c>
       <c r="D245" s="18" t="n">
-        <v>0.05580293280229319</v>
+        <v>0.03982349545033839</v>
       </c>
       <c r="E245" s="18" t="n">
-        <v>8.856417170795826e-30</v>
+        <v>2.607262166249015e-27</v>
       </c>
     </row>
     <row r="246">
@@ -5762,16 +5762,16 @@
         </is>
       </c>
       <c r="B246" s="18" t="n">
-        <v>0.6669255032178935</v>
+        <v>0.5524765530770338</v>
       </c>
       <c r="C246" s="18" t="n">
-        <v>0.3177659954934816</v>
+        <v>0.2305492981731137</v>
       </c>
       <c r="D246" s="18" t="n">
-        <v>1.399739535225268</v>
+        <v>1.323926570666421</v>
       </c>
       <c r="E246" s="18" t="n">
-        <v>0.2842080600304258</v>
+        <v>0.183297870332655</v>
       </c>
     </row>
     <row r="247">
@@ -5781,16 +5781,16 @@
         </is>
       </c>
       <c r="B247" s="18" t="n">
-        <v>2.076021874744788</v>
+        <v>1.720081707216226</v>
       </c>
       <c r="C247" s="18" t="n">
-        <v>1.47858360953565</v>
+        <v>1.154912102130645</v>
       </c>
       <c r="D247" s="18" t="n">
-        <v>2.914861761366597</v>
+        <v>2.561823600290921</v>
       </c>
       <c r="E247" s="18" t="n">
-        <v>2.458209087953318e-05</v>
+        <v>0.007616872842289187</v>
       </c>
     </row>
     <row r="248">
@@ -5800,16 +5800,16 @@
         </is>
       </c>
       <c r="B248" s="18" t="n">
-        <v>1.243365865671108</v>
+        <v>1.4650883599481</v>
       </c>
       <c r="C248" s="18" t="n">
-        <v>0.8826065421803896</v>
+        <v>0.9878422186406968</v>
       </c>
       <c r="D248" s="18" t="n">
-        <v>1.751583069050145</v>
+        <v>2.172901564593024</v>
       </c>
       <c r="E248" s="18" t="n">
-        <v>0.2128480394355131</v>
+        <v>0.05754647417412548</v>
       </c>
     </row>
     <row r="249">
@@ -5819,16 +5819,16 @@
         </is>
       </c>
       <c r="B249" s="18" t="n">
-        <v>1.041542433253086</v>
+        <v>0.9358545641585758</v>
       </c>
       <c r="C249" s="18" t="n">
-        <v>0.7041041255179393</v>
+        <v>0.589211285748405</v>
       </c>
       <c r="D249" s="18" t="n">
-        <v>1.540696327363191</v>
+        <v>1.48643413057505</v>
       </c>
       <c r="E249" s="18" t="n">
-        <v>0.8385463175879454</v>
+        <v>0.7788356451782399</v>
       </c>
     </row>
     <row r="250">
@@ -5838,16 +5838,16 @@
         </is>
       </c>
       <c r="B250" s="18" t="n">
-        <v>5.589610780216073</v>
+        <v>3.963807382165004</v>
       </c>
       <c r="C250" s="18" t="n">
-        <v>2.888512518705153</v>
+        <v>1.836332193384906</v>
       </c>
       <c r="D250" s="18" t="n">
-        <v>10.81655297388619</v>
+        <v>8.556060292089263</v>
       </c>
       <c r="E250" s="18" t="n">
-        <v>3.235499429458743e-07</v>
+        <v>0.0004512797412887346</v>
       </c>
     </row>
     <row r="251">
@@ -5857,16 +5857,16 @@
         </is>
       </c>
       <c r="B251" s="18" t="n">
-        <v>0.4437282968749986</v>
+        <v>0.3212734795521583</v>
       </c>
       <c r="C251" s="18" t="n">
-        <v>0.1329051128210752</v>
+        <v>0.04281602105476547</v>
       </c>
       <c r="D251" s="18" t="n">
-        <v>1.481468976386622</v>
+        <v>2.410701557987555</v>
       </c>
       <c r="E251" s="18" t="n">
-        <v>0.1865048194220119</v>
+        <v>0.2694885897248011</v>
       </c>
     </row>
     <row r="252">
@@ -5876,16 +5876,16 @@
         </is>
       </c>
       <c r="B252" s="18" t="n">
-        <v>1.000000000181017</v>
+        <v>1.000000000021757</v>
       </c>
       <c r="C252" s="18" t="n">
-        <v>0.999999567207104</v>
+        <v>0.9999999223249101</v>
       </c>
       <c r="D252" s="18" t="n">
-        <v>1.000000433155118</v>
+        <v>1.000000077718611</v>
       </c>
       <c r="E252" s="18" t="n">
-        <v>0.9993461969791613</v>
+        <v>0.9995620828278956</v>
       </c>
     </row>
     <row r="253">
@@ -5895,16 +5895,16 @@
         </is>
       </c>
       <c r="B253" s="18" t="n">
-        <v>0.5113539780108236</v>
+        <v>0.3890162634245708</v>
       </c>
       <c r="C253" s="18" t="n">
-        <v>0.2699812706456613</v>
+        <v>0.1725341866318366</v>
       </c>
       <c r="D253" s="18" t="n">
-        <v>0.9685223356500121</v>
+        <v>0.8771227092039422</v>
       </c>
       <c r="E253" s="18" t="n">
-        <v>0.03957954869899567</v>
+        <v>0.02284436960335355</v>
       </c>
     </row>
     <row r="254">
@@ -5914,16 +5914,16 @@
         </is>
       </c>
       <c r="B254" s="18" t="n">
-        <v>8.57905103879509</v>
+        <v>8.037808447340625</v>
       </c>
       <c r="C254" s="18" t="n">
-        <v>4.741888142926279</v>
+        <v>4.156117229943009</v>
       </c>
       <c r="D254" s="18" t="n">
-        <v>15.52126800714273</v>
+        <v>15.54488506019024</v>
       </c>
       <c r="E254" s="18" t="n">
-        <v>1.201350488743744e-12</v>
+        <v>5.896019029138317e-10</v>
       </c>
     </row>
     <row r="255">
@@ -5933,16 +5933,16 @@
         </is>
       </c>
       <c r="B255" s="18" t="n">
-        <v>1.715255922337146</v>
+        <v>1.842180788706986</v>
       </c>
       <c r="C255" s="18" t="n">
-        <v>0.6113741691283806</v>
+        <v>0.5932306073819177</v>
       </c>
       <c r="D255" s="18" t="n">
-        <v>4.812278679204144</v>
+        <v>5.720591648596947</v>
       </c>
       <c r="E255" s="18" t="n">
-        <v>0.3053064560865795</v>
+        <v>0.2906203332201726</v>
       </c>
     </row>
     <row r="256">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B256" s="18" t="n">
-        <v>5.16727771697659e-10</v>
+        <v>1.82521779930501e-09</v>
       </c>
       <c r="C256" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5961,7 +5961,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E256" s="18" t="n">
-        <v>0.9992030750468766</v>
+        <v>0.9988564339892622</v>
       </c>
     </row>
     <row r="257">
@@ -5971,16 +5971,16 @@
         </is>
       </c>
       <c r="B257" s="18" t="n">
-        <v>0.7384752852970617</v>
+        <v>0.7049729669721491</v>
       </c>
       <c r="C257" s="18" t="n">
-        <v>0.4452543797335514</v>
+        <v>0.3996192564872628</v>
       </c>
       <c r="D257" s="18" t="n">
-        <v>1.224795918506005</v>
+        <v>1.243650990520662</v>
       </c>
       <c r="E257" s="18" t="n">
-        <v>0.2402193969427563</v>
+        <v>0.2274016006370255</v>
       </c>
     </row>
     <row r="258">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="B258" s="18" t="n">
-        <v>1.757893717879382</v>
+        <v>1.960800196196869</v>
       </c>
       <c r="C258" s="18" t="n">
-        <v>0.7279395352184567</v>
+        <v>0.7711608720824789</v>
       </c>
       <c r="D258" s="18" t="n">
-        <v>4.245119510417058</v>
+        <v>4.985648972338509</v>
       </c>
       <c r="E258" s="18" t="n">
-        <v>0.2098197201769865</v>
+        <v>0.1573031701081236</v>
       </c>
     </row>
     <row r="259">
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="B259" s="18" t="n">
-        <v>7.668397975541751e-10</v>
+        <v>2.501109593889407e-09</v>
       </c>
       <c r="C259" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -6018,7 +6018,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E259" s="18" t="n">
-        <v>0.999474226098751</v>
+        <v>0.9991855474853423</v>
       </c>
     </row>
     <row r="260">
@@ -6028,16 +6028,16 @@
         </is>
       </c>
       <c r="B260" s="18" t="n">
-        <v>0.6744064518387922</v>
+        <v>0.7422833948819164</v>
       </c>
       <c r="C260" s="18" t="n">
-        <v>0.2721746782092361</v>
+        <v>0.276135190157902</v>
       </c>
       <c r="D260" s="18" t="n">
-        <v>1.671074125169499</v>
+        <v>1.995343795198121</v>
       </c>
       <c r="E260" s="18" t="n">
-        <v>0.3948394123437013</v>
+        <v>0.5547156582209726</v>
       </c>
     </row>
     <row r="261">
@@ -6047,16 +6047,16 @@
         </is>
       </c>
       <c r="B261" s="18" t="n">
-        <v>1.823942570144014</v>
+        <v>2.75396182855841</v>
       </c>
       <c r="C261" s="18" t="n">
-        <v>1.112341481819554</v>
+        <v>1.611105036455845</v>
       </c>
       <c r="D261" s="18" t="n">
-        <v>2.990778060116638</v>
+        <v>4.707517872230699</v>
       </c>
       <c r="E261" s="18" t="n">
-        <v>0.01722257193913048</v>
+        <v>0.0002126425680882026</v>
       </c>
     </row>
     <row r="262">
@@ -6066,16 +6066,16 @@
         </is>
       </c>
       <c r="B262" s="18" t="n">
-        <v>2.39090079920365</v>
+        <v>2.803176034744242</v>
       </c>
       <c r="C262" s="18" t="n">
-        <v>1.317147438489974</v>
+        <v>1.407722482750835</v>
       </c>
       <c r="D262" s="18" t="n">
-        <v>4.339989939308657</v>
+        <v>5.581921137189987</v>
       </c>
       <c r="E262" s="18" t="n">
-        <v>0.004162942684026138</v>
+        <v>0.003356295661775941</v>
       </c>
     </row>
     <row r="263">
@@ -6085,16 +6085,16 @@
         </is>
       </c>
       <c r="B263" s="18" t="n">
-        <v>2.788892715938317</v>
+        <v>3.049893524544781</v>
       </c>
       <c r="C263" s="18" t="n">
-        <v>1.376348027128713</v>
+        <v>1.343814584395691</v>
       </c>
       <c r="D263" s="18" t="n">
-        <v>5.651130693477159</v>
+        <v>6.921974667541801</v>
       </c>
       <c r="E263" s="18" t="n">
-        <v>0.004420333345359666</v>
+        <v>0.007661210246188071</v>
       </c>
     </row>
     <row r="264">
@@ -6104,16 +6104,16 @@
         </is>
       </c>
       <c r="B264" s="18" t="n">
-        <v>1.304747414145783</v>
+        <v>1.570591164182373</v>
       </c>
       <c r="C264" s="18" t="n">
-        <v>0.3606986337620886</v>
+        <v>0.3406980676503913</v>
       </c>
       <c r="D264" s="18" t="n">
-        <v>4.719634773673588</v>
+        <v>7.240301132376875</v>
       </c>
       <c r="E264" s="18" t="n">
-        <v>0.6851050284367951</v>
+        <v>0.5625910155522527</v>
       </c>
     </row>
     <row r="265">
@@ -6123,16 +6123,16 @@
         </is>
       </c>
       <c r="B265" s="18" t="n">
-        <v>0.9342008179855855</v>
+        <v>0.952926479401809</v>
       </c>
       <c r="C265" s="18" t="n">
-        <v>0.84698924688341</v>
+        <v>0.8491424738889585</v>
       </c>
       <c r="D265" s="18" t="n">
-        <v>1.030392264761622</v>
+        <v>1.069395187578232</v>
       </c>
       <c r="E265" s="18" t="n">
-        <v>0.1734490646119403</v>
+        <v>0.4124644185366982</v>
       </c>
     </row>
     <row r="266">
@@ -6142,16 +6142,16 @@
         </is>
       </c>
       <c r="B266" s="18" t="n">
-        <v>1.047101558155796</v>
+        <v>1.043402510286877</v>
       </c>
       <c r="C266" s="18" t="n">
-        <v>0.9772115482993279</v>
+        <v>0.9634033389088166</v>
       </c>
       <c r="D266" s="18" t="n">
-        <v>1.121990090068454</v>
+        <v>1.130044659909568</v>
       </c>
       <c r="E266" s="18" t="n">
-        <v>0.1915859030131092</v>
+        <v>0.2965259820827366</v>
       </c>
     </row>
     <row r="267">
@@ -6176,12 +6176,12 @@
       <c r="A269" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 193,
-  "llf": -636.3735895956061,
-  "aic": 1330.7471791912121,
-  "pseudo_r2_mcfadden": 0.16361189897920558,
-  "lr_vs_null_chi2": 248.97124032940337,
+  "n_obs": 3614,
+  "n_events": 136,
+  "llf": -483.04691405995766,
+  "aic": 1024.0938281199153,
+  "pseudo_r2_mcfadden": 0.16668423742757854,
+  "lr_vs_null_chi2": 193.24321014468183,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing')) + C(multifocal_flag_path_fac, Treatment(reference='missing')) + C(bilateral_disease_fac, Treatment(reference='missing')) + C(margin_involved_fac, Treatment(reference='missing')) + C(aggressive_variant_fac, Treatment(reference='missing')) + C(braf_positive_fac, Treatment(reference='missing')) + C(surg_tt_fac, Treatment(reference='missing'))",
   "change_note": "coefficient attenuated vs primary"
@@ -6200,16 +6200,16 @@
         </is>
       </c>
       <c r="B270" s="18" t="n">
-        <v>0.2569000145316158</v>
+        <v>0.1510494980453048</v>
       </c>
       <c r="C270" s="18" t="n">
-        <v>0.1527709823249613</v>
+        <v>0.08169219174681522</v>
       </c>
       <c r="D270" s="18" t="n">
-        <v>0.4320036204647814</v>
+        <v>0.2792916969402772</v>
       </c>
       <c r="E270" s="18" t="n">
-        <v>2.974723093457755e-07</v>
+        <v>1.668111019128902e-09</v>
       </c>
     </row>
     <row r="271">
@@ -6219,16 +6219,16 @@
         </is>
       </c>
       <c r="B271" s="18" t="n">
-        <v>1.507918166655319</v>
+        <v>2.269896889003301</v>
       </c>
       <c r="C271" s="18" t="n">
-        <v>0.5259457685579816</v>
+        <v>0.737054471301422</v>
       </c>
       <c r="D271" s="18" t="n">
-        <v>4.323292121093409</v>
+        <v>6.990571372030591</v>
       </c>
       <c r="E271" s="18" t="n">
-        <v>0.4446949206287111</v>
+        <v>0.1531906309098012</v>
       </c>
     </row>
     <row r="272">
@@ -6238,16 +6238,16 @@
         </is>
       </c>
       <c r="B272" s="18" t="n">
-        <v>1.821599442885074</v>
+        <v>1.584147212400748</v>
       </c>
       <c r="C272" s="18" t="n">
-        <v>1.284888858634383</v>
+        <v>1.052340948087099</v>
       </c>
       <c r="D272" s="18" t="n">
-        <v>2.582499262890268</v>
+        <v>2.384704686364969</v>
       </c>
       <c r="E272" s="18" t="n">
-        <v>0.000758385662750599</v>
+        <v>0.02749444701425259</v>
       </c>
     </row>
     <row r="273">
@@ -6257,16 +6257,16 @@
         </is>
       </c>
       <c r="B273" s="18" t="n">
-        <v>1.268180975101935</v>
+        <v>1.497904280872553</v>
       </c>
       <c r="C273" s="18" t="n">
-        <v>0.8969462903129783</v>
+        <v>1.006254192357701</v>
       </c>
       <c r="D273" s="18" t="n">
-        <v>1.793064983912585</v>
+        <v>2.229771812825132</v>
       </c>
       <c r="E273" s="18" t="n">
-        <v>0.1787893148851736</v>
+        <v>0.04651607974178668</v>
       </c>
     </row>
     <row r="274">
@@ -6276,16 +6276,16 @@
         </is>
       </c>
       <c r="B274" s="18" t="n">
-        <v>1.008000416455425</v>
+        <v>0.8937157744290992</v>
       </c>
       <c r="C274" s="18" t="n">
-        <v>0.679174845213538</v>
+        <v>0.5604527701222028</v>
       </c>
       <c r="D274" s="18" t="n">
-        <v>1.496028374335408</v>
+        <v>1.425147537925894</v>
       </c>
       <c r="E274" s="18" t="n">
-        <v>0.9684478417405459</v>
+        <v>0.6369561555533545</v>
       </c>
     </row>
     <row r="275">
@@ -6295,16 +6295,16 @@
         </is>
       </c>
       <c r="B275" s="18" t="n">
-        <v>4.692219568614115</v>
+        <v>3.399007229397192</v>
       </c>
       <c r="C275" s="18" t="n">
-        <v>2.405243540331351</v>
+        <v>1.557849318176489</v>
       </c>
       <c r="D275" s="18" t="n">
-        <v>9.153719409657844</v>
+        <v>7.41615380299926</v>
       </c>
       <c r="E275" s="18" t="n">
-        <v>5.785514248232934e-06</v>
+        <v>0.002114647693832361</v>
       </c>
     </row>
     <row r="276">
@@ -6314,16 +6314,16 @@
         </is>
       </c>
       <c r="B276" s="18" t="n">
-        <v>0.5465064056350517</v>
+        <v>0.4031471343461719</v>
       </c>
       <c r="C276" s="18" t="n">
-        <v>0.1610008209546971</v>
+        <v>0.05330942838388029</v>
       </c>
       <c r="D276" s="18" t="n">
-        <v>1.855079058784328</v>
+        <v>3.048759231878681</v>
       </c>
       <c r="E276" s="18" t="n">
-        <v>0.3325541551006228</v>
+        <v>0.3788243069507335</v>
       </c>
     </row>
     <row r="277">
@@ -6333,16 +6333,16 @@
         </is>
       </c>
       <c r="B277" s="18" t="n">
-        <v>0.9999999999155477</v>
+        <v>1.000000000231506</v>
       </c>
       <c r="C277" s="18" t="n">
-        <v>0.9999997104503192</v>
+        <v>0.9999996892313043</v>
       </c>
       <c r="D277" s="18" t="n">
-        <v>1.00000028938086</v>
+        <v>1.000000311231805</v>
       </c>
       <c r="E277" s="18" t="n">
-        <v>0.9995437496511856</v>
+        <v>0.9988359003520918</v>
       </c>
     </row>
     <row r="278">
@@ -6352,16 +6352,16 @@
         </is>
       </c>
       <c r="B278" s="18" t="n">
-        <v>0.6241988240191877</v>
+        <v>0.4443750066815842</v>
       </c>
       <c r="C278" s="18" t="n">
-        <v>0.3227216797610402</v>
+        <v>0.1925452180326325</v>
       </c>
       <c r="D278" s="18" t="n">
-        <v>1.207307089487867</v>
+        <v>1.025572842477921</v>
       </c>
       <c r="E278" s="18" t="n">
-        <v>0.1614433749243808</v>
+        <v>0.05732987731743916</v>
       </c>
     </row>
     <row r="279">
@@ -6371,16 +6371,16 @@
         </is>
       </c>
       <c r="B279" s="18" t="n">
-        <v>9.017693660266431</v>
+        <v>9.114702689402966</v>
       </c>
       <c r="C279" s="18" t="n">
-        <v>4.862700985386842</v>
+        <v>4.68155511234732</v>
       </c>
       <c r="D279" s="18" t="n">
-        <v>16.7229692294025</v>
+        <v>17.74577103601684</v>
       </c>
       <c r="E279" s="18" t="n">
-        <v>2.968161437026701e-12</v>
+        <v>7.982264814336491e-11</v>
       </c>
     </row>
     <row r="280">
@@ -6390,16 +6390,16 @@
         </is>
       </c>
       <c r="B280" s="18" t="n">
-        <v>2.188323971289851</v>
+        <v>2.261264737555708</v>
       </c>
       <c r="C280" s="18" t="n">
-        <v>0.7602702563666991</v>
+        <v>0.7086930896587771</v>
       </c>
       <c r="D280" s="18" t="n">
-        <v>6.298762529797082</v>
+        <v>7.215137677968405</v>
       </c>
       <c r="E280" s="18" t="n">
-        <v>0.1465440080869578</v>
+        <v>0.1681106907758559</v>
       </c>
     </row>
     <row r="281">
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="B281" s="18" t="n">
-        <v>5.821868636193188e-10</v>
+        <v>2.148916997079973e-09</v>
       </c>
       <c r="C281" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -6418,7 +6418,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E281" s="18" t="n">
-        <v>0.9992088105883246</v>
+        <v>0.9988724396983985</v>
       </c>
     </row>
     <row r="282">
@@ -6428,16 +6428,16 @@
         </is>
       </c>
       <c r="B282" s="18" t="n">
-        <v>0.6497784646596605</v>
+        <v>0.6698829608217883</v>
       </c>
       <c r="C282" s="18" t="n">
-        <v>0.3880027269369928</v>
+        <v>0.3774792097003962</v>
       </c>
       <c r="D282" s="18" t="n">
-        <v>1.088167746831398</v>
+        <v>1.188789129752421</v>
       </c>
       <c r="E282" s="18" t="n">
-        <v>0.1012587521982251</v>
+        <v>0.1709869036181597</v>
       </c>
     </row>
     <row r="283">
@@ -6447,16 +6447,16 @@
         </is>
       </c>
       <c r="B283" s="18" t="n">
-        <v>1.482568729461025</v>
+        <v>1.886875187522622</v>
       </c>
       <c r="C283" s="18" t="n">
-        <v>0.6042450457358023</v>
+        <v>0.7320833517063747</v>
       </c>
       <c r="D283" s="18" t="n">
-        <v>3.637613668638545</v>
+        <v>4.863241275723615</v>
       </c>
       <c r="E283" s="18" t="n">
-        <v>0.3898549103105284</v>
+        <v>0.1887212639242754</v>
       </c>
     </row>
     <row r="284">
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="B284" s="18" t="n">
-        <v>4.792562307739752e-10</v>
+        <v>1.888542116257521e-09</v>
       </c>
       <c r="C284" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -6475,7 +6475,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E284" s="18" t="n">
-        <v>0.9994648160034991</v>
+        <v>0.9991768616701323</v>
       </c>
     </row>
     <row r="285">
@@ -6485,16 +6485,16 @@
         </is>
       </c>
       <c r="B285" s="18" t="n">
-        <v>0.680769187345277</v>
+        <v>0.8104882834353939</v>
       </c>
       <c r="C285" s="18" t="n">
-        <v>0.2729344970609212</v>
+        <v>0.3010369397151444</v>
       </c>
       <c r="D285" s="18" t="n">
-        <v>1.698014327354537</v>
+        <v>2.182095188077694</v>
       </c>
       <c r="E285" s="18" t="n">
-        <v>0.4096040552189486</v>
+        <v>0.6775456145811056</v>
       </c>
     </row>
     <row r="286">
@@ -6504,16 +6504,16 @@
         </is>
       </c>
       <c r="B286" s="18" t="n">
-        <v>1.677730182811396</v>
+        <v>2.425908142941559</v>
       </c>
       <c r="C286" s="18" t="n">
-        <v>1.018781501161789</v>
+        <v>1.418029139867584</v>
       </c>
       <c r="D286" s="18" t="n">
-        <v>2.762887393524979</v>
+        <v>4.150147660956889</v>
       </c>
       <c r="E286" s="18" t="n">
-        <v>0.04204507706803557</v>
+        <v>0.001216924024527618</v>
       </c>
     </row>
     <row r="287">
@@ -6523,16 +6523,16 @@
         </is>
       </c>
       <c r="B287" s="18" t="n">
-        <v>2.088299313337765</v>
+        <v>2.446659055748627</v>
       </c>
       <c r="C287" s="18" t="n">
-        <v>1.139555207597329</v>
+        <v>1.218308954025585</v>
       </c>
       <c r="D287" s="18" t="n">
-        <v>3.826926499929586</v>
+        <v>4.913483164756464</v>
       </c>
       <c r="E287" s="18" t="n">
-        <v>0.01718700007875044</v>
+        <v>0.01190238100572179</v>
       </c>
     </row>
     <row r="288">
@@ -6542,16 +6542,16 @@
         </is>
       </c>
       <c r="B288" s="18" t="n">
-        <v>2.329701490577631</v>
+        <v>2.596207928815898</v>
       </c>
       <c r="C288" s="18" t="n">
-        <v>1.113565733332385</v>
+        <v>1.101388221483155</v>
       </c>
       <c r="D288" s="18" t="n">
-        <v>4.873990706374939</v>
+        <v>6.119818133309882</v>
       </c>
       <c r="E288" s="18" t="n">
-        <v>0.02473145160901895</v>
+        <v>0.02920564353095204</v>
       </c>
     </row>
     <row r="289">
@@ -6561,16 +6561,16 @@
         </is>
       </c>
       <c r="B289" s="18" t="n">
-        <v>1.174904493076838</v>
+        <v>1.35409381760619</v>
       </c>
       <c r="C289" s="18" t="n">
-        <v>0.3130135013985568</v>
+        <v>0.2814120451400744</v>
       </c>
       <c r="D289" s="18" t="n">
-        <v>4.410035227504427</v>
+        <v>6.515606202878187</v>
       </c>
       <c r="E289" s="18" t="n">
-        <v>0.8112250937714095</v>
+        <v>0.7053052557753039</v>
       </c>
     </row>
     <row r="290">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="B290" s="18" t="n">
-        <v>0.3829991502059606</v>
+        <v>0.2991799467111269</v>
       </c>
       <c r="C290" s="18" t="n">
-        <v>0.283645282180823</v>
+        <v>0.2103747045678792</v>
       </c>
       <c r="D290" s="18" t="n">
-        <v>0.5171542002414643</v>
+        <v>0.4254724478303047</v>
       </c>
       <c r="E290" s="18" t="n">
-        <v>3.761064347255035e-10</v>
+        <v>1.86651844063363e-11</v>
       </c>
     </row>
     <row r="291">
@@ -6599,16 +6599,16 @@
         </is>
       </c>
       <c r="B291" s="18" t="n">
-        <v>0.6707587064464695</v>
+        <v>0.504878417676706</v>
       </c>
       <c r="C291" s="18" t="n">
-        <v>0.489761450607343</v>
+        <v>0.3477496134837931</v>
       </c>
       <c r="D291" s="18" t="n">
-        <v>0.9186456829458667</v>
+        <v>0.733005032218718</v>
       </c>
       <c r="E291" s="18" t="n">
-        <v>0.0128177199070952</v>
+        <v>0.0003271711767420813</v>
       </c>
     </row>
     <row r="292">
@@ -6618,16 +6618,16 @@
         </is>
       </c>
       <c r="B292" s="18" t="n">
-        <v>1.478428736465799</v>
+        <v>1.601840298027167</v>
       </c>
       <c r="C292" s="18" t="n">
-        <v>0.9654875475687518</v>
+        <v>0.9844170388518424</v>
       </c>
       <c r="D292" s="18" t="n">
-        <v>2.263883707575434</v>
+        <v>2.606509476285018</v>
       </c>
       <c r="E292" s="18" t="n">
-        <v>0.07211188680654161</v>
+        <v>0.05786263002073521</v>
       </c>
     </row>
     <row r="293">
@@ -6637,16 +6637,16 @@
         </is>
       </c>
       <c r="B293" s="18" t="n">
-        <v>1.341403969539692</v>
+        <v>1.394922584605317</v>
       </c>
       <c r="C293" s="18" t="n">
-        <v>0.9053618078824965</v>
+        <v>0.874984552034116</v>
       </c>
       <c r="D293" s="18" t="n">
-        <v>1.987453627743899</v>
+        <v>2.223820994917531</v>
       </c>
       <c r="E293" s="18" t="n">
-        <v>0.1431097626596375</v>
+        <v>0.1618930296556971</v>
       </c>
     </row>
     <row r="294">
@@ -6656,16 +6656,16 @@
         </is>
       </c>
       <c r="B294" s="18" t="n">
-        <v>1.619269540817887</v>
+        <v>4.706887955586375</v>
       </c>
       <c r="C294" s="18" t="n">
-        <v>0.4806606887660818</v>
+        <v>1.136655528512191</v>
       </c>
       <c r="D294" s="18" t="n">
-        <v>5.455061974283086</v>
+        <v>19.49121230725309</v>
       </c>
       <c r="E294" s="18" t="n">
-        <v>0.4367052344178606</v>
+        <v>0.0326268973728887</v>
       </c>
     </row>
     <row r="295">
@@ -6675,16 +6675,16 @@
         </is>
       </c>
       <c r="B295" s="18" t="n">
-        <v>2.805997122414412</v>
+        <v>6.595774534968638</v>
       </c>
       <c r="C295" s="18" t="n">
-        <v>0.8247482160722029</v>
+        <v>1.569231812281991</v>
       </c>
       <c r="D295" s="18" t="n">
-        <v>9.546695218688003</v>
+        <v>27.72327286232904</v>
       </c>
       <c r="E295" s="18" t="n">
-        <v>0.09862749066643212</v>
+        <v>0.01002325029590177</v>
       </c>
     </row>
     <row r="296">
@@ -6694,16 +6694,16 @@
         </is>
       </c>
       <c r="B296" s="18" t="n">
-        <v>0.5619147415812717</v>
+        <v>0.4671455112153282</v>
       </c>
       <c r="C296" s="18" t="n">
-        <v>0.3104866771069246</v>
+        <v>0.2327503064821669</v>
       </c>
       <c r="D296" s="18" t="n">
-        <v>1.016945975745075</v>
+        <v>0.9375924437949154</v>
       </c>
       <c r="E296" s="18" t="n">
-        <v>0.05685244078067574</v>
+        <v>0.03225358609689162</v>
       </c>
     </row>
     <row r="297">
@@ -6713,16 +6713,16 @@
         </is>
       </c>
       <c r="B297" s="18" t="n">
-        <v>0.4571868213529854</v>
+        <v>0.3233457113513531</v>
       </c>
       <c r="C297" s="18" t="n">
-        <v>0.2035136855745858</v>
+        <v>0.1248031592877071</v>
       </c>
       <c r="D297" s="18" t="n">
-        <v>1.027055202841594</v>
+        <v>0.8377388012132702</v>
       </c>
       <c r="E297" s="18" t="n">
-        <v>0.05805041142654126</v>
+        <v>0.02010000804190413</v>
       </c>
     </row>
     <row r="298">
@@ -6732,16 +6732,16 @@
         </is>
       </c>
       <c r="B298" s="18" t="n">
-        <v>0.4288235052548739</v>
+        <v>0.3286494191174074</v>
       </c>
       <c r="C298" s="18" t="n">
-        <v>0.3072307692955564</v>
+        <v>0.2220454095775436</v>
       </c>
       <c r="D298" s="18" t="n">
-        <v>0.5985390040220055</v>
+        <v>0.4864340176710091</v>
       </c>
       <c r="E298" s="18" t="n">
-        <v>6.461859568288532e-07</v>
+        <v>2.664558607002183e-08</v>
       </c>
     </row>
     <row r="299">
@@ -6751,16 +6751,16 @@
         </is>
       </c>
       <c r="B299" s="18" t="n">
-        <v>0.5990810004455327</v>
+        <v>0.4596067707104544</v>
       </c>
       <c r="C299" s="18" t="n">
-        <v>0.4014782918454663</v>
+        <v>0.2890714771275717</v>
       </c>
       <c r="D299" s="18" t="n">
-        <v>0.8939413472272231</v>
+        <v>0.7307479305184769</v>
       </c>
       <c r="E299" s="18" t="n">
-        <v>0.01210789915536751</v>
+        <v>0.001016713321096593</v>
       </c>
     </row>
     <row r="300">
@@ -6770,16 +6770,16 @@
         </is>
       </c>
       <c r="B300" s="18" t="n">
-        <v>0.4247494045818319</v>
+        <v>0.3651140852646933</v>
       </c>
       <c r="C300" s="18" t="n">
-        <v>0.3043453849425314</v>
+        <v>0.2477495398131849</v>
       </c>
       <c r="D300" s="18" t="n">
-        <v>0.5927872266789502</v>
+        <v>0.5380768632676154</v>
       </c>
       <c r="E300" s="18" t="n">
-        <v>4.78723974833185e-07</v>
+        <v>3.53737107976149e-07</v>
       </c>
     </row>
     <row r="301">
@@ -6789,16 +6789,16 @@
         </is>
       </c>
       <c r="B301" s="18" t="n">
-        <v>0.6048272504128508</v>
+        <v>0.4137049330708368</v>
       </c>
       <c r="C301" s="18" t="n">
-        <v>0.4356655661971757</v>
+        <v>0.2818339097079093</v>
       </c>
       <c r="D301" s="18" t="n">
-        <v>0.8396715995599398</v>
+        <v>0.6072788466956518</v>
       </c>
       <c r="E301" s="18" t="n">
-        <v>0.00266514129187637</v>
+        <v>6.581198440590895e-06</v>
       </c>
     </row>
     <row r="302">
@@ -6808,16 +6808,16 @@
         </is>
       </c>
       <c r="B302" s="18" t="n">
-        <v>0.9203801264734032</v>
+        <v>0.9497727079979655</v>
       </c>
       <c r="C302" s="18" t="n">
-        <v>0.8316485171553893</v>
+        <v>0.8428580299559578</v>
       </c>
       <c r="D302" s="18" t="n">
-        <v>1.018578834367021</v>
+        <v>1.070249276624825</v>
       </c>
       <c r="E302" s="18" t="n">
-        <v>0.108699269417467</v>
+        <v>0.3976968659605509</v>
       </c>
     </row>
     <row r="303">
@@ -6827,16 +6827,16 @@
         </is>
       </c>
       <c r="B303" s="18" t="n">
-        <v>1.048882343825277</v>
+        <v>1.048902516460092</v>
       </c>
       <c r="C303" s="18" t="n">
-        <v>0.9757344109651043</v>
+        <v>0.9647183949490935</v>
       </c>
       <c r="D303" s="18" t="n">
-        <v>1.12751396161199</v>
+        <v>1.140432788258763</v>
       </c>
       <c r="E303" s="18" t="n">
-        <v>0.1956829844783866</v>
+        <v>0.2633548131001169</v>
       </c>
     </row>
     <row r="304">
@@ -6861,12 +6861,12 @@
       <c r="A306" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 3750,
-  "n_events": 470,
-  "llf": -1257.2160427331457,
-  "aic": 2556.4320854662915,
-  "pseudo_r2_mcfadden": 0.11221166240903802,
-  "lr_vs_null_chi2": 317.8106676760531,
+  "n_obs": 3614,
+  "n_events": 455,
+  "llf": -1209.3633091449326,
+  "aic": 2460.726618289865,
+  "pseudo_r2_mcfadden": 0.11636977583139219,
+  "lr_vs_null_chi2": 318.5344578187555,
   "lr_vs_null_pvalue": 0.0
 }</t>
         </is>
@@ -6883,16 +6883,16 @@
         </is>
       </c>
       <c r="B307" s="18" t="n">
-        <v>0.2121465789650938</v>
+        <v>0.2255855878461239</v>
       </c>
       <c r="C307" s="18" t="n">
-        <v>0.1447620495987536</v>
+        <v>0.1529351109740711</v>
       </c>
       <c r="D307" s="18" t="n">
-        <v>0.3108975804870083</v>
+        <v>0.3327480335925546</v>
       </c>
       <c r="E307" s="18" t="n">
-        <v>1.845469936715041e-15</v>
+        <v>5.975318253488757e-14</v>
       </c>
     </row>
     <row r="308">
@@ -6902,16 +6902,16 @@
         </is>
       </c>
       <c r="B308" s="18" t="n">
-        <v>0.1481709302516655</v>
+        <v>0.1453885094584064</v>
       </c>
       <c r="C308" s="18" t="n">
-        <v>0.0728150677899998</v>
+        <v>0.07034645781665316</v>
       </c>
       <c r="D308" s="18" t="n">
-        <v>0.301512107836822</v>
+        <v>0.3004816353032229</v>
       </c>
       <c r="E308" s="18" t="n">
-        <v>1.382185754473308e-07</v>
+        <v>1.928810669064066e-07</v>
       </c>
     </row>
     <row r="309">
@@ -6921,16 +6921,16 @@
         </is>
       </c>
       <c r="B309" s="18" t="n">
-        <v>1.266858202336832</v>
+        <v>1.284662412215402</v>
       </c>
       <c r="C309" s="18" t="n">
-        <v>1.008378639800018</v>
+        <v>1.019670953448447</v>
       </c>
       <c r="D309" s="18" t="n">
-        <v>1.591594309401872</v>
+        <v>1.618519687922574</v>
       </c>
       <c r="E309" s="18" t="n">
-        <v>0.04219134827079978</v>
+        <v>0.03356707633428441</v>
       </c>
     </row>
     <row r="310">
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="B310" s="18" t="n">
-        <v>1.000927484046316</v>
+        <v>1.036172652069018</v>
       </c>
       <c r="C310" s="18" t="n">
-        <v>0.7871210841082436</v>
+        <v>0.8123040077961068</v>
       </c>
       <c r="D310" s="18" t="n">
-        <v>1.272810306503635</v>
+        <v>1.321738849730304</v>
       </c>
       <c r="E310" s="18" t="n">
-        <v>0.9939669776747947</v>
+        <v>0.7747887103306752</v>
       </c>
     </row>
     <row r="311">
@@ -6959,16 +6959,16 @@
         </is>
       </c>
       <c r="B311" s="18" t="n">
-        <v>0.868448685341453</v>
+        <v>0.8693876149182368</v>
       </c>
       <c r="C311" s="18" t="n">
-        <v>0.6845751774163154</v>
+        <v>0.6823078048262835</v>
       </c>
       <c r="D311" s="18" t="n">
-        <v>1.101709708373839</v>
+        <v>1.107762244000209</v>
       </c>
       <c r="E311" s="18" t="n">
-        <v>0.2452437467003592</v>
+        <v>0.257572234775595</v>
       </c>
     </row>
     <row r="312">
@@ -6978,16 +6978,16 @@
         </is>
       </c>
       <c r="B312" s="18" t="n">
-        <v>2.773620309514969</v>
+        <v>2.837685853771721</v>
       </c>
       <c r="C312" s="18" t="n">
-        <v>1.549815930104473</v>
+        <v>1.569684891469663</v>
       </c>
       <c r="D312" s="18" t="n">
-        <v>4.963795681746108</v>
+        <v>5.129985673211643</v>
       </c>
       <c r="E312" s="18" t="n">
-        <v>0.0005916727631447432</v>
+        <v>0.0005556014265937056</v>
       </c>
     </row>
     <row r="313">
@@ -6997,16 +6997,16 @@
         </is>
       </c>
       <c r="B313" s="18" t="n">
-        <v>0.6926461139556217</v>
+        <v>0.5687134155774649</v>
       </c>
       <c r="C313" s="18" t="n">
-        <v>0.394088637124336</v>
+        <v>0.2834120673499976</v>
       </c>
       <c r="D313" s="18" t="n">
-        <v>1.217387648318464</v>
+        <v>1.141217987229749</v>
       </c>
       <c r="E313" s="18" t="n">
-        <v>0.20184412780219</v>
+        <v>0.1122344283141526</v>
       </c>
     </row>
     <row r="314">
@@ -7016,16 +7016,16 @@
         </is>
       </c>
       <c r="B314" s="18" t="n">
-        <v>1.000000000027197</v>
+        <v>0.9999999999001982</v>
       </c>
       <c r="C314" s="18" t="n">
-        <v>0.999999968673107</v>
+        <v>0.9999998853649777</v>
       </c>
       <c r="D314" s="18" t="n">
-        <v>1.000000031381287</v>
+        <v>1.000000114435432</v>
       </c>
       <c r="E314" s="18" t="n">
-        <v>0.998643529701507</v>
+        <v>0.9986373398153121</v>
       </c>
     </row>
     <row r="315">
@@ -7035,16 +7035,16 @@
         </is>
       </c>
       <c r="B315" s="18" t="n">
-        <v>1.071424148750146</v>
+        <v>1.031516781981791</v>
       </c>
       <c r="C315" s="18" t="n">
-        <v>0.7691735683880994</v>
+        <v>0.7340110220395133</v>
       </c>
       <c r="D315" s="18" t="n">
-        <v>1.492445598372094</v>
+        <v>1.449606122471538</v>
       </c>
       <c r="E315" s="18" t="n">
-        <v>0.6832889925151044</v>
+        <v>0.8581419411500605</v>
       </c>
     </row>
     <row r="316">
@@ -7054,16 +7054,16 @@
         </is>
       </c>
       <c r="B316" s="18" t="n">
-        <v>15.11279260106012</v>
+        <v>15.1152706533026</v>
       </c>
       <c r="C316" s="18" t="n">
-        <v>8.440112611810511</v>
+        <v>8.401853163843354</v>
       </c>
       <c r="D316" s="18" t="n">
-        <v>27.06083564371585</v>
+        <v>27.19297784276899</v>
       </c>
       <c r="E316" s="18" t="n">
-        <v>6.457500862694149e-20</v>
+        <v>1.261031019472058e-19</v>
       </c>
     </row>
     <row r="317">
@@ -7073,16 +7073,16 @@
         </is>
       </c>
       <c r="B317" s="18" t="n">
-        <v>1.321481870785394</v>
+        <v>1.372947140188969</v>
       </c>
       <c r="C317" s="18" t="n">
-        <v>0.561728102537479</v>
+        <v>0.5824663878039061</v>
       </c>
       <c r="D317" s="18" t="n">
-        <v>3.108824940261825</v>
+        <v>3.236210516558887</v>
       </c>
       <c r="E317" s="18" t="n">
-        <v>0.5230598484323455</v>
+        <v>0.4687504594471719</v>
       </c>
     </row>
     <row r="318">
@@ -7092,16 +7092,16 @@
         </is>
       </c>
       <c r="B318" s="18" t="n">
-        <v>0.3479305781815146</v>
+        <v>0.3509607891054504</v>
       </c>
       <c r="C318" s="18" t="n">
-        <v>0.04221587777756792</v>
+        <v>0.04243460426475029</v>
       </c>
       <c r="D318" s="18" t="n">
-        <v>2.86753926737129</v>
+        <v>2.902665822474478</v>
       </c>
       <c r="E318" s="18" t="n">
-        <v>0.3265682275253238</v>
+        <v>0.3313600178017192</v>
       </c>
     </row>
     <row r="319">
@@ -7111,16 +7111,16 @@
         </is>
       </c>
       <c r="B319" s="18" t="n">
-        <v>0.5839324058902089</v>
+        <v>0.5542928315616387</v>
       </c>
       <c r="C319" s="18" t="n">
-        <v>0.4060018849379343</v>
+        <v>0.3875675593891785</v>
       </c>
       <c r="D319" s="18" t="n">
-        <v>0.8398410630552934</v>
+        <v>0.7927406091594512</v>
       </c>
       <c r="E319" s="18" t="n">
-        <v>0.003716508413346185</v>
+        <v>0.001228291535219422</v>
       </c>
     </row>
     <row r="320">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="B320" s="18" t="n">
-        <v>1.251285385774938</v>
+        <v>1.17664096693568</v>
       </c>
       <c r="C320" s="18" t="n">
-        <v>0.6170159457505956</v>
+        <v>0.5817839827362654</v>
       </c>
       <c r="D320" s="18" t="n">
-        <v>2.537560216129026</v>
+        <v>2.379721694227094</v>
       </c>
       <c r="E320" s="18" t="n">
-        <v>0.5343195291870322</v>
+        <v>0.6507959683842788</v>
       </c>
     </row>
     <row r="321">
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="B321" s="18" t="n">
-        <v>2.01472617828268e-09</v>
+        <v>1.906431006882531e-09</v>
       </c>
       <c r="C321" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -7158,7 +7158,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E321" s="18" t="n">
-        <v>0.9986435259058022</v>
+        <v>0.9986373352848978</v>
       </c>
     </row>
     <row r="322">
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="B322" s="18" t="n">
-        <v>0.7729013050052385</v>
+        <v>0.772571639092854</v>
       </c>
       <c r="C322" s="18" t="n">
-        <v>0.4448679420783668</v>
+        <v>0.4456724639899127</v>
       </c>
       <c r="D322" s="18" t="n">
-        <v>1.342817431366112</v>
+        <v>1.339250202238495</v>
       </c>
       <c r="E322" s="18" t="n">
-        <v>0.3606933796773942</v>
+        <v>0.3579515569743027</v>
       </c>
     </row>
     <row r="323">
@@ -7187,16 +7187,16 @@
         </is>
       </c>
       <c r="B323" s="18" t="n">
-        <v>1.947800313575637</v>
+        <v>2.207597346045535</v>
       </c>
       <c r="C323" s="18" t="n">
-        <v>1.379229957871424</v>
+        <v>1.582942487590842</v>
       </c>
       <c r="D323" s="18" t="n">
-        <v>2.750756710230211</v>
+        <v>3.078751174140565</v>
       </c>
       <c r="E323" s="18" t="n">
-        <v>0.0001533139669903146</v>
+        <v>3.066568623509898e-06</v>
       </c>
     </row>
     <row r="324">
@@ -7206,16 +7206,16 @@
         </is>
       </c>
       <c r="B324" s="18" t="n">
-        <v>2.102017488094829</v>
+        <v>2.303318889336426</v>
       </c>
       <c r="C324" s="18" t="n">
-        <v>1.416008527883012</v>
+        <v>1.550919797967125</v>
       </c>
       <c r="D324" s="18" t="n">
-        <v>3.120374936485933</v>
+        <v>3.420730016425029</v>
       </c>
       <c r="E324" s="18" t="n">
-        <v>0.0002280835182906418</v>
+        <v>3.553708743409143e-05</v>
       </c>
     </row>
     <row r="325">
@@ -7225,16 +7225,16 @@
         </is>
       </c>
       <c r="B325" s="18" t="n">
-        <v>1.92596153357261</v>
+        <v>2.164580296276422</v>
       </c>
       <c r="C325" s="18" t="n">
-        <v>1.164609708115182</v>
+        <v>1.306131969331554</v>
       </c>
       <c r="D325" s="18" t="n">
-        <v>3.185039419604856</v>
+        <v>3.587239244611705</v>
       </c>
       <c r="E325" s="18" t="n">
-        <v>0.010658593491598</v>
+        <v>0.002733911032774274</v>
       </c>
     </row>
     <row r="326">
@@ -7244,16 +7244,16 @@
         </is>
       </c>
       <c r="B326" s="18" t="n">
-        <v>0.8286562662072231</v>
+        <v>0.9755154201181317</v>
       </c>
       <c r="C326" s="18" t="n">
-        <v>0.2932358696188989</v>
+        <v>0.3448486427085989</v>
       </c>
       <c r="D326" s="18" t="n">
-        <v>2.341702631458156</v>
+        <v>2.759559461837273</v>
       </c>
       <c r="E326" s="18" t="n">
-        <v>0.722884606305388</v>
+        <v>0.9627334147629257</v>
       </c>
     </row>
     <row r="327">
@@ -7263,16 +7263,16 @@
         </is>
       </c>
       <c r="B327" s="18" t="n">
-        <v>0.8209842993608983</v>
+        <v>0.8083052773144015</v>
       </c>
       <c r="C327" s="18" t="n">
-        <v>0.7675122378997297</v>
+        <v>0.7544068550776691</v>
       </c>
       <c r="D327" s="18" t="n">
-        <v>0.8781817233840129</v>
+        <v>0.8660544597875451</v>
       </c>
       <c r="E327" s="18" t="n">
-        <v>9.451936694502102e-09</v>
+        <v>1.499834337221748e-09</v>
       </c>
     </row>
     <row r="328">
@@ -7282,16 +7282,16 @@
         </is>
       </c>
       <c r="B328" s="18" t="n">
-        <v>1.131946612372168</v>
+        <v>1.111215149901482</v>
       </c>
       <c r="C328" s="18" t="n">
-        <v>1.07592686808832</v>
+        <v>1.054747217564731</v>
       </c>
       <c r="D328" s="18" t="n">
-        <v>1.190883108567978</v>
+        <v>1.170706202213604</v>
       </c>
       <c r="E328" s="18" t="n">
-        <v>1.702073040213375e-06</v>
+        <v>7.399034706860755e-05</v>
       </c>
     </row>
     <row r="329"/>
@@ -7308,59 +7308,59 @@
           <t>[
   {
     "stratum": "N0",
-    "n": 1115,
-    "events": 39,
-    "gross_or": 1.740487686615032,
+    "n": 1083,
+    "events": 28,
+    "gross_or": 1.6878771490713238,
     "gross_ci": [
-      0.8528797712492094,
-      3.5518457458799224
+      0.7307601084020486,
+      3.898583457965278
     ],
-    "gross_p": 0.12783408907872904,
-    "noneg_or": 2.8330706750819927,
+    "gross_p": 0.22035612037228347,
+    "noneg_or": 1.9437704179034592,
     "noneg_ci": [
-      0.505507240440091,
-      15.877694339297511
+      0.2021897078666493,
+      18.68662592859802
     ],
-    "noneg_p": 0.23633444494411338
+    "noneg_p": 0.5648961707623461
   },
   {
     "stratum": "N1a",
-    "n": 2372,
-    "events": 128,
-    "gross_or": 2.166171497313047,
+    "n": 2337,
+    "events": 91,
+    "gross_or": 1.81884688713735,
     "gross_ci": [
-      1.4363522901951746,
-      3.2668162175825604
+      1.1220461526468861,
+      2.9483671336025132
     ],
-    "gross_p": 0.0002265759946471743,
-    "noneg_or": 0.7282490109442497,
+    "gross_p": 0.015215883582812693,
+    "noneg_or": 0.8989676646837724,
     "noneg_ci": [
-      0.30249724388588256,
-      1.7532279472316505
+      0.3272583702273686,
+      2.4694337430866136
     ],
-    "noneg_p": 0.47929846452204217
+    "noneg_p": 0.8363349636521434
   },
   {
     "stratum": "N1b",
-    "n": 76,
-    "events": 23,
-    "gross_or": 3.776898980170589,
+    "n": 74,
+    "events": 16,
+    "gross_or": 1.2085786099691649,
     "gross_ci": [
-      0.5865487191236326,
-      24.320172291445875
+      0.06997696814309133,
+      20.87347158979775
     ],
-    "gross_p": 0.16195778052707288,
-    "noneg_or": 0.15109828304029313,
+    "gross_p": 0.8963079285665041,
+    "noneg_or": 0.02710709065564281,
     "noneg_ci": [
-      0.008687683131828751,
-      2.62793782775992
+      0.000695221764298665,
+      1.056920829506097
     ],
-    "noneg_p": 0.19466430889482844
+    "noneg_p": 0.05356408484175754
   },
   {
     "stratum": "Nx",
-    "n": 193,
-    "events": 3,
+    "n": 125,
+    "events": 1,
     "note": "skipped_sparse_events_for_stable_GLMs"
   },
   {
@@ -7385,14 +7385,14 @@
       <c r="A334" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 190,
-  "n_events": 19,
-  "llf": -44.268871112647304,
-  "aic": 110.53774222529461,
-  "pseudo_r2_mcfadden": 0.2832781856985851,
-  "lr_vs_null_chi2": 34.993787663455734,
-  "lr_vs_null_pvalue": 0.0001251704165162737,
-  "events": 19,
+  "n_obs": 172,
+  "n_events": 27,
+  "llf": -48.02067885668218,
+  "aic": 118.04135771336436,
+  "pseudo_r2_mcfadden": 0.3590857920385425,
+  "lr_vs_null_chi2": 53.809209679799096,
+  "lr_vs_null_pvalue": 5.265862401682142e-08,
+  "events": 27,
   "formula": "y_comp ~ tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + central_pos_flag + lateral_pos_flag + rai_received_flag + ge2 + days_per_100"
 }</t>
         </is>
@@ -7405,16 +7405,16 @@
         </is>
       </c>
       <c r="B335" s="18" t="n">
-        <v>0.02411789512997222</v>
+        <v>0.01430553687569563</v>
       </c>
       <c r="C335" s="18" t="n">
-        <v>0.003095426568054629</v>
+        <v>0.001611860874790714</v>
       </c>
       <c r="D335" s="18" t="n">
-        <v>0.1879136373329959</v>
+        <v>0.1269640503734289</v>
       </c>
       <c r="E335" s="18" t="n">
-        <v>0.0003766088038001654</v>
+        <v>0.0001374378731494298</v>
       </c>
     </row>
     <row r="336">
@@ -7424,16 +7424,16 @@
         </is>
       </c>
       <c r="B336" s="18" t="n">
-        <v>0.8040871828013403</v>
+        <v>0.9641496473996137</v>
       </c>
       <c r="C336" s="18" t="n">
-        <v>0.08807263284518131</v>
+        <v>0.1007742051272875</v>
       </c>
       <c r="D336" s="18" t="n">
-        <v>7.34117031203037</v>
+        <v>9.22442942027322</v>
       </c>
       <c r="E336" s="18" t="n">
-        <v>0.8467687891006692</v>
+        <v>0.9747234021620237</v>
       </c>
     </row>
     <row r="337">
@@ -7443,16 +7443,16 @@
         </is>
       </c>
       <c r="B337" s="18" t="n">
-        <v>1.215463783755397</v>
+        <v>2.287274858977679</v>
       </c>
       <c r="C337" s="18" t="n">
-        <v>0.05425189302784397</v>
+        <v>0.1132010652920106</v>
       </c>
       <c r="D337" s="18" t="n">
-        <v>27.23134856995235</v>
+        <v>46.21534494411332</v>
       </c>
       <c r="E337" s="18" t="n">
-        <v>0.90210646662468</v>
+        <v>0.5895677172274274</v>
       </c>
     </row>
     <row r="338">
@@ -7462,16 +7462,16 @@
         </is>
       </c>
       <c r="B338" s="18" t="n">
-        <v>1.094107558560973</v>
+        <v>0.8609152476078046</v>
       </c>
       <c r="C338" s="18" t="n">
-        <v>0.1059296698756102</v>
+        <v>0.05013569644886012</v>
       </c>
       <c r="D338" s="18" t="n">
-        <v>11.3006238111186</v>
+        <v>14.7833802272923</v>
       </c>
       <c r="E338" s="18" t="n">
-        <v>0.9398200139470939</v>
+        <v>0.9177769004330493</v>
       </c>
     </row>
     <row r="339">
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="B339" s="18" t="n">
-        <v>7.731246178897265e-09</v>
+        <v>7.293306854869124e-09</v>
       </c>
       <c r="C339" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -7490,7 +7490,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E339" s="18" t="n">
-        <v>0.9988893345361833</v>
+        <v>0.9988487210369908</v>
       </c>
     </row>
     <row r="340">
@@ -7500,16 +7500,16 @@
         </is>
       </c>
       <c r="B340" s="18" t="n">
-        <v>0.9516299292814678</v>
+        <v>1.069167920930331</v>
       </c>
       <c r="C340" s="18" t="n">
-        <v>0.7675933343348874</v>
+        <v>0.9180575879292715</v>
       </c>
       <c r="D340" s="18" t="n">
-        <v>1.179790758721146</v>
+        <v>1.245150694440481</v>
       </c>
       <c r="E340" s="18" t="n">
-        <v>0.6511648987734149</v>
+        <v>0.389642447610299</v>
       </c>
     </row>
     <row r="341">
@@ -7519,16 +7519,16 @@
         </is>
       </c>
       <c r="B341" s="18" t="n">
-        <v>1.376884772637402</v>
+        <v>1.343745804674761</v>
       </c>
       <c r="C341" s="18" t="n">
-        <v>0.3573457546158765</v>
+        <v>0.4023955723995962</v>
       </c>
       <c r="D341" s="18" t="n">
-        <v>5.305258709897432</v>
+        <v>4.48725808987761</v>
       </c>
       <c r="E341" s="18" t="n">
-        <v>0.642135476936865</v>
+        <v>0.6310396786099663</v>
       </c>
     </row>
     <row r="342">
@@ -7538,16 +7538,16 @@
         </is>
       </c>
       <c r="B342" s="18" t="n">
-        <v>2.524185711263305</v>
+        <v>4.730784218791998</v>
       </c>
       <c r="C342" s="18" t="n">
-        <v>0.6101216624634787</v>
+        <v>1.230173035595127</v>
       </c>
       <c r="D342" s="18" t="n">
-        <v>10.44302128073879</v>
+        <v>18.19282221053104</v>
       </c>
       <c r="E342" s="18" t="n">
-        <v>0.2012525917947889</v>
+        <v>0.02373445475730844</v>
       </c>
     </row>
     <row r="343">
@@ -7557,16 +7557,16 @@
         </is>
       </c>
       <c r="B343" s="18" t="n">
-        <v>8.843888533396296</v>
+        <v>16.04566099907401</v>
       </c>
       <c r="C343" s="18" t="n">
-        <v>2.771343352277366</v>
+        <v>5.288402466270496</v>
       </c>
       <c r="D343" s="18" t="n">
-        <v>28.22254569317995</v>
+        <v>48.68450132895686</v>
       </c>
       <c r="E343" s="18" t="n">
-        <v>0.0002317142154913127</v>
+        <v>9.533674458230535e-07</v>
       </c>
     </row>
     <row r="344">
@@ -7576,16 +7576,16 @@
         </is>
       </c>
       <c r="B344" s="18" t="n">
-        <v>3.308184753372745</v>
+        <v>4.347373795627257</v>
       </c>
       <c r="C344" s="18" t="n">
-        <v>0.6587459583168344</v>
+        <v>0.8191096408000731</v>
       </c>
       <c r="D344" s="18" t="n">
-        <v>16.61351576321043</v>
+        <v>23.07341774227698</v>
       </c>
       <c r="E344" s="18" t="n">
-        <v>0.1462195968305471</v>
+        <v>0.08440935667253573</v>
       </c>
     </row>
     <row r="345">
@@ -7595,16 +7595,16 @@
         </is>
       </c>
       <c r="B345" s="18" t="n">
-        <v>1.088031671121559</v>
+        <v>1.027415883700668</v>
       </c>
       <c r="C345" s="18" t="n">
-        <v>0.9466969428213032</v>
+        <v>0.8810902853441516</v>
       </c>
       <c r="D345" s="18" t="n">
-        <v>1.25046661060891</v>
+        <v>1.198042261546576</v>
       </c>
       <c r="E345" s="18" t="n">
-        <v>0.2346731667024146</v>
+        <v>0.7300734773233346</v>
       </c>
     </row>
     <row r="346"/>
@@ -7619,14 +7619,14 @@
       <c r="A348" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 171,
-  "n_events": 17,
-  "llf": -43.72348369239609,
-  "aic": 105.44696738479217,
-  "pseudo_r2_mcfadden": 0.21032757118954393,
-  "lr_vs_null_chi2": 23.29131369780839,
-  "lr_vs_null_pvalue": 0.0030096903863037205,
-  "events": 17,
+  "n_obs": 155,
+  "n_events": 10,
+  "llf": -20.92060613937189,
+  "aic": 59.84121227874378,
+  "pseudo_r2_mcfadden": 0.4357775593762361,
+  "lr_vs_null_chi2": 32.31608680437516,
+  "lr_vs_null_pvalue": 8.174784541103985e-05,
+  "events": 10,
   "formula": "y_pp ~ tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + central_pos_flag + lateral_pos_flag + ge2 + days_per_100"
 }</t>
         </is>
@@ -7639,16 +7639,16 @@
         </is>
       </c>
       <c r="B349" s="18" t="n">
-        <v>0.04922383763851679</v>
+        <v>0.008064035047903031</v>
       </c>
       <c r="C349" s="18" t="n">
-        <v>0.008558428624978697</v>
+        <v>0.0004374421368055661</v>
       </c>
       <c r="D349" s="18" t="n">
-        <v>0.2831111057924016</v>
+        <v>0.1486566011419981</v>
       </c>
       <c r="E349" s="18" t="n">
-        <v>0.0007416006127659506</v>
+        <v>0.001187257437931411</v>
       </c>
     </row>
     <row r="350">
@@ -7658,16 +7658,16 @@
         </is>
       </c>
       <c r="B350" s="18" t="n">
-        <v>0.6101636481989928</v>
+        <v>0.5207912504519859</v>
       </c>
       <c r="C350" s="18" t="n">
-        <v>0.07575595587047168</v>
+        <v>0.02350053518559257</v>
       </c>
       <c r="D350" s="18" t="n">
-        <v>4.914460827608937</v>
+        <v>11.54116382479756</v>
       </c>
       <c r="E350" s="18" t="n">
-        <v>0.6425530500487189</v>
+        <v>0.6798233359632306</v>
       </c>
     </row>
     <row r="351">
@@ -7677,16 +7677,16 @@
         </is>
       </c>
       <c r="B351" s="18" t="n">
-        <v>2.760569677045763</v>
+        <v>0.4569921788097005</v>
       </c>
       <c r="C351" s="18" t="n">
-        <v>0.1496531861902959</v>
+        <v>0.0007215570490022236</v>
       </c>
       <c r="D351" s="18" t="n">
-        <v>50.9227042592609</v>
+        <v>289.4322102209741</v>
       </c>
       <c r="E351" s="18" t="n">
-        <v>0.4947450252775966</v>
+        <v>0.8119429127401673</v>
       </c>
     </row>
     <row r="352">
@@ -7696,16 +7696,16 @@
         </is>
       </c>
       <c r="B352" s="18" t="n">
-        <v>0.2889497250519529</v>
+        <v>3.805318600069539e-09</v>
       </c>
       <c r="C352" s="18" t="n">
-        <v>0.0201071220311442</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D352" s="18" t="n">
-        <v>4.152356736000177</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E352" s="18" t="n">
-        <v>0.3612440745991894</v>
+        <v>0.9986737003404704</v>
       </c>
     </row>
     <row r="353">
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="B353" s="18" t="n">
-        <v>1</v>
+        <v>0.9999999999971753</v>
       </c>
       <c r="C353" s="18" t="n">
-        <v>0.9999999999999988</v>
+        <v>0.9999999966661635</v>
       </c>
       <c r="D353" s="18" t="n">
-        <v>1.000000000000002</v>
+        <v>1.000000003328187</v>
       </c>
       <c r="E353" s="18" t="n">
-        <v>0.7463453472040671</v>
+        <v>0.9986738471783234</v>
       </c>
     </row>
     <row r="354">
@@ -7734,16 +7734,16 @@
         </is>
       </c>
       <c r="B354" s="18" t="n">
-        <v>0.9869548136095684</v>
+        <v>0.9489693050266782</v>
       </c>
       <c r="C354" s="18" t="n">
-        <v>0.8140775973964304</v>
+        <v>0.6894536452963146</v>
       </c>
       <c r="D354" s="18" t="n">
-        <v>1.196544171246554</v>
+        <v>1.306168656916419</v>
       </c>
       <c r="E354" s="18" t="n">
-        <v>0.8936812272882472</v>
+        <v>0.7479530407009922</v>
       </c>
     </row>
     <row r="355">
@@ -7753,16 +7753,16 @@
         </is>
       </c>
       <c r="B355" s="18" t="n">
-        <v>1.63226533864375</v>
+        <v>2.9660465529389</v>
       </c>
       <c r="C355" s="18" t="n">
-        <v>0.4313154498324233</v>
+        <v>0.4989009922593401</v>
       </c>
       <c r="D355" s="18" t="n">
-        <v>6.177126594405416</v>
+        <v>17.63362328537447</v>
       </c>
       <c r="E355" s="18" t="n">
-        <v>0.4705611936807946</v>
+        <v>0.231922391911053</v>
       </c>
     </row>
     <row r="356">
@@ -7772,16 +7772,16 @@
         </is>
       </c>
       <c r="B356" s="18" t="n">
-        <v>2.689750688613711</v>
+        <v>5.635648978998322</v>
       </c>
       <c r="C356" s="18" t="n">
-        <v>0.6788461432656692</v>
+        <v>0.7607577131065111</v>
       </c>
       <c r="D356" s="18" t="n">
-        <v>10.65743517683444</v>
+        <v>41.74856050396448</v>
       </c>
       <c r="E356" s="18" t="n">
-        <v>0.1589728430816552</v>
+        <v>0.09058136682602706</v>
       </c>
     </row>
     <row r="357">
@@ -7791,16 +7791,16 @@
         </is>
       </c>
       <c r="B357" s="18" t="n">
-        <v>4.729983405246534</v>
+        <v>21.41979971221927</v>
       </c>
       <c r="C357" s="18" t="n">
-        <v>0.9399959378094223</v>
+        <v>2.173159068637772</v>
       </c>
       <c r="D357" s="18" t="n">
-        <v>23.80089329539583</v>
+        <v>211.124821156874</v>
       </c>
       <c r="E357" s="18" t="n">
-        <v>0.05944280025238249</v>
+        <v>0.008669377912430411</v>
       </c>
     </row>
     <row r="358">
@@ -7810,16 +7810,16 @@
         </is>
       </c>
       <c r="B358" s="18" t="n">
-        <v>1.099003722075374</v>
+        <v>1.09345738038431</v>
       </c>
       <c r="C358" s="18" t="n">
-        <v>0.9508170949000114</v>
+        <v>0.9171411847717404</v>
       </c>
       <c r="D358" s="18" t="n">
-        <v>1.27028551296981</v>
+        <v>1.303669557718633</v>
       </c>
       <c r="E358" s="18" t="n">
-        <v>0.2014294484859358</v>
+        <v>0.3193134743678741</v>
       </c>
     </row>
     <row r="359"/>
@@ -7834,21 +7834,21 @@
       <c r="A361" s="18" t="inlineStr">
         <is>
           <t>{
-  "n": 2511,
-  "events": 178,
-  "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_summary.csv",
+  "n": 2431,
+  "events": 132,
+  "coef_table_path": "/Users/loganglosser/THYROID_2026/data/m044/m044_cox_primary_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 0.9103037356162789,
-    "hr_ci_low": 0.47923951497127887,
-    "hr_ci_high": 1.729099678115261,
-    "p": 0.7740423569506414,
+    "hr": 1.3402360628323684,
+    "hr_ci_low": 0.9073993089820943,
+    "hr_ci_high": 1.9795394225408793,
+    "p": 0.14111782850255308,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 2.443341372260798,
-    "hr_ci_low": 0.6480998157458978,
-    "hr_ci_high": 9.21141607567116,
-    "p": 0.18703020836101486,
+    "hr": 0.9723481503072717,
+    "hr_ci_low": 0.44585922630245495,
+    "hr_ci_high": 2.1205368637243494,
+    "p": 0.9438054455510679,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -7862,16 +7862,16 @@
         </is>
       </c>
       <c r="B362" s="18" t="n">
-        <v>0.9103037356162788</v>
+        <v>1.340236062832368</v>
       </c>
       <c r="C362" s="18" t="n">
-        <v>0.4792395149712788</v>
+        <v>0.9073993089820944</v>
       </c>
       <c r="D362" s="18" t="n">
-        <v>1.729099678115261</v>
+        <v>1.97953942254088</v>
       </c>
       <c r="E362" s="18" t="n">
-        <v>0.7740423569506414</v>
+        <v>0.141117828502553</v>
       </c>
     </row>
     <row r="363">
@@ -7881,16 +7881,16 @@
         </is>
       </c>
       <c r="B363" s="18" t="n">
-        <v>2.443341372260798</v>
+        <v>0.9723481503072716</v>
       </c>
       <c r="C363" s="18" t="n">
-        <v>0.6480998157458978</v>
+        <v>0.4458592263024549</v>
       </c>
       <c r="D363" s="18" t="n">
-        <v>9.21141607567116</v>
+        <v>2.120536863724349</v>
       </c>
       <c r="E363" s="18" t="n">
-        <v>0.1870302083610148</v>
+        <v>0.943805445551068</v>
       </c>
     </row>
     <row r="364">
@@ -7900,16 +7900,16 @@
         </is>
       </c>
       <c r="B364" s="18" t="n">
-        <v>0.936808656010379</v>
+        <v>1.004859364304688</v>
       </c>
       <c r="C364" s="18" t="n">
-        <v>0.7873572846824738</v>
+        <v>0.9005332076517591</v>
       </c>
       <c r="D364" s="18" t="n">
-        <v>1.114627977729191</v>
+        <v>1.121271634905988</v>
       </c>
       <c r="E364" s="18" t="n">
-        <v>0.4616448505866697</v>
+        <v>0.9309286841680916</v>
       </c>
     </row>
     <row r="365">
@@ -7919,16 +7919,16 @@
         </is>
       </c>
       <c r="B365" s="18" t="n">
-        <v>1.292464933823215</v>
+        <v>1.349729672404668</v>
       </c>
       <c r="C365" s="18" t="n">
-        <v>0.7674325569331557</v>
+        <v>0.9322497577434476</v>
       </c>
       <c r="D365" s="18" t="n">
-        <v>2.176693691284387</v>
+        <v>1.95416536549099</v>
       </c>
       <c r="E365" s="18" t="n">
-        <v>0.3347185829241387</v>
+        <v>0.1121957901562477</v>
       </c>
     </row>
     <row r="366">
@@ -7938,16 +7938,16 @@
         </is>
       </c>
       <c r="B366" s="18" t="n">
-        <v>0.9684746094521792</v>
+        <v>1.041143737059909</v>
       </c>
       <c r="C366" s="18" t="n">
-        <v>0.8403511120544364</v>
+        <v>0.9644057203222832</v>
       </c>
       <c r="D366" s="18" t="n">
-        <v>1.116132359080871</v>
+        <v>1.123987817966106</v>
       </c>
       <c r="E366" s="18" t="n">
-        <v>0.6581697063897802</v>
+        <v>0.3019963102549033</v>
       </c>
     </row>
     <row r="367">
@@ -7957,16 +7957,16 @@
         </is>
       </c>
       <c r="B367" s="18" t="n">
-        <v>0.6912735971194832</v>
+        <v>0.8826757023607671</v>
       </c>
       <c r="C367" s="18" t="n">
-        <v>0.3652516338182929</v>
+        <v>0.5569285424622322</v>
       </c>
       <c r="D367" s="18" t="n">
-        <v>1.308301296503542</v>
+        <v>1.398952174534866</v>
       </c>
       <c r="E367" s="18" t="n">
-        <v>0.2566481166469044</v>
+        <v>0.5953257497872817</v>
       </c>
     </row>
     <row r="368">
@@ -7976,16 +7976,16 @@
         </is>
       </c>
       <c r="B368" s="18" t="n">
-        <v>1.735444020336766e-120</v>
+        <v>3.780639220729016</v>
       </c>
       <c r="C368" s="18" t="n">
-        <v>1.315134973274594e-131</v>
+        <v>1.891945870802638</v>
       </c>
       <c r="D368" s="18" t="n">
-        <v>2.290081253199094e-109</v>
+        <v>7.554778991246059</v>
       </c>
       <c r="E368" s="18" t="n">
-        <v>6.764359580967242e-99</v>
+        <v>0.0001664709950325</v>
       </c>
     </row>
     <row r="369">
@@ -7995,16 +7995,16 @@
         </is>
       </c>
       <c r="B369" s="18" t="n">
-        <v>0.0926517228106373</v>
+        <v>0.2708884332478242</v>
       </c>
       <c r="C369" s="18" t="n">
-        <v>0.0025175244798904</v>
+        <v>0.0372210516151641</v>
       </c>
       <c r="D369" s="18" t="n">
-        <v>3.409834465702075</v>
+        <v>1.971479581666769</v>
       </c>
       <c r="E369" s="18" t="n">
-        <v>0.195956430476354</v>
+        <v>0.1971602723952421</v>
       </c>
     </row>
     <row r="370">
@@ -8014,16 +8014,16 @@
         </is>
       </c>
       <c r="B370" s="18" t="n">
-        <v>0.8224286004197328</v>
+        <v>0.4067209203142086</v>
       </c>
       <c r="C370" s="18" t="n">
-        <v>0.3030537526080663</v>
+        <v>0.1835935193457857</v>
       </c>
       <c r="D370" s="18" t="n">
-        <v>2.231910335930145</v>
+        <v>0.9010225829903944</v>
       </c>
       <c r="E370" s="18" t="n">
-        <v>0.7011317863804092</v>
+        <v>0.026637706370686</v>
       </c>
     </row>
     <row r="371">
@@ -8033,16 +8033,16 @@
         </is>
       </c>
       <c r="B371" s="18" t="n">
-        <v>0.0009815781044031999</v>
+        <v>0.0075461200999803</v>
       </c>
       <c r="C371" s="18" t="n">
-        <v>1.596000780572613e-33</v>
+        <v>2.845102152337882e-15</v>
       </c>
       <c r="D371" s="18" t="n">
-        <v>6.036936740709404e+26</v>
+        <v>20014721972.82458</v>
       </c>
       <c r="E371" s="18" t="n">
-        <v>0.8431102437330177</v>
+        <v>0.7377665391684372</v>
       </c>
     </row>
     <row r="372">
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="B372" s="18" t="n">
-        <v>4.524320048617943</v>
+        <v>4.518264935052531</v>
       </c>
       <c r="C372" s="18" t="n">
-        <v>1.18278999739249</v>
+        <v>2.546961579959695</v>
       </c>
       <c r="D372" s="18" t="n">
-        <v>17.30609148492299</v>
+        <v>8.015322329144954</v>
       </c>
       <c r="E372" s="18" t="n">
-        <v>0.0274387810476094</v>
+        <v>2.515336724842402e-07</v>
       </c>
     </row>
     <row r="373">
@@ -8071,16 +8071,16 @@
         </is>
       </c>
       <c r="B373" s="18" t="n">
-        <v>82.52812661832206</v>
+        <v>1.817648660155162</v>
       </c>
       <c r="C373" s="18" t="n">
-        <v>36.92243205135421</v>
+        <v>0.6434328148049326</v>
       </c>
       <c r="D373" s="18" t="n">
-        <v>184.4648714812922</v>
+        <v>5.134718925961949</v>
       </c>
       <c r="E373" s="18" t="n">
-        <v>5.679377375479022e-27</v>
+        <v>0.2594186845749119</v>
       </c>
     </row>
     <row r="374">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="B374" s="18" t="n">
-        <v>167.9575168918756</v>
+        <v>2.485917271109072</v>
       </c>
       <c r="C374" s="18" t="n">
-        <v>65.27575447295933</v>
+        <v>1.057204623159351</v>
       </c>
       <c r="D374" s="18" t="n">
-        <v>432.1624117293142</v>
+        <v>5.84540073267056</v>
       </c>
       <c r="E374" s="18" t="n">
-        <v>2.26199839463582e-26</v>
+        <v>0.0368446073727358</v>
       </c>
     </row>
     <row r="375">
@@ -8109,16 +8109,16 @@
         </is>
       </c>
       <c r="B375" s="18" t="n">
-        <v>6.800892356123554e-05</v>
+        <v>0.008979097228941999</v>
       </c>
       <c r="C375" s="18" t="n">
-        <v>2.378212457213654e-47</v>
+        <v>1.363361196501315e-20</v>
       </c>
       <c r="D375" s="18" t="n">
-        <v>1.94482779279398e+38</v>
+        <v>5913633691034676</v>
       </c>
       <c r="E375" s="18" t="n">
-        <v>0.8474394875745951</v>
+        <v>0.8218744791695178</v>
       </c>
     </row>
     <row r="376">
@@ -8128,16 +8128,16 @@
         </is>
       </c>
       <c r="B376" s="18" t="n">
-        <v>0.3712374815082589</v>
+        <v>0.8706189959733224</v>
       </c>
       <c r="C376" s="18" t="n">
-        <v>0.0250800268175174</v>
+        <v>0.3387842896952702</v>
       </c>
       <c r="D376" s="18" t="n">
-        <v>5.495100490894795</v>
+        <v>2.237345293760173</v>
       </c>
       <c r="E376" s="18" t="n">
-        <v>0.4710864563016359</v>
+        <v>0.7735669622557722</v>
       </c>
     </row>
     <row r="377">
@@ -8147,16 +8147,16 @@
         </is>
       </c>
       <c r="B377" s="18" t="n">
-        <v>0.2729954301672874</v>
+        <v>0.7862157214340246</v>
       </c>
       <c r="C377" s="18" t="n">
-        <v>0.0591887523669318</v>
+        <v>0.4545596288522218</v>
       </c>
       <c r="D377" s="18" t="n">
-        <v>1.259132891164969</v>
+        <v>1.359854948383418</v>
       </c>
       <c r="E377" s="18" t="n">
-        <v>0.0960045354923339</v>
+        <v>0.3895650256240796</v>
       </c>
     </row>
     <row r="378">
@@ -8166,16 +8166,16 @@
         </is>
       </c>
       <c r="B378" s="18" t="n">
-        <v>1.838518534199694</v>
+        <v>2.87959494208754</v>
       </c>
       <c r="C378" s="18" t="n">
-        <v>0.6301882818520425</v>
+        <v>1.36299448754352</v>
       </c>
       <c r="D378" s="18" t="n">
-        <v>5.363715095847168</v>
+        <v>6.083712814892353</v>
       </c>
       <c r="E378" s="18" t="n">
-        <v>0.2649653065047122</v>
+        <v>0.0055805837443682</v>
       </c>
     </row>
     <row r="379">
@@ -8185,16 +8185,16 @@
         </is>
       </c>
       <c r="B379" s="18" t="n">
-        <v>0.7805629636388375</v>
+        <v>2.377548947593914</v>
       </c>
       <c r="C379" s="18" t="n">
-        <v>0.2418644301979245</v>
+        <v>1.248136008535317</v>
       </c>
       <c r="D379" s="18" t="n">
-        <v>2.519091127645579</v>
+        <v>4.528944730020565</v>
       </c>
       <c r="E379" s="18" t="n">
-        <v>0.6785596777827072</v>
+        <v>0.008435967541962</v>
       </c>
     </row>
     <row r="380">
@@ -8204,16 +8204,16 @@
         </is>
       </c>
       <c r="B380" s="18" t="n">
-        <v>2.227525371486014</v>
+        <v>2.112698991541666</v>
       </c>
       <c r="C380" s="18" t="n">
-        <v>0.1779417025391863</v>
+        <v>0.5005488373458631</v>
       </c>
       <c r="D380" s="18" t="n">
-        <v>27.88480277421873</v>
+        <v>8.917205866521748</v>
       </c>
       <c r="E380" s="18" t="n">
-        <v>0.534513006589991</v>
+        <v>0.3086613627342999</v>
       </c>
     </row>
     <row r="381">
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="B381" s="18" t="n">
-        <v>1.479952097268279</v>
+        <v>2.561098596212626</v>
       </c>
       <c r="C381" s="18" t="n">
-        <v>0.5350423956356825</v>
+        <v>1.545119005397009</v>
       </c>
       <c r="D381" s="18" t="n">
-        <v>4.093616184576434</v>
+        <v>4.245126748561953</v>
       </c>
       <c r="E381" s="18" t="n">
-        <v>0.4501466216197959</v>
+        <v>0.0002647828657647</v>
       </c>
     </row>
     <row r="382">
@@ -8246,21 +8246,21 @@
       <c r="A383" s="18" t="inlineStr">
         <is>
           <t>{
-  "n": 2511,
-  "events": 178,
-  "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_with_rai_summary.csv",
+  "n": 2431,
+  "events": 132,
+  "coef_table_path": "/Users/loganglosser/THYROID_2026/data/m044/m044_cox_primary_with_rai_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 0.6195679029743909,
-    "hr_ci_low": 0.2887910192490381,
-    "hr_ci_high": 1.3292116472121316,
-    "p": 0.218983236437501,
+    "hr": 1.0251857457439537,
+    "hr_ci_low": 0.7047990094271923,
+    "hr_ci_high": 1.4912135221795575,
+    "p": 0.8964848433300046,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 5.167153773864532,
-    "hr_ci_low": 0.6368362954626577,
-    "hr_ci_high": 41.92518283425644,
-    "p": 0.12416666927802668,
+    "hr": 0.6474956022062716,
+    "hr_ci_low": 0.10467581337860118,
+    "hr_ci_high": 4.005228536988559,
+    "p": 0.6401476335369112,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -8274,16 +8274,16 @@
         </is>
       </c>
       <c r="B384" s="18" t="n">
-        <v>0.6195679029743909</v>
+        <v>1.025185745743953</v>
       </c>
       <c r="C384" s="18" t="n">
-        <v>0.2887910192490381</v>
+        <v>0.7047990094271923</v>
       </c>
       <c r="D384" s="18" t="n">
-        <v>1.329211647212132</v>
+        <v>1.491213522179557</v>
       </c>
       <c r="E384" s="18" t="n">
-        <v>0.218983236437501</v>
+        <v>0.8964848433300046</v>
       </c>
     </row>
     <row r="385">
@@ -8293,16 +8293,16 @@
         </is>
       </c>
       <c r="B385" s="18" t="n">
-        <v>5.167153773864532</v>
+        <v>0.6474956022062716</v>
       </c>
       <c r="C385" s="18" t="n">
-        <v>0.6368362954626577</v>
+        <v>0.1046758133786011</v>
       </c>
       <c r="D385" s="18" t="n">
-        <v>41.92518283425644</v>
+        <v>4.005228536988559</v>
       </c>
       <c r="E385" s="18" t="n">
-        <v>0.1241666692780266</v>
+        <v>0.6401476335369112</v>
       </c>
     </row>
     <row r="386">
@@ -8312,16 +8312,16 @@
         </is>
       </c>
       <c r="B386" s="18" t="n">
-        <v>0.7863070086627305</v>
+        <v>0.9638222789955712</v>
       </c>
       <c r="C386" s="18" t="n">
-        <v>0.6240342904607402</v>
+        <v>0.8577024246183169</v>
       </c>
       <c r="D386" s="18" t="n">
-        <v>0.9907768232025208</v>
+        <v>1.08307188929961</v>
       </c>
       <c r="E386" s="18" t="n">
-        <v>0.0414964955672526</v>
+        <v>0.5358300140766238</v>
       </c>
     </row>
     <row r="387">
@@ -8331,16 +8331,16 @@
         </is>
       </c>
       <c r="B387" s="18" t="n">
-        <v>1.797606236232786</v>
+        <v>2.133088137238956</v>
       </c>
       <c r="C387" s="18" t="n">
-        <v>0.8660663278899774</v>
+        <v>1.431915515359345</v>
       </c>
       <c r="D387" s="18" t="n">
-        <v>3.73110935788917</v>
+        <v>3.177607164964408</v>
       </c>
       <c r="E387" s="18" t="n">
-        <v>0.1154812929439595</v>
+        <v>0.0001949580657007</v>
       </c>
     </row>
     <row r="388">
@@ -8350,16 +8350,16 @@
         </is>
       </c>
       <c r="B388" s="18" t="n">
-        <v>1.068541698187198</v>
+        <v>0.9902081101452836</v>
       </c>
       <c r="C388" s="18" t="n">
-        <v>0.9630806915513695</v>
+        <v>0.8931722316948478</v>
       </c>
       <c r="D388" s="18" t="n">
-        <v>1.185551087028392</v>
+        <v>1.097786145385324</v>
       </c>
       <c r="E388" s="18" t="n">
-        <v>0.2111437289383263</v>
+        <v>0.8516609766894032</v>
       </c>
     </row>
     <row r="389">
@@ -8369,16 +8369,16 @@
         </is>
       </c>
       <c r="B389" s="18" t="n">
-        <v>117.6132179872576</v>
+        <v>21.90767007744524</v>
       </c>
       <c r="C389" s="18" t="n">
-        <v>12.10022176593432</v>
+        <v>6.140130692115092</v>
       </c>
       <c r="D389" s="18" t="n">
-        <v>1143.191365654286</v>
+        <v>78.16543853675897</v>
       </c>
       <c r="E389" s="18" t="n">
-        <v>3.978763320899973e-05</v>
+        <v>1.970819120446868e-06</v>
       </c>
     </row>
     <row r="390">
@@ -8388,16 +8388,16 @@
         </is>
       </c>
       <c r="B390" s="18" t="n">
-        <v>2.121731602928528e-100</v>
+        <v>32.01469997194729</v>
       </c>
       <c r="C390" s="18" t="n">
-        <v>1.607867152276966e-111</v>
+        <v>5.987455364206204</v>
       </c>
       <c r="D390" s="18" t="n">
-        <v>2.799823970836494e-89</v>
+        <v>171.1814037764747</v>
       </c>
       <c r="E390" s="18" t="n">
-        <v>4.385630028864638e-69</v>
+        <v>5.073978280604224e-05</v>
       </c>
     </row>
     <row r="391">
@@ -8407,16 +8407,16 @@
         </is>
       </c>
       <c r="B391" s="18" t="n">
-        <v>0.51667350299869</v>
+        <v>1.379201871859657</v>
       </c>
       <c r="C391" s="18" t="n">
-        <v>1.022602544094179e-06</v>
+        <v>0.0541391960562571</v>
       </c>
       <c r="D391" s="18" t="n">
-        <v>261051.0899299618</v>
+        <v>35.1353167742751</v>
       </c>
       <c r="E391" s="18" t="n">
-        <v>0.9214948614902508</v>
+        <v>0.8456864186987447</v>
       </c>
     </row>
     <row r="392">
@@ -8426,16 +8426,16 @@
         </is>
       </c>
       <c r="B392" s="18" t="n">
-        <v>5.275814328773673</v>
+        <v>12.31243372469729</v>
       </c>
       <c r="C392" s="18" t="n">
-        <v>1.734829405598675</v>
+        <v>7.963558835808774</v>
       </c>
       <c r="D392" s="18" t="n">
-        <v>16.04435383782778</v>
+        <v>19.03621576114936</v>
       </c>
       <c r="E392" s="18" t="n">
-        <v>0.0033811494546532</v>
+        <v>1.422338654868268e-29</v>
       </c>
     </row>
     <row r="393">
@@ -8445,16 +8445,16 @@
         </is>
       </c>
       <c r="B393" s="18" t="n">
-        <v>0.0007539449476274</v>
+        <v>0.0019963571577365</v>
       </c>
       <c r="C393" s="18" t="n">
-        <v>7.885724289615266e-34</v>
+        <v>3.868558806563272e-31</v>
       </c>
       <c r="D393" s="18" t="n">
-        <v>7.208380145898187e+26</v>
+        <v>1.030213601634879e+25</v>
       </c>
       <c r="E393" s="18" t="n">
-        <v>0.838241934116758</v>
+        <v>0.8485733088426775</v>
       </c>
     </row>
     <row r="394">
@@ -8464,16 +8464,16 @@
         </is>
       </c>
       <c r="B394" s="18" t="n">
-        <v>0.2147113890850175</v>
+        <v>0.5585306401659619</v>
       </c>
       <c r="C394" s="18" t="n">
-        <v>0.0083525840177399</v>
+        <v>0.0902956336270401</v>
       </c>
       <c r="D394" s="18" t="n">
-        <v>5.519367480159952</v>
+        <v>3.45483456368127</v>
       </c>
       <c r="E394" s="18" t="n">
-        <v>0.3530294384880128</v>
+        <v>0.5310044072235816</v>
       </c>
     </row>
     <row r="395">
@@ -8483,16 +8483,16 @@
         </is>
       </c>
       <c r="B395" s="18" t="n">
-        <v>1872.628714966891</v>
+        <v>1.067561336782824</v>
       </c>
       <c r="C395" s="18" t="n">
-        <v>706.3861810513191</v>
+        <v>0.0552022152389201</v>
       </c>
       <c r="D395" s="18" t="n">
-        <v>4964.335937177381</v>
+        <v>20.64567885293848</v>
       </c>
       <c r="E395" s="18" t="n">
-        <v>7.788175008546828e-52</v>
+        <v>0.9654957007284511</v>
       </c>
     </row>
     <row r="396">
@@ -8502,16 +8502,16 @@
         </is>
       </c>
       <c r="B396" s="18" t="n">
-        <v>1.503991751504678</v>
+        <v>3.07092353522997</v>
       </c>
       <c r="C396" s="18" t="n">
-        <v>0.9170436666850992</v>
+        <v>2.122165598586879</v>
       </c>
       <c r="D396" s="18" t="n">
-        <v>2.46661230077591</v>
+        <v>4.443843291734172</v>
       </c>
       <c r="E396" s="18" t="n">
-        <v>0.1059049444034784</v>
+        <v>2.669630795986853e-09</v>
       </c>
     </row>
     <row r="397">
@@ -8521,16 +8521,16 @@
         </is>
       </c>
       <c r="B397" s="18" t="n">
-        <v>0.0996147536797593</v>
+        <v>0.7101668630161693</v>
       </c>
       <c r="C397" s="18" t="n">
-        <v>0.0162759499609488</v>
+        <v>0.0188007453940678</v>
       </c>
       <c r="D397" s="18" t="n">
-        <v>0.6096786469906684</v>
+        <v>26.82537116243052</v>
       </c>
       <c r="E397" s="18" t="n">
-        <v>0.0125848832600914</v>
+        <v>0.8534533433730029</v>
       </c>
     </row>
     <row r="398">
@@ -8540,16 +8540,16 @@
         </is>
       </c>
       <c r="B398" s="18" t="n">
-        <v>3.184477097328247e-05</v>
+        <v>0.0006836981666639</v>
       </c>
       <c r="C398" s="18" t="n">
-        <v>8.278552790267166e-48</v>
+        <v>2.133639061031807e-46</v>
       </c>
       <c r="D398" s="18" t="n">
-        <v>1.224959801588808e+38</v>
+        <v>2.190825953821933e+39</v>
       </c>
       <c r="E398" s="18" t="n">
-        <v>0.8360323977225377</v>
+        <v>0.8839638594141704</v>
       </c>
     </row>
     <row r="399">
@@ -8559,16 +8559,16 @@
         </is>
       </c>
       <c r="B399" s="18" t="n">
-        <v>4.349421678705429</v>
+        <v>0.7934391289837374</v>
       </c>
       <c r="C399" s="18" t="n">
-        <v>2.085509217147165</v>
+        <v>0.1973225501994678</v>
       </c>
       <c r="D399" s="18" t="n">
-        <v>9.070911211349411</v>
+        <v>3.190439464552236</v>
       </c>
       <c r="E399" s="18" t="n">
-        <v>8.859188475476247e-05</v>
+        <v>0.7445046440307495</v>
       </c>
     </row>
     <row r="400">
@@ -8578,16 +8578,16 @@
         </is>
       </c>
       <c r="B400" s="18" t="n">
-        <v>1.255370520701112</v>
+        <v>2.924740638021893</v>
       </c>
       <c r="C400" s="18" t="n">
-        <v>0.6551809314904289</v>
+        <v>1.816274937669224</v>
       </c>
       <c r="D400" s="18" t="n">
-        <v>2.405373948628728</v>
+        <v>4.709698747852546</v>
       </c>
       <c r="E400" s="18" t="n">
-        <v>0.4930353877669128</v>
+        <v>1.009525328547464e-05</v>
       </c>
     </row>
     <row r="401">
@@ -8597,16 +8597,16 @@
         </is>
       </c>
       <c r="B401" s="18" t="n">
-        <v>2.286744666806819</v>
+        <v>0.3222180608691155</v>
       </c>
       <c r="C401" s="18" t="n">
-        <v>0.8921604001332837</v>
+        <v>0.1341641686980543</v>
       </c>
       <c r="D401" s="18" t="n">
-        <v>5.861279171759041</v>
+        <v>0.773861454647531</v>
       </c>
       <c r="E401" s="18" t="n">
-        <v>0.0850058938994806</v>
+        <v>0.0112948383514082</v>
       </c>
     </row>
     <row r="402">
@@ -8616,16 +8616,16 @@
         </is>
       </c>
       <c r="B402" s="18" t="n">
-        <v>0.1767500360564004</v>
+        <v>1.140251794800116</v>
       </c>
       <c r="C402" s="18" t="n">
-        <v>0.0328444541491056</v>
+        <v>0.7047603550312281</v>
       </c>
       <c r="D402" s="18" t="n">
-        <v>0.9511674361861652</v>
+        <v>1.844845763901225</v>
       </c>
       <c r="E402" s="18" t="n">
-        <v>0.0435631735366287</v>
+        <v>0.5928940322947128</v>
       </c>
     </row>
     <row r="403">
@@ -8635,16 +8635,16 @@
         </is>
       </c>
       <c r="B403" s="18" t="n">
-        <v>0.0630401414450845</v>
+        <v>0.3430484104040695</v>
       </c>
       <c r="C403" s="18" t="n">
-        <v>1.682742170756617e-09</v>
+        <v>0.02276038497951</v>
       </c>
       <c r="D403" s="18" t="n">
-        <v>2361656.766246844</v>
+        <v>5.170484242103192</v>
       </c>
       <c r="E403" s="18" t="n">
-        <v>0.7560698860865616</v>
+        <v>0.4395441010256917</v>
       </c>
     </row>
     <row r="404">
@@ -8654,16 +8654,16 @@
         </is>
       </c>
       <c r="B404" s="18" t="n">
-        <v>0.5213933439270377</v>
+        <v>0.1298383127132583</v>
       </c>
       <c r="C404" s="18" t="n">
-        <v>0.1898912323532288</v>
+        <v>0.0577726333528609</v>
       </c>
       <c r="D404" s="18" t="n">
-        <v>1.431614381151262</v>
+        <v>0.2917988409020833</v>
       </c>
       <c r="E404" s="18" t="n">
-        <v>0.2063294534311404</v>
+        <v>7.767290633018164e-07</v>
       </c>
     </row>
   </sheetData>
@@ -8679,7 +8679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="70" customWidth="1" style="18" min="1" max="1"/>
@@ -9108,335 +9108,282 @@
     </row>
     <row r="25"/>
     <row r="26"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>OR pooled=1.720509958843602 p=0.001948210925390039</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 5.35% expected 4.1% (n=318)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 11.44% expected 7.0% (n=341)</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 3.75% expected 2.6% (n=267)</t>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>OR pooled=2.183267567544981 p=0.0001440425701642091</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 11.61% expected 8.6% (n=336)</t>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 10.0% expected 11.4% (n=40)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.56% expected 2.7% (n=702)</t>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 8.33% expected 7.0% (n=36)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.2% expected 2.3% (n=625)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 1.73% expected 1.1% (n=924)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 6.92% expected 5.6% (n=260)</t>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&lt;=1'): got 4.35% expected 3.8% (n=46)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 18.18% expected 11.4% (n=44)</t>
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>Strict-DTC Cox/KM inclusion flow</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>/Users/loganglosser/THYROID_2026/data/m044/m044_inclusion_flow_qc.csv</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 9.3% expected 7.0% (n=43)</t>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>excluded_at_step</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>cum_excluded_from_cohort</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>path_proven_events_final_only</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 7.84% expected 3.8% (n=51)</t>
-        </is>
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3868</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Strict-DTC histology (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3648</v>
+      </c>
+      <c r="D40" t="n">
+        <v>220</v>
+      </c>
+      <c r="E40" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3619</v>
+      </c>
+      <c r="D41" t="n">
+        <v>29</v>
+      </c>
+      <c r="E41" t="n">
+        <v>249</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="inlineStr">
-        <is>
-          <t>Strict-DTC Cox/KM inclusion flow</t>
-        </is>
+      <c r="A42" t="n">
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
-        </is>
+          <t>Sex known female/male (same frame as primary logistic/Cox categoricals)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3619</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>249</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
+      <c r="A43" t="n">
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>excluded_at_step</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>cum_excluded_from_cohort</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>path_proven_events_final_only</t>
-        </is>
+          <t>Positive analytic follow-up (followup_years &gt; 0)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2437</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1182</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1431</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+          <t>Known surgery date (CPM surg_first_date; mig_258/mig_254 lineage)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4012</v>
+        <v>2437</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Strict-DTC histology (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list)</t>
+          <t>Finite positive Cox time_days (path-proven TTE if event else censor at FU×365.25)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3789</v>
+        <v>2434</v>
       </c>
       <c r="D45" t="n">
-        <v>223</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>223</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+          <t>Tumor size known (cm; Cox covariate complete-case)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3756</v>
+        <v>2431</v>
       </c>
       <c r="D46" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>256</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sex known female/male (same frame as primary logistic/Cox categoricals)</t>
+          <t>Age at surgery known (Cox covariate complete-case)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3756</v>
+        <v>2431</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>256</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Positive analytic follow-up (followup_years &gt; 0)</t>
+          <t>Final Cox PH + Kaplan–Meier rows (lifelines sample; aligns Figure 6)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2525</v>
+        <v>2431</v>
       </c>
       <c r="D48" t="n">
-        <v>1231</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1487</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>5</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Known surgery date (CPM surg_first_date; mig_258/mig_254 lineage)</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>2525</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1487</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>6</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Finite positive Cox time_days (path-proven TTE if event else censor at FU×365.25)</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>2515</v>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>7</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Tumor size known (cm; Cox covariate complete-case)</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>2511</v>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>8</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Age at surgery known (Cox covariate complete-case)</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2511</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>9</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Final Cox PH + Kaplan–Meier rows (lifelines sample; aligns Figure 6)</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>2511</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1501</v>
-      </c>
-      <c r="F53" t="n">
-        <v>178</v>
+        <v>1437</v>
+      </c>
+      <c r="F48" t="n">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -11189,16 +11136,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04922383763851679</v>
+        <v>0.008064035047903031</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008558428624978697</v>
+        <v>0.0004374421368055661</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2831111057924016</v>
+        <v>0.1486566011419981</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007416006127659506</v>
+        <v>0.001187257437931411</v>
       </c>
     </row>
     <row r="5">
@@ -11208,16 +11155,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6101636481989928</v>
+        <v>0.5207912504519859</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07575595587047168</v>
+        <v>0.02350053518559257</v>
       </c>
       <c r="D5" t="n">
-        <v>4.914460827608937</v>
+        <v>11.54116382479756</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6425530500487189</v>
+        <v>0.6798233359632306</v>
       </c>
     </row>
     <row r="6">
@@ -11227,16 +11174,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.760569677045763</v>
+        <v>0.4569921788097005</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1496531861902959</v>
+        <v>0.0007215570490022236</v>
       </c>
       <c r="D6" t="n">
-        <v>50.9227042592609</v>
+        <v>289.4322102209741</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4947450252775966</v>
+        <v>0.8119429127401673</v>
       </c>
     </row>
     <row r="7">
@@ -11246,16 +11193,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2889497250519529</v>
+        <v>3.805318600069539e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0201071220311442</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>4.152356736000177</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3612440745991894</v>
+        <v>0.9986737003404704</v>
       </c>
     </row>
     <row r="8">
@@ -11265,16 +11212,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.9999999999971753</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9999999999999988</v>
+        <v>0.9999999966661635</v>
       </c>
       <c r="D8" t="n">
-        <v>1.000000000000002</v>
+        <v>1.000000003328187</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7463453472040671</v>
+        <v>0.9986738471783234</v>
       </c>
     </row>
     <row r="9">
@@ -11284,16 +11231,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9869548136095684</v>
+        <v>0.9489693050266782</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8140775973964304</v>
+        <v>0.6894536452963146</v>
       </c>
       <c r="D9" t="n">
-        <v>1.196544171246554</v>
+        <v>1.306168656916419</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8936812272882472</v>
+        <v>0.7479530407009922</v>
       </c>
     </row>
     <row r="10">
@@ -11303,16 +11250,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.63226533864375</v>
+        <v>2.9660465529389</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4313154498324233</v>
+        <v>0.4989009922593401</v>
       </c>
       <c r="D10" t="n">
-        <v>6.177126594405416</v>
+        <v>17.63362328537447</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4705611936807946</v>
+        <v>0.231922391911053</v>
       </c>
     </row>
     <row r="11">
@@ -11322,16 +11269,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.689750688613711</v>
+        <v>5.635648978998322</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6788461432656692</v>
+        <v>0.7607577131065111</v>
       </c>
       <c r="D11" t="n">
-        <v>10.65743517683444</v>
+        <v>41.74856050396448</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1589728430816552</v>
+        <v>0.09058136682602706</v>
       </c>
     </row>
     <row r="12">
@@ -11341,16 +11288,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.729983405246534</v>
+        <v>21.41979971221927</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9399959378094223</v>
+        <v>2.173159068637772</v>
       </c>
       <c r="D12" t="n">
-        <v>23.80089329539583</v>
+        <v>211.124821156874</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05944280025238249</v>
+        <v>0.008669377912430411</v>
       </c>
     </row>
     <row r="13">
@@ -11360,16 +11307,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.099003722075374</v>
+        <v>1.09345738038431</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9508170949000114</v>
+        <v>0.9171411847717404</v>
       </c>
       <c r="D13" t="n">
-        <v>1.27028551296981</v>
+        <v>1.303669557718633</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2014294484859358</v>
+        <v>0.3193134743678741</v>
       </c>
     </row>
   </sheetData>
@@ -12139,40 +12086,40 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>2517</v>
+        <v>2413</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="E5" s="28" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="H5" s="28" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>5.80%</t>
         </is>
       </c>
       <c r="I5" s="28" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J5" s="28" t="n">
-        <v>8050.9</v>
+        <v>7736.4</v>
       </c>
       <c r="K5" s="28" t="n">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="L5" s="28" t="n">
         <v>1.78</v>
@@ -12193,40 +12140,40 @@
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>1262</v>
+        <v>1243</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D6" s="28" t="inlineStr">
         <is>
-          <t>8.32%</t>
+          <t>5.79%</t>
         </is>
       </c>
       <c r="E6" s="28" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>7.08%</t>
         </is>
       </c>
       <c r="G6" s="28" t="n">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="H6" s="28" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>12.87%</t>
         </is>
       </c>
       <c r="I6" s="28" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>4135.6</v>
+        <v>4124.5</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>2.49</v>
+        <v>1.75</v>
       </c>
       <c r="L6" s="28" t="n">
         <v>3.94</v>
@@ -12247,40 +12194,40 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="C7" s="28" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>9.47%</t>
+          <t>6.36%</t>
         </is>
       </c>
       <c r="E7" s="28" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>9.25%</t>
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>15.61%</t>
         </is>
       </c>
       <c r="I7" s="28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J7" s="28" t="n">
-        <v>700.8</v>
+        <v>663</v>
       </c>
       <c r="K7" s="28" t="n">
-        <v>2.43</v>
+        <v>1.66</v>
       </c>
       <c r="L7" s="28" t="n">
         <v>4.14</v>
@@ -12301,14 +12248,14 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="28" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="E8" s="28" t="n">
@@ -12324,17 +12271,17 @@
       </c>
       <c r="H8" s="28" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="I8" s="28" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>86.5</v>
+        <v>72.7</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="L8" s="28" t="n">
         <v>1.16</v>
@@ -12355,7 +12302,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>0</v>
@@ -12385,7 +12332,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="28" t="n">
-        <v>35.5</v>
+        <v>24.1</v>
       </c>
       <c r="K9" s="28" t="n">
         <v>0</v>
@@ -12493,16 +12440,16 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>0.6669255032178935</v>
+        <v>0.5524765530770338</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>0.3177659954934816</v>
+        <v>0.2305492981731137</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>1.399739535225268</v>
+        <v>1.323926570666421</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>0.2842080600304258</v>
+        <v>0.183297870332655</v>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
@@ -12517,16 +12464,16 @@
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>2.076021874744788</v>
+        <v>1.720081707216226</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>1.47858360953565</v>
+        <v>1.154912102130645</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>2.914861761366597</v>
+        <v>2.561823600290921</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>2.458209087953318e-05</v>
+        <v>0.007616872842289187</v>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
@@ -12541,16 +12488,16 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>0.9342008179855855</v>
+        <v>0.952926479401809</v>
       </c>
       <c r="C7" s="28" t="n">
-        <v>0.84698924688341</v>
+        <v>0.8491424738889585</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>1.030392264761622</v>
+        <v>1.069395187578232</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>0.1734490646119403</v>
+        <v>0.4124644185366982</v>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
@@ -12565,16 +12512,16 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>1.243365865671108</v>
+        <v>1.4650883599481</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>0.8826065421803896</v>
+        <v>0.9878422186406968</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>1.751583069050145</v>
+        <v>2.172901564593024</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>0.2128480394355131</v>
+        <v>0.05754647417412548</v>
       </c>
       <c r="F8" s="28" t="n"/>
     </row>
@@ -12585,16 +12532,16 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>1.047101558155796</v>
+        <v>1.043402510286877</v>
       </c>
       <c r="C9" s="28" t="n">
-        <v>0.9772115482993279</v>
+        <v>0.9634033389088166</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>1.121990090068454</v>
+        <v>1.130044659909568</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>0.1915859030131092</v>
+        <v>0.2965259820827366</v>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
@@ -12609,16 +12556,16 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>1.041542433253086</v>
+        <v>0.9358545641585758</v>
       </c>
       <c r="C10" s="28" t="n">
-        <v>0.7041041255179393</v>
+        <v>0.589211285748405</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>1.540696327363191</v>
+        <v>1.48643413057505</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>0.8385463175879454</v>
+        <v>0.7788356451782399</v>
       </c>
       <c r="F10" s="28" t="n"/>
     </row>
@@ -12629,16 +12576,16 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>5.589610780216073</v>
+        <v>3.963807382165004</v>
       </c>
       <c r="C11" s="28" t="n">
-        <v>2.888512518705153</v>
+        <v>1.836332193384906</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>10.81655297388619</v>
+        <v>8.556060292089263</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>3.235499429458743e-07</v>
+        <v>0.0004512797412887346</v>
       </c>
       <c r="F11" s="28" t="n"/>
     </row>
@@ -12649,16 +12596,16 @@
         </is>
       </c>
       <c r="B12" s="28" t="n">
-        <v>0.4437282968749986</v>
+        <v>0.3212734795521583</v>
       </c>
       <c r="C12" s="28" t="n">
-        <v>0.1329051128210752</v>
+        <v>0.04281602105476547</v>
       </c>
       <c r="D12" s="28" t="n">
-        <v>1.481468976386622</v>
+        <v>2.410701557987555</v>
       </c>
       <c r="E12" s="28" t="n">
-        <v>0.1865048194220119</v>
+        <v>0.2694885897248011</v>
       </c>
       <c r="F12" s="28" t="n"/>
     </row>
@@ -12669,16 +12616,16 @@
         </is>
       </c>
       <c r="B13" s="28" t="n">
-        <v>1.000000000181017</v>
+        <v>1.000000000021757</v>
       </c>
       <c r="C13" s="28" t="n">
-        <v>0.999999567207104</v>
+        <v>0.9999999223249101</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>1.000000433155118</v>
+        <v>1.000000077718611</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>0.9993461969791613</v>
+        <v>0.9995620828278956</v>
       </c>
       <c r="F13" s="28" t="n"/>
     </row>
@@ -12689,16 +12636,16 @@
         </is>
       </c>
       <c r="B14" s="28" t="n">
-        <v>0.5113539780108236</v>
+        <v>0.3890162634245708</v>
       </c>
       <c r="C14" s="28" t="n">
-        <v>0.2699812706456613</v>
+        <v>0.1725341866318366</v>
       </c>
       <c r="D14" s="28" t="n">
-        <v>0.9685223356500121</v>
+        <v>0.8771227092039422</v>
       </c>
       <c r="E14" s="28" t="n">
-        <v>0.03957954869899567</v>
+        <v>0.02284436960335355</v>
       </c>
       <c r="F14" s="28" t="n"/>
     </row>
@@ -12709,16 +12656,16 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>8.57905103879509</v>
+        <v>8.037808447340625</v>
       </c>
       <c r="C15" s="28" t="n">
-        <v>4.741888142926279</v>
+        <v>4.156117229943009</v>
       </c>
       <c r="D15" s="28" t="n">
-        <v>15.52126800714273</v>
+        <v>15.54488506019024</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>1.201350488743744e-12</v>
+        <v>5.896019029138317e-10</v>
       </c>
       <c r="F15" s="28" t="n"/>
     </row>
@@ -12729,16 +12676,16 @@
         </is>
       </c>
       <c r="B16" s="28" t="n">
-        <v>1.715255922337146</v>
+        <v>1.842180788706986</v>
       </c>
       <c r="C16" s="28" t="n">
-        <v>0.6113741691283806</v>
+        <v>0.5932306073819177</v>
       </c>
       <c r="D16" s="28" t="n">
-        <v>4.812278679204144</v>
+        <v>5.720591648596947</v>
       </c>
       <c r="E16" s="28" t="n">
-        <v>0.3053064560865795</v>
+        <v>0.2906203332201726</v>
       </c>
       <c r="F16" s="28" t="n"/>
     </row>
@@ -12749,7 +12696,7 @@
         </is>
       </c>
       <c r="B17" s="28" t="n">
-        <v>5.16727771697659e-10</v>
+        <v>1.82521779930501e-09</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>1.388794386496402e-11</v>
@@ -12758,7 +12705,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>0.9992030750468766</v>
+        <v>0.9988564339892622</v>
       </c>
       <c r="F17" s="28" t="n"/>
     </row>
@@ -12769,16 +12716,16 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>0.7384752852970617</v>
+        <v>0.7049729669721491</v>
       </c>
       <c r="C18" s="28" t="n">
-        <v>0.4452543797335514</v>
+        <v>0.3996192564872628</v>
       </c>
       <c r="D18" s="28" t="n">
-        <v>1.224795918506005</v>
+        <v>1.243650990520662</v>
       </c>
       <c r="E18" s="28" t="n">
-        <v>0.2402193969427563</v>
+        <v>0.2274016006370255</v>
       </c>
       <c r="F18" s="28" t="n"/>
     </row>
@@ -12789,16 +12736,16 @@
         </is>
       </c>
       <c r="B19" s="28" t="n">
-        <v>1.757893717879382</v>
+        <v>1.960800196196869</v>
       </c>
       <c r="C19" s="28" t="n">
-        <v>0.7279395352184567</v>
+        <v>0.7711608720824789</v>
       </c>
       <c r="D19" s="28" t="n">
-        <v>4.245119510417058</v>
+        <v>4.985648972338509</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>0.2098197201769865</v>
+        <v>0.1573031701081236</v>
       </c>
       <c r="F19" s="28" t="n"/>
     </row>
@@ -12809,7 +12756,7 @@
         </is>
       </c>
       <c r="B20" s="28" t="n">
-        <v>7.668397975541751e-10</v>
+        <v>2.501109593889407e-09</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>1.388794386496402e-11</v>
@@ -12818,7 +12765,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>0.999474226098751</v>
+        <v>0.9991855474853423</v>
       </c>
       <c r="F20" s="28" t="n"/>
     </row>
@@ -12829,16 +12776,16 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>0.6744064518387922</v>
+        <v>0.7422833948819164</v>
       </c>
       <c r="C21" s="28" t="n">
-        <v>0.2721746782092361</v>
+        <v>0.276135190157902</v>
       </c>
       <c r="D21" s="28" t="n">
-        <v>1.671074125169499</v>
+        <v>1.995343795198121</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>0.3948394123437013</v>
+        <v>0.5547156582209726</v>
       </c>
       <c r="F21" s="28" t="n"/>
     </row>
@@ -12849,16 +12796,16 @@
         </is>
       </c>
       <c r="B22" s="28" t="n">
-        <v>1.823942570144014</v>
+        <v>2.75396182855841</v>
       </c>
       <c r="C22" s="28" t="n">
-        <v>1.112341481819554</v>
+        <v>1.611105036455845</v>
       </c>
       <c r="D22" s="28" t="n">
-        <v>2.990778060116638</v>
+        <v>4.707517872230699</v>
       </c>
       <c r="E22" s="28" t="n">
-        <v>0.01722257193913048</v>
+        <v>0.0002126425680882026</v>
       </c>
       <c r="F22" s="28" t="n"/>
     </row>
@@ -12869,16 +12816,16 @@
         </is>
       </c>
       <c r="B23" s="28" t="n">
-        <v>2.39090079920365</v>
+        <v>2.803176034744242</v>
       </c>
       <c r="C23" s="28" t="n">
-        <v>1.317147438489974</v>
+        <v>1.407722482750835</v>
       </c>
       <c r="D23" s="28" t="n">
-        <v>4.339989939308657</v>
+        <v>5.581921137189987</v>
       </c>
       <c r="E23" s="28" t="n">
-        <v>0.004162942684026138</v>
+        <v>0.003356295661775941</v>
       </c>
       <c r="F23" s="28" t="n"/>
     </row>
@@ -12889,16 +12836,16 @@
         </is>
       </c>
       <c r="B24" s="28" t="n">
-        <v>2.788892715938317</v>
+        <v>3.049893524544781</v>
       </c>
       <c r="C24" s="28" t="n">
-        <v>1.376348027128713</v>
+        <v>1.343814584395691</v>
       </c>
       <c r="D24" s="28" t="n">
-        <v>5.651130693477159</v>
+        <v>6.921974667541801</v>
       </c>
       <c r="E24" s="28" t="n">
-        <v>0.004420333345359666</v>
+        <v>0.007661210246188071</v>
       </c>
       <c r="F24" s="28" t="n"/>
     </row>
@@ -12909,16 +12856,16 @@
         </is>
       </c>
       <c r="B25" s="18" t="n">
-        <v>1.304747414145783</v>
+        <v>1.570591164182373</v>
       </c>
       <c r="C25" s="18" t="n">
-        <v>0.3606986337620886</v>
+        <v>0.3406980676503913</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>4.719634773673588</v>
+        <v>7.240301132376875</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>0.6851050284367951</v>
+        <v>0.5625910155522527</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="19">
@@ -12935,16 +12882,16 @@
         </is>
       </c>
       <c r="B27" s="18" t="n">
-        <v>1.605347833573521</v>
+        <v>1.35550179769246</v>
       </c>
       <c r="C27" s="18" t="n">
-        <v>1.144503489899247</v>
+        <v>0.9096029584447941</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>2.251755184238075</v>
+        <v>2.019985870196581</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>0.006110978617229343</v>
+        <v>0.135057119508862</v>
       </c>
     </row>
     <row r="28">
@@ -12954,16 +12901,16 @@
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>1.234036811889456</v>
+        <v>0.9942646397911438</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.6296290952169418</v>
+        <v>0.443867186878169</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>2.418641172504247</v>
+        <v>2.227157589394752</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>0.5402052351946247</v>
+        <v>0.9888470288982417</v>
       </c>
     </row>
     <row r="29">
@@ -12973,16 +12920,16 @@
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>1.588785874419103</v>
+        <v>1.333785302808943</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>1.117522728799781</v>
+        <v>0.8841108708522141</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>2.258782295609063</v>
+        <v>2.012172107186446</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>0.009911220692569871</v>
+        <v>0.1697964367673447</v>
       </c>
     </row>
     <row r="30">
@@ -12992,16 +12939,16 @@
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>0.6605652523227008</v>
+        <v>0.5061923590587584</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>0.3089484868535126</v>
+        <v>0.2068132293429193</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>1.412359895399152</v>
+        <v>1.238947359332667</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>0.2848553724927133</v>
+        <v>0.1360131450792832</v>
       </c>
     </row>
     <row r="31">
@@ -13011,16 +12958,16 @@
         </is>
       </c>
       <c r="B31" s="18" t="n">
-        <v>4.413484571074677</v>
+        <v>4.027195014478223</v>
       </c>
       <c r="C31" s="18" t="n">
-        <v>3.192075222553084</v>
+        <v>2.750179223887142</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>6.102251576494701</v>
+        <v>5.897179188822129</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>2.675251785808035e-19</v>
+        <v>8.14297521841454e-13</v>
       </c>
     </row>
     <row r="32"/>
@@ -13032,7 +12979,7 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>LR χ²=3.70, df=6, p=0.7177</t>
+          <t>LR χ²=5.73, df=6, p=0.4546</t>
         </is>
       </c>
     </row>
@@ -13044,16 +12991,16 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>1.740487686615032</v>
+        <v>1.687877149071324</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>0.8528797712492094</v>
+        <v>0.7307601084020486</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>3.551845745879922</v>
+        <v>3.898583457965278</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.127834089078729</v>
+        <v>0.2203561203722835</v>
       </c>
     </row>
     <row r="36">
@@ -13063,16 +13010,16 @@
         </is>
       </c>
       <c r="B36" s="18" t="n">
-        <v>2.166171497313047</v>
+        <v>1.81884688713735</v>
       </c>
       <c r="C36" s="18" t="n">
-        <v>1.436352290195175</v>
+        <v>1.122046152646886</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>3.26681621758256</v>
+        <v>2.948367133602513</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.0002265759946471743</v>
+        <v>0.01521588358281269</v>
       </c>
     </row>
     <row r="37">
@@ -13082,16 +13029,16 @@
         </is>
       </c>
       <c r="B37" s="18" t="n">
-        <v>3.776898980170589</v>
+        <v>1.208578609969165</v>
       </c>
       <c r="C37" s="18" t="n">
-        <v>0.5865487191236326</v>
+        <v>0.06997696814309133</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>24.32017229144587</v>
+        <v>20.87347158979775</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>0.1619577805270729</v>
+        <v>0.8963079285665041</v>
       </c>
     </row>
     <row r="38">
